--- a/ftmo_trading_bot/logs/ftmo_trades.xlsx
+++ b/ftmo_trading_bot/logs/ftmo_trades.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN2"/>
+  <dimension ref="A1:BN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1056,6 +1056,173 @@
         <v>3</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>439789872</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.59049</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.5893</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5929</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.006925951052562299</v>
+      </c>
+      <c r="I3" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0004680895585355479</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-05-04 10:03:41.511277</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาขึ้น; ✅ MTF (H1) Bullish Bias; ✅ Fresh BOS Bullish; ✅ Bullish OB Cluster (score=100); ✅ Bullish FVG (score=90); ✅ IDM Bullish (wick/body=12.25, 1 bars ago); ✅ RSI=37.9 (Below mid +8); ❌ Volatility ผิดปกติ; ✅ LTF (M15) ขาขึ้น; ✅ BB %B=-0.01 (ต่ำมาก — pullback แรง +12); 📊 Session multiplier: ×0.90</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>10</v>
+      </c>
+      <c r="W3" t="n">
+        <v>8</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>quiet</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.4423305588585018</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.4096078948238601</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.59041</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.59049</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.7999999999996898</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>14.79209072602663</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>22.89478998411912</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>9875.9</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>184.241904</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>[1.0, 0.25, 1.0, -1.0319, 0.3739, 1.0, 2.0, -0.2424, -0.3772, 0.2879, 1.41, 0.2552, -0.8803, -0.0071, 0.0205, -2.8841, -0.1153, -0.1373, -0.0291, -0.1241, 0.1333, 0.3333, 0.0, 0.0, 0.0, 0.0, 1.0, -1.0, 3.0]</t>
+        </is>
+      </c>
+      <c r="BM3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1566,7 +1733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2182,7 +2349,6 @@
       <c r="P7" t="n">
         <v>-1</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
         <v>0.5000000000023874</v>
       </c>
@@ -2191,7 +2357,6 @@
           <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ⚠️ ไม่มี Bearish OB ใกล้ราคา; ✅ Bearish FVG (score=66); ✅ IDM Bearish (wick/body=4.67, 0 bars ago)</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>[0.6134, 0.375, -1.0, 0.2175, 0.0, 1.0, 1.5, 0.0552, 0.0928, 0.2988, 0.0, 0.346, 0.6593, 0.5439, 0.274, 0.7977, -0.5211, -0.1218, 0.0, -0.1241, 0.1333, 0.3333, 0.0, 0.0, 0.0, 0.0, 1.0, 1.0, 3.0]</t>
@@ -2201,6 +2366,1019 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-04 10:02:39.475283+03:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>92.18223224061059</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0004123938915305859</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6592592592592592</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5099106120458556</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M8" t="n">
+        <v>14.79209072602663</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ✅ Fresh BOS Bearish; ✅ Bearish OB Cluster (score=99); ✅ Bearish FVG (score=66)</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด USDCHF (SELL) เปิดอยู่แล้ว (Ticket 439787803)</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>[0.8436, 0.125, -1.0, -1.0876, 0.7594, 1.0, 2.0, 0.1336, 0.0927, 0.1944, 1.4307, 0.1546, 0.6548, 0.8367, -0.19, 1.3094, 0.3185, -0.1258, -0.0058, -0.1241, 0.1333, 0.3333, 0.0, 0.0, 0.0, 0.0, 1.0, 1.0, 3.0]</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-04 10:02:39.632192+03:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>89.40268898928109</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0004545181299641177</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2804705882352941</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.3142283655476142</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M9" t="n">
+        <v>14.79209072602663</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.8000000000008001</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาขึ้น; ✅ MTF (H1) Bullish Bias; ✅ Fresh BOS Bullish; ✅ Bullish OB Cluster (score=37); ✅ IDM Bullish (wick/body=12.25, 1 bars ago)</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>[0.7881, 0.25, 1.0, -1.0455, 0.3735, 1.0, 2.0, -0.1864, -0.3547, 0.291, 1.4521, 0.2552, -0.6752, 0.0842, -0.0085, -2.4421, -0.4391, -0.1258, -0.0058, -0.1241, 0.1333, 0.3333, 0.0, 0.0, 0.0, 0.0, 1.0, -1.0, 3.0]</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-04 10:03:40.868615+03:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0004680895585355479</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4423305588585018</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.4096078948238601</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M10" t="n">
+        <v>14.79209072602663</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.7999999999996898</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาขึ้น; ✅ MTF (H1) Bullish Bias; ✅ Fresh BOS Bullish; ✅ Bullish OB Cluster (score=100); ✅ Bullish FVG (score=90)</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>[1.0, 0.25, 1.0, -1.0319, 0.3739, 1.0, 2.0, -0.2424, -0.3772, 0.2879, 1.41, 0.2552, -0.8803, -0.0071, 0.0205, -2.8841, -0.1153, -0.1373, -0.0291, -0.1241, 0.1333, 0.3333, 0.0, 0.0, 0.0, 0.0, 1.0, -1.0, 3.0]</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-04 10:03:40.742742+03:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>92.38471890977645</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0004216796058162976</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6683673469387755</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.5176195793034337</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M11" t="n">
+        <v>14.79209072602663</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.5999999999994898</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ✅ Fresh BOS Bearish; ✅ Bearish OB Cluster (score=99); ✅ Bearish FVG (score=68)</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด USDCHF (SELL) เปิดอยู่แล้ว (Ticket 439787803)</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>[0.8477, 0.125, -1.0, -1.0783, 0.7596, 1.0, 2.0, 0.1796, 0.1148, 0.1927, 1.3992, 0.1546, 0.8452, 0.9521, -0.1721, 1.66, 0.3367, -0.141, -0.0366, -0.1255, 0.1333, 0.6667, 0.0, 0.0, 0.0, 0.0, 1.0, 1.0, 3.0]</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-04 10:04:43.256056+03:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.0004688038442498304</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2920203735144312</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.3173317519279764</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M12" t="n">
+        <v>14.79209072602663</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.7999999999996898</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาขึ้น; ✅ MTF (H1) Bullish Bias; ✅ Fresh BOS Bullish; ✅ Bullish OB Cluster (score=100); ✅ IDM Bullish (wick/body=12.25, 1 bars ago)</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>[1.0, 0.25, 1.0, -1.0312, 0.3736, 1.0, 2.0, -0.2083, -0.3562, 0.2898, 1.4078, 0.2552, -0.7521, 0.0485, 0.022, -2.5597, -0.416, -0.1296, -0.0134, -0.1255, 0.1333, 0.6667, 0.0, 0.0, 0.0, 0.0, 1.0, -1.0, 3.0]</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-04 10:04:43.124417+03:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>92.32925352694683</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0004223938915305801</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6592592592592592</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5086839270988828</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M13" t="n">
+        <v>14.79209072602663</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.6000000000006001</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ✅ Fresh BOS Bearish; ✅ Bearish OB Cluster (score=99); ✅ Bearish FVG (score=68)</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด USDCHF (SELL) เปิดอยู่แล้ว (Ticket 439787803)</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>[0.8466, 0.125, -1.0, -1.0776, 0.7598, 1.0, 2.0, 0.1658, 0.1071, 0.1933, 1.3968, 0.1546, 0.7857, 0.9178, -0.1707, 1.5388, 0.3185, -0.1296, -0.0134, -0.1255, 0.1333, 0.6667, 0.0, 0.0, 0.0, 0.0, 1.0, 1.0, 3.0]</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-04 10:05:44.485025+03:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.0004716609871069761</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3170944648157848</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.3303973846906586</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M14" t="n">
+        <v>14.79209072602663</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.7999999999996898</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาขึ้น; ✅ MTF (H1) Bullish Bias; ✅ Fresh BOS Bullish; ✅ Bullish OB Cluster (score=100); ✅ IDM Bullish (wick/body=12.25, 1 bars ago)</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>[1.0, 0.25, 1.0, -1.0283, 0.3738, 1.0, 2.0, -0.2291, -0.3662, 0.2887, 1.3993, 0.2552, -0.8291, 0.0145, 0.0281, -2.735, -0.3658, -0.1428, -0.0402, -0.1255, 0.1333, 0.6667, 0.0, 0.0, 0.0, 0.0, 1.0, -1.0, 3.0]</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-04 10:05:44.373493+03:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>92.51933650917557</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.0004359653201020103</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6592592592592592</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.5087477838922791</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M15" t="n">
+        <v>14.79209072602663</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.5999999999994898</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ✅ Fresh BOS Bearish; ✅ Bearish OB Cluster (score=99); ✅ Bearish FVG (score=70)</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด USDCHF (SELL) เปิดอยู่แล้ว (Ticket 439787803)</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>[0.8504, 0.125, -1.0, -1.064, 0.7593, 1.0, 2.0, 0.2059, 0.1257, 0.1917, 1.3533, 0.1568, 0.8644, 1.0158, -0.1445, 1.835, 0.3185, -0.1428, -0.0402, -0.1255, 0.1333, 0.6667, 0.0, 0.0, 0.0, 0.0, 1.0, 1.0, 3.0]</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-04 10:06:46.258447+03:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.0004795181299641149</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5507487520798668</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.4692839475650847</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M16" t="n">
+        <v>14.79209072602663</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.700000000000145</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาขึ้น; ✅ MTF (H1) Bullish Bias; ✅ Fresh BOS Bullish; ✅ Bullish OB Cluster (score=100); ✅ Bullish FVG (score=92)</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด NZDUSD (BUY) เปิดอยู่แล้ว (Ticket 439789872)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>[1.0, 0.25, 1.0, -1.0205, 0.3742, 1.0, 2.0, -0.2676, -0.3842, 0.2863, 1.3764, 0.2556, -0.9661, -0.048, 0.0449, -3.0, 0.1015, -0.1554, -0.0656, -0.1255, 0.1333, 0.6667, 0.0, 0.0, 0.0, 0.0, 1.0, -1.0, 3.0]</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-04 10:06:46.133916+03:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>92.56339180709114</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.0004359653201020103</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6592592592592592</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.5058110906202768</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M17" t="n">
+        <v>14.79209072602663</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.5999999999994898</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ✅ Fresh BOS Bearish; ✅ Bearish OB Cluster (score=99); ✅ Bearish FVG (score=70)</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด USDCHF (SELL) เปิดอยู่แล้ว (Ticket 439787803)</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>[0.8513, 0.125, -1.0, -1.064, 0.9451, 1.0, 2.0, 0.216, 0.1316, 0.1912, 3.0, 0.1568, 0.9096, 1.0395, -0.1445, 1.9268, 0.3185, -0.1554, -0.0656, -0.1255, 0.1333, 0.6667, 0.0, 0.0, 0.0, 0.0, 1.0, 1.0, 3.0]</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-04 10:07:47.424187+03:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.0004823752728212606</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5507487520798668</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.4692839475650847</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M18" t="n">
+        <v>14.79209072602663</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.5999999999994898</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาขึ้น; ✅ MTF (H1) Bullish Bias; ✅ Fresh BOS Bullish; ✅ Bullish OB Cluster (score=100); ✅ Bullish FVG (score=92)</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด NZDUSD (BUY) เปิดอยู่แล้ว (Ticket 439789872)</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>[1.0, 0.25, 1.0, -1.0176, 0.3741, 1.0, 2.0, -0.2756, -0.3872, 0.2857, 1.3682, 0.2563, -0.9667, -0.0609, 0.051, -3.0, 0.1015, -0.1588, -0.0725, -0.1255, 0.1333, 0.6667, 0.0, 0.0, 0.0, 0.0, 1.0, -1.0, 3.0]</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-04 10:07:47.304230+03:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>92.6074468217593</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.0004359653201020103</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6692307692307692</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.5338958150667142</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M19" t="n">
+        <v>14.79209072602663</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ✅ Fresh BOS Bearish; ✅ Bearish OB Cluster (score=99); ✅ Bearish FVG (score=70)</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด USDCHF (SELL) เปิดอยู่แล้ว (Ticket 439787803)</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>[0.8521, 0.125, -1.0, -1.064, 0.9452, 1.0, 2.0, 0.2258, 0.1374, 0.1908, 3.0, 0.1568, 0.9548, 1.0621, -0.1445, 2.0185, 0.3385, -0.1582, -0.0714, -0.1255, 0.1333, 0.6667, 0.0, 0.0, 0.0, 0.0, 1.0, 1.0, 3.0]</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
         <v>3</v>
       </c>
     </row>

--- a/ftmo_trading_bot/logs/ftmo_trades.xlsx
+++ b/ftmo_trading_bot/logs/ftmo_trades.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,8 +33,15 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +78,11 @@
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -90,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -106,6 +118,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -883,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -969,6 +986,80 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -980,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -996,6 +1087,378 @@
       <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>📊 Total Trades</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>✅ Wins</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>❌ Losses</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>🏆 Win Rate %</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>💰 Total P/L</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>📈 Avg Win</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>📉 Avg Loss</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>🏅 Largest Win</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>💀 Largest Loss</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>─</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>──────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>⚖️ Profit Factor</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>🎯 Expectancy $/trade</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>📐 Avg R-Multiple</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>📊 Win/Loss Ratio</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>──</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>──────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>📈 Sharpe Ratio</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>📈 Sortino Ratio</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>📉 Max Drawdown $</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>📉 Max Drawdown %</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>📈 Calmar Ratio</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>───</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>──────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>📅 Days Traded</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>📈 Winning Days %</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>🏅 Best Day</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>💀 Worst Day</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>🔥 Max Win Streak</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>❄️ Max Loss Streak</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>────</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>──────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>🎯 FTMO Target</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>$1,000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>📊 Progress</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>💰 Remaining</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>$1,000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>📉 Max DD vs Limit</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>0.00% / 8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>📉 Worst Daily vs Limit</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>0.00% / 4%</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1945,7 +2408,6 @@
       <c r="P11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
         <v>1.800000000000068</v>
       </c>
@@ -1954,7 +2416,6 @@
           <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ⚠️ ไม่มี Bearish OB ใกล้ราคา; ✅ Bearish Liquidity Sweep (score=70, 6 bars ago); ⚠️ ไม่มี IDM rejection ใน 8 bars — entry อาจเป็น obvious swing (-2)</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>[0.53, 0.25, -1.0, -0.1497, 0.0, 1.0, 2.0, 0.3442, 0.2964, 0.0328, 0.0, 0.2047, 0.3223, 0.8412, 0.6763, 0.4591, -0.1405, -0.0, -0.0, 0.0, 0.1556, 0.0, 0.0, 0.0, 0.0001, 0.0, 1.0, -1.0, 2.2215, 0.0, 0.0, 0.325]</t>
@@ -1965,6 +2426,1140 @@
       </c>
       <c r="W11" t="n">
         <v>2.2215</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:37:22.897117+03:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>81</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7.272132407715968</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3203389830508475</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.3287611671728611</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20.24915666599896</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>50</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ✅ Fresh BOS Bearish; ⚠️ ไม่มี Bearish OB ใกล้ราคา; ✅ IDM Bearish (wick/body=2.36, 6 bars ago)</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>[0.62, 0.25, -1.0, 2.0, 0.0, 1.0, 1.9237, 0.0967, -0.0927, 0.3098, 0.0, 0.2534, 0.0579, 0.5987, -0.0035, 0.0041, -0.3116, -0.0, -0.0, 0.0, 0.1556, 0.0, 0.0, 0.0, 0.0007, 0.0, 1.0, -1.0, 0.4701, 0.0, 0.0, 0.3271]</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.4701</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:37:22.680510+03:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1350346909578138</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.425414364640884</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.3993909167217274</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20.24915666599896</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.700000000002433</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ⚠️ ไม่มี Bearish OB ใกล้ราคา; ✅ Bearish Liquidity Sweep (score=70, 6 bars ago); ⚠️ ไม่มี IDM rejection ใน 8 bars — entry อาจเป็น obvious swing (-2)</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>[0.53, 0.25, -1.0, -0.1497, 0.0, 1.0, 2.0, 0.3647, 0.302, 0.0323, 0.0, 0.2047, 0.3529, 0.8539, 0.6763, 0.548, -0.1405, -0.0, -0.0, 0.0, 0.1556, 0.0, 0.0, 0.0, 0.0001, 0.0, 1.0, -1.0, 2.2215, 0.0, 0.0, 0.3271]</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.2215</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:38:24.292824+03:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>88</v>
+      </c>
+      <c r="F14" t="n">
+        <v>7.272132407715968</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3203389830508475</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.3282052302724725</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20.24915666599896</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>46.00000000000364</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ✅ Fresh BOS Bearish; ⚠️ ไม่มี Bearish OB ใกล้ราคา; ✅ IDM Bearish (wick/body=2.36, 6 bars ago)</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>[0.76, 0.25, -1.0, 2.0, 0.0, 1.0, 1.9237, 0.1082, -0.0868, 0.3085, 0.0, 0.2534, 0.1373, 0.6293, -0.0035, 0.0976, -0.3163, -0.0, -0.0, 0.0, 0.1556, 0.0, 0.0, 0.0, 0.0006, 0.0, 1.0, -1.0, 0.4701, 0.0, 0.0, 0.3292]</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.4701</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:38:24.052072+03:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1350346909578138</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.425414364640884</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.3993909167217274</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20.24915666599896</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.400000000001</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ⚠️ ไม่มี Bearish OB ใกล้ราคา; ✅ Bearish Liquidity Sweep (score=70, 6 bars ago); ⚠️ ไม่มี IDM rejection ใน 8 bars — entry อาจเป็น obvious swing (-2)</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>[0.53, 0.25, -1.0, -0.1497, 0.0, 1.0, 2.0, 0.3595, 0.3006, 0.0324, 0.0, 0.2047, 0.3453, 0.8507, 0.6763, 0.5258, -0.1405, -0.0, -0.0, 0.0, 0.1556, 0.0, 0.0, 0.0, 0.0001, 0.0, 1.0, -1.0, 2.2215, 0.0, 0.0, 0.3292]</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.2215</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:39:25.602133+03:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>81</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7.272132407715968</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3203389830508475</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.329888859907906</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20.24915666599896</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>44.00000000005093</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ✅ Fresh BOS Bearish; ⚠️ ไม่มี Bearish OB ใกล้ราคา; ✅ IDM Bearish (wick/body=2.36, 6 bars ago)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>[0.62, 0.25, -1.0, 2.0, 0.0, 1.0, 1.9237, 0.0969, -0.0926, 0.3098, 0.0, 0.2534, 0.059, 0.5991, -0.0035, 0.0055, -0.3116, -0.0, -0.0, 0.0, 0.1556, 0.0, 0.0, 0.0, 0.0006, 0.0, 1.0, -1.0, 0.4701, 0.0, 0.0, 0.3313]</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.4701</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:39:25.360863+03:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1350346909578138</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4108298999411419</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.3888148251522621</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20.24915666599896</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.200000000000045</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ⚠️ ไม่มี Bearish OB ใกล้ราคา; ✅ Bearish Liquidity Sweep (score=70, 6 bars ago); ⚠️ ไม่มี IDM rejection ใน 8 bars — entry อาจเป็น obvious swing (-2)</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>[0.53, 0.25, -1.0, -0.1497, 0.0, 1.0, 2.0, 0.3751, 0.3049, 0.032, 0.0, 0.2047, 0.3683, 0.8602, 0.6763, 0.5924, -0.1492, -0.0, -0.0, 0.0, 0.1556, 0.0, 0.0, 0.0, 0.0001, 0.0, 1.0, -1.0, 2.2215, 0.0, 0.0, 0.3313]</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.2215</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:40:26.851188+03:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>81</v>
+      </c>
+      <c r="F18" t="n">
+        <v>7.272132407715968</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.3203389830508475</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.3292869586132275</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20.24915666599896</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>44.99999999998181</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ✅ Fresh BOS Bearish; ⚠️ ไม่มี Bearish OB ใกล้ราคา; ✅ IDM Bearish (wick/body=2.36, 6 bars ago)</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>[0.62, 0.25, -1.0, 2.0, 0.0, 1.0, 1.9237, 0.043, -0.1186, 0.3152, 0.0, 0.2534, -0.287, 0.464, -0.0035, -0.4015, -0.3116, -0.0, -0.0, 0.0, 0.1556, 0.0, 0.0, 0.0, 0.0006, 0.0, 1.0, -1.0, 0.4701, 0.0, 0.0, 0.3333]</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.4701</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:40:26.629949+03:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1350346909578138</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.425414364640884</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.3993909167217274</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20.24915666599896</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.800000000000068</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ⚠️ ไม่มี Bearish OB ใกล้ราคา; ✅ Bearish Liquidity Sweep (score=70, 6 bars ago); ⚠️ ไม่มี IDM rejection ใน 8 bars — entry อาจเป็น obvious swing (-2)</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>[0.53, 0.25, -1.0, -0.1497, 0.0, 1.0, 2.0, 0.3681, 0.303, 0.0322, 0.0, 0.2047, 0.3581, 0.856, 0.6763, 0.5628, -0.1405, -0.0, -0.0, 0.0, 0.1556, 0.0, 0.0, 0.0, 0.0001, 0.0, 1.0, -1.0, 2.2215, 0.0, 0.0, 0.3333]</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.2215</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:41:28.046414+03:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>81</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7.272132407715968</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3203389830508475</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.3292869586132275</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M20" t="n">
+        <v>20.24915666599896</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>43.0000000000291</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ✅ Fresh BOS Bearish; ⚠️ ไม่มี Bearish OB ใกล้ราคา; ✅ IDM Bearish (wick/body=2.36, 6 bars ago)</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>[0.62, 0.25, -1.0, 2.0, 0.0, 1.0, 1.9237, 0.0395, -0.1202, 0.3156, 0.0, 0.2534, -0.308, 0.4558, -0.0035, -0.4263, -0.3116, -0.0, -0.0, 0.0, 0.1556, 0.0, 0.0, 0.0, 0.0006, 0.0, 1.0, -1.0, 0.4701, 0.0, 0.0, 0.3354]</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.4701</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:41:27.825086+03:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1350346909578138</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4198008849557521</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.3921203206813852</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M21" t="n">
+        <v>20.24915666599896</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.800000000000068</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ⚠️ ไม่มี Bearish OB ใกล้ราคา; ✅ Bearish Liquidity Sweep (score=70, 6 bars ago); ⚠️ ไม่มี IDM rejection ใน 8 bars — entry อาจเป็น obvious swing (-2)</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>[0.53, 0.25, -1.0, -0.1497, 0.0, 1.0, 2.0, 0.3875, 0.3082, 0.0317, 0.0, 0.2047, 0.3862, 0.8675, 0.6763, 0.6443, -0.1492, -0.0, -0.0, 0.0, 0.1556, 0.0, 0.0, 0.0, 0.0001, 0.0, 1.0, -1.0, 2.2215, 0.0, 0.0, 0.3354]</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.2215</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:42:29.054363+03:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1350346909578138</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.4108298999411419</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.3888148251522621</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M22" t="n">
+        <v>20.24915666599896</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.500000000001478</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ⚠️ ไม่มี Bearish OB ใกล้ราคา; ✅ Bearish Liquidity Sweep (score=70, 6 bars ago); ⚠️ ไม่มี IDM rejection ใน 8 bars — entry อาจเป็น obvious swing (-2)</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>[0.53, 0.25, -1.0, -0.1497, 0.0, 1.0, 2.0, 0.3699, 0.3035, 0.0321, 0.0, 0.2047, 0.3606, 0.857, 0.6763, 0.5702, -0.1492, -0.0, -0.0, 0.0, 0.1556, 0.0, 0.0, 0.0, 0.0001, 0.0, 1.0, -1.0, 2.2215, 0.0, 0.0, 0.3375]</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.2215</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:42:29.251925+03:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>75</v>
+      </c>
+      <c r="F23" t="n">
+        <v>7.272132407715968</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3588342440801457</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.3547325950207223</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M23" t="n">
+        <v>20.24915666599896</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>44.99999999998181</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ✅ Fresh BOS Bearish; ⚠️ ไม่มี Bearish OB ใกล้ราคา; ✅ IDM Bearish (wick/body=6.11, 0 bars ago)</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>[0.5, 0.25, -1.0, 2.0, 0.0, 1.0, 1.9237, -0.0085, -0.141, 0.3199, 0.0, 0.2534, -0.585, 0.3488, -0.0035, -0.7522, -0.2012, -0.0, -0.0, 0.0, 0.1556, 0.0, 0.0, 0.0, 0.0006, 0.0, 1.0, -1.0, 0.4701, 0.0, 0.0, 0.3375]</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.4701</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:43:30.297205+03:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.1350346909578138</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.425414364640884</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.3993909167217274</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M24" t="n">
+        <v>20.22237678126024</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.200000000000045</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ⚠️ ไม่มี Bearish OB ใกล้ราคา; ✅ Bearish Liquidity Sweep (score=70, 6 bars ago); ⚠️ ไม่มี IDM rejection ใน 8 bars — entry อาจเป็น obvious swing (-2)</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>[0.53, 0.25, -1.0, -0.1497, 0.0, 1.0, 2.0, 0.3561, 0.2997, 0.0325, 0.0, 0.2047, 0.3402, 0.8486, 0.6763, 0.511, -0.1405, -0.0, -0.0, 0.0, 0.1556, 0.0, 0.0, 0.0, 0.0001, 0.0, 1.0, -1.0, 2.2215, 0.0, 0.0, 0.3396]</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.2215</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:43:30.529909+03:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>75</v>
+      </c>
+      <c r="F25" t="n">
+        <v>7.294989550573155</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.3588342440801457</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.3547325950207223</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M25" t="n">
+        <v>20.22237678126024</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>✅ HTF (H4) ขาลง; ✅ MTF (H1) Bearish Bias; ✅ Fresh BOS Bearish; ⚠️ ไม่มี Bearish OB ใกล้ราคา; ✅ IDM Bearish (wick/body=4.45, 0 bars ago)</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>[0.5, 0.25, -1.0, 2.0, 0.0, 1.0, 1.9464, -0.0161, -0.1439, 0.3206, 0.0, 0.2527, -0.6295, 0.332, -0.0004, -0.8019, -0.2012, -0.0, -0.0, 0.0, 0.1556, 0.0, 0.0, 0.0, 0.0007, 0.0, 1.0, -1.0, 0.4691, 0.0, 0.0, 0.3396]</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.4691</v>
       </c>
     </row>
   </sheetData>

--- a/ftmo_trading_bot/logs/ftmo_trades.xlsx
+++ b/ftmo_trading_bot/logs/ftmo_trades.xlsx
@@ -2416,7 +2416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T171"/>
+  <dimension ref="A1:T173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15686,6 +15686,157 @@
         <v>2.8071</v>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-05-25 07:27:41.543031+00:00</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>77.09546976037487</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.0004190616880042195</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0.4690438457474909</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0.4735326603537954</v>
+      </c>
+      <c r="J172" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M172" t="n">
+        <v>21.60859193313387</v>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O172" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>BB%B=-0.06 (extreme=1.21); RSI=39.0 (extreme=0.03); Wick ratio=1.71; ADX H1=16.4 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>[0.5419, 0.0, 1.0, -1.0809, 1.0, -1.0, 2.0, -0.221, -0.238, 0.1071, 0.8903, 0.1544, -0.4146, -0.0637, -0.0632, -2.0283, -0.0788, -0.372, -0.141, -0.372, 0.4667, 0.0, -1.0, 0.8, 0.0, 0.0, 0.6911, -1.0, 3.0, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="S172" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T172" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-05-25 07:28:41.999812+00:00</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>75.38197806368606</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.0004190616880042195</v>
+      </c>
+      <c r="G173" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0.4690438457474909</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0.4754218547517314</v>
+      </c>
+      <c r="J173" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L173" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M173" t="n">
+        <v>21.60859193313387</v>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O173" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>BB%B=-0.09 (extreme=1.31); RSI=38.3 (extreme=0.04); Wick ratio=1.30; ADX H1=16.4 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr"/>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>[0.5076, 0.0, 1.0, -1.0809, 1.0, -1.0, 2.0, -0.2347, -0.2456, 0.1064, 0.9097, 0.1544, -0.4756, -0.0933, -0.0632, -2.1477, -0.0788, -0.372, -0.141, -0.372, 0.4667, 0.0, -1.0, 0.8, 0.0, 0.0, 0.6911, -1.0, 3.0, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="S173" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T173" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ftmo_trading_bot/logs/ftmo_trades.xlsx
+++ b/ftmo_trading_bot/logs/ftmo_trades.xlsx
@@ -15824,7 +15824,6 @@
           <t>BB%B=-0.09 (extreme=1.31); RSI=38.3 (extreme=0.04); Wick ratio=1.30; ADX H1=16.4 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
         </is>
       </c>
-      <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr">
         <is>
           <t>[0.5076, 0.0, 1.0, -1.0809, 1.0, -1.0, 2.0, -0.2347, -0.2456, 0.1064, 0.9097, 0.1544, -0.4756, -0.0933, -0.0632, -2.1477, -0.0788, -0.372, -0.141, -0.372, 0.4667, 0.0, -1.0, 0.8, 0.0, 0.0, 0.6911, -1.0, 3.0, 0.0, 0.0, 0.0]</t>

--- a/ftmo_trading_bot/logs/ftmo_trades.xlsx
+++ b/ftmo_trading_bot/logs/ftmo_trades.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF5"/>
+  <dimension ref="A1:BF6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1647,6 +1647,147 @@
         <v>2.7441</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>556182717</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.34931</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.35054</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.34814</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.006979678955540899</v>
+      </c>
+      <c r="I6" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>78.74805185847578</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.000586687750064259</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-05-25 12:01:05.486665</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>BB%B=0.97 (extreme=0.88); RSI=64.5 (extreme=0.11); Wick ratio=5.00; ADX H1=29.0 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>12</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>quiet</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.5037664107898699</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.5151911103177456</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.34934</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.34935</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.1000000000006551</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>21.64168446351065</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>9627.950000000001</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>[0.575, 0.0, -1.0, -0.9133, 0.8838, -1.0, 2.0, 0.2894, 0.1305, 0.2273, 1.0, 0.2201, 0.9485, 0.9651, -0.0757, 1.4488, 0.1105, -0.372, -0.141, -0.372, 0.4667, 0.0, -1.0, 0.8, 0.0, 0.0, 0.5599, -1.0, 3.0, 0.0, 0.0, 0.1271]</t>
+        </is>
+      </c>
+      <c r="BE6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2416,7 +2557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T173"/>
+  <dimension ref="A1:T177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15836,6 +15977,321 @@
         <v>3</v>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:00:04.852646+00:00</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D174" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>75.85563797469224</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.0005809734622605491</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0.5037664107898699</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0.5160741771282911</v>
+      </c>
+      <c r="J174" t="n">
+        <v>1</v>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L174" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M174" t="n">
+        <v>21.64168446351066</v>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>BB%B=0.96 (extreme=0.86); RSI=64.2 (extreme=0.11); Wick ratio=2.00; ADX H1=29.0 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=1.34929 &lt; C=1.34933) — SELL needs bearish c</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>[0.5171, 0.0, -1.0, -0.919, 0.8582, -1.0, 2.0, 0.2844, 0.1296, 0.2272, 1.0, 0.2201, 0.9313, 0.9575, -0.0845, 1.4286, 0.1105, -0.372, -0.141, -0.372, 0.4667, 0.0, -1.0, 0.8, 0.0, 0.0, 0.5599, -1.0, 3.0, 0.0, 0.0, 0.125]</t>
+        </is>
+      </c>
+      <c r="S174" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T174" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:01:06.420574+00:00</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>78.74805185847578</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.000586687750064259</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0.5037664107898699</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0.5151911103177456</v>
+      </c>
+      <c r="J175" t="n">
+        <v>1</v>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L175" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M175" t="n">
+        <v>21.64168446351065</v>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O175" t="n">
+        <v>0.1000000000006551</v>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>BB%B=0.97 (extreme=0.88); RSI=64.5 (extreme=0.11); Wick ratio=5.00; ADX H1=29.0 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>[0.575, 0.0, -1.0, -0.9133, 0.8838, -1.0, 2.0, 0.2894, 0.1305, 0.2273, 1.0, 0.2201, 0.9485, 0.9651, -0.0757, 1.4488, 0.1105, -0.372, -0.141, -0.372, 0.4667, 0.0, -1.0, 0.8, 0.0, 0.0, 0.5599, -1.0, 3.0, 0.0, 0.0, 0.1271]</t>
+        </is>
+      </c>
+      <c r="S175" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T175" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:03:07.285563+00:00</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D176" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>76.34759111807142</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0.0005931163238434208</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0.5546043635931276</v>
+      </c>
+      <c r="I176" t="n">
+        <v>0.5305930418205558</v>
+      </c>
+      <c r="J176" t="n">
+        <v>1</v>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L176" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M176" t="n">
+        <v>21.64168446351061</v>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O176" t="n">
+        <v>0.09999999999843467</v>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>BB%B=0.98 (extreme=0.95); RSI=64.9 (extreme=0.12); Wick ratio=1.50; ADX H1=29.1 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด GBPUSD (SELL) เปิดอยู่แล้ว (Ticket 556182717)</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>[0.527, 0.0, -1.0, -0.9069, 0.9465, -1.0, 2.0, 0.2981, 0.1345, 0.2276, 1.0, 0.2213, 0.9253, 0.984, -0.0657, 1.5174, 0.1717, -0.3793, -0.1561, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0, 0.0, 0.5574, -1.0, 3.0, 0.0, 0.0, 0.1312]</t>
+        </is>
+      </c>
+      <c r="S176" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T176" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:04:07.811519+00:00</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D177" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>80.01512015894676</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0.0005931163238434208</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0.5546043635931276</v>
+      </c>
+      <c r="I177" t="n">
+        <v>0.5305930418205558</v>
+      </c>
+      <c r="J177" t="n">
+        <v>1</v>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M177" t="n">
+        <v>21.6416844635106</v>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O177" t="n">
+        <v>0.1000000000006551</v>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>BB%B=0.98 (extreme=0.92); RSI=64.7 (extreme=0.12); Wick ratio=2.75; ADX H1=29.1 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด GBPUSD (SELL) เปิดอยู่แล้ว (Ticket 556182717)</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>[0.6003, 0.0, -1.0, -0.9069, 0.9217, -1.0, 2.0, 0.2946, 0.1323, 0.2274, 1.0, 0.2213, 0.9087, 0.9765, -0.0657, 1.4837, 0.1717, -0.3782, -0.1537, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0, 0.0, 0.5574, -1.0, 3.0, 0.0, 0.0, 0.1333]</t>
+        </is>
+      </c>
+      <c r="S177" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T177" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ftmo_trading_bot/logs/ftmo_trades.xlsx
+++ b/ftmo_trading_bot/logs/ftmo_trades.xlsx
@@ -2557,7 +2557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T177"/>
+  <dimension ref="A1:T178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16292,6 +16292,82 @@
         <v>3</v>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:06:08.957064+00:00</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>76.87099322570126</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0.08524176291789666</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0.4847432826961701</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0.4914966111833602</v>
+      </c>
+      <c r="J178" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M178" t="n">
+        <v>21.6416844635106</v>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O178" t="n">
+        <v>2.400000000000091</v>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>BB%B=0.97 (extreme=0.90); RSI=68.5 (extreme=0.21); Wick ratio=1.50; ADX H1=18.4 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>[0.5374, 0.0, -1.0, -0.6476, 0.9048, -1.0, 2.0, 0.3691, 0.1324, 0.1817, 1.0, 0.2633, 0.9545, 0.9714, -0.1751, 0.8447, 0.0601, -0.3866, -0.1711, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0003, 0.0, 0.4734, -1.0, 2.4222, 0.0, 0.0, 0.1375]</t>
+        </is>
+      </c>
+      <c r="S178" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T178" t="n">
+        <v>2.4222</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ftmo_trading_bot/logs/ftmo_trades.xlsx
+++ b/ftmo_trading_bot/logs/ftmo_trades.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF6"/>
+  <dimension ref="A1:BF8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1693,6 +1693,25 @@
           <t>2026-05-25 12:01:05.486665</t>
         </is>
       </c>
+      <c r="N6" t="n">
+        <v>1.34908</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:00:03.644012</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>12.87999999999734</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Pre-news close</t>
+        </is>
+      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>BB%B=0.97 (extreme=0.88); RSI=64.5 (extreme=0.11); Wick ratio=5.00; ADX H1=29.0 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
@@ -1726,6 +1745,15 @@
       <c r="AA6" t="n">
         <v>0.75</v>
       </c>
+      <c r="AB6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
       <c r="AF6" t="n">
         <v>0.5037664107898699</v>
       </c>
@@ -1743,6 +1771,18 @@
       <c r="AJ6" t="n">
         <v>0.3</v>
       </c>
+      <c r="AK6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.35054</v>
+      </c>
       <c r="AO6" t="n">
         <v>1.34934</v>
       </c>
@@ -1752,6 +1792,12 @@
       <c r="AQ6" t="n">
         <v>0.1000000000006551</v>
       </c>
+      <c r="AR6" t="n">
+        <v>1.34908</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.34908</v>
+      </c>
       <c r="AT6" t="n">
         <v>21.64168446351065</v>
       </c>
@@ -1761,6 +1807,12 @@
       <c r="AV6" t="n">
         <v>9627.950000000001</v>
       </c>
+      <c r="AW6" t="n">
+        <v>9636.639999999999</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>9650.559999999999</v>
+      </c>
       <c r="AY6" t="n">
         <v>0</v>
       </c>
@@ -1785,6 +1837,397 @@
         <v>-1</v>
       </c>
       <c r="BF6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>556209566</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4571.38</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4581.39</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4561.39</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.006233306426227261</v>
+      </c>
+      <c r="I7" t="n">
+        <v>60</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>76.70738864889893</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5.851689691269982</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-05-25 13:16:06.467317</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>4569.1</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:00:04.884069</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>13.67999999999847</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Pre-news close</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>BB%B=1.00 (extreme=1.01); RSI=62.5 (extreme=0.06); Wick ratio=1.49; ADX H1=22.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>13</v>
+      </c>
+      <c r="W7" t="n">
+        <v>42</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>270</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>261</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.585844093735055</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.5429948870684755</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AK7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>4581.39</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>4571.39</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4571.81</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>42.00000000000728</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4568.7</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4569.1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>22.45602516871704</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>9625.709999999999</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>9636.639999999999</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>9650.32</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>[0.5341, 0.0, -1.0, 2.0, 1.0, -1.0, 1.7089, 0.25, 0.2374, 0.4741, 1.0, 0.1574, 0.8574, 1.0018, -0.2793, 2.7838, 0.294, -0.3653, -0.1272, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0007, 0.0, 0.6851, 1.0, 0.577, 0.0, 0.0, 0.2833]</t>
+        </is>
+      </c>
+      <c r="BE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.577</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>556274286</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.16504</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.16607</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.16407</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.006943055545480641</v>
+      </c>
+      <c r="I8" t="n">
+        <v>67</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>80.9598831860536</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0004256629166969047</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:48:52.485963</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1.16401</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-05-25 17:02:37.994602</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v>62.15000000000001</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>🔴 SL Hit</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>BB%B=1.03 (extreme=1.12); RSI=61.9 (extreme=0.05); Wick ratio=11.50; ADX H1=22.1 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>15</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>quiet</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-20774</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>🔴 SL Hit</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.5783856595171482</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.5415128563879286</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AK8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.16401</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1.16507</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.16507</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.164</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.164</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>22.34957953002953</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>9649.93</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>9712.08</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9712.08</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>[0.6192, 0.0, -1.0, -1.0743, 1.0, -1.0, 2.0, 0.2384, 0.1342, 0.1578, 0.9939, 0.2432, 0.6406, 1.0346, -0.0629, 0.1879, 0.1568, -0.3501, -0.0957, -0.3501, 0.4667, 0.0, -0.3333, 0.0, 0.0, 0.0, 0.5136, 1.0, 3.0, 0.0, 0.0, 0.6]</t>
+        </is>
+      </c>
+      <c r="BE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1799,7 +2242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2144,6 +2587,302 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9625.709999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>100</v>
+      </c>
+      <c r="J11" t="n">
+        <v>100</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
+      <c r="F12" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K12" t="n">
+        <v>9649.93</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>100</v>
+      </c>
+      <c r="J13" t="n">
+        <v>100</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K14" t="n">
+        <v>9647.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>100</v>
+      </c>
+      <c r="J15" t="n">
+        <v>100</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="K16" t="n">
+        <v>9665.73</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>100</v>
+      </c>
+      <c r="J17" t="n">
+        <v>100</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2181,7 +2920,7 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -2191,7 +2930,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2212,7 +2951,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2963,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>$-68.38</t>
+          <t>$-41.82</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2975,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$13.28</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2999,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$-1.32</t>
+          <t>$13.68</t>
         </is>
       </c>
     </row>
@@ -2295,7 +3034,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="13">
@@ -2306,7 +3045,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>$-17.09</t>
+          <t>$-6.97</t>
         </is>
       </c>
     </row>
@@ -2317,7 +3056,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>-0.28</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="15">
@@ -2327,7 +3066,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="16">
@@ -2349,7 +3088,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>-21.29</v>
+        <v>-10.73</v>
       </c>
     </row>
     <row r="18">
@@ -2359,7 +3098,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>-17.68</v>
+        <v>-8.83</v>
       </c>
     </row>
     <row r="19">
@@ -2393,7 +3132,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="22">
@@ -2438,7 +3177,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>$-68.38</t>
+          <t>$-41.82</t>
         </is>
       </c>
     </row>
@@ -2450,7 +3189,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>$-68.38</t>
+          <t>$-41.82</t>
         </is>
       </c>
     </row>
@@ -2506,7 +3245,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-4.2%</t>
         </is>
       </c>
     </row>
@@ -2518,7 +3257,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>$1,068.38</t>
+          <t>$1,041.82</t>
         </is>
       </c>
     </row>
@@ -2542,7 +3281,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>0.68% / 4%</t>
+          <t>0.42% / 4%</t>
         </is>
       </c>
     </row>
@@ -2557,7 +3296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T178"/>
+  <dimension ref="A1:T217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16355,7 +17094,6 @@
           <t>BB%B=0.97 (extreme=0.90); RSI=68.5 (extreme=0.21); Wick ratio=1.50; ADX H1=18.4 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
         </is>
       </c>
-      <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr">
         <is>
           <t>[0.5374, 0.0, -1.0, -0.6476, 0.9048, -1.0, 2.0, 0.3691, 0.1324, 0.1817, 1.0, 0.2633, 0.9545, 0.9714, -0.1751, 0.8447, 0.0601, -0.3866, -0.1711, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0003, 0.0, 0.4734, -1.0, 2.4222, 0.0, 0.0, 0.1375]</t>
@@ -16366,6 +17104,3081 @@
       </c>
       <c r="T178" t="n">
         <v>2.4222</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:07:09.504397+00:00</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D179" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>80.2952873944844</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0.0006002591835980503</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0.5546043635931276</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0.5305930418205558</v>
+      </c>
+      <c r="J179" t="n">
+        <v>1</v>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M179" t="n">
+        <v>21.6416844635106</v>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>BB%B=0.99 (extreme=0.97); RSI=65.1 (extreme=0.13); Wick ratio=2.12; ADX H1=29.1 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด GBPUSD (SELL) เปิดอยู่แล้ว (Ticket 556182717)</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>[0.6059, 0.0, -1.0, -0.8997, 0.9711, -1.0, 1.9991, 0.3015, 0.135, 0.2277, 1.0, 0.2228, 0.8645, 0.9913, -0.0547, 1.5327, 0.1717, -0.3799, -0.1572, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0, 0.0, 0.5545, -1.0, 3.0, 0.0, 0.0, 0.1396]</t>
+        </is>
+      </c>
+      <c r="S179" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T179" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:09:10.855415+00:00</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D180" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>79.71456757581913</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0.08524176291789666</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0.5037664107898699</v>
+      </c>
+      <c r="I180" t="n">
+        <v>0.516445101352937</v>
+      </c>
+      <c r="J180" t="n">
+        <v>1</v>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M180" t="n">
+        <v>21.6416844635106</v>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O180" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>BB%B=0.96 (extreme=0.86); RSI=68.0 (extreme=0.20); Wick ratio=5.00; ADX H1=18.4 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">correlation:กลุ่ม GBP_PAIRS มี effective exposure เดียวกันเปิดแล้ว 1 ตัว (จำกัด </t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>[0.5943, 0.0, -1.0, -0.6476, 0.8571, -1.0, 2.0, 0.3601, 0.1279, 0.1815, 1.0, 0.2633, 0.9091, 0.9571, -0.1751, 0.7743, 0.1717, -0.3816, -0.1607, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0003, 0.0, 0.4734, -1.0, 2.4222, 0.0, 0.0, 0.1437]</t>
+        </is>
+      </c>
+      <c r="S180" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T180" t="n">
+        <v>2.4222</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:09:11.052862+00:00</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D181" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>77.02758069466731</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0.0006002591835980503</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0.5546043635931276</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0.5305930418205558</v>
+      </c>
+      <c r="J181" t="n">
+        <v>1</v>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M181" t="n">
+        <v>21.6416844635106</v>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>BB%B=1.00 (extreme=1.01); RSI=65.3 (extreme=0.13); Wick ratio=1.27; ADX H1=29.1 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด GBPUSD (SELL) เปิดอยู่แล้ว (Ticket 556182717)</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>[0.5406, 0.0, -1.0, -0.8997, 1.0, -1.0, 1.9991, 0.3066, 0.1382, 0.2278, 1.0, 0.2228, 0.8884, 1.0022, -0.0547, 1.5826, 0.1717, -0.3816, -0.1607, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0, 0.0, 0.5545, -1.0, 3.0, 0.0, 0.0, 0.1437]</t>
+        </is>
+      </c>
+      <c r="S181" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T181" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:10:11.574145+00:00</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D182" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>80.84759111809917</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0.0006002591835980503</v>
+      </c>
+      <c r="G182" t="n">
+        <v>1</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0.5546043635931276</v>
+      </c>
+      <c r="I182" t="n">
+        <v>0.5305930418205558</v>
+      </c>
+      <c r="J182" t="n">
+        <v>1</v>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M182" t="n">
+        <v>21.64168446351059</v>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>BB%B=0.98 (extreme=0.95); RSI=64.9 (extreme=0.12); Wick ratio=3.17; ADX H1=29.1 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด GBPUSD (SELL) เปิดอยู่แล้ว (Ticket 556182717)</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>[0.617, 0.0, -1.0, -0.8997, 0.9465, -1.0, 1.9991, 0.2981, 0.1329, 0.2276, 1.0, 0.2228, 0.8486, 0.984, -0.0547, 1.4994, 0.1717, -0.3788, -0.1549, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0, 0.0, 0.5545, -1.0, 3.0, 0.0, 0.0, 0.1458]</t>
+        </is>
+      </c>
+      <c r="S182" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T182" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:12:12.494673+00:00</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D183" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>77.58013935421327</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0.08631319188109225</v>
+      </c>
+      <c r="G183" t="n">
+        <v>1</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0.4847432826961701</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0.5024584883074371</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0.5223950743675232</v>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L183" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M183" t="n">
+        <v>21.64168446351059</v>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O183" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>BB%B=0.99 (extreme=0.96); RSI=68.9 (extreme=0.22); Wick ratio=1.27; ADX H1=18.4 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">correlation:กลุ่ม GBP_PAIRS มี effective exposure เดียวกันเปิดแล้ว 1 ตัว (จำกัด </t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>[0.5516, 0.0, -1.0, -0.6369, 0.9592, -1.0, 2.0, 0.3777, 0.1359, 0.1819, 1.0, 0.265, 0.8996, 0.9877, -0.1649, 0.9153, 0.1105, -0.3855, -0.1688, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0003, 0.0, 0.4701, -1.0, 2.416, 0.0, 0.0, 0.15]</t>
+        </is>
+      </c>
+      <c r="S183" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T183" t="n">
+        <v>2.416</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:13:13.169428+00:00</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D184" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>76.88011055562367</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0.08667033486882345</v>
+      </c>
+      <c r="G184" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0.4847432826961701</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0.5024584883074371</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0.5665579438209534</v>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L184" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M184" t="n">
+        <v>21.64168446351059</v>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O184" t="n">
+        <v>2.199999999999136</v>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>BB%B=1.00 (extreme=1.00); RSI=69.2 (extreme=0.23); Wick ratio=0.88; ADX H1=18.4 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">correlation:กลุ่ม GBP_PAIRS มี effective exposure เดียวกันเปิดแล้ว 1 ตัว (จำกัด </t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>[0.5376, 0.0, -1.0, -0.6333, 0.9971, -1.0, 2.0, 0.3837, 0.1391, 0.1821, 1.0, 0.2655, 0.9014, 0.9991, -0.1615, 0.9692, 0.1105, -0.3821, -0.1618, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0003, 0.0, 0.469, -1.0, 2.4139, 0.0, 0.0, 0.1521]</t>
+        </is>
+      </c>
+      <c r="S184" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T184" t="n">
+        <v>2.4139</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:13:13.549116+00:00</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D185" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>76.12246877513356</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.0006002591835980503</v>
+      </c>
+      <c r="G185" t="n">
+        <v>1</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0.5546043635931276</v>
+      </c>
+      <c r="I185" t="n">
+        <v>0.5305930418205558</v>
+      </c>
+      <c r="J185" t="n">
+        <v>1</v>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L185" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M185" t="n">
+        <v>21.64168446351059</v>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>BB%B=1.01 (extreme=1.02); RSI=65.4 (extreme=0.14); Wick ratio=1.08; ADX H1=29.1 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด GBPUSD (SELL) เปิดอยู่แล้ว (Ticket 556182717)</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>[0.5224, 0.0, -1.0, -0.8997, 1.0, -1.0, 1.9991, 0.3082, 0.1392, 0.2279, 1.0, 0.2228, 0.8964, 1.0058, -0.0547, 1.5993, 0.1717, -0.3821, -0.1618, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0, 0.0, 0.5545, -1.0, 3.0, 0.0, 0.0, 0.1521]</t>
+        </is>
+      </c>
+      <c r="S185" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T185" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:14:14.048914+00:00</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D186" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>75.82017820064235</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0.08667033486882345</v>
+      </c>
+      <c r="G186" t="n">
+        <v>1</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0.5037664107898699</v>
+      </c>
+      <c r="I186" t="n">
+        <v>0.5124270210778886</v>
+      </c>
+      <c r="J186" t="n">
+        <v>1</v>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L186" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M186" t="n">
+        <v>21.64168446351059</v>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O186" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>BB%B=0.93 (extreme=0.77); RSI=66.6 (extreme=0.16); Wick ratio=2.31; ADX H1=18.4 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">correlation:กลุ่ม GBP_PAIRS มี effective exposure เดียวกันเปิดแล้ว 1 ตัว (จำกัด </t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>[0.5164, 0.0, -1.0, -0.6333, 0.7668, -1.0, 2.0, 0.3311, 0.1177, 0.1811, 1.0, 0.2655, 0.6972, 0.9301, -0.1615, 0.6346, 0.1568, -0.3726, -0.1422, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0003, 0.0, 0.469, -1.0, 2.4139, 0.0, 0.0, 0.1542]</t>
+        </is>
+      </c>
+      <c r="S186" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T186" t="n">
+        <v>2.4139</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:14:14.238486+00:00</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D187" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>75.50231500960682</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0.000600973469573518</v>
+      </c>
+      <c r="G187" t="n">
+        <v>1</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0.5546043635931276</v>
+      </c>
+      <c r="I187" t="n">
+        <v>0.5305930418205558</v>
+      </c>
+      <c r="J187" t="n">
+        <v>1</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L187" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M187" t="n">
+        <v>21.64168446351059</v>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O187" t="n">
+        <v>0.09999999999843467</v>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>BB%B=0.94 (extreme=0.79); RSI=63.4 (extreme=0.09); Wick ratio=4.17; ADX H1=29.1 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด GBPUSD (SELL) เปิดอยู่แล้ว (Ticket 556182717)</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>[0.51, 0.0, -1.0, -0.899, 0.7929, -1.0, 1.9968, 0.2687, 0.12, 0.2269, 1.0, 0.2228, 0.753, 0.9379, -0.0536, 1.2979, 0.1717, -0.3732, -0.1434, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0, 0.0, 0.5545, -1.0, 3.0, 0.0, 0.0, 0.1542]</t>
+        </is>
+      </c>
+      <c r="S187" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T187" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:20:16.597125+00:00</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>80.59671906438967</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0.08319387456899234</v>
+      </c>
+      <c r="G188" t="n">
+        <v>1</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0.4847432826961701</v>
+      </c>
+      <c r="I188" t="n">
+        <v>0.4898432534255825</v>
+      </c>
+      <c r="J188" t="n">
+        <v>-0.9624511003494263</v>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M188" t="n">
+        <v>21.64168446351059</v>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O188" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>BB%B=0.96 (extreme=0.86); RSI=69.5 (extreme=0.24); Wick ratio=3.00; ADX H1=18.4 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>[0.6119, 0.0, -1.0, -0.6681, 0.8609, -1.0, 2.0, 0.3908, 0.1547, 0.1859, 1.0, 0.2806, 0.9437, 0.9583, -0.1945, 1.2381, 0.0883, -0.3793, -0.1561, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0003, 0.0, 0.4388, -1.0, 2.4342, 0.0, 0.0, 0.1667]</t>
+        </is>
+      </c>
+      <c r="S188" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T188" t="n">
+        <v>2.4342</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:22:17.435652+00:00</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D189" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>79.4269339113756</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0.08390816054445471</v>
+      </c>
+      <c r="G189" t="n">
+        <v>1</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0.4847432826961701</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0.5008045722577176</v>
+      </c>
+      <c r="J189" t="n">
+        <v>1</v>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L189" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M189" t="n">
+        <v>21.64168446351059</v>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O189" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>BB%B=0.95 (extreme=0.83); RSI=69.1 (extreme=0.23); Wick ratio=4.67; ADX H1=18.5 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">correlation:กลุ่ม GBP_PAIRS มี effective exposure เดียวกันเปิดแล้ว 1 ตัว (จำกัด </t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>[0.5885, 0.0, -1.0, -0.6609, 0.83, -1.0, 2.0, 0.381, 0.1504, 0.1857, 1.0, 0.2811, 0.8824, 0.949, -0.1877, 1.1799, 0.1467, -0.3749, -0.1468, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0003, 0.0, 0.4377, -1.0, 2.43, 0.0, 0.0, 0.1708]</t>
+        </is>
+      </c>
+      <c r="S189" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T189" t="n">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:23:17.954084+00:00</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D190" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>79.12319114975713</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0.08390816054445471</v>
+      </c>
+      <c r="G190" t="n">
+        <v>1</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.4847432826961701</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0.5008045722577176</v>
+      </c>
+      <c r="J190" t="n">
+        <v>1</v>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L190" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M190" t="n">
+        <v>21.64168446351059</v>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O190" t="n">
+        <v>2.400000000000091</v>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>BB%B=0.95 (extreme=0.82); RSI=68.9 (extreme=0.22); Wick ratio=3.50; ADX H1=18.5 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">correlation:กลุ่ม GBP_PAIRS มี effective exposure เดียวกันเปิดแล้ว 1 ตัว (จำกัด </t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>[0.5825, 0.0, -1.0, -0.6609, 0.8223, -1.0, 2.0, 0.3782, 0.1496, 0.1857, 1.0, 0.2811, 0.8754, 0.9467, -0.1877, 1.1679, 0.1467, -0.3743, -0.1457, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0003, 0.0, 0.4377, -1.0, 2.43, 0.0, 0.0, 0.1729]</t>
+        </is>
+      </c>
+      <c r="S190" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T190" t="n">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:24:18.440583+00:00</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D191" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>80.85736795373717</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0.08390816054445471</v>
+      </c>
+      <c r="G191" t="n">
+        <v>1</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0.4847432826961701</v>
+      </c>
+      <c r="I191" t="n">
+        <v>0.5008045722577176</v>
+      </c>
+      <c r="J191" t="n">
+        <v>1</v>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L191" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M191" t="n">
+        <v>21.64168446351059</v>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O191" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>BB%B=0.96 (extreme=0.87); RSI=69.6 (extreme=0.24); Wick ratio=6.00; ADX H1=18.5 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">correlation:กลุ่ม GBP_PAIRS มี effective exposure เดียวกันเปิดแล้ว 1 ตัว (จำกัด </t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>[0.6171, 0.0, -1.0, -0.6609, 0.8686, -1.0, 2.0, 0.392, 0.1542, 0.1859, 1.0, 0.2811, 0.917, 0.9606, -0.1877, 1.2395, 0.1467, -0.376, -0.1491, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0003, 0.0, 0.4377, -1.0, 2.43, 0.0, 0.0, 0.175]</t>
+        </is>
+      </c>
+      <c r="S191" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T191" t="n">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:26:19.275304+00:00</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D192" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>79.12319114975713</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0.08390816054445471</v>
+      </c>
+      <c r="G192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0.4847432826961701</v>
+      </c>
+      <c r="I192" t="n">
+        <v>0.5008045722577176</v>
+      </c>
+      <c r="J192" t="n">
+        <v>1</v>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L192" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M192" t="n">
+        <v>21.64168446351059</v>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O192" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>BB%B=0.95 (extreme=0.82); RSI=68.9 (extreme=0.22); Wick ratio=3.50; ADX H1=18.5 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">correlation:กลุ่ม GBP_PAIRS มี effective exposure เดียวกันเปิดแล้ว 1 ตัว (จำกัด </t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>[0.5825, 0.0, -1.0, -0.6609, 0.8223, -1.0, 2.0, 0.3782, 0.1496, 0.1857, 1.0, 0.2811, 0.8754, 0.9467, -0.1877, 1.1679, 0.1467, -0.3737, -0.1445, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0003, 0.0, 0.4377, -1.0, 2.43, 0.0, 0.0, 0.1792]</t>
+        </is>
+      </c>
+      <c r="S192" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T192" t="n">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:27:19.781693+00:00</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>75.14684035941866</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0.08390816054445471</v>
+      </c>
+      <c r="G193" t="n">
+        <v>1</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0.4847432826961701</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0.4862951332085237</v>
+      </c>
+      <c r="J193" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L193" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M193" t="n">
+        <v>21.64168446351059</v>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O193" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>BB%B=0.97 (extreme=0.91); RSI=69.9 (extreme=0.25); Wick ratio=1.00; ADX H1=18.5 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>[0.5029, 0.0, -1.0, -0.6609, 0.9064, -1.0, 2.0, 0.3982, 0.158, 0.1861, 1.0, 0.2811, 0.9516, 0.9719, -0.1877, 1.299, 0.0601, -0.3838, -0.1653, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0003, 0.0, 0.4377, -1.0, 2.43, 0.0, 0.0, 0.1813]</t>
+        </is>
+      </c>
+      <c r="S193" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T193" t="n">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:29:20.580218+00:00</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D194" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>80.85736795373717</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0.08447958932482584</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0.4847432826961701</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0.5008045722577176</v>
+      </c>
+      <c r="J194" t="n">
+        <v>1</v>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L194" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M194" t="n">
+        <v>21.64168446351059</v>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O194" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>BB%B=0.96 (extreme=0.87); RSI=69.6 (extreme=0.24); Wick ratio=10.00; ADX H1=18.5 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">correlation:กลุ่ม GBP_PAIRS มี effective exposure เดียวกันเปิดแล้ว 1 ตัว (จำกัด </t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>[0.6171, 0.0, -1.0, -0.6552, 0.8686, -1.0, 2.0, 0.392, 0.1531, 0.1859, 1.0, 0.282, 0.8653, 0.9606, -0.1822, 1.2311, 0.1467, -0.3776, -0.1526, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0003, 0.0, 0.4361, -1.0, 2.4266, 0.0, 0.0, 0.1854]</t>
+        </is>
+      </c>
+      <c r="S194" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T194" t="n">
+        <v>2.4266</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:35:22.670435+00:00</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D195" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>75.07177435977303</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0.08015961612534694</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0.4847432826961701</v>
+      </c>
+      <c r="I195" t="n">
+        <v>0.5024584883074371</v>
+      </c>
+      <c r="J195" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L195" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M195" t="n">
+        <v>21.6511395383872</v>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O195" t="n">
+        <v>2.300000000002456</v>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>BB%B=0.90 (extreme=0.68); RSI=69.3 (extreme=0.23); Wick ratio=11.00; ADX H1=18.5 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>[0.5014, 0.0, -1.0, -0.6984, 0.6802, -1.0, 2.0, 0.3867, 0.1464, 0.1888, 1.0, 0.2973, 0.8451, 0.904, -0.2187, 1.0604, 0.1105, -0.3805, -0.1584, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0003, 0.0, 0.4054, -1.0, 2.4527, 0.0, 0.0, 0.1979]</t>
+        </is>
+      </c>
+      <c r="S195" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T195" t="n">
+        <v>2.4527</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:37:23.490547+00:00</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D196" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>76.14562409329754</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0.08051675911308016</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0.4847432826961701</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0.5024584883074371</v>
+      </c>
+      <c r="J196" t="n">
+        <v>-0.8098490834236145</v>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L196" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M196" t="n">
+        <v>21.68792566270117</v>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O196" t="n">
+        <v>2.199999999999136</v>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>BB%B=0.91 (extreme=0.71); RSI=69.6 (extreme=0.24); Wick ratio=4.33; ADX H1=18.5 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>[0.5229, 0.0, -1.0, -0.6948, 0.7115, -1.0, 2.0, 0.392, 0.1489, 0.1889, 1.0, 0.2973, 0.8721, 0.9134, -0.2153, 1.1054, 0.1105, -0.381, -0.1595, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0003, 0.0, 0.4054, -1.0, 2.4505, 0.0, 0.0, 0.2021]</t>
+        </is>
+      </c>
+      <c r="S196" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T196" t="n">
+        <v>2.4505</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:38:54.616768+00:00</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D197" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>75.87843903335359</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0.08051675911308016</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0.4847432826961701</v>
+      </c>
+      <c r="I197" t="n">
+        <v>0.5024584883074371</v>
+      </c>
+      <c r="J197" t="n">
+        <v>-0.8062736988067627</v>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L197" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M197" t="n">
+        <v>21.69007445394793</v>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O197" t="n">
+        <v>2.199999999999136</v>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>BB%B=0.91 (extreme=0.70); RSI=69.5 (extreme=0.24); Wick ratio=7.00; ADX H1=18.5 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>[0.5176, 0.0, -1.0, -0.6948, 0.7037, -1.0, 2.0, 0.3907, 0.1481, 0.1889, 1.0, 0.2973, 0.8653, 0.9111, -0.2153, 1.0929, 0.1105, -0.3816, -0.1607, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0003, 0.0, 0.4054, -1.0, 2.5194, 0.0, 0.0, 0.2042]</t>
+        </is>
+      </c>
+      <c r="S197" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T197" t="n">
+        <v>2.5194</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:40:55.412046+00:00</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D198" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>75.610402221504</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0.08051675911308016</v>
+      </c>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0.4847432826961701</v>
+      </c>
+      <c r="I198" t="n">
+        <v>0.5024584883074371</v>
+      </c>
+      <c r="J198" t="n">
+        <v>-0.7557495832443237</v>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L198" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M198" t="n">
+        <v>21.69293691888741</v>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O198" t="n">
+        <v>2.199999999999136</v>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>BB%B=0.91 (extreme=0.70); RSI=69.5 (extreme=0.24); Wick ratio=15.00; ADX H1=18.5 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>[0.5122, 0.0, -1.0, -0.6948, 0.6959, -1.0, 2.0, 0.3894, 0.1473, 0.1889, 1.0, 0.2973, 0.8586, 0.9088, -0.2153, 1.0805, 0.1105, -0.3855, -0.1688, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0003, 0.0, 0.4054, -1.0, 2.5194, 0.0, 0.0, 0.2083]</t>
+        </is>
+      </c>
+      <c r="S198" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T198" t="n">
+        <v>2.5194</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-05-25 10:15:05.746988+00:00</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D199" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>79.4341411780709</v>
+      </c>
+      <c r="F199" t="n">
+        <v>5.778118235797244</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0.5552555047777317</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0.5356282856320583</v>
+      </c>
+      <c r="J199" t="n">
+        <v>1</v>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L199" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M199" t="n">
+        <v>22.45602516871704</v>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O199" t="n">
+        <v>40.99999999998545</v>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>BB%B=1.03 (extreme=1.10); RSI=63.5 (extreme=0.09); Wick ratio=1.93; ADX H1=22.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=4570.80000 &lt; C=4571.98000) — SELL needs bea</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>[0.5887, 0.0, -1.0, 2.0, 1.0, -1.0, 1.7307, 0.2707, 0.2502, 0.4755, 1.0, 0.1574, 0.9437, 1.0291, -0.2882, 2.9733, 0.2411, -0.3648, -0.126, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0007, 0.0, 0.6851, 1.0, 0.5814, 0.0, 0.0, 0.2812]</t>
+        </is>
+      </c>
+      <c r="S199" t="n">
+        <v>1</v>
+      </c>
+      <c r="T199" t="n">
+        <v>0.5814</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-05-25 10:16:07.680920+00:00</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D200" s="6" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>76.70738864889893</v>
+      </c>
+      <c r="F200" t="n">
+        <v>5.851689691269982</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0.585844093735055</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0.5429948870684755</v>
+      </c>
+      <c r="J200" t="n">
+        <v>1</v>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L200" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M200" t="n">
+        <v>22.45602516871704</v>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O200" t="n">
+        <v>42.00000000000728</v>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>BB%B=1.00 (extreme=1.01); RSI=62.5 (extreme=0.06); Wick ratio=1.49; ADX H1=22.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>[0.5341, 0.0, -1.0, 2.0, 1.0, -1.0, 1.7089, 0.25, 0.2374, 0.4741, 1.0, 0.1574, 0.8574, 1.0018, -0.2793, 2.7838, 0.294, -0.3653, -0.1272, -0.3743, 0.4667, 0.3333, -1.0, 0.8, 0.0007, 0.0, 0.6851, 1.0, 0.577, 0.0, 0.0, 0.2833]</t>
+        </is>
+      </c>
+      <c r="S200" t="n">
+        <v>1</v>
+      </c>
+      <c r="T200" t="n">
+        <v>0.577</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-05-25 10:18:08.460183+00:00</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D201" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>81.53974607791794</v>
+      </c>
+      <c r="F201" t="n">
+        <v>5.851689691269982</v>
+      </c>
+      <c r="G201" t="n">
+        <v>1</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0.5923647262975231</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0.546516583511323</v>
+      </c>
+      <c r="J201" t="n">
+        <v>1</v>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L201" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M201" t="n">
+        <v>22.45602516871704</v>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O201" t="n">
+        <v>43.0000000000291</v>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>BB%B=1.02 (extreme=1.05); RSI=63.1 (extreme=0.08); Wick ratio=5.50; ADX H1=22.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (SELL) เปิดอยู่แล้ว (Ticket 556209566)</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>[0.6308, 0.0, -1.0, 2.0, 1.0, -1.0, 1.7089, 0.2616, 0.2421, 0.4748, 1.0, 0.1574, 0.8991, 1.0152, -0.2793, 2.8573, 0.345, -0.381, -0.1594, -0.3746, 0.4667, 0.6667, -1.0, 0.8, 0.0007, 0.0, 0.6851, 1.0, 0.577, 0.0, 0.0, 0.2875]</t>
+        </is>
+      </c>
+      <c r="S201" t="n">
+        <v>1</v>
+      </c>
+      <c r="T201" t="n">
+        <v>0.577</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-05-25 10:19:08.947119+00:00</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D202" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>76.45129359376202</v>
+      </c>
+      <c r="F202" t="n">
+        <v>5.92811829064457</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0.585844093735055</v>
+      </c>
+      <c r="I202" t="n">
+        <v>0.5429948870684755</v>
+      </c>
+      <c r="J202" t="n">
+        <v>1</v>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L202" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M202" t="n">
+        <v>22.5237057764246</v>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O202" t="n">
+        <v>39.99999999996362</v>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>BB%B=1.05 (extreme=1.15); RSI=64.0 (extreme=0.10); Wick ratio=1.29; ADX H1=22.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (SELL) เปิดอยู่แล้ว (Ticket 556209566)</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>[0.529, 0.0, -1.0, 2.0, 1.0, -1.0, 1.6869, 0.2792, 0.2498, 0.4764, 1.0, 0.159, 0.8986, 1.0453, -0.27, 2.9908, 0.294, -0.3845, -0.1668, -0.3746, 0.4667, 0.6667, -1.0, 0.8, 0.0007, 0.0, 0.6821, 1.0, 0.5726, 0.0, 0.0, 0.2896]</t>
+        </is>
+      </c>
+      <c r="S202" t="n">
+        <v>1</v>
+      </c>
+      <c r="T202" t="n">
+        <v>0.5726</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-05-25 10:20:09.448907+00:00</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D203" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>81.27651169796479</v>
+      </c>
+      <c r="F203" t="n">
+        <v>5.92811829064457</v>
+      </c>
+      <c r="G203" t="n">
+        <v>1</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0.5923647262975231</v>
+      </c>
+      <c r="I203" t="n">
+        <v>0.546516583511323</v>
+      </c>
+      <c r="J203" t="n">
+        <v>1</v>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L203" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M203" t="n">
+        <v>22.5237057764246</v>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O203" t="n">
+        <v>40.99999999998545</v>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>BB%B=1.00 (extreme=1.01); RSI=62.6 (extreme=0.06); Wick ratio=3.55; ADX H1=22.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (SELL) เปิดอยู่แล้ว (Ticket 556209566)</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>[0.6255, 0.0, -1.0, 2.0, 1.0, -1.0, 1.6869, 0.2511, 0.2347, 0.4741, 1.0, 0.159, 0.7695, 1.0031, -0.27, 2.7547, 0.345, -0.3667, -0.13, -0.3746, 0.4667, 0.6667, -1.0, 0.8, 0.0007, 0.0, 0.6821, 1.0, 0.5726, 0.0, 0.0, 0.2917]</t>
+        </is>
+      </c>
+      <c r="S203" t="n">
+        <v>1</v>
+      </c>
+      <c r="T203" t="n">
+        <v>0.5726</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-05-25 10:21:09.953133+00:00</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D204" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>81.08841286315629</v>
+      </c>
+      <c r="F204" t="n">
+        <v>5.944546868080189</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0.5733618460949218</v>
+      </c>
+      <c r="I204" t="n">
+        <v>0.5387321486444179</v>
+      </c>
+      <c r="J204" t="n">
+        <v>1</v>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L204" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M204" t="n">
+        <v>22.5237057764246</v>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O204" t="n">
+        <v>40.99999999998545</v>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>BB%B=1.00 (extreme=1.00); RSI=62.4 (extreme=0.06); Wick ratio=2.87; ADX H1=22.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (SELL) เปิดอยู่แล้ว (Ticket 556209566)</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>[0.6218, 0.0, -1.0, 2.0, 0.9966, -1.0, 1.6822, 0.2476, 0.2327, 0.4739, 1.0, 0.159, 0.7575, 0.999, -0.268, 2.7252, 0.2411, -0.3615, -0.1192, -0.3746, 0.4667, 0.6667, -1.0, 0.8, 0.0007, 0.0, 0.6821, 1.0, 0.5717, 0.0, 0.0, 0.2937]</t>
+        </is>
+      </c>
+      <c r="S204" t="n">
+        <v>1</v>
+      </c>
+      <c r="T204" t="n">
+        <v>0.5717</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-05-25 10:22:10.468394+00:00</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D205" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>81.63532453667062</v>
+      </c>
+      <c r="F205" t="n">
+        <v>5.944546868080189</v>
+      </c>
+      <c r="G205" t="n">
+        <v>1</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0.5733618460949218</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0.5387321486444179</v>
+      </c>
+      <c r="J205" t="n">
+        <v>1</v>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L205" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M205" t="n">
+        <v>22.5237057764246</v>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O205" t="n">
+        <v>39.99999999996362</v>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>BB%B=1.02 (extreme=1.06); RSI=63.3 (extreme=0.08); Wick ratio=97.50; ADX H1=22.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (SELL) เปิดอยู่แล้ว (Ticket 556209566)</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>[0.6327, 0.0, -1.0, 2.0, 1.0, -1.0, 1.6822, 0.2654, 0.2398, 0.475, 1.0, 0.159, 0.8183, 1.0195, -0.268, 2.8362, 0.2411, -0.3692, -0.1352, -0.3746, 0.4667, 0.6667, -1.0, 0.8, 0.0007, 0.0, 0.6821, 1.0, 0.5717, 0.0, 0.0, 0.2958]</t>
+        </is>
+      </c>
+      <c r="S205" t="n">
+        <v>1</v>
+      </c>
+      <c r="T205" t="n">
+        <v>0.5717</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-05-25 10:23:10.939238+00:00</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D206" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>81.08841286315629</v>
+      </c>
+      <c r="F206" t="n">
+        <v>5.944546868080189</v>
+      </c>
+      <c r="G206" t="n">
+        <v>1</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0.5733618460949218</v>
+      </c>
+      <c r="I206" t="n">
+        <v>0.5387321486444179</v>
+      </c>
+      <c r="J206" t="n">
+        <v>1</v>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L206" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M206" t="n">
+        <v>22.5237057764246</v>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O206" t="n">
+        <v>40.99999999998545</v>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>BB%B=1.00 (extreme=1.00); RSI=62.4 (extreme=0.06); Wick ratio=2.87; ADX H1=22.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (SELL) เปิดอยู่แล้ว (Ticket 556209566)</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>[0.6218, 0.0, -1.0, 2.0, 0.9966, -1.0, 1.6822, 0.2476, 0.2327, 0.4739, 1.0, 0.159, 0.7575, 0.999, -0.268, 2.7252, 0.2411, -0.3637, -0.1237, -0.3746, 0.4667, 0.6667, -1.0, 0.8, 0.0007, 0.0, 0.6821, 1.0, 0.5717, 0.0, 0.0, 0.2979]</t>
+        </is>
+      </c>
+      <c r="S206" t="n">
+        <v>1</v>
+      </c>
+      <c r="T206" t="n">
+        <v>0.5717</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-05-25 10:24:11.551709+00:00</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D207" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>81.24976153024429</v>
+      </c>
+      <c r="F207" t="n">
+        <v>5.944546868080189</v>
+      </c>
+      <c r="G207" t="n">
+        <v>1</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0.5733618460949218</v>
+      </c>
+      <c r="I207" t="n">
+        <v>0.5387321486444179</v>
+      </c>
+      <c r="J207" t="n">
+        <v>1</v>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L207" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M207" t="n">
+        <v>22.5237057764246</v>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O207" t="n">
+        <v>40.99999999998545</v>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>BB%B=1.00 (extreme=1.01); RSI=62.5 (extreme=0.06); Wick ratio=3.31; ADX H1=22.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (SELL) เปิดอยู่แล้ว (Ticket 556209566)</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>[0.625, 0.0, -1.0, 2.0, 1.0, -1.0, 1.6822, 0.25, 0.2337, 0.4741, 1.0, 0.159, 0.7658, 1.0018, -0.268, 2.7403, 0.2411, -0.3642, -0.1249, -0.3746, 0.4667, 0.6667, -1.0, 0.8, 0.0007, 0.0, 0.6821, 1.0, 0.5717, 0.0, 0.0, 0.3]</t>
+        </is>
+      </c>
+      <c r="S207" t="n">
+        <v>1</v>
+      </c>
+      <c r="T207" t="n">
+        <v>0.5717</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-05-25 10:25:12.038799+00:00</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D208" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>81.63532453667062</v>
+      </c>
+      <c r="F208" t="n">
+        <v>5.944546868080189</v>
+      </c>
+      <c r="G208" t="n">
+        <v>1</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0.5733618460949218</v>
+      </c>
+      <c r="I208" t="n">
+        <v>0.5387321486444179</v>
+      </c>
+      <c r="J208" t="n">
+        <v>1</v>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L208" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M208" t="n">
+        <v>22.5237057764246</v>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O208" t="n">
+        <v>40.99999999998545</v>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>BB%B=1.02 (extreme=1.06); RSI=63.3 (extreme=0.08); Wick ratio=97.50; ADX H1=22.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (SELL) เปิดอยู่แล้ว (Ticket 556209566)</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>[0.6327, 0.0, -1.0, 2.0, 1.0, -1.0, 1.6822, 0.2654, 0.2398, 0.475, 1.0, 0.159, 0.8183, 1.0195, -0.268, 2.8362, 0.2411, -0.3642, -0.1249, -0.3746, 0.4667, 0.6667, -1.0, 0.8, 0.0007, 0.0, 0.6821, 1.0, 0.5717, 0.0, 0.0, 0.3021]</t>
+        </is>
+      </c>
+      <c r="S208" t="n">
+        <v>1</v>
+      </c>
+      <c r="T208" t="n">
+        <v>0.5717</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-05-25 10:27:12.844948+00:00</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D209" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>76.33377260175696</v>
+      </c>
+      <c r="F209" t="n">
+        <v>6.022404039405669</v>
+      </c>
+      <c r="G209" t="n">
+        <v>1</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0.5733618460949218</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0.5404558991219713</v>
+      </c>
+      <c r="J209" t="n">
+        <v>1</v>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L209" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M209" t="n">
+        <v>22.5237057764246</v>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O209" t="n">
+        <v>39.99999999996362</v>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>BB%B=0.99 (extreme=0.95); RSI=61.8 (extreme=0.05); Wick ratio=1.77; ADX H1=22.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (SELL) เปิดอยู่แล้ว (Ticket 556209566)</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>[0.5267, 0.0, -1.0, 2.0, 0.9519, -1.0, 1.6605, 0.2365, 0.2252, 0.4732, 1.0, 0.159, 0.7188, 0.9856, -0.2586, 2.6202, 0.2411, -0.36, -0.1161, -0.3746, 0.4667, 0.6667, -1.0, 0.8, 0.0007, 0.0, 0.6821, 1.0, 0.5672, 0.0, 0.0, 0.3063]</t>
+        </is>
+      </c>
+      <c r="S209" t="n">
+        <v>1</v>
+      </c>
+      <c r="T209" t="n">
+        <v>0.5672</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-05-25 10:28:13.350811+00:00</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D210" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>78.76457722591705</v>
+      </c>
+      <c r="F210" t="n">
+        <v>6.022404039405669</v>
+      </c>
+      <c r="G210" t="n">
+        <v>1</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0.585844093735055</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0.5439807295235619</v>
+      </c>
+      <c r="J210" t="n">
+        <v>1</v>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L210" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M210" t="n">
+        <v>22.5237057764246</v>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O210" t="n">
+        <v>46.00000000000364</v>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>BB%B=0.99 (extreme=0.97); RSI=62.1 (extreme=0.05); Wick ratio=2.12; ADX H1=22.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (SELL) เปิดอยู่แล้ว (Ticket 556209566)</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>[0.5753, 0.0, -1.0, 2.0, 0.9712, -1.0, 1.6605, 0.2412, 0.2272, 0.4735, 1.0, 0.159, 0.7354, 0.9914, -0.2586, 2.6501, 0.294, -0.3608, -0.1179, -0.3746, 0.4667, 0.6667, -1.0, 0.8, 0.0008, 0.0, 0.6821, 1.0, 0.5672, 0.0, 0.0, 0.3083]</t>
+        </is>
+      </c>
+      <c r="S210" t="n">
+        <v>1</v>
+      </c>
+      <c r="T210" t="n">
+        <v>0.5672</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-05-25 10:29:14.085815+00:00</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D211" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>81.28320639719547</v>
+      </c>
+      <c r="F211" t="n">
+        <v>6.022404039405669</v>
+      </c>
+      <c r="G211" t="n">
+        <v>1</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0.585844093735055</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0.5439807295235619</v>
+      </c>
+      <c r="J211" t="n">
+        <v>1</v>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L211" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M211" t="n">
+        <v>22.5237057764246</v>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O211" t="n">
+        <v>41.0000000000764</v>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>BB%B=1.00 (extreme=1.01); RSI=62.6 (extreme=0.06); Wick ratio=3.61; ADX H1=22.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (SELL) เปิดอยู่แล้ว (Ticket 556209566)</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>[0.6257, 0.0, -1.0, 2.0, 1.0, -1.0, 1.6605, 0.2513, 0.2312, 0.4741, 1.0, 0.159, 0.7704, 1.0034, -0.2586, 2.7132, 0.294, -0.3695, -0.1359, -0.3746, 0.4667, 0.6667, -1.0, 0.8, 0.0007, 0.0, 0.6821, 1.0, 0.5672, 0.0, 0.0, 0.3104]</t>
+        </is>
+      </c>
+      <c r="S211" t="n">
+        <v>1</v>
+      </c>
+      <c r="T211" t="n">
+        <v>0.5672</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-05-25 11:45:36.051554+00:00</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D212" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>78.65692175425185</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0.0003279187491309768</v>
+      </c>
+      <c r="G212" t="n">
+        <v>1</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0.4924691921497034</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0.5068028533896619</v>
+      </c>
+      <c r="J212" t="n">
+        <v>1</v>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L212" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M212" t="n">
+        <v>23.27024722018826</v>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O212" t="n">
+        <v>0.3999999999992898</v>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>BB%B=1.15 (extreme=1.50); RSI=63.3 (extreme=0.08); Wick ratio=1.80; ADX H1=13.3 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=0.58763 &lt; C=0.58767) — SELL needs bearish c</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>[0.5731, 0.0, -1.0, -1.1721, 1.0, -1.0, 2.0, 0.2663, 0.2351, 0.0757, 1.0, 0.1823, 0.8393, 1.1494, -0.2051, 2.2567, 0.3799, -0.3501, -0.0957, -0.3501, 0.4667, 0.0, -0.3333, 0.0, 0.0, 0.0, 0.6353, -1.0, 3.0, 0.0, 0.0, 0.4688]</t>
+        </is>
+      </c>
+      <c r="S212" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T212" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-05-25 11:47:36.743536+00:00</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D213" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>80.93325340582204</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0.0003336330369346788</v>
+      </c>
+      <c r="G213" t="n">
+        <v>1</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0.5037664107898699</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0.5122182767700348</v>
+      </c>
+      <c r="J213" t="n">
+        <v>1</v>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L213" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M213" t="n">
+        <v>23.27024722018826</v>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O213" t="n">
+        <v>0.2000000000002</v>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>BB%B=1.10 (extreme=1.34); RSI=61.9 (extreme=0.05); Wick ratio=4.67; ADX H1=13.3 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=0.58761 &lt; C=0.58766) — SELL needs bearish c</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>[0.6187, 0.0, -1.0, -1.1664, 1.0, -1.0, 2.0, 0.2373, 0.2158, 0.0747, 1.0, 0.1823, 0.6964, 1.1009, -0.1915, 1.9782, 0.3799, -0.3501, -0.0957, -0.3501, 0.4667, 0.0, -0.3333, 0.0, 0.0, 0.0, 0.6353, -1.0, 3.0, 0.0, 0.0, 0.4729]</t>
+        </is>
+      </c>
+      <c r="S213" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T213" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-05-25 12:47:51.823426+00:00</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D214" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>78.24036981753017</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0.0004256629166969047</v>
+      </c>
+      <c r="G214" t="n">
+        <v>1</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0.5783856595171482</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0.5415128563879286</v>
+      </c>
+      <c r="J214" t="n">
+        <v>1</v>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L214" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M214" t="n">
+        <v>22.34957953002953</v>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>BB%B=1.07 (extreme=1.24); RSI=62.7 (extreme=0.07); Wick ratio=1.78; ADX H1=22.1 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=1.16514 &lt; C=1.16525) — SELL needs bearish c</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>[0.5648, 0.0, -1.0, -1.0743, 1.0, -1.0, 2.0, 0.2541, 0.1447, 0.1582, 1.0, 0.2432, 0.75, 1.0723, -0.0629, 0.3524, 0.1568, -0.3501, -0.0957, -0.3501, 0.4667, 0.0, -0.3333, 0.0, 0.0, 0.0, 0.5136, 1.0, 3.0, 0.0, 0.0, 0.5979]</t>
+        </is>
+      </c>
+      <c r="S214" t="n">
+        <v>1</v>
+      </c>
+      <c r="T214" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-05-25 12:48:53.412537+00:00</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D215" s="6" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>80.9598831860536</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0.0004256629166969047</v>
+      </c>
+      <c r="G215" t="n">
+        <v>1</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0.5783856595171482</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0.5415128563879286</v>
+      </c>
+      <c r="J215" t="n">
+        <v>1</v>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L215" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M215" t="n">
+        <v>22.34957953002953</v>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O215" t="n">
+        <v>0</v>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>BB%B=1.03 (extreme=1.12); RSI=61.9 (extreme=0.05); Wick ratio=11.50; ADX H1=22.1 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>[0.6192, 0.0, -1.0, -1.0743, 1.0, -1.0, 2.0, 0.2384, 0.1342, 0.1578, 0.9939, 0.2432, 0.6406, 1.0346, -0.0629, 0.1879, 0.1568, -0.3501, -0.0957, -0.3501, 0.4667, 0.0, -0.3333, 0.0, 0.0, 0.0, 0.5136, 1.0, 3.0, 0.0, 0.0, 0.6]</t>
+        </is>
+      </c>
+      <c r="S215" t="n">
+        <v>1</v>
+      </c>
+      <c r="T215" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-05-25 12:49:53.927643+00:00</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D216" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>79.09295758204681</v>
+      </c>
+      <c r="F216" t="n">
+        <v>0.0004256629166969047</v>
+      </c>
+      <c r="G216" t="n">
+        <v>1</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0.5377168853152771</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0.5257256030953441</v>
+      </c>
+      <c r="J216" t="n">
+        <v>1</v>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L216" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M216" t="n">
+        <v>22.34957953002953</v>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O216" t="n">
+        <v>0</v>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>BB%B=0.99 (extreme=0.96); RSI=60.6 (extreme=0.01); Wick ratio=4.17; ADX H1=22.1 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด EURUSD (SELL) เปิดอยู่แล้ว (Ticket 556274286)</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>[0.5819, 0.0, -1.0, -1.0743, 0.9599, -1.0, 2.0, 0.2119, 0.1222, 0.1572, 0.9669, 0.2432, 0.5156, 0.988, -0.0629, 0.0, 0.0883, -0.3494, -0.0943, -0.3528, 0.4667, 0.3333, -0.3333, 0.0, 0.0, 0.0, 0.5136, 1.0, 3.0, 0.0, 0.0, 0.6021]</t>
+        </is>
+      </c>
+      <c r="S216" t="n">
+        <v>1</v>
+      </c>
+      <c r="T216" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-05-25 12:50:54.481242+00:00</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D217" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>76.97759527519361</v>
+      </c>
+      <c r="F217" t="n">
+        <v>0.0004256629166969047</v>
+      </c>
+      <c r="G217" t="n">
+        <v>1</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0.5037664107898699</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0.5123985069467029</v>
+      </c>
+      <c r="J217" t="n">
+        <v>-0.6068247556686401</v>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L217" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M217" t="n">
+        <v>22.34957953002953</v>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>BB%B=0.97 (extreme=0.90); RSI=60.1 (extreme=0.00); Wick ratio=2.78; ADX H1=22.1 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>[0.5396, 0.0, -1.0, -1.0743, 0.8983, -1.0, 2.0, 0.2012, 0.1177, 0.157, 0.9574, 0.2432, 0.4687, 0.9695, -0.0629, -0.0705, -0.012, -0.3474, -0.0902, -0.3528, 0.4667, 0.3333, -0.3333, 0.0, 0.0, 0.0, 0.5136, 1.0, 3.0, 0.0, 0.0, 0.6042]</t>
+        </is>
+      </c>
+      <c r="S217" t="n">
+        <v>1</v>
+      </c>
+      <c r="T217" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/ftmo_trading_bot/logs/ftmo_trades.xlsx
+++ b/ftmo_trading_bot/logs/ftmo_trades.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF15"/>
+  <dimension ref="A1:BF16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3465,6 +3465,25 @@
           <t>2026-05-26 10:41:47.738259</t>
         </is>
       </c>
+      <c r="N15" t="n">
+        <v>1.34775</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:23:15.837150</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>39.32</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>58.51</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>🔴 SL Hit</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr">
         <is>
           <t>BB%B=0.08 (extreme=0.73); RSI=25.2 (extreme=0.37); Wick ratio=7.25; ADX H1=24.6 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
@@ -3498,6 +3517,20 @@
       <c r="AA15" t="n">
         <v>0.65</v>
       </c>
+      <c r="AB15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>6088</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>🔴 SL Hit</t>
+        </is>
+      </c>
       <c r="AF15" t="n">
         <v>0.4847432826961701</v>
       </c>
@@ -3515,6 +3548,18 @@
       <c r="AJ15" t="n">
         <v>0.3</v>
       </c>
+      <c r="AK15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.34775</v>
+      </c>
       <c r="AO15" t="n">
         <v>1.3471</v>
       </c>
@@ -3524,6 +3569,12 @@
       <c r="AQ15" t="n">
         <v>0</v>
       </c>
+      <c r="AR15" t="n">
+        <v>1.34766</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.34766</v>
+      </c>
       <c r="AT15" t="n">
         <v>23.57346092112552</v>
       </c>
@@ -3533,6 +3584,12 @@
       <c r="AV15" t="n">
         <v>9655.27</v>
       </c>
+      <c r="AW15" t="n">
+        <v>9619.440000000001</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>9619.440000000001</v>
+      </c>
       <c r="AY15" t="n">
         <v>6</v>
       </c>
@@ -3557,6 +3614,204 @@
         <v>1</v>
       </c>
       <c r="BF15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>556613725</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.16395</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.16498</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.16298</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.006991861264775525</v>
+      </c>
+      <c r="I16" t="n">
+        <v>67</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>75.80770263821364</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.0004421880284299552</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-05-26 11:27:19.906395</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>1.16398</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2026-05-26 11:53:18.811288</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="n">
+        <v>-4.69</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-7</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>🔴 SL Hit</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>BB%B=0.96 (extreme=0.85); RSI=60.5 (extreme=0.01); Wick ratio=2.50; ADX H1=15.9 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>11</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>quiet</t>
+        </is>
+      </c>
+      <c r="Z16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1558</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>🔴 SL Hit</t>
+        </is>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.6205603883308504</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.5555900324286286</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AK16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.16395</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1.16398</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.16398</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.16395</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.16395</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>24.38973959512997</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9582.57</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>9577.879999999999</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>9614.84</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2730.294557</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>[0.5162, 0.0, -1.0, -1.0578, 0.8514, -1.0, 2.0, 0.2107, 0.2605, 0.0016, 1.0, 0.1748, 0.7283, 0.9554, 0.3533, 2.171, 0.2411, -0.3984, -0.2275, -0.4174, 0.4889, 0.3333, -0.2, 0.6, 0.0, 0.0, 0.6504, -1.0, 3.0, 0.0, 0.0, 0.0562]</t>
+        </is>
+      </c>
+      <c r="BE16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BF16" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3571,7 +3826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4323,6 +4578,154 @@
         <v>9712.08</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>8</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>25</v>
+      </c>
+      <c r="F21" t="n">
+        <v>71.59</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-164.23</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>-92.64</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K21" t="n">
+        <v>9619.440000000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>100</v>
+      </c>
+      <c r="J22" t="n">
+        <v>100</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K23" t="n">
+        <v>9619.440000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>100</v>
+      </c>
+      <c r="J24" t="n">
+        <v>100</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4360,7 +4763,7 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -4370,7 +4773,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -4380,7 +4783,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -4403,7 +4806,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>$-33.64</t>
+          <t>$-72.31</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4818,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>$30.24</t>
+          <t>$32.06</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4830,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>$19.33</t>
+          <t>$23.26</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4877,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.78</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -4485,7 +4888,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>$-2.80</t>
+          <t>$-4.82</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4899,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -4506,7 +4909,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="16">
@@ -4528,7 +4931,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>-3.14</v>
+        <v>-5.58</v>
       </c>
     </row>
     <row r="18">
@@ -4538,7 +4941,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>-3.2</v>
+        <v>-5.47</v>
       </c>
     </row>
     <row r="19">
@@ -4549,7 +4952,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>$400.51</t>
+          <t>$439.07</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4964,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>3.88%</t>
+          <t>4.25%</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4975,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="22">
@@ -4629,7 +5032,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>$-53.97</t>
+          <t>$-92.64</t>
         </is>
       </c>
     </row>
@@ -4685,7 +5088,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-7.2%</t>
         </is>
       </c>
     </row>
@@ -4697,7 +5100,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>$1,033.64</t>
+          <t>$1,072.31</t>
         </is>
       </c>
     </row>
@@ -4709,7 +5112,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>3.88% / 8%</t>
+          <t>4.25% / 8%</t>
         </is>
       </c>
     </row>
@@ -4721,7 +5124,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>0.54% / 4%</t>
+          <t>0.93% / 4%</t>
         </is>
       </c>
     </row>
@@ -4736,7 +5139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T497"/>
+  <dimension ref="A1:T527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -43621,6 +44024,2386 @@
         <v>2.4713</v>
       </c>
     </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:25:17.377908+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D498" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>75.79742571715184</v>
+      </c>
+      <c r="F498" t="n">
+        <v>0.09678221050278532</v>
+      </c>
+      <c r="G498" t="n">
+        <v>1</v>
+      </c>
+      <c r="H498" t="n">
+        <v>0.5441459206310081</v>
+      </c>
+      <c r="I498" t="n">
+        <v>0.5287546638030387</v>
+      </c>
+      <c r="J498" t="n">
+        <v>1</v>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L498" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M498" t="n">
+        <v>24.38973959513009</v>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O498" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>BB%B=1.10 (extreme=1.34); RSI=71.6 (extreme=0.29); Wick ratio=0.40; ADX H1=16.0 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>risk_manager:🚫 GBPJPY: เทรดครบ 3 ครั้งวันนี้แล้ว — หยุดเพื่อไม่ over-trade</t>
+        </is>
+      </c>
+      <c r="R498" t="inlineStr">
+        <is>
+          <t>[0.5159, 0.0, -1.0, -0.5322, 1.0, -1.0, 2.0, 0.4319, 0.3261, 0.0423, 1.0, 0.2628, 0.7692, 1.1017, 0.2444, 1.7772, 0.0754, -0.3827, -0.1952, -0.4174, 0.4889, 0.3333, -0.2, 0.6, 0.0002, 0.0, 0.4743, 1.0, 2.4918, 0.0, 0.0, 0.0521]</t>
+        </is>
+      </c>
+      <c r="S498" t="n">
+        <v>1</v>
+      </c>
+      <c r="T498" t="n">
+        <v>2.4918</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:26:18.092464+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D499" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>84.56151524365811</v>
+      </c>
+      <c r="F499" t="n">
+        <v>0.09678221050278532</v>
+      </c>
+      <c r="G499" t="n">
+        <v>1</v>
+      </c>
+      <c r="H499" t="n">
+        <v>0.5037664107898699</v>
+      </c>
+      <c r="I499" t="n">
+        <v>0.5142702225049485</v>
+      </c>
+      <c r="J499" t="n">
+        <v>-0.796989917755127</v>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L499" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M499" t="n">
+        <v>24.38973959513001</v>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O499" t="n">
+        <v>2.199999999999136</v>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>BB%B=1.03 (extreme=1.11); RSI=69.1 (extreme=0.23); Wick ratio=4.73; ADX H1=16.0 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>[0.6912, 0.0, -1.0, -0.5322, 1.0, -1.0, 2.0, 0.3825, 0.3036, 0.0411, 1.0, 0.2628, 0.5949, 1.0333, 0.2444, 1.4259, 0.0075, -0.3917, -0.2137, -0.4174, 0.4889, 0.3333, -0.2, 0.6, 0.0002, 0.0, 0.4743, 1.0, 2.4918, 0.0, 0.0, 0.0542]</t>
+        </is>
+      </c>
+      <c r="S499" t="n">
+        <v>1</v>
+      </c>
+      <c r="T499" t="n">
+        <v>2.4918</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:26:18.449336+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D500" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>81.04094991376549</v>
+      </c>
+      <c r="F500" t="n">
+        <v>0.06900690488065282</v>
+      </c>
+      <c r="G500" t="n">
+        <v>1</v>
+      </c>
+      <c r="H500" t="n">
+        <v>0.4847432826961701</v>
+      </c>
+      <c r="I500" t="n">
+        <v>0.5040279635672866</v>
+      </c>
+      <c r="J500" t="n">
+        <v>1</v>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L500" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M500" t="n">
+        <v>24.38973959513001</v>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O500" t="n">
+        <v>0.9999999999990905</v>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>BB%B=0.99 (extreme=0.98); RSI=82.3 (extreme=0.56); Wick ratio=0.48; ADX H1=20.0 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>risk_manager:🧊 Cooldown EURJPY: เหลือ 53.0 นาที</t>
+        </is>
+      </c>
+      <c r="R500" t="inlineStr">
+        <is>
+          <t>[0.6208, 0.0, -1.0, -0.8099, 0.9831, -1.0, 2.0, 0.6451, 0.5779, 0.0723, 1.0, 0.2997, 0.9368, 0.9949, 0.2795, 3.0, 0.2411, -0.3917, -0.2137, -0.4174, 0.4889, 0.3333, -0.2, 0.6, 0.0001, 0.0, 0.4006, -1.0, 2.4703, 0.0, 0.0, 0.0542]</t>
+        </is>
+      </c>
+      <c r="S500" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T500" t="n">
+        <v>2.4703</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:27:19.096003+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D501" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>84.07232863653707</v>
+      </c>
+      <c r="F501" t="n">
+        <v>0.09678221050278532</v>
+      </c>
+      <c r="G501" t="n">
+        <v>1</v>
+      </c>
+      <c r="H501" t="n">
+        <v>0.5037664107898699</v>
+      </c>
+      <c r="I501" t="n">
+        <v>0.5155476985335439</v>
+      </c>
+      <c r="J501" t="n">
+        <v>-0.7821622490882874</v>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L501" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M501" t="n">
+        <v>24.38973959512997</v>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O501" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>BB%B=1.01 (extreme=1.02); RSI=68.1 (extreme=0.20); Wick ratio=63.00; ADX H1=16.0 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R501" t="inlineStr">
+        <is>
+          <t>[0.6814, 0.0, -1.0, -0.5322, 1.0, -1.0, 2.0, 0.3629, 0.2957, 0.0407, 1.0, 0.2628, 0.5333, 1.0068, 0.2444, 1.3019, 0.0075, -0.3984, -0.2275, -0.4174, 0.4889, 0.3333, -0.2, 0.6, 0.0002, 0.0, 0.4743, 1.0, 2.4918, 0.0, 0.0, 0.0562]</t>
+        </is>
+      </c>
+      <c r="S501" t="n">
+        <v>1</v>
+      </c>
+      <c r="T501" t="n">
+        <v>2.4918</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:27:21.200132+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D502" s="6" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>75.80770263821364</v>
+      </c>
+      <c r="F502" t="n">
+        <v>0.0004421880284299552</v>
+      </c>
+      <c r="G502" t="n">
+        <v>1</v>
+      </c>
+      <c r="H502" t="n">
+        <v>0.6205603883308504</v>
+      </c>
+      <c r="I502" t="n">
+        <v>0.5555900324286286</v>
+      </c>
+      <c r="J502" t="n">
+        <v>1</v>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L502" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M502" t="n">
+        <v>24.38973959512997</v>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O502" t="n">
+        <v>0</v>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>BB%B=0.96 (extreme=0.85); RSI=60.5 (extreme=0.01); Wick ratio=2.50; ADX H1=15.9 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>[0.5162, 0.0, -1.0, -1.0578, 0.8514, -1.0, 2.0, 0.2107, 0.2605, 0.0016, 1.0, 0.1748, 0.7283, 0.9554, 0.3533, 2.171, 0.2411, -0.3984, -0.2275, -0.4174, 0.4889, 0.3333, -0.2, 0.6, 0.0, 0.0, 0.6504, -1.0, 3.0, 0.0, 0.0, 0.0562]</t>
+        </is>
+      </c>
+      <c r="S502" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T502" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:28:21.921790+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D503" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>87.573559394478</v>
+      </c>
+      <c r="F503" t="n">
+        <v>0.06900690488065282</v>
+      </c>
+      <c r="G503" t="n">
+        <v>1</v>
+      </c>
+      <c r="H503" t="n">
+        <v>0.5441459206310081</v>
+      </c>
+      <c r="I503" t="n">
+        <v>0.5285818540297125</v>
+      </c>
+      <c r="J503" t="n">
+        <v>1</v>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L503" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M503" t="n">
+        <v>24.38973959512997</v>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O503" t="n">
+        <v>1.099999999999568</v>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>BB%B=0.97 (extreme=0.90); RSI=81.4 (extreme=0.54); Wick ratio=3.60; ADX H1=20.0 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t xml:space="preserve">correlation:กลุ่ม EUR_PAIRS มี effective exposure เดียวกันเปิดแล้ว 1 ตัว (จำกัด </t>
+        </is>
+      </c>
+      <c r="R503" t="inlineStr">
+        <is>
+          <t>[0.7515, 0.0, -1.0, -0.8099, 0.8957, -1.0, 2.0, 0.6281, 0.5585, 0.0714, 1.0, 0.2997, 0.8484, 0.9687, 0.2795, 3.0, 0.0883, -0.392, -0.2144, -0.4201, 0.4889, 0.6667, -0.2, 0.6, 0.0002, 0.0, 0.4006, -1.0, 2.4703, 0.0, 0.0, 0.0583]</t>
+        </is>
+      </c>
+      <c r="S503" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T503" t="n">
+        <v>2.4703</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:28:22.394210+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D504" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>84.23879938319295</v>
+      </c>
+      <c r="F504" t="n">
+        <v>0.09678221050278532</v>
+      </c>
+      <c r="G504" t="n">
+        <v>1</v>
+      </c>
+      <c r="H504" t="n">
+        <v>0.5149457924625712</v>
+      </c>
+      <c r="I504" t="n">
+        <v>0.518759157003828</v>
+      </c>
+      <c r="J504" t="n">
+        <v>0.8114963173866272</v>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L504" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M504" t="n">
+        <v>24.38973959512997</v>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O504" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>BB%B=1.02 (extreme=1.05); RSI=68.5 (extreme=0.21); Wick ratio=20.00; ADX H1=16.0 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t xml:space="preserve">risk_manager:⏱️ Cluster cooldown: เพิ่งเปิดไม้ 61s ที่แล้ว — รออีก 239s (global </t>
+        </is>
+      </c>
+      <c r="R504" t="inlineStr">
+        <is>
+          <t>[0.6848, 0.0, -1.0, -0.5322, 1.0, -1.0, 2.0, 0.3696, 0.2984, 0.0408, 1.0, 0.2628, 0.5538, 1.0158, 0.2444, 1.3432, 0.0299, -0.3914, -0.213, -0.4201, 0.4889, 0.6667, -0.2, 0.6, 0.0002, 0.0, 0.4743, 1.0, 2.4918, 0.0, 0.0, 0.0583]</t>
+        </is>
+      </c>
+      <c r="S504" t="n">
+        <v>1</v>
+      </c>
+      <c r="T504" t="n">
+        <v>2.4918</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:29:23.329242+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D505" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>87.573559394478</v>
+      </c>
+      <c r="F505" t="n">
+        <v>0.06900690488065282</v>
+      </c>
+      <c r="G505" t="n">
+        <v>1</v>
+      </c>
+      <c r="H505" t="n">
+        <v>0.5783856595171482</v>
+      </c>
+      <c r="I505" t="n">
+        <v>0.5425060160602938</v>
+      </c>
+      <c r="J505" t="n">
+        <v>1</v>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L505" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M505" t="n">
+        <v>24.38973959512995</v>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O505" t="n">
+        <v>1.099999999999568</v>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>BB%B=0.97 (extreme=0.90); RSI=81.4 (extreme=0.54); Wick ratio=3.60; ADX H1=20.0 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t xml:space="preserve">correlation:กลุ่ม EUR_PAIRS มี effective exposure เดียวกันเปิดแล้ว 1 ตัว (จำกัด </t>
+        </is>
+      </c>
+      <c r="R505" t="inlineStr">
+        <is>
+          <t>[0.7515, 0.0, -1.0, -0.8099, 0.8957, -1.0, 2.0, 0.6281, 0.5585, 0.0714, 1.0, 0.2997, 0.8484, 0.9687, 0.2795, 3.0, 0.0883, -0.3926, -0.2155, -0.4201, 0.4889, 0.6667, -0.2, 0.6, 0.0002, 0.0, 0.4006, -1.0, 2.4703, 0.0, 0.0, 0.0604]</t>
+        </is>
+      </c>
+      <c r="S505" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T505" t="n">
+        <v>2.4703</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:29:23.717780+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D506" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>84.15600126918859</v>
+      </c>
+      <c r="F506" t="n">
+        <v>0.0972822106856098</v>
+      </c>
+      <c r="G506" t="n">
+        <v>1</v>
+      </c>
+      <c r="H506" t="n">
+        <v>0.5149457924625712</v>
+      </c>
+      <c r="I506" t="n">
+        <v>0.5195389256839401</v>
+      </c>
+      <c r="J506" t="n">
+        <v>0.9283030033111572</v>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L506" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M506" t="n">
+        <v>24.38973959512995</v>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O506" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>BB%B=1.01 (extreme=1.04); RSI=68.3 (extreme=0.21); Wick ratio=62.00; ADX H1=16.0 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q506" t="inlineStr">
+        <is>
+          <t>risk_manager:⏱️ Cluster cooldown: เพิ่งเปิดไม้ 122s ที่แล้ว — รออีก 178s (global</t>
+        </is>
+      </c>
+      <c r="R506" t="inlineStr">
+        <is>
+          <t>[0.6831, 0.0, -1.0, -0.5272, 1.0, -1.0, 2.0, 0.3662, 0.2955, 0.0407, 1.0, 0.2628, 0.5436, 1.0113, 0.2507, 1.3158, 0.0299, -0.3926, -0.2155, -0.4201, 0.4889, 0.6667, -0.2, 0.6, 0.0002, 0.0, 0.4743, 1.0, 2.4892, 0.0, 0.0, 0.0604]</t>
+        </is>
+      </c>
+      <c r="S506" t="n">
+        <v>1</v>
+      </c>
+      <c r="T506" t="n">
+        <v>2.4892</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:30:24.352465+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D507" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>79.40197798201999</v>
+      </c>
+      <c r="F507" t="n">
+        <v>0.06472069553481974</v>
+      </c>
+      <c r="G507" t="n">
+        <v>1</v>
+      </c>
+      <c r="H507" t="n">
+        <v>0.5783856595171482</v>
+      </c>
+      <c r="I507" t="n">
+        <v>0.5423361858453758</v>
+      </c>
+      <c r="J507" t="n">
+        <v>1</v>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L507" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M507" t="n">
+        <v>24.4614111345589</v>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O507" t="n">
+        <v>0.9999999999990905</v>
+      </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>BB%B=0.91 (extreme=0.70); RSI=81.0 (extreme=0.52); Wick ratio=2.00; ADX H1=20.0 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q507" t="inlineStr">
+        <is>
+          <t xml:space="preserve">correlation:กลุ่ม EUR_PAIRS มี effective exposure เดียวกันเปิดแล้ว 1 ตัว (จำกัด </t>
+        </is>
+      </c>
+      <c r="R507" t="inlineStr">
+        <is>
+          <t>[0.588, 0.0, -1.0, -0.8528, 0.6971, -1.0, 2.0, 0.6196, 0.5619, 0.0804, 1.0, 0.3214, 0.8504, 0.9091, 0.1881, 2.1786, 0.1717, -0.3906, -0.2114, -0.4201, 0.4889, 0.6667, -0.2, 0.6, 0.0002, 0.0, 0.3571, -1.0, 2.5021, 0.0, 0.0, 0.0625]</t>
+        </is>
+      </c>
+      <c r="S507" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T507" t="n">
+        <v>2.5021</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:32:25.382085+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D508" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>77.49072150052943</v>
+      </c>
+      <c r="F508" t="n">
+        <v>0.09476205095125449</v>
+      </c>
+      <c r="G508" t="n">
+        <v>1</v>
+      </c>
+      <c r="H508" t="n">
+        <v>0.5552555047777317</v>
+      </c>
+      <c r="I508" t="n">
+        <v>0.5353130939870816</v>
+      </c>
+      <c r="J508" t="n">
+        <v>1</v>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L508" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M508" t="n">
+        <v>24.4614111345589</v>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O508" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>BB%B=1.00 (extreme=1.01); RSI=70.9 (extreme=0.27); Wick ratio=0.81; ADX H1=16.0 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q508" t="inlineStr">
+        <is>
+          <t>risk_manager:🚫 GBPJPY: เทรดครบ 3 ครั้งวันนี้แล้ว — หยุดเพื่อไม่ over-trade</t>
+        </is>
+      </c>
+      <c r="R508" t="inlineStr">
+        <is>
+          <t>[0.5498, 0.0, -1.0, -0.5524, 1.0, -1.0, 2.0, 0.4181, 0.3248, 0.0458, 1.0, 0.2683, 0.7077, 1.0028, 0.2062, 1.8573, 0.1105, -0.392, -0.2143, -0.4201, 0.4889, 0.6667, -0.2, 0.6, 0.0002, 0.0, 0.4633, 1.0, 2.5022, 0.0, 0.0, 0.0667]</t>
+        </is>
+      </c>
+      <c r="S508" t="n">
+        <v>1</v>
+      </c>
+      <c r="T508" t="n">
+        <v>2.5022</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:32:25.788771+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D509" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>77.26571304344432</v>
+      </c>
+      <c r="F509" t="n">
+        <v>0.06722069644894008</v>
+      </c>
+      <c r="G509" t="n">
+        <v>1</v>
+      </c>
+      <c r="H509" t="n">
+        <v>0.5234693308031478</v>
+      </c>
+      <c r="I509" t="n">
+        <v>0.5228603719053183</v>
+      </c>
+      <c r="J509" t="n">
+        <v>1</v>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L509" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M509" t="n">
+        <v>24.4614111345589</v>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O509" t="n">
+        <v>1.099999999999568</v>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>BB%B=0.94 (extreme=0.79); RSI=82.4 (extreme=0.56); Wick ratio=0.86; ADX H1=20.0 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t xml:space="preserve">correlation:กลุ่ม EUR_PAIRS มี effective exposure เดียวกันเปิดแล้ว 1 ตัว (จำกัด </t>
+        </is>
+      </c>
+      <c r="R509" t="inlineStr">
+        <is>
+          <t>[0.5453, 0.0, -1.0, -0.8278, 0.7921, -1.0, 2.0, 0.6486, 0.5629, 0.0814, 1.0, 0.3218, 0.9241, 0.9376, 0.2328, 2.4397, 0.4183, -0.3913, -0.2129, -0.4201, 0.4889, 0.6667, -0.2, 0.6, 0.0002, 0.0, 0.3563, -1.0, 2.4833, 0.0, 0.0, 0.0667]</t>
+        </is>
+      </c>
+      <c r="S509" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T509" t="n">
+        <v>2.4833</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:33:26.452416+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D510" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>78.04942287582</v>
+      </c>
+      <c r="F510" t="n">
+        <v>0.09476205095125449</v>
+      </c>
+      <c r="G510" t="n">
+        <v>1</v>
+      </c>
+      <c r="H510" t="n">
+        <v>0.5552555047777317</v>
+      </c>
+      <c r="I510" t="n">
+        <v>0.5353130939870816</v>
+      </c>
+      <c r="J510" t="n">
+        <v>1</v>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L510" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M510" t="n">
+        <v>24.4614111345589</v>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O510" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>BB%B=1.00 (extreme=1.00); RSI=70.8 (extreme=0.27); Wick ratio=0.96; ADX H1=16.0 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>risk_manager:🚫 GBPJPY: เทรดครบ 3 ครั้งวันนี้แล้ว — หยุดเพื่อไม่ over-trade</t>
+        </is>
+      </c>
+      <c r="R510" t="inlineStr">
+        <is>
+          <t>[0.561, 0.0, -1.0, -0.5524, 0.996, -1.0, 2.0, 0.4151, 0.3235, 0.0458, 1.0, 0.2683, 0.6974, 0.9988, 0.2062, 1.8362, 0.1105, -0.3909, -0.212, -0.4201, 0.4889, 0.6667, -0.2, 0.6, 0.0002, 0.0, 0.4633, 1.0, 2.5022, 0.0, 0.0, 0.0688]</t>
+        </is>
+      </c>
+      <c r="S510" t="n">
+        <v>1</v>
+      </c>
+      <c r="T510" t="n">
+        <v>2.5022</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:33:26.975667+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D511" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>77.26571304344432</v>
+      </c>
+      <c r="F511" t="n">
+        <v>0.06722069644894008</v>
+      </c>
+      <c r="G511" t="n">
+        <v>1</v>
+      </c>
+      <c r="H511" t="n">
+        <v>0.5234693308031478</v>
+      </c>
+      <c r="I511" t="n">
+        <v>0.5228603719053183</v>
+      </c>
+      <c r="J511" t="n">
+        <v>1</v>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L511" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M511" t="n">
+        <v>24.4614111345589</v>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O511" t="n">
+        <v>0.9999999999990905</v>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>BB%B=0.94 (extreme=0.79); RSI=82.4 (extreme=0.56); Wick ratio=0.86; ADX H1=20.0 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t xml:space="preserve">correlation:กลุ่ม EUR_PAIRS มี effective exposure เดียวกันเปิดแล้ว 1 ตัว (จำกัด </t>
+        </is>
+      </c>
+      <c r="R511" t="inlineStr">
+        <is>
+          <t>[0.5453, 0.0, -1.0, -0.8278, 0.7921, -1.0, 2.0, 0.6486, 0.5629, 0.0814, 1.0, 0.3218, 0.9241, 0.9376, 0.2328, 2.4397, 0.4183, -0.3914, -0.2131, -0.4201, 0.4889, 0.6667, -0.2, 0.6, 0.0001, 0.0, 0.3563, -1.0, 2.4833, 0.0, 0.0, 0.0688]</t>
+        </is>
+      </c>
+      <c r="S511" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T511" t="n">
+        <v>2.4833</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:34:27.681829+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D512" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>81.58876415530499</v>
+      </c>
+      <c r="F512" t="n">
+        <v>0.09476205095125449</v>
+      </c>
+      <c r="G512" t="n">
+        <v>1</v>
+      </c>
+      <c r="H512" t="n">
+        <v>0.585844093735055</v>
+      </c>
+      <c r="I512" t="n">
+        <v>0.5457593348734199</v>
+      </c>
+      <c r="J512" t="n">
+        <v>1</v>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L512" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M512" t="n">
+        <v>24.4614111345589</v>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O512" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>BB%B=0.97 (extreme=0.89); RSI=69.6 (extreme=0.24); Wick ratio=4.22; ADX H1=16.0 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>risk_manager:🚫 GBPJPY: เทรดครบ 3 ครั้งวันนี้แล้ว — หยุดเพื่อไม่ over-trade</t>
+        </is>
+      </c>
+      <c r="R512" t="inlineStr">
+        <is>
+          <t>[0.6318, 0.0, -1.0, -0.5524, 0.8936, -1.0, 2.0, 0.3912, 0.3134, 0.0452, 1.0, 0.2683, 0.6205, 0.9681, 0.2062, 1.6779, 0.1717, -0.3916, -0.2134, -0.4201, 0.4889, 0.6667, -0.2, 0.6, 0.0002, 0.0, 0.4633, 1.0, 2.5022, 0.0, 0.0, 0.0708]</t>
+        </is>
+      </c>
+      <c r="S512" t="n">
+        <v>1</v>
+      </c>
+      <c r="T512" t="n">
+        <v>2.5022</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:35:28.441366+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D513" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>83.54380989946188</v>
+      </c>
+      <c r="F513" t="n">
+        <v>0.06743498224157798</v>
+      </c>
+      <c r="G513" t="n">
+        <v>1</v>
+      </c>
+      <c r="H513" t="n">
+        <v>0.5733618460949218</v>
+      </c>
+      <c r="I513" t="n">
+        <v>0.5394999055095673</v>
+      </c>
+      <c r="J513" t="n">
+        <v>1</v>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L513" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M513" t="n">
+        <v>24.48921277128338</v>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O513" t="n">
+        <v>1.099999999999568</v>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>BB%B=0.93 (extreme=0.75); RSI=82.0 (extreme=0.55); Wick ratio=2.55; ADX H1=20.0 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t xml:space="preserve">correlation:กลุ่ม EUR_PAIRS มี effective exposure เดียวกันเปิดแล้ว 1 ตัว (จำกัด </t>
+        </is>
+      </c>
+      <c r="R513" t="inlineStr">
+        <is>
+          <t>[0.6709, 0.0, -1.0, -0.8257, 0.7513, -1.0, 2.0, 0.6402, 0.5516, 0.081, 1.0, 0.3218, 0.8819, 0.9254, 0.2366, 2.2837, 0.1568, -0.3926, -0.2155, -0.4201, 0.4889, 0.6667, -0.2, 0.6, 0.0002, 0.0, 0.3563, -1.0, 2.4817, 0.0, 0.0, 0.0729]</t>
+        </is>
+      </c>
+      <c r="S513" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T513" t="n">
+        <v>2.4817</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:35:29.091436+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D514" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>82.33867553269216</v>
+      </c>
+      <c r="F514" t="n">
+        <v>0.09519062253653232</v>
+      </c>
+      <c r="G514" t="n">
+        <v>1</v>
+      </c>
+      <c r="H514" t="n">
+        <v>0.5575842696629213</v>
+      </c>
+      <c r="I514" t="n">
+        <v>0.5367826975224808</v>
+      </c>
+      <c r="J514" t="n">
+        <v>1</v>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L514" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M514" t="n">
+        <v>24.48921277128338</v>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O514" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>BB%B=0.97 (extreme=0.91); RSI=69.8 (extreme=0.25); Wick ratio=2.92; ADX H1=16.0 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>risk_manager:🚫 GBPJPY: เทรดครบ 3 ครั้งวันนี้แล้ว — หยุดเพื่อไม่ over-trade</t>
+        </is>
+      </c>
+      <c r="R514" t="inlineStr">
+        <is>
+          <t>[0.6468, 0.0, -1.0, -0.5481, 0.9145, -1.0, 2.0, 0.3961, 0.314, 0.0453, 1.0, 0.2683, 0.6359, 0.9744, 0.2115, 1.7018, 0.1105, -0.3931, -0.2166, -0.4201, 0.4889, 0.6667, -0.2, 0.6, 0.0002, 0.0, 0.4633, 1.0, 2.5, 0.0, 0.0, 0.0729]</t>
+        </is>
+      </c>
+      <c r="S514" t="n">
+        <v>1</v>
+      </c>
+      <c r="T514" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:36:29.821346+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D515" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>83.10696612290748</v>
+      </c>
+      <c r="F515" t="n">
+        <v>0.06743498224157798</v>
+      </c>
+      <c r="G515" t="n">
+        <v>1</v>
+      </c>
+      <c r="H515" t="n">
+        <v>0.5552555047777317</v>
+      </c>
+      <c r="I515" t="n">
+        <v>0.5340089355869302</v>
+      </c>
+      <c r="J515" t="n">
+        <v>0.5243434906005859</v>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L515" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M515" t="n">
+        <v>24.48921277128338</v>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O515" t="n">
+        <v>1.099999999999568</v>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>BB%B=0.92 (extreme=0.74); RSI=81.9 (extreme=0.55); Wick ratio=3.87; ADX H1=20.0 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t xml:space="preserve">correlation:กลุ่ม EUR_PAIRS มี effective exposure เดียวกันเปิดแล้ว 1 ตัว (จำกัด </t>
+        </is>
+      </c>
+      <c r="R515" t="inlineStr">
+        <is>
+          <t>[0.6621, 0.0, -1.0, -0.8257, 0.7389, -1.0, 2.0, 0.6377, 0.5488, 0.0809, 1.0, 0.3218, 0.8692, 0.9217, 0.2366, 2.2392, 0.1105, -0.3923, -0.215, -0.4201, 0.4889, 0.6667, -0.2, 0.6, 0.0002, 0.0, 0.3563, -1.0, 2.4817, 0.0, 0.0, 0.075]</t>
+        </is>
+      </c>
+      <c r="S515" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T515" t="n">
+        <v>2.4817</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:36:30.260731+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D516" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>82.33867553269216</v>
+      </c>
+      <c r="F516" t="n">
+        <v>0.09519062253653232</v>
+      </c>
+      <c r="G516" t="n">
+        <v>1</v>
+      </c>
+      <c r="H516" t="n">
+        <v>0.5575842696629213</v>
+      </c>
+      <c r="I516" t="n">
+        <v>0.5367826975224808</v>
+      </c>
+      <c r="J516" t="n">
+        <v>1</v>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L516" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M516" t="n">
+        <v>24.48921277128338</v>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O516" t="n">
+        <v>2.400000000000091</v>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>BB%B=0.97 (extreme=0.91); RSI=69.8 (extreme=0.25); Wick ratio=2.92; ADX H1=16.0 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q516" t="inlineStr">
+        <is>
+          <t>risk_manager:🚫 GBPJPY: เทรดครบ 3 ครั้งวันนี้แล้ว — หยุดเพื่อไม่ over-trade</t>
+        </is>
+      </c>
+      <c r="R516" t="inlineStr">
+        <is>
+          <t>[0.6468, 0.0, -1.0, -0.5481, 0.9145, -1.0, 2.0, 0.3961, 0.314, 0.0453, 1.0, 0.2683, 0.6359, 0.9744, 0.2115, 1.7018, 0.1105, -0.391, -0.2123, -0.4201, 0.4889, 0.6667, -0.2, 0.6, 0.0003, 0.0, 0.4633, 1.0, 2.5, 0.0, 0.0, 0.075]</t>
+        </is>
+      </c>
+      <c r="S516" t="n">
+        <v>1</v>
+      </c>
+      <c r="T516" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:37:30.953175+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D517" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>82.22488764456881</v>
+      </c>
+      <c r="F517" t="n">
+        <v>0.06743498224157798</v>
+      </c>
+      <c r="G517" t="n">
+        <v>1</v>
+      </c>
+      <c r="H517" t="n">
+        <v>0.585844093735055</v>
+      </c>
+      <c r="I517" t="n">
+        <v>0.5438916027903801</v>
+      </c>
+      <c r="J517" t="n">
+        <v>1</v>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L517" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M517" t="n">
+        <v>24.48921277128338</v>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O517" t="n">
+        <v>1.200000000000045</v>
+      </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>BB%B=0.91 (extreme=0.71); RSI=81.6 (extreme=0.54); Wick ratio=18.50; ADX H1=20.0 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q517" t="inlineStr">
+        <is>
+          <t xml:space="preserve">correlation:กลุ่ม EUR_PAIRS มี effective exposure เดียวกันเปิดแล้ว 1 ตัว (จำกัด </t>
+        </is>
+      </c>
+      <c r="R517" t="inlineStr">
+        <is>
+          <t>[0.6445, 0.0, -1.0, -0.8257, 0.7139, -1.0, 2.0, 0.6324, 0.5431, 0.0806, 1.0, 0.3218, 0.8439, 0.9142, 0.2366, 2.1502, 0.1717, -0.3927, -0.2158, -0.4201, 0.4889, 0.6667, -0.2, 0.6, 0.0002, 0.0, 0.3563, -1.0, 2.4817, 0.0, 0.0, 0.0771]</t>
+        </is>
+      </c>
+      <c r="S517" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T517" t="n">
+        <v>2.4817</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:37:31.377956+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D518" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>80.57619308754869</v>
+      </c>
+      <c r="F518" t="n">
+        <v>0.09519062253653232</v>
+      </c>
+      <c r="G518" t="n">
+        <v>1</v>
+      </c>
+      <c r="H518" t="n">
+        <v>0.5149457924625712</v>
+      </c>
+      <c r="I518" t="n">
+        <v>0.5202717297355524</v>
+      </c>
+      <c r="J518" t="n">
+        <v>-0.5850766897201538</v>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L518" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M518" t="n">
+        <v>24.48921277128338</v>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O518" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>BB%B=0.96 (extreme=0.87); RSI=69.2 (extreme=0.23); Wick ratio=8.40; ADX H1=16.0 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R518" t="inlineStr">
+        <is>
+          <t>[0.6115, 0.0, -1.0, -0.5481, 0.8654, -1.0, 2.0, 0.3845, 0.3093, 0.0451, 1.0, 0.2683, 0.6, 0.9596, 0.2115, 1.6283, 0.0299, -0.3934, -0.2171, -0.4201, 0.4889, 0.6667, -0.2, 0.6, 0.0002, 0.0, 0.4633, 1.0, 2.5, 0.0, 0.0, 0.0771]</t>
+        </is>
+      </c>
+      <c r="S518" t="n">
+        <v>1</v>
+      </c>
+      <c r="T518" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:38:32.085643+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D519" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>81.62663583491958</v>
+      </c>
+      <c r="F519" t="n">
+        <v>0.06757783943667127</v>
+      </c>
+      <c r="G519" t="n">
+        <v>1</v>
+      </c>
+      <c r="H519" t="n">
+        <v>0.585844093735055</v>
+      </c>
+      <c r="I519" t="n">
+        <v>0.5438916027903801</v>
+      </c>
+      <c r="J519" t="n">
+        <v>1</v>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L519" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M519" t="n">
+        <v>24.48921277128338</v>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O519" t="n">
+        <v>1.099999999999568</v>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>BB%B=0.91 (extreme=0.70); RSI=81.2 (extreme=0.53); Wick ratio=39.00; ADX H1=20.0 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q519" t="inlineStr">
+        <is>
+          <t xml:space="preserve">correlation:กลุ่ม EUR_PAIRS มี effective exposure เดียวกันเปิดแล้ว 1 ตัว (จำกัด </t>
+        </is>
+      </c>
+      <c r="R519" t="inlineStr">
+        <is>
+          <t>[0.6325, 0.0, -1.0, -0.8242, 0.7013, -1.0, 2.0, 0.6235, 0.5391, 0.0805, 1.0, 0.3218, 0.8312, 0.9104, 0.2392, 2.1013, 0.1717, -0.3901, -0.2104, -0.4201, 0.4889, 0.6667, -0.2, 0.6, 0.0002, 0.0, 0.3563, -1.0, 2.4807, 0.0, 0.0, 0.0792]</t>
+        </is>
+      </c>
+      <c r="S519" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T519" t="n">
+        <v>2.4807</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:38:32.580355+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D520" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>78.61509862953659</v>
+      </c>
+      <c r="F520" t="n">
+        <v>0.09519062253653232</v>
+      </c>
+      <c r="G520" t="n">
+        <v>1</v>
+      </c>
+      <c r="H520" t="n">
+        <v>0.5312239800166529</v>
+      </c>
+      <c r="I520" t="n">
+        <v>0.5247564552329623</v>
+      </c>
+      <c r="J520" t="n">
+        <v>0.9799360036849976</v>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L520" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M520" t="n">
+        <v>24.48921277128338</v>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O520" t="n">
+        <v>2.300000000002456</v>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>BB%B=0.94 (extreme=0.82); RSI=68.3 (extreme=0.21); Wick ratio=23.50; ADX H1=16.0 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q520" t="inlineStr">
+        <is>
+          <t>risk_manager:🚫 GBPJPY: เทรดครบ 3 ครั้งวันนี้แล้ว — หยุดเพื่อไม่ over-trade</t>
+        </is>
+      </c>
+      <c r="R520" t="inlineStr">
+        <is>
+          <t>[0.5723, 0.0, -1.0, -0.5481, 0.8153, -1.0, 2.0, 0.3663, 0.3046, 0.0448, 1.0, 0.2683, 0.5641, 0.9446, 0.2115, 1.5548, 0.0601, -0.3907, -0.2116, -0.4201, 0.4889, 0.6667, -0.2, 0.6, 0.0002, 0.0, 0.4633, 1.0, 2.5, 0.0, 0.0, 0.0792]</t>
+        </is>
+      </c>
+      <c r="S520" t="n">
+        <v>1</v>
+      </c>
+      <c r="T520" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:39:33.215835+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D521" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>82.52016255408708</v>
+      </c>
+      <c r="F521" t="n">
+        <v>0.06757783943667127</v>
+      </c>
+      <c r="G521" t="n">
+        <v>1</v>
+      </c>
+      <c r="H521" t="n">
+        <v>0.585844093735055</v>
+      </c>
+      <c r="I521" t="n">
+        <v>0.5438916027903801</v>
+      </c>
+      <c r="J521" t="n">
+        <v>1</v>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L521" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M521" t="n">
+        <v>24.48921277128338</v>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O521" t="n">
+        <v>0.9999999999990905</v>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>BB%B=0.92 (extreme=0.72); RSI=81.7 (extreme=0.54); Wick ratio=8.75; ADX H1=20.0 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q521" t="inlineStr">
+        <is>
+          <t xml:space="preserve">correlation:กลุ่ม EUR_PAIRS มี effective exposure เดียวกันเปิดแล้ว 1 ตัว (จำกัด </t>
+        </is>
+      </c>
+      <c r="R521" t="inlineStr">
+        <is>
+          <t>[0.6504, 0.0, -1.0, -0.8242, 0.7222, -1.0, 2.0, 0.6341, 0.5438, 0.0807, 1.0, 0.3218, 0.8523, 0.9167, 0.2392, 2.1753, 0.1717, -0.392, -0.2143, -0.4201, 0.4889, 0.6667, -0.2, 0.6, 0.0001, 0.0, 0.3563, -1.0, 2.4807, 0.0, 0.0, 0.0812]</t>
+        </is>
+      </c>
+      <c r="S521" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T521" t="n">
+        <v>2.4807</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:39:33.648353+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D522" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>82.33867553269216</v>
+      </c>
+      <c r="F522" t="n">
+        <v>0.09519062253653232</v>
+      </c>
+      <c r="G522" t="n">
+        <v>1</v>
+      </c>
+      <c r="H522" t="n">
+        <v>0.5575842696629213</v>
+      </c>
+      <c r="I522" t="n">
+        <v>0.5367826975224808</v>
+      </c>
+      <c r="J522" t="n">
+        <v>1</v>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L522" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M522" t="n">
+        <v>24.48921277128338</v>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O522" t="n">
+        <v>2.200000000001978</v>
+      </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>BB%B=0.97 (extreme=0.91); RSI=69.8 (extreme=0.25); Wick ratio=2.92; ADX H1=16.0 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q522" t="inlineStr">
+        <is>
+          <t>risk_manager:🚫 GBPJPY: เทรดครบ 3 ครั้งวันนี้แล้ว — หยุดเพื่อไม่ over-trade</t>
+        </is>
+      </c>
+      <c r="R522" t="inlineStr">
+        <is>
+          <t>[0.6468, 0.0, -1.0, -0.5481, 0.9145, -1.0, 2.0, 0.3961, 0.314, 0.0453, 1.0, 0.2683, 0.6359, 0.9744, 0.2115, 1.7018, 0.1105, -0.3908, -0.2118, -0.4201, 0.4889, 0.6667, -0.2, 0.6, 0.0002, 0.0, 0.4633, 1.0, 2.5, 0.0, 0.0, 0.0812]</t>
+        </is>
+      </c>
+      <c r="S522" t="n">
+        <v>1</v>
+      </c>
+      <c r="T522" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:23:52.250557+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D523" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>75.7865994458969</v>
+      </c>
+      <c r="F523" t="n">
+        <v>0.0003907006519457914</v>
+      </c>
+      <c r="G523" t="n">
+        <v>1</v>
+      </c>
+      <c r="H523" t="n">
+        <v>0.4605809128630706</v>
+      </c>
+      <c r="I523" t="n">
+        <v>0.4690075791018995</v>
+      </c>
+      <c r="J523" t="n">
+        <v>0.8208042979240417</v>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L523" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M523" t="n">
+        <v>25.44914117147982</v>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O523" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>BB%B=0.07 (extreme=0.75); RSI=33.5 (extreme=0.16); Wick ratio=2.50; ADX H1=26.8 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q523" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bearish (O=0.58450 &gt; C=0.58436) — BUY needs bullish co</t>
+        </is>
+      </c>
+      <c r="R523" t="inlineStr">
+        <is>
+          <t>[0.5157, 0.0, 1.0, -1.1093, 0.7515, -1.0, 2.0, -0.3297, -0.0218, 0.2426, 0.9495, 0.4054, -0.9167, 0.0745, 0.0171, -1.0238, -0.0788, -0.3806, -0.1908, -0.3806, 0.4889, 0.0, -0.2, 0.0, 0.0, 0.0, 0.1892, 1.0, 3.0, 0.0, 0.0, 0.1729]</t>
+        </is>
+      </c>
+      <c r="S523" t="n">
+        <v>1</v>
+      </c>
+      <c r="T523" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:34:55.411178+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D524" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>76.38271541608705</v>
+      </c>
+      <c r="F524" t="n">
+        <v>0.0004937621011556069</v>
+      </c>
+      <c r="G524" t="n">
+        <v>1</v>
+      </c>
+      <c r="H524" t="n">
+        <v>0.5733618460949218</v>
+      </c>
+      <c r="I524" t="n">
+        <v>0.537720929686584</v>
+      </c>
+      <c r="J524" t="n">
+        <v>1</v>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L524" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M524" t="n">
+        <v>25.53132154938546</v>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O524" t="n">
+        <v>0</v>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>BB%B=0.95 (extreme=0.84); RSI=62.5 (extreme=0.06); Wick ratio=2.75; ADX H1=15.7 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q524" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=1.16406 &lt; C=1.16425) — SELL needs bearish c</t>
+        </is>
+      </c>
+      <c r="R524" t="inlineStr">
+        <is>
+          <t>[0.5277, 0.0, -1.0, -1.0062, 0.8383, -1.0, 2.0, 0.2493, 0.2131, 0.0121, 1.0, 0.1369, 0.8883, 0.9515, 0.41, 0.6481, 0.1105, -0.3806, -0.1908, -0.3806, 0.4889, 0.0, -0.2, 0.0, 0.0, 0.0, 0.7263, -1.0, 3.0, 0.0, 0.0, 0.1958]</t>
+        </is>
+      </c>
+      <c r="S524" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T524" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:40:57.265587+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D525" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>76.38271541608705</v>
+      </c>
+      <c r="F525" t="n">
+        <v>0.0004937621011556069</v>
+      </c>
+      <c r="G525" t="n">
+        <v>1</v>
+      </c>
+      <c r="H525" t="n">
+        <v>0.5733618460949218</v>
+      </c>
+      <c r="I525" t="n">
+        <v>0.537720929686584</v>
+      </c>
+      <c r="J525" t="n">
+        <v>1</v>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L525" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M525" t="n">
+        <v>25.61170668873758</v>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O525" t="n">
+        <v>0</v>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>BB%B=0.95 (extreme=0.84); RSI=62.5 (extreme=0.06); Wick ratio=2.75; ADX H1=15.7 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q525" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=1.16410 &lt; C=1.16414) — SELL needs bearish c</t>
+        </is>
+      </c>
+      <c r="R525" t="inlineStr">
+        <is>
+          <t>[0.5277, 0.0, -1.0, -1.0062, 0.8383, -1.0, 2.0, 0.2493, 0.2131, 0.0121, 1.0, 0.1369, 0.8883, 0.9515, 0.41, 0.6481, 0.1105, -0.3806, -0.1908, -0.3806, 0.4889, 0.0, -0.2, 0.0, 0.0, 0.0, 0.7263, -1.0, 3.0, 0.0, 0.0, 0.2083]</t>
+        </is>
+      </c>
+      <c r="S525" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T525" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:42:58.293727+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D526" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>75.36894383843531</v>
+      </c>
+      <c r="F526" t="n">
+        <v>0.0004937621011556069</v>
+      </c>
+      <c r="G526" t="n">
+        <v>1</v>
+      </c>
+      <c r="H526" t="n">
+        <v>0.5733618460949218</v>
+      </c>
+      <c r="I526" t="n">
+        <v>0.5399390721678856</v>
+      </c>
+      <c r="J526" t="n">
+        <v>1</v>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L526" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M526" t="n">
+        <v>25.80788133304734</v>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O526" t="n">
+        <v>0</v>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>BB%B=0.94 (extreme=0.81); RSI=62.2 (extreme=0.05); Wick ratio=6.50; ADX H1=15.7 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q526" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=1.16416 &lt; C=1.16422) — SELL needs bearish c</t>
+        </is>
+      </c>
+      <c r="R526" t="inlineStr">
+        <is>
+          <t>[0.5074, 0.0, -1.0, -1.0062, 0.8091, -1.0, 2.0, 0.2439, 0.2105, 0.012, 1.0, 0.1369, 0.868, 0.9427, 0.41, 0.6076, 0.1105, -0.3806, -0.1908, -0.3806, 0.4889, 0.0, -0.2, 0.0, 0.0, 0.0, 0.7263, -1.0, 3.0, 0.0, 0.0, 0.2125]</t>
+        </is>
+      </c>
+      <c r="S526" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T526" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:43:59.077528+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D527" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>75.87746700950575</v>
+      </c>
+      <c r="F527" t="n">
+        <v>0.0004937621011556069</v>
+      </c>
+      <c r="G527" t="n">
+        <v>1</v>
+      </c>
+      <c r="H527" t="n">
+        <v>0.5733618460949218</v>
+      </c>
+      <c r="I527" t="n">
+        <v>0.5399390721678856</v>
+      </c>
+      <c r="J527" t="n">
+        <v>1</v>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L527" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M527" t="n">
+        <v>25.80788133304734</v>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="O527" t="n">
+        <v>0</v>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>BB%B=0.95 (extreme=0.82); RSI=62.3 (extreme=0.06); Wick ratio=4.00; ADX H1=15.7 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q527" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=1.16421 &lt; C=1.16423) — SELL needs bearish c</t>
+        </is>
+      </c>
+      <c r="R527" t="inlineStr">
+        <is>
+          <t>[0.5175, 0.0, -1.0, -1.0062, 0.8238, -1.0, 2.0, 0.2466, 0.2118, 0.012, 1.0, 0.1369, 0.8782, 0.9471, 0.41, 0.6278, 0.1105, -0.3806, -0.1908, -0.3806, 0.4889, 0.0, -0.2, 0.0, 0.0, 0.0, 0.7263, -1.0, 3.0, 0.0, 0.0, 0.2146]</t>
+        </is>
+      </c>
+      <c r="S527" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T527" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ftmo_trading_bot/logs/ftmo_trades.xlsx
+++ b/ftmo_trading_bot/logs/ftmo_trades.xlsx
@@ -4806,7 +4806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5889,6 +5889,80 @@
       </c>
       <c r="K29" t="n">
         <v>9647.360000000001</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>9647.360000000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>100</v>
+      </c>
+      <c r="J31" t="n">
+        <v>100</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/ftmo_trading_bot/logs/ftmo_trades.xlsx
+++ b/ftmo_trading_bot/logs/ftmo_trades.xlsx
@@ -6138,7 +6138,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="15">

--- a/ftmo_trading_bot/logs/ftmo_trades.xlsx
+++ b/ftmo_trading_bot/logs/ftmo_trades.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF21"/>
+  <dimension ref="A1:BF22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4795,6 +4795,204 @@
         <v>0.4501</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>557127016</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>4482.91</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4472.77</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4492.77</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.006219318031046835</v>
+      </c>
+      <c r="I22" t="n">
+        <v>60</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>75.05792386113919</v>
+      </c>
+      <c r="L22" t="n">
+        <v>8.352333667282569</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:34:52.807300</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>4482.88</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:09:03.613667</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>🔴 SL Hit</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>BB%B=-0.12 (extreme=1.41); RSI=33.2 (extreme=0.17); Wick ratio=0.73; ADX H1=27.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" t="n">
+        <v>9</v>
+      </c>
+      <c r="W22" t="n">
+        <v>41</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>243</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>702</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2050</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>🔴 SL Hit</t>
+        </is>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.5037664107898699</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.5133086988515869</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AK22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>4482.91</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>4482.36</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>4482.77</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>41.0000000000764</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>4482.89</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>4483.3</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>27.51604332463016</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>9647.360000000001</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>9646.639999999999</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>9646.639999999999</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>[0.5012, 0.0, 1.0, 2.0, 1.0, -1.0, 1.1973, -0.3361, -0.2665, 0.5046, 1.0, 0.2417, -0.8381, -0.1226, 0.0721, -2.962, 0.0299, -0.3526, -0.0, -0.3526, 0.5111, 0.0, -0.4, 0.2, 0.0005, 0.0, 0.5165, 1.0, 0.4168, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="BE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0.4168</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6378,7 +6576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T686"/>
+  <dimension ref="A1:T701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -60138,6 +60336,1201 @@
         <v>3</v>
       </c>
     </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-05-27 05:46:38.169821+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D687" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E687" t="n">
+        <v>76.58026888161241</v>
+      </c>
+      <c r="F687" t="n">
+        <v>7.694643862963689</v>
+      </c>
+      <c r="G687" t="n">
+        <v>1</v>
+      </c>
+      <c r="H687" t="n">
+        <v>0.5037664107898699</v>
+      </c>
+      <c r="I687" t="n">
+        <v>0.511708171340427</v>
+      </c>
+      <c r="J687" t="n">
+        <v>1</v>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L687" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M687" t="n">
+        <v>27.07402111017177</v>
+      </c>
+      <c r="N687" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O687" t="n">
+        <v>42.00000000000728</v>
+      </c>
+      <c r="P687" t="inlineStr">
+        <is>
+          <t>BB%B=0.04 (extreme=0.86); RSI=38.7 (extreme=0.03); Wick ratio=12.85; ADX H1=27.1 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q687" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bearish (O=4493.51000 &gt; C=4492.29000) — BUY needs bull</t>
+        </is>
+      </c>
+      <c r="R687" t="inlineStr">
+        <is>
+          <t>[0.5316, 0.0, 1.0, 2.0, 0.8647, -1.0, 1.2996, -0.2255, -0.1384, 0.4447, 1.0, 0.2055, -0.8661, 0.0406, -0.0139, -1.9663, 0.0883, -0.3526, -0.0, -0.3526, 0.5111, 0.0, -0.4, 0.2, 0.0005, 0.0, 0.589, 1.0, 0.4404, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="S687" t="n">
+        <v>1</v>
+      </c>
+      <c r="T687" t="n">
+        <v>0.4404</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-05-27 06:32:50.808550+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D688" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E688" t="n">
+        <v>75.33914031680767</v>
+      </c>
+      <c r="F688" t="n">
+        <v>8.352333667282569</v>
+      </c>
+      <c r="G688" t="n">
+        <v>1</v>
+      </c>
+      <c r="H688" t="n">
+        <v>0.5234693308031478</v>
+      </c>
+      <c r="I688" t="n">
+        <v>0.5224717499385005</v>
+      </c>
+      <c r="J688" t="n">
+        <v>1</v>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L688" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M688" t="n">
+        <v>27.51604332463016</v>
+      </c>
+      <c r="N688" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O688" t="n">
+        <v>39.99999999996362</v>
+      </c>
+      <c r="P688" t="inlineStr">
+        <is>
+          <t>BB%B=-0.12 (extreme=1.40); RSI=33.3 (extreme=0.17); Wick ratio=0.80; ADX H1=27.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q688" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bearish (O=4485.02000 &gt; C=4482.92000) — BUY needs bull</t>
+        </is>
+      </c>
+      <c r="R688" t="inlineStr">
+        <is>
+          <t>[0.5068, 0.0, 1.0, 2.0, 1.0, -1.0, 1.1973, -0.3346, -0.2653, 0.5043, 1.0, 0.2417, -0.8302, -0.1195, 0.0721, -2.9441, 0.0883, -0.3526, -0.0, -0.3526, 0.5111, 0.0, -0.4, 0.2, 0.0005, 0.0, 0.5165, 1.0, 0.4168, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="S688" t="n">
+        <v>1</v>
+      </c>
+      <c r="T688" t="n">
+        <v>0.4168</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-05-27 06:33:51.824174+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D689" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E689" t="n">
+        <v>79.18802620767903</v>
+      </c>
+      <c r="F689" t="n">
+        <v>8.352333667282569</v>
+      </c>
+      <c r="G689" t="n">
+        <v>1</v>
+      </c>
+      <c r="H689" t="n">
+        <v>0.5234693308031478</v>
+      </c>
+      <c r="I689" t="n">
+        <v>0.5224717499385005</v>
+      </c>
+      <c r="J689" t="n">
+        <v>1</v>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L689" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M689" t="n">
+        <v>27.51604332463016</v>
+      </c>
+      <c r="N689" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O689" t="n">
+        <v>40.99999999998545</v>
+      </c>
+      <c r="P689" t="inlineStr">
+        <is>
+          <t>BB%B=-0.09 (extreme=1.31); RSI=34.0 (extreme=0.15); Wick ratio=1.63; ADX H1=27.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q689" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bearish (O=4482.93000 &gt; C=4482.04000) — BUY needs bull</t>
+        </is>
+      </c>
+      <c r="R689" t="inlineStr">
+        <is>
+          <t>[0.5838, 0.0, 1.0, 2.0, 1.0, -1.0, 1.1973, -0.3207, -0.2555, 0.5019, 1.0, 0.2417, -0.7621, -0.0923, 0.0721, -2.7896, 0.0883, -0.3526, -0.0, -0.3526, 0.5111, 0.0, -0.4, 0.2, 0.0005, 0.0, 0.5165, 1.0, 0.4168, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="S689" t="n">
+        <v>1</v>
+      </c>
+      <c r="T689" t="n">
+        <v>0.4168</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-05-27 06:34:54.038007+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D690" s="6" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE</t>
+        </is>
+      </c>
+      <c r="E690" t="n">
+        <v>75.05792386113919</v>
+      </c>
+      <c r="F690" t="n">
+        <v>8.352333667282569</v>
+      </c>
+      <c r="G690" t="n">
+        <v>1</v>
+      </c>
+      <c r="H690" t="n">
+        <v>0.5037664107898699</v>
+      </c>
+      <c r="I690" t="n">
+        <v>0.5133086988515869</v>
+      </c>
+      <c r="J690" t="n">
+        <v>1</v>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L690" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M690" t="n">
+        <v>27.51604332463016</v>
+      </c>
+      <c r="N690" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O690" t="n">
+        <v>41.0000000000764</v>
+      </c>
+      <c r="P690" t="inlineStr">
+        <is>
+          <t>BB%B=-0.12 (extreme=1.41); RSI=33.2 (extreme=0.17); Wick ratio=0.73; ADX H1=27.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R690" t="inlineStr">
+        <is>
+          <t>[0.5012, 0.0, 1.0, 2.0, 1.0, -1.0, 1.1973, -0.3361, -0.2665, 0.5046, 1.0, 0.2417, -0.8381, -0.1226, 0.0721, -2.962, 0.0299, -0.3526, -0.0, -0.3526, 0.5111, 0.0, -0.4, 0.2, 0.0005, 0.0, 0.5165, 1.0, 0.4168, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="S690" t="n">
+        <v>1</v>
+      </c>
+      <c r="T690" t="n">
+        <v>0.4168</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-05-27 06:35:53.201858+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D691" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E691" t="n">
+        <v>79.85335325212723</v>
+      </c>
+      <c r="F691" t="n">
+        <v>8.352333667282569</v>
+      </c>
+      <c r="G691" t="n">
+        <v>1</v>
+      </c>
+      <c r="H691" t="n">
+        <v>0.5234693308031478</v>
+      </c>
+      <c r="I691" t="n">
+        <v>0.5224717499385005</v>
+      </c>
+      <c r="J691" t="n">
+        <v>1</v>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L691" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M691" t="n">
+        <v>27.51604332463016</v>
+      </c>
+      <c r="N691" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O691" t="n">
+        <v>41.0000000000764</v>
+      </c>
+      <c r="P691" t="inlineStr">
+        <is>
+          <t>BB%B=-0.09 (extreme=1.30); RSI=34.0 (extreme=0.15); Wick ratio=1.77; ADX H1=27.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q691" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (BUY) เปิดอยู่แล้ว (Ticket 557127016)</t>
+        </is>
+      </c>
+      <c r="R691" t="inlineStr">
+        <is>
+          <t>[0.5971, 0.0, 1.0, 2.0, 1.0, -1.0, 1.1973, -0.3192, -0.2544, 0.5016, 1.0, 0.2417, -0.7547, -0.0892, 0.0721, -2.7729, 0.0883, -0.3467, 0.0, -0.3529, 0.5111, 0.3333, -0.4, 0.2, 0.0005, 0.0, 0.5165, 1.0, 0.4168, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="S691" t="n">
+        <v>1</v>
+      </c>
+      <c r="T691" t="n">
+        <v>0.4168</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-05-27 06:36:53.294128+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D692" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E692" t="n">
+        <v>82.71671115028147</v>
+      </c>
+      <c r="F692" t="n">
+        <v>8.352333667282569</v>
+      </c>
+      <c r="G692" t="n">
+        <v>1</v>
+      </c>
+      <c r="H692" t="n">
+        <v>0.7415220293724967</v>
+      </c>
+      <c r="I692" t="n">
+        <v>0.5798564205996106</v>
+      </c>
+      <c r="J692" t="n">
+        <v>1</v>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L692" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M692" t="n">
+        <v>27.51604332463016</v>
+      </c>
+      <c r="N692" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O692" t="n">
+        <v>42.99999999993815</v>
+      </c>
+      <c r="P692" t="inlineStr">
+        <is>
+          <t>BB%B=-0.07 (extreme=1.23); RSI=34.6 (extreme=0.14); Wick ratio=3.33; ADX H1=27.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q692" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (BUY) เปิดอยู่แล้ว (Ticket 557127016)</t>
+        </is>
+      </c>
+      <c r="R692" t="inlineStr">
+        <is>
+          <t>[0.6543, 0.0, 1.0, 2.0, 1.0, -1.0, 1.1973, -0.3087, -0.2472, 0.4998, 1.0, 0.2417, -0.7052, -0.0681, 0.0721, -2.6603, 0.5029, -0.3413, 0.0, -0.3529, 0.5111, 0.3333, -0.4, 0.2, 0.0005, 0.0, 0.5165, 1.0, 0.4168, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="S692" t="n">
+        <v>1</v>
+      </c>
+      <c r="T692" t="n">
+        <v>0.4168</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-05-27 06:37:53.442763+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D693" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E693" t="n">
+        <v>82.71671115028147</v>
+      </c>
+      <c r="F693" t="n">
+        <v>8.352333667282569</v>
+      </c>
+      <c r="G693" t="n">
+        <v>1</v>
+      </c>
+      <c r="H693" t="n">
+        <v>0.7415220293724967</v>
+      </c>
+      <c r="I693" t="n">
+        <v>0.5798564205996106</v>
+      </c>
+      <c r="J693" t="n">
+        <v>1</v>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L693" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M693" t="n">
+        <v>27.51604332463016</v>
+      </c>
+      <c r="N693" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O693" t="n">
+        <v>39.99999999996362</v>
+      </c>
+      <c r="P693" t="inlineStr">
+        <is>
+          <t>BB%B=-0.07 (extreme=1.23); RSI=34.6 (extreme=0.14); Wick ratio=3.33; ADX H1=27.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q693" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (BUY) เปิดอยู่แล้ว (Ticket 557127016)</t>
+        </is>
+      </c>
+      <c r="R693" t="inlineStr">
+        <is>
+          <t>[0.6543, 0.0, 1.0, 2.0, 1.0, -1.0, 1.1973, -0.3087, -0.2472, 0.4998, 1.0, 0.2417, -0.7052, -0.0681, 0.0721, -2.6603, 0.5029, -0.3411, 0.0, -0.3529, 0.5111, 0.3333, -0.4, 0.2, 0.0005, 0.0, 0.5165, 1.0, 0.4168, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="S693" t="n">
+        <v>1</v>
+      </c>
+      <c r="T693" t="n">
+        <v>0.4168</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-05-27 06:38:53.901367+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D694" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E694" t="n">
+        <v>82.10179688375732</v>
+      </c>
+      <c r="F694" t="n">
+        <v>8.352333667282569</v>
+      </c>
+      <c r="G694" t="n">
+        <v>1</v>
+      </c>
+      <c r="H694" t="n">
+        <v>0.5234693308031478</v>
+      </c>
+      <c r="I694" t="n">
+        <v>0.5224717499385005</v>
+      </c>
+      <c r="J694" t="n">
+        <v>1</v>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L694" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M694" t="n">
+        <v>27.51604332463016</v>
+      </c>
+      <c r="N694" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O694" t="n">
+        <v>43.0000000000291</v>
+      </c>
+      <c r="P694" t="inlineStr">
+        <is>
+          <t>BB%B=-0.08 (extreme=1.27); RSI=34.3 (extreme=0.14); Wick ratio=2.25; ADX H1=27.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q694" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (BUY) เปิดอยู่แล้ว (Ticket 557127016)</t>
+        </is>
+      </c>
+      <c r="R694" t="inlineStr">
+        <is>
+          <t>[0.642, 0.0, 1.0, 2.0, 1.0, -1.0, 1.1973, -0.315, -0.2515, 0.5009, 1.0, 0.2417, -0.7347, -0.0808, 0.0721, -2.7274, 0.0883, -0.3444, 0.0, -0.3529, 0.5111, 0.3333, -0.4, 0.2, 0.0005, 0.0, 0.5165, 1.0, 0.4168, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="S694" t="n">
+        <v>1</v>
+      </c>
+      <c r="T694" t="n">
+        <v>0.4168</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-05-27 06:39:53.968119+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D695" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E695" t="n">
+        <v>78.16234147936932</v>
+      </c>
+      <c r="F695" t="n">
+        <v>8.352333667282569</v>
+      </c>
+      <c r="G695" t="n">
+        <v>1</v>
+      </c>
+      <c r="H695" t="n">
+        <v>0.5441459206310081</v>
+      </c>
+      <c r="I695" t="n">
+        <v>0.5275337020954891</v>
+      </c>
+      <c r="J695" t="n">
+        <v>1</v>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L695" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M695" t="n">
+        <v>27.51604332463016</v>
+      </c>
+      <c r="N695" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O695" t="n">
+        <v>42.99999999993815</v>
+      </c>
+      <c r="P695" t="inlineStr">
+        <is>
+          <t>BB%B=-0.10 (extreme=1.33); RSI=33.8 (extreme=0.15); Wick ratio=1.42; ADX H1=27.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q695" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (BUY) เปิดอยู่แล้ว (Ticket 557127016)</t>
+        </is>
+      </c>
+      <c r="R695" t="inlineStr">
+        <is>
+          <t>[0.5632, 0.0, 1.0, 2.0, 1.0, -1.0, 1.1973, -0.3234, -0.2574, 0.5024, 1.0, 0.2417, -0.7753, -0.0977, 0.0721, -2.8196, 0.0883, -0.3492, 0.0, -0.3529, 0.5111, 0.3333, -0.4, 0.2, 0.0005, 0.0, 0.5165, 1.0, 0.4168, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="S695" t="n">
+        <v>1</v>
+      </c>
+      <c r="T695" t="n">
+        <v>0.4168</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-05-27 06:40:54.008205+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D696" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E696" t="n">
+        <v>79.23317900488989</v>
+      </c>
+      <c r="F696" t="n">
+        <v>8.352333667282569</v>
+      </c>
+      <c r="G696" t="n">
+        <v>1</v>
+      </c>
+      <c r="H696" t="n">
+        <v>0.5441459206310081</v>
+      </c>
+      <c r="I696" t="n">
+        <v>0.5275337020954891</v>
+      </c>
+      <c r="J696" t="n">
+        <v>1</v>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L696" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M696" t="n">
+        <v>27.51604332463016</v>
+      </c>
+      <c r="N696" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O696" t="n">
+        <v>39.99999999996362</v>
+      </c>
+      <c r="P696" t="inlineStr">
+        <is>
+          <t>BB%B=-0.09 (extreme=1.31); RSI=34.0 (extreme=0.15); Wick ratio=1.64; ADX H1=27.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q696" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (BUY) เปิดอยู่แล้ว (Ticket 557127016)</t>
+        </is>
+      </c>
+      <c r="R696" t="inlineStr">
+        <is>
+          <t>[0.5847, 0.0, 1.0, 2.0, 1.0, -1.0, 1.1973, -0.3206, -0.2554, 0.5019, 1.0, 0.2417, -0.7616, -0.0921, 0.0721, -2.7884, 0.0883, -0.3475, 0.0, -0.3529, 0.5111, 0.3333, -0.4, 0.2, 0.0005, 0.0, 0.5165, 1.0, 0.4168, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="S696" t="n">
+        <v>1</v>
+      </c>
+      <c r="T696" t="n">
+        <v>0.4168</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-05-27 06:41:54.060791+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D697" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E697" t="n">
+        <v>80.76914401714021</v>
+      </c>
+      <c r="F697" t="n">
+        <v>8.352333667282569</v>
+      </c>
+      <c r="G697" t="n">
+        <v>1</v>
+      </c>
+      <c r="H697" t="n">
+        <v>0.5441459206310081</v>
+      </c>
+      <c r="I697" t="n">
+        <v>0.5275337020954891</v>
+      </c>
+      <c r="J697" t="n">
+        <v>1</v>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L697" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M697" t="n">
+        <v>27.51604332463016</v>
+      </c>
+      <c r="N697" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O697" t="n">
+        <v>44.99999999998181</v>
+      </c>
+      <c r="P697" t="inlineStr">
+        <is>
+          <t>BB%B=-0.09 (extreme=1.28); RSI=34.1 (extreme=0.15); Wick ratio=1.97; ADX H1=27.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q697" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (BUY) เปิดอยู่แล้ว (Ticket 557127016)</t>
+        </is>
+      </c>
+      <c r="R697" t="inlineStr">
+        <is>
+          <t>[0.6154, 0.0, 1.0, 2.0, 1.0, -1.0, 1.1973, -0.3173, -0.2531, 0.5013, 1.0, 0.2417, -0.7458, -0.0855, 0.0721, -2.7525, 0.0883, -0.3458, 0.0, -0.3529, 0.5111, 0.3333, -0.4, 0.2, 0.0005, 0.0, 0.5165, 1.0, 0.4168, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="S697" t="n">
+        <v>1</v>
+      </c>
+      <c r="T697" t="n">
+        <v>0.4168</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-05-27 06:42:54.082916+00:00</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D698" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E698" t="n">
+        <v>76.63080970571957</v>
+      </c>
+      <c r="F698" t="n">
+        <v>8.352333667282569</v>
+      </c>
+      <c r="G698" t="n">
+        <v>1</v>
+      </c>
+      <c r="H698" t="n">
+        <v>0.5441459206310081</v>
+      </c>
+      <c r="I698" t="n">
+        <v>0.5275337020954891</v>
+      </c>
+      <c r="J698" t="n">
+        <v>1</v>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L698" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M698" t="n">
+        <v>27.51604332463016</v>
+      </c>
+      <c r="N698" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O698" t="n">
+        <v>43.0000000000291</v>
+      </c>
+      <c r="P698" t="inlineStr">
+        <is>
+          <t>BB%B=-0.11 (extreme=1.36); RSI=33.6 (extreme=0.16); Wick ratio=1.08; ADX H1=27.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q698" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (BUY) เปิดอยู่แล้ว (Ticket 557127016)</t>
+        </is>
+      </c>
+      <c r="R698" t="inlineStr">
+        <is>
+          <t>[0.5326, 0.0, 1.0, 2.0, 1.0, -1.0, 1.1973, -0.3286, -0.2611, 0.5033, 1.0, 0.2417, -0.8006, -0.1079, 0.0721, -2.877, 0.0883, -0.3519, 0.0, -0.3529, 0.5111, 0.3333, -0.4, 0.2, 0.0005, 0.0, 0.5165, 1.0, 0.4168, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="S698" t="n">
+        <v>1</v>
+      </c>
+      <c r="T698" t="n">
+        <v>0.4168</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-05-27 06:43:54.960151+00:00</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D699" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E699" t="n">
+        <v>82.74220358837439</v>
+      </c>
+      <c r="F699" t="n">
+        <v>8.352333667282569</v>
+      </c>
+      <c r="G699" t="n">
+        <v>1</v>
+      </c>
+      <c r="H699" t="n">
+        <v>0.7383741569045084</v>
+      </c>
+      <c r="I699" t="n">
+        <v>0.5772204685668473</v>
+      </c>
+      <c r="J699" t="n">
+        <v>1</v>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L699" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M699" t="n">
+        <v>27.51604332463016</v>
+      </c>
+      <c r="N699" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O699" t="n">
+        <v>42.00000000000728</v>
+      </c>
+      <c r="P699" t="inlineStr">
+        <is>
+          <t>BB%B=-0.07 (extreme=1.23); RSI=34.5 (extreme=0.14); Wick ratio=3.11; ADX H1=27.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q699" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (BUY) เปิดอยู่แล้ว (Ticket 557127016)</t>
+        </is>
+      </c>
+      <c r="R699" t="inlineStr">
+        <is>
+          <t>[0.6548, 0.0, 1.0, 2.0, 1.0, -1.0, 1.1973, -0.3097, -0.2479, 0.5, 1.0, 0.2417, -0.7099, -0.0702, 0.0721, -2.6711, 0.4767, -0.3423, 0.0, -0.3529, 0.5111, 0.3333, -0.4, 0.2, 0.0005, 0.0, 0.5165, 1.0, 0.4168, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="S699" t="n">
+        <v>1</v>
+      </c>
+      <c r="T699" t="n">
+        <v>0.4168</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-05-27 06:44:55.574729+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D700" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E700" t="n">
+        <v>82.17717244367962</v>
+      </c>
+      <c r="F700" t="n">
+        <v>8.385905108129348</v>
+      </c>
+      <c r="G700" t="n">
+        <v>1</v>
+      </c>
+      <c r="H700" t="n">
+        <v>0.5552555047777317</v>
+      </c>
+      <c r="I700" t="n">
+        <v>0.5319384527901853</v>
+      </c>
+      <c r="J700" t="n">
+        <v>1</v>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L700" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M700" t="n">
+        <v>27.51604332463016</v>
+      </c>
+      <c r="N700" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O700" t="n">
+        <v>40.00000000005457</v>
+      </c>
+      <c r="P700" t="inlineStr">
+        <is>
+          <t>BB%B=-0.03 (extreme=1.08); RSI=35.6 (extreme=0.11); Wick ratio=72.70; ADX H1=27.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q700" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (BUY) เปิดอยู่แล้ว (Ticket 557127016)</t>
+        </is>
+      </c>
+      <c r="R700" t="inlineStr">
+        <is>
+          <t>[0.6435, 0.0, 1.0, 2.0, 1.0, -1.0, 1.1925, -0.2871, -0.2327, 0.4965, 1.0, 0.2417, -0.6113, -0.0254, 0.0763, -2.4374, 0.1105, -0.3304, 0.0, -0.3529, 0.5111, 0.3333, -0.4, 0.2, 0.0005, 0.0, 0.5165, 1.0, 0.4156, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="S700" t="n">
+        <v>1</v>
+      </c>
+      <c r="T700" t="n">
+        <v>0.4156</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-05-27 06:54:00.067862+00:00</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D701" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E701" t="n">
+        <v>75.04185735228845</v>
+      </c>
+      <c r="F701" t="n">
+        <v>8.07930982267461</v>
+      </c>
+      <c r="G701" t="n">
+        <v>1</v>
+      </c>
+      <c r="H701" t="n">
+        <v>0.5733618460949218</v>
+      </c>
+      <c r="I701" t="n">
+        <v>0.5381634913512248</v>
+      </c>
+      <c r="J701" t="n">
+        <v>1</v>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L701" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M701" t="n">
+        <v>27.51604332463016</v>
+      </c>
+      <c r="N701" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O701" t="n">
+        <v>44.99999999998181</v>
+      </c>
+      <c r="P701" t="inlineStr">
+        <is>
+          <t>BB%B=0.07 (extreme=0.78); RSI=36.6 (extreme=0.08); Wick ratio=4.18; ADX H1=27.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q701" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด XAUUSD (BUY) เปิดอยู่แล้ว (Ticket 557127016)</t>
+        </is>
+      </c>
+      <c r="R701" t="inlineStr">
+        <is>
+          <t>[0.5008, 0.0, 1.0, 2.0, 0.7782, -1.0, 1.2377, -0.2678, -0.2353, 0.5118, 1.0, 0.2528, -0.5643, 0.0665, 0.0376, -0.7377, 0.1467, -0.3249, 0.0, -0.3529, 0.5111, 0.3333, -0.4, 0.2, 0.0006, 0.0, 0.4944, 1.0, 0.4262, 0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="S701" t="n">
+        <v>1</v>
+      </c>
+      <c r="T701" t="n">
+        <v>0.4262</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ftmo_trading_bot/logs/ftmo_trades.xlsx
+++ b/ftmo_trading_bot/logs/ftmo_trades.xlsx
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -6220,7 +6220,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>$-41.62</t>
+          <t>$-42.34</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>$20.84</t>
+          <t>$19.40</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="13">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>$-2.08</t>
+          <t>$-2.02</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="16">
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>-2.91</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="18">
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>-3</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="19">
@@ -6434,7 +6434,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>$1,041.62</t>
+          <t>$1,042.34</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T701"/>
+  <dimension ref="A1:T703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -61531,6 +61531,156 @@
         <v>0.4262</v>
       </c>
     </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-05-27 08:01:23.182505+00:00</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D702" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E702" t="n">
+        <v>79.9636010618018</v>
+      </c>
+      <c r="F702" t="n">
+        <v>0.0004543642909535594</v>
+      </c>
+      <c r="G702" t="n">
+        <v>1</v>
+      </c>
+      <c r="H702" t="n">
+        <v>0.4333650370933993</v>
+      </c>
+      <c r="I702" t="n">
+        <v>0.4636941687360415</v>
+      </c>
+      <c r="J702" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L702" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M702" t="n">
+        <v>28.68248152368505</v>
+      </c>
+      <c r="N702" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O702" t="n">
+        <v>0</v>
+      </c>
+      <c r="P702" t="inlineStr">
+        <is>
+          <t>BB%B=0.01 (extreme=0.96); RSI=37.8 (extreme=0.05); Wick ratio=4.50; ADX H1=29.2 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R702" t="inlineStr">
+        <is>
+          <t>[0.5993, 0.0, 1.0, -1.0456, 0.9627, -1.0, 2.0, -0.2433, -0.2382, 0.1099, 1.0, 0.1806, -0.7267, 0.0112, 0.0539, -2.0468, -0.1515, -0.3534, -0.0015, -0.3534, 0.5111, 0.0, -0.4, 0.4, 0.0, 0.0, 0.6388, 1.0, 3.0, 0.0, 0.0, 0.0021]</t>
+        </is>
+      </c>
+      <c r="S702" t="n">
+        <v>1</v>
+      </c>
+      <c r="T702" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-05-27 08:03:24.657001+00:00</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D703" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E703" t="n">
+        <v>75.24997741604449</v>
+      </c>
+      <c r="F703" t="n">
+        <v>0.0004829357299720773</v>
+      </c>
+      <c r="G703" t="n">
+        <v>1</v>
+      </c>
+      <c r="H703" t="n">
+        <v>0.4605809128630706</v>
+      </c>
+      <c r="I703" t="n">
+        <v>0.4665839317561276</v>
+      </c>
+      <c r="J703" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L703" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M703" t="n">
+        <v>28.68248152368492</v>
+      </c>
+      <c r="N703" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O703" t="n">
+        <v>0</v>
+      </c>
+      <c r="P703" t="inlineStr">
+        <is>
+          <t>BB%B=0.03 (extreme=0.89); RSI=38.8 (extreme=0.03); Wick ratio=2.00; ADX H1=29.2 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R703" t="inlineStr">
+        <is>
+          <t>[0.505, 0.0, 1.0, -1.0171, 0.8882, -1.0, 2.0, -0.2242, -0.2175, 0.1096, 1.0, 0.1806, -0.6646, 0.0335, 0.1187, -1.8222, -0.1333, -0.3534, -0.0015, -0.3534, 0.5111, 0.0, -0.4, 0.4, 0.0, 0.0, 0.6388, 1.0, 3.0, 0.0, 0.0, 0.0063]</t>
+        </is>
+      </c>
+      <c r="S703" t="n">
+        <v>1</v>
+      </c>
+      <c r="T703" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ftmo_trading_bot/logs/ftmo_trades.xlsx
+++ b/ftmo_trading_bot/logs/ftmo_trades.xlsx
@@ -7157,7 +7157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T842"/>
+  <dimension ref="A1:T846"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -73147,6 +73147,326 @@
         <v>0</v>
       </c>
     </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:02:32.502667+00:00</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D843" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E843" t="n">
+        <v>75.58604900672078</v>
+      </c>
+      <c r="F843" t="n">
+        <v>0.09585700426369975</v>
+      </c>
+      <c r="G843" t="n">
+        <v>1</v>
+      </c>
+      <c r="H843" t="n">
+        <v>0.5897765097479788</v>
+      </c>
+      <c r="I843" t="n">
+        <v>0.5439867701775886</v>
+      </c>
+      <c r="J843" t="n">
+        <v>1</v>
+      </c>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L843" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M843" t="n">
+        <v>34.25119827108041</v>
+      </c>
+      <c r="N843" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O843" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P843" t="inlineStr">
+        <is>
+          <t>BB%B=0.06 (extreme=0.81); RSI=37.2 (extreme=0.07); Wick ratio=5.40; ADX H1=26.9 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q843" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bearish (O=213.53700 &gt; C=213.51000) — BUY needs bullis</t>
+        </is>
+      </c>
+      <c r="R843" t="inlineStr">
+        <is>
+          <t>[0.5117, 0.0, 1.0, -0.5414, 0.806, -1.0, 2.0, -0.2563, -0.1182, 0.1703, 1.0, 0.2499, -0.8605, 0.0582, 0.0609, -1.6587, 0.1086, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0002, 0.0, 0.5002, 0.0, 0.0, 0.0, 0.0, 0.2542, -0.3711, -0.3259, 0.4696]</t>
+        </is>
+      </c>
+      <c r="S843" t="n">
+        <v>0</v>
+      </c>
+      <c r="T843" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:10:36.060869+00:00</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D844" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E844" t="n">
+        <v>76.18000518019372</v>
+      </c>
+      <c r="F844" t="n">
+        <v>0.1016427206649495</v>
+      </c>
+      <c r="G844" t="n">
+        <v>1</v>
+      </c>
+      <c r="H844" t="n">
+        <v>0.4705304518664047</v>
+      </c>
+      <c r="I844" t="n">
+        <v>0.4733133452489413</v>
+      </c>
+      <c r="J844" t="n">
+        <v>1</v>
+      </c>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L844" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M844" t="n">
+        <v>33.84721866263406</v>
+      </c>
+      <c r="N844" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O844" t="n">
+        <v>2.199999999999136</v>
+      </c>
+      <c r="P844" t="inlineStr">
+        <is>
+          <t>BB%B=-0.03 (extreme=1.10); RSI=34.9 (extreme=0.13); Wick ratio=1.13; ADX H1=27.2 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q844" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC filter: dist -0.45 &gt; -0.6 — price not overextended down</t>
+        </is>
+      </c>
+      <c r="R844" t="inlineStr">
+        <is>
+          <t>[0.5236, 0.0, 1.0, -0.4836, 1.0, -1.0, 1.9677, -0.3022, -0.1385, 0.172, 1.0, 0.2553, -0.7637, -0.0304, 0.1235, -1.9874, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0002, 0.0, 0.4895, 0.0, 0.0, 0.0, 0.0, 0.2708, -0.4525, -0.333, 0.4383]</t>
+        </is>
+      </c>
+      <c r="S844" t="n">
+        <v>0</v>
+      </c>
+      <c r="T844" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:11:37.232460+00:00</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D845" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E845" t="n">
+        <v>75.6298497609011</v>
+      </c>
+      <c r="F845" t="n">
+        <v>0.1016427206649495</v>
+      </c>
+      <c r="G845" t="n">
+        <v>1</v>
+      </c>
+      <c r="H845" t="n">
+        <v>0.4705304518664047</v>
+      </c>
+      <c r="I845" t="n">
+        <v>0.4733133452489413</v>
+      </c>
+      <c r="J845" t="n">
+        <v>1</v>
+      </c>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L845" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M845" t="n">
+        <v>33.84721866263406</v>
+      </c>
+      <c r="N845" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O845" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P845" t="inlineStr">
+        <is>
+          <t>BB%B=-0.04 (extreme=1.12); RSI=34.7 (extreme=0.13); Wick ratio=1.00; ADX H1=27.2 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q845" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC filter: dist -0.46 &gt; -0.6 — price not overextended down</t>
+        </is>
+      </c>
+      <c r="R845" t="inlineStr">
+        <is>
+          <t>[0.5126, 0.0, 1.0, -0.4836, 1.0, -1.0, 1.9677, -0.3052, -0.1404, 0.1721, 1.0, 0.2553, -0.7768, -0.0361, 0.1235, -2.0169, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0002, 0.0, 0.4895, 0.0, 0.0, 0.0, 0.0, 0.2729, -0.4597, -0.3348, 0.4383]</t>
+        </is>
+      </c>
+      <c r="S845" t="n">
+        <v>0</v>
+      </c>
+      <c r="T845" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:12:38.143908+00:00</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D846" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E846" t="n">
+        <v>75.00137649031903</v>
+      </c>
+      <c r="F846" t="n">
+        <v>0.1016427206649495</v>
+      </c>
+      <c r="G846" t="n">
+        <v>1</v>
+      </c>
+      <c r="H846" t="n">
+        <v>0.4705304518664047</v>
+      </c>
+      <c r="I846" t="n">
+        <v>0.4733133452489413</v>
+      </c>
+      <c r="J846" t="n">
+        <v>1</v>
+      </c>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L846" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M846" t="n">
+        <v>33.84721866263406</v>
+      </c>
+      <c r="N846" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O846" t="n">
+        <v>2.199999999999136</v>
+      </c>
+      <c r="P846" t="inlineStr">
+        <is>
+          <t>BB%B=-0.04 (extreme=1.15); RSI=34.5 (extreme=0.14); Wick ratio=0.85; ADX H1=27.2 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q846" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bearish (O=213.49300 &gt; C=213.48600) — BUY needs bullis</t>
+        </is>
+      </c>
+      <c r="R846" t="inlineStr">
+        <is>
+          <t>[0.5, 0.0, 1.0, -0.4836, 1.0, -1.0, 1.9677, -0.3091, -0.1429, 0.1722, 1.0, 0.2553, -0.7943, -0.0437, 0.1235, -2.0562, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0002, 0.0, 0.4895, 0.0, 0.0, 0.0, 0.0, 0.275, -0.4692, -0.3372, 0.4383]</t>
+        </is>
+      </c>
+      <c r="S846" t="n">
+        <v>0</v>
+      </c>
+      <c r="T846" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ftmo_trading_bot/logs/ftmo_trades.xlsx
+++ b/ftmo_trading_bot/logs/ftmo_trades.xlsx
@@ -5400,7 +5400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6744,6 +6744,80 @@
         <v>9646.709999999999</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>9646.709999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>100</v>
+      </c>
+      <c r="J38" t="n">
+        <v>100</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7157,7 +7231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T846"/>
+  <dimension ref="A1:T954"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -73467,6 +73541,8631 @@
         <v>0</v>
       </c>
     </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:19:41.909378+00:00</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D847" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E847" t="n">
+        <v>78.93214345230309</v>
+      </c>
+      <c r="F847" t="n">
+        <v>0.1006682406958079</v>
+      </c>
+      <c r="G847" t="n">
+        <v>1</v>
+      </c>
+      <c r="H847" t="n">
+        <v>0.4872522487015775</v>
+      </c>
+      <c r="I847" t="n">
+        <v>0.4951323799035704</v>
+      </c>
+      <c r="J847" t="n">
+        <v>1</v>
+      </c>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L847" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M847" t="n">
+        <v>33.84721866263406</v>
+      </c>
+      <c r="N847" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O847" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P847" t="inlineStr">
+        <is>
+          <t>BB%B=-0.01 (extreme=1.03); RSI=34.1 (extreme=0.15); Wick ratio=1.60; ADX H1=27.2 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q847" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bearish (O=213.50000 &gt; C=213.48800) — BUY needs bullis</t>
+        </is>
+      </c>
+      <c r="R847" t="inlineStr">
+        <is>
+          <t>[0.5786, 0.0, 1.0, -0.4933, 1.0, -1.0, 1.9867, -0.3173, -0.182, 0.1769, 1.0, 0.2686, -0.8293, -0.0082, 0.1098, -2.4536, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0002, 0.0, 0.4628, 0.0, 0.0, 0.0, 0.0, 0.2896, -0.4493, -0.4598, 0.4451]</t>
+        </is>
+      </c>
+      <c r="S847" t="n">
+        <v>0</v>
+      </c>
+      <c r="T847" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:21:43.324965+00:00</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D848" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E848" t="n">
+        <v>82.14594886873448</v>
+      </c>
+      <c r="F848" t="n">
+        <v>0.1018110982565481</v>
+      </c>
+      <c r="G848" t="n">
+        <v>1</v>
+      </c>
+      <c r="H848" t="n">
+        <v>0.4872522487015775</v>
+      </c>
+      <c r="I848" t="n">
+        <v>0.4885487212779195</v>
+      </c>
+      <c r="J848" t="n">
+        <v>1</v>
+      </c>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L848" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M848" t="n">
+        <v>33.84721866263406</v>
+      </c>
+      <c r="N848" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O848" t="n">
+        <v>2.199999999999136</v>
+      </c>
+      <c r="P848" t="inlineStr">
+        <is>
+          <t>BB%B=-0.02 (extreme=1.05); RSI=33.9 (extreme=0.15); Wick ratio=2.22; ADX H1=27.2 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q848" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bearish (O=213.47700 &gt; C=213.46700) — BUY needs bullis</t>
+        </is>
+      </c>
+      <c r="R848" t="inlineStr">
+        <is>
+          <t>[0.6429, 0.0, 1.0, -0.4819, 1.0, -1.0, 1.9644, -0.3214, -0.1824, 0.1771, 1.0, 0.2686, -0.8468, -0.0153, 0.1221, -2.4654, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0002, 0.0, 0.4628, 0.0, 0.0, 0.0, 0.0, 0.2937, -0.4538, -0.4571, 0.439]</t>
+        </is>
+      </c>
+      <c r="S848" t="n">
+        <v>0</v>
+      </c>
+      <c r="T848" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:22:44.496663+00:00</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D849" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E849" t="n">
+        <v>79.26754106181279</v>
+      </c>
+      <c r="F849" t="n">
+        <v>0.1018110982565481</v>
+      </c>
+      <c r="G849" t="n">
+        <v>1</v>
+      </c>
+      <c r="H849" t="n">
+        <v>0.4872522487015775</v>
+      </c>
+      <c r="I849" t="n">
+        <v>0.483795897026376</v>
+      </c>
+      <c r="J849" t="n">
+        <v>1</v>
+      </c>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L849" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M849" t="n">
+        <v>33.84721866263406</v>
+      </c>
+      <c r="N849" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O849" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P849" t="inlineStr">
+        <is>
+          <t>BB%B=-0.02 (extreme=1.06); RSI=33.8 (extreme=0.15); Wick ratio=1.64; ADX H1=27.2 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q849" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC filter: dist -0.46 &gt; -0.6 — price not overextended down</t>
+        </is>
+      </c>
+      <c r="R849" t="inlineStr">
+        <is>
+          <t>[0.5854, 0.0, 1.0, -0.4819, 1.0, -1.0, 1.9644, -0.3234, -0.1837, 0.1771, 1.0, 0.2686, -0.8556, -0.0188, 0.1221, -2.485, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0002, 0.0, 0.4628, 0.0, 0.0, 0.0, 0.0, 0.2958, -0.4586, -0.4582, 0.439]</t>
+        </is>
+      </c>
+      <c r="S849" t="n">
+        <v>0</v>
+      </c>
+      <c r="T849" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:23:45.488829+00:00</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D850" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E850" t="n">
+        <v>75.27411016291471</v>
+      </c>
+      <c r="F850" t="n">
+        <v>0.1018110982565481</v>
+      </c>
+      <c r="G850" t="n">
+        <v>1</v>
+      </c>
+      <c r="H850" t="n">
+        <v>0.4872522487015775</v>
+      </c>
+      <c r="I850" t="n">
+        <v>0.4822872701578125</v>
+      </c>
+      <c r="J850" t="n">
+        <v>1</v>
+      </c>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L850" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M850" t="n">
+        <v>33.84721866263406</v>
+      </c>
+      <c r="N850" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O850" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P850" t="inlineStr">
+        <is>
+          <t>BB%B=-0.03 (extreme=1.09); RSI=33.6 (extreme=0.16); Wick ratio=0.81; ADX H1=27.2 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q850" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC filter: dist -0.47 &gt; -0.6 — price not overextended down</t>
+        </is>
+      </c>
+      <c r="R850" t="inlineStr">
+        <is>
+          <t>[0.5055, 0.0, 1.0, -0.4819, 1.0, -1.0, 1.9644, -0.3285, -0.1868, 0.1773, 1.0, 0.2686, -0.8775, -0.0275, 0.1221, -2.5341, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0002, 0.0, 0.4628, 0.0, 0.0, 0.0, 0.0, 0.2979, -0.4705, -0.4612, 0.439]</t>
+        </is>
+      </c>
+      <c r="S850" t="n">
+        <v>0</v>
+      </c>
+      <c r="T850" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-05-28 10:24:46.482819+00:00</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D851" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E851" t="n">
+        <v>75.24466010324323</v>
+      </c>
+      <c r="F851" t="n">
+        <v>0.1018110982565481</v>
+      </c>
+      <c r="G851" t="n">
+        <v>1</v>
+      </c>
+      <c r="H851" t="n">
+        <v>0.4872522487015775</v>
+      </c>
+      <c r="I851" t="n">
+        <v>0.483795897026376</v>
+      </c>
+      <c r="J851" t="n">
+        <v>1</v>
+      </c>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L851" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M851" t="n">
+        <v>33.84721866263406</v>
+      </c>
+      <c r="N851" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O851" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P851" t="inlineStr">
+        <is>
+          <t>BB%B=0.03 (extreme=0.89); RSI=36.1 (extreme=0.10); Wick ratio=1.71; ADX H1=27.2 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q851" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC filter: dist -0.39 &gt; -0.6 — price not overextended down</t>
+        </is>
+      </c>
+      <c r="R851" t="inlineStr">
+        <is>
+          <t>[0.5049, 0.0, 1.0, -0.4819, 0.8914, -1.0, 1.9644, -0.2789, -0.1661, 0.1761, 1.0, 0.2686, -0.733, 0.0326, 0.1221, -2.21, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0002, 0.0, 0.4628, 0.0, 0.0, 0.0, 0.0, 0.3, -0.3919, -0.4416, 0.439]</t>
+        </is>
+      </c>
+      <c r="S851" t="n">
+        <v>0</v>
+      </c>
+      <c r="T851" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-05-28 11:09:02.464598+00:00</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D852" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E852" t="n">
+        <v>75.70320899227643</v>
+      </c>
+      <c r="F852" t="n">
+        <v>0.06865836483335529</v>
+      </c>
+      <c r="G852" t="n">
+        <v>1</v>
+      </c>
+      <c r="H852" t="n">
+        <v>0.5145018915510718</v>
+      </c>
+      <c r="I852" t="n">
+        <v>0.5198522335190428</v>
+      </c>
+      <c r="J852" t="n">
+        <v>1</v>
+      </c>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L852" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M852" t="n">
+        <v>34.90398339809495</v>
+      </c>
+      <c r="N852" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O852" t="n">
+        <v>1.200000000000045</v>
+      </c>
+      <c r="P852" t="inlineStr">
+        <is>
+          <t>BB%B=0.04 (extreme=0.87); RSI=38.5 (extreme=0.04); Wick ratio=2.17; ADX H1=24.4 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q852" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bearish (O=185.05100 &gt; C=185.03400) — BUY needs bullis</t>
+        </is>
+      </c>
+      <c r="R852" t="inlineStr">
+        <is>
+          <t>[0.5141, 0.0, 1.0, -0.8134, 0.8699, -1.0, 2.0, -0.2309, -0.1597, 0.1029, 1.0, 0.2546, -0.8273, 0.039, 0.0529, -1.1943, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0002, 0.0, 0.4909, 0.0, 0.0, 0.0, 0.0, 0.3938, -0.3372, -0.357, 0.4735]</t>
+        </is>
+      </c>
+      <c r="S852" t="n">
+        <v>0</v>
+      </c>
+      <c r="T852" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:30:32.940392+00:00</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D853" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E853" t="n">
+        <v>82.56197879910331</v>
+      </c>
+      <c r="F853" t="n">
+        <v>0.0004541775122229826</v>
+      </c>
+      <c r="G853" t="n">
+        <v>1</v>
+      </c>
+      <c r="H853" t="n">
+        <v>0.5062639137456895</v>
+      </c>
+      <c r="I853" t="n">
+        <v>0.515094368103133</v>
+      </c>
+      <c r="J853" t="n">
+        <v>0.8693667054176331</v>
+      </c>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L853" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M853" t="n">
+        <v>34.86141840616028</v>
+      </c>
+      <c r="N853" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O853" t="n">
+        <v>1.20000000000009</v>
+      </c>
+      <c r="P853" t="inlineStr">
+        <is>
+          <t>BB%B=1.02 (extreme=1.08); RSI=65.1 (extreme=0.13); Wick ratio=4.38; ADX H1=26.4 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q853" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (1 นาทีหลัง) — block signal NZD</t>
+        </is>
+      </c>
+      <c r="R853" t="inlineStr">
+        <is>
+          <t>[0.6512, 0.0, -1.0, -1.0458, 1.0, -1.0, 2.0, 0.3025, 0.1774, 0.1383, 1.0, 0.1429, 0.5833, 1.0232, -0.1129, 1.9156, 0.0125, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.7142, 0.0, 0.0, 0.0, 0.0, 0.5625, 0.4333, 0.3524, 0.5565]</t>
+        </is>
+      </c>
+      <c r="S853" t="n">
+        <v>0</v>
+      </c>
+      <c r="T853" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:30:33.526983+00:00</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D854" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E854" t="n">
+        <v>80.63182532726468</v>
+      </c>
+      <c r="F854" t="n">
+        <v>0.08473059732149126</v>
+      </c>
+      <c r="G854" t="n">
+        <v>1</v>
+      </c>
+      <c r="H854" t="n">
+        <v>0.5282837066108902</v>
+      </c>
+      <c r="I854" t="n">
+        <v>0.5202027563436283</v>
+      </c>
+      <c r="J854" t="n">
+        <v>0.25723597407341</v>
+      </c>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L854" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M854" t="n">
+        <v>34.86141840616028</v>
+      </c>
+      <c r="N854" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O854" t="n">
+        <v>4.300000000000637</v>
+      </c>
+      <c r="P854" t="inlineStr">
+        <is>
+          <t>BB%B=1.00 (extreme=1.01); RSI=63.4 (extreme=0.09); Wick ratio=2.18; ADX H1=22.7 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q854" t="inlineStr">
+        <is>
+          <t>spread_high:43&gt;25</t>
+        </is>
+      </c>
+      <c r="R854" t="inlineStr">
+        <is>
+          <t>[0.6126, 0.0, -1.0, -0.6527, 1.0, -1.0, 1.7703, 0.2689, 0.2739, 0.074, 1.0, 0.2649, 0.5989, 1.0027, 0.2679, 2.0772, 0.0125, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0005, 0.0, 0.4702, 0.0, 0.0, 0.0, 0.0, 0.5625, 0.421, 0.3492, 0.366]</t>
+        </is>
+      </c>
+      <c r="S854" t="n">
+        <v>0</v>
+      </c>
+      <c r="T854" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:30:34.167065+00:00</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D855" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E855" t="n">
+        <v>80.58951371979428</v>
+      </c>
+      <c r="F855" t="n">
+        <v>0.0006050575199462577</v>
+      </c>
+      <c r="G855" t="n">
+        <v>1</v>
+      </c>
+      <c r="H855" t="n">
+        <v>0.5376988297946883</v>
+      </c>
+      <c r="I855" t="n">
+        <v>0.529596246630294</v>
+      </c>
+      <c r="J855" t="n">
+        <v>0.9522737264633179</v>
+      </c>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L855" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M855" t="n">
+        <v>34.86141840616028</v>
+      </c>
+      <c r="N855" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O855" t="n">
+        <v>0.8000000000008001</v>
+      </c>
+      <c r="P855" t="inlineStr">
+        <is>
+          <t>BB%B=1.08 (extreme=1.26); RSI=67.9 (extreme=0.20); Wick ratio=1.73; ADX H1=19.3 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q855" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (1 นาทีหลัง) — block signal EUR</t>
+        </is>
+      </c>
+      <c r="R855" t="inlineStr">
+        <is>
+          <t>[0.6118, 0.0, -1.0, -0.8949, 1.0, -1.0, 1.6527, 0.3586, 0.2483, 0.0742, 1.0, 0.2421, 0.5505, 1.0783, 0.2685, 2.727, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5157, 0.0, 0.0, 0.0, 0.0, 0.5625, 0.5802, 0.4293, 0.3657]</t>
+        </is>
+      </c>
+      <c r="S855" t="n">
+        <v>0</v>
+      </c>
+      <c r="T855" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:31:35.117360+00:00</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D856" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E856" t="n">
+        <v>77.89250324427641</v>
+      </c>
+      <c r="F856" t="n">
+        <v>0.0006050575199462577</v>
+      </c>
+      <c r="G856" t="n">
+        <v>1</v>
+      </c>
+      <c r="H856" t="n">
+        <v>0.5897765097479788</v>
+      </c>
+      <c r="I856" t="n">
+        <v>0.5431821982283581</v>
+      </c>
+      <c r="J856" t="n">
+        <v>1</v>
+      </c>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L856" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M856" t="n">
+        <v>34.8352182707566</v>
+      </c>
+      <c r="N856" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O856" t="n">
+        <v>0.8000000000008001</v>
+      </c>
+      <c r="P856" t="inlineStr">
+        <is>
+          <t>BB%B=1.11 (extreme=1.37); RSI=68.8 (extreme=0.22); Wick ratio=1.10; ADX H1=19.3 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q856" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (2 นาทีหลัง) — block signal EUR</t>
+        </is>
+      </c>
+      <c r="R856" t="inlineStr">
+        <is>
+          <t>[0.5579, 0.0, -1.0, -0.8949, 1.0, -1.0, 1.6527, 0.3765, 0.261, 0.0734, 1.0, 0.2421, 0.6287, 1.112, 0.2685, 2.9253, 0.1909, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5157, 0.0, 0.0, 0.0, 0.0, 0.5646, 0.6283, 0.4413, 0.3657]</t>
+        </is>
+      </c>
+      <c r="S856" t="n">
+        <v>0</v>
+      </c>
+      <c r="T856" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:31:36.122182+00:00</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D857" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E857" t="n">
+        <v>75.96388611693655</v>
+      </c>
+      <c r="F857" t="n">
+        <v>0.08473059732149126</v>
+      </c>
+      <c r="G857" t="n">
+        <v>1</v>
+      </c>
+      <c r="H857" t="n">
+        <v>0.5543191559512035</v>
+      </c>
+      <c r="I857" t="n">
+        <v>0.5345142352004351</v>
+      </c>
+      <c r="J857" t="n">
+        <v>1</v>
+      </c>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L857" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M857" t="n">
+        <v>34.8352182707566</v>
+      </c>
+      <c r="N857" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O857" t="n">
+        <v>4.200000000000159</v>
+      </c>
+      <c r="P857" t="inlineStr">
+        <is>
+          <t>BB%B=1.04 (extreme=1.14); RSI=64.5 (extreme=0.11); Wick ratio=1.14; ADX H1=22.7 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q857" t="inlineStr">
+        <is>
+          <t>spread_high:42&gt;25</t>
+        </is>
+      </c>
+      <c r="R857" t="inlineStr">
+        <is>
+          <t>[0.5193, 0.0, -1.0, -0.6527, 1.0, -1.0, 1.7703, 0.29, 0.2859, 0.0733, 1.0, 0.2649, 0.688, 1.0425, 0.2679, 2.266, 0.1255, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0005, 0.0, 0.4702, 0.0, 0.0, 0.0, 0.0, 0.5646, 0.4668, 0.3606, 0.366]</t>
+        </is>
+      </c>
+      <c r="S857" t="n">
+        <v>0</v>
+      </c>
+      <c r="T857" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:32:37.134654+00:00</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D858" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E858" t="n">
+        <v>80.29544277806093</v>
+      </c>
+      <c r="F858" t="n">
+        <v>0.0006050575199462577</v>
+      </c>
+      <c r="G858" t="n">
+        <v>1</v>
+      </c>
+      <c r="H858" t="n">
+        <v>0.5376988297946883</v>
+      </c>
+      <c r="I858" t="n">
+        <v>0.529596246630294</v>
+      </c>
+      <c r="J858" t="n">
+        <v>0.9283071756362915</v>
+      </c>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L858" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M858" t="n">
+        <v>34.78841689395949</v>
+      </c>
+      <c r="N858" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O858" t="n">
+        <v>0</v>
+      </c>
+      <c r="P858" t="inlineStr">
+        <is>
+          <t>BB%B=1.08 (extreme=1.27); RSI=68.0 (extreme=0.20); Wick ratio=1.66; ADX H1=19.3 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q858" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (3 นาทีหลัง) — block signal EUR</t>
+        </is>
+      </c>
+      <c r="R858" t="inlineStr">
+        <is>
+          <t>[0.6059, 0.0, -1.0, -0.8949, 1.0, -1.0, 1.6527, 0.3601, 0.2494, 0.0741, 1.0, 0.2421, 0.557, 1.0812, 0.2685, 2.7435, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5157, 0.0, 0.0, 0.0, 0.0, 0.5667, 0.5842, 0.4303, 0.3657]</t>
+        </is>
+      </c>
+      <c r="S858" t="n">
+        <v>0</v>
+      </c>
+      <c r="T858" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:32:37.779511+00:00</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D859" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E859" t="n">
+        <v>78.38547252502711</v>
+      </c>
+      <c r="F859" t="n">
+        <v>0.08473059732149126</v>
+      </c>
+      <c r="G859" t="n">
+        <v>1</v>
+      </c>
+      <c r="H859" t="n">
+        <v>0.5543191559512035</v>
+      </c>
+      <c r="I859" t="n">
+        <v>0.5345142352004351</v>
+      </c>
+      <c r="J859" t="n">
+        <v>1</v>
+      </c>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L859" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M859" t="n">
+        <v>34.78841689395949</v>
+      </c>
+      <c r="N859" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O859" t="n">
+        <v>1.099999999999568</v>
+      </c>
+      <c r="P859" t="inlineStr">
+        <is>
+          <t>BB%B=1.02 (extreme=1.06); RSI=63.8 (extreme=0.10); Wick ratio=1.69; ADX H1=22.7 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q859" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=185.32300 &lt; C=185.33100) — SELL needs beari</t>
+        </is>
+      </c>
+      <c r="R859" t="inlineStr">
+        <is>
+          <t>[0.5677, 0.0, -1.0, -0.6527, 1.0, -1.0, 1.7703, 0.277, 0.2784, 0.0738, 1.0, 0.2649, 0.6323, 1.018, 0.2679, 2.148, 0.1255, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.4702, 0.0, 0.0, 0.0, 0.0, 0.5667, 0.4382, 0.3535, 0.366]</t>
+        </is>
+      </c>
+      <c r="S859" t="n">
+        <v>0</v>
+      </c>
+      <c r="T859" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:32:38.437041+00:00</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D860" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E860" t="n">
+        <v>78.09921983498606</v>
+      </c>
+      <c r="F860" t="n">
+        <v>0.0004541775122229826</v>
+      </c>
+      <c r="G860" t="n">
+        <v>1</v>
+      </c>
+      <c r="H860" t="n">
+        <v>0.5470931708555471</v>
+      </c>
+      <c r="I860" t="n">
+        <v>0.5319208482203956</v>
+      </c>
+      <c r="J860" t="n">
+        <v>1</v>
+      </c>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L860" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M860" t="n">
+        <v>34.78841689395949</v>
+      </c>
+      <c r="N860" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O860" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P860" t="inlineStr">
+        <is>
+          <t>BB%B=1.07 (extreme=1.23); RSI=66.3 (extreme=0.16); Wick ratio=1.39; ADX H1=26.4 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q860" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (3 นาทีหลัง) — block signal NZD</t>
+        </is>
+      </c>
+      <c r="R860" t="inlineStr">
+        <is>
+          <t>[0.562, 0.0, -1.0, -1.0458, 1.0, -1.0, 2.0, 0.3262, 0.1914, 0.1397, 1.0, 0.1429, 0.7024, 1.0704, -0.1129, 2.1357, 0.0942, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.7142, 0.0, 0.0, 0.0, 0.0, 0.5667, 0.4867, 0.3657, 0.5565]</t>
+        </is>
+      </c>
+      <c r="S860" t="n">
+        <v>0</v>
+      </c>
+      <c r="T860" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:33:39.620535+00:00</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D861" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E861" t="n">
+        <v>77.42875926186822</v>
+      </c>
+      <c r="F861" t="n">
+        <v>0.0006050575199462577</v>
+      </c>
+      <c r="G861" t="n">
+        <v>1</v>
+      </c>
+      <c r="H861" t="n">
+        <v>0.5897765097479788</v>
+      </c>
+      <c r="I861" t="n">
+        <v>0.5431821982283581</v>
+      </c>
+      <c r="J861" t="n">
+        <v>1</v>
+      </c>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L861" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M861" t="n">
+        <v>34.78841689395949</v>
+      </c>
+      <c r="N861" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O861" t="n">
+        <v>0</v>
+      </c>
+      <c r="P861" t="inlineStr">
+        <is>
+          <t>BB%B=1.12 (extreme=1.40); RSI=69.0 (extreme=0.23); Wick ratio=0.98; ADX H1=19.3 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q861" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (4 นาทีหลัง) — block signal EUR</t>
+        </is>
+      </c>
+      <c r="R861" t="inlineStr">
+        <is>
+          <t>[0.5486, 0.0, -1.0, -0.8949, 1.0, -1.0, 1.6527, 0.3808, 0.2641, 0.0731, 1.0, 0.2421, 0.6482, 1.12, 0.2685, 2.9749, 0.1909, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5157, 0.0, 0.0, 0.0, 0.0, 0.5688, 0.6403, 0.4444, 0.3657]</t>
+        </is>
+      </c>
+      <c r="S861" t="n">
+        <v>0</v>
+      </c>
+      <c r="T861" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:33:40.588324+00:00</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D862" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E862" t="n">
+        <v>75.78413851152709</v>
+      </c>
+      <c r="F862" t="n">
+        <v>0.0004541775122229826</v>
+      </c>
+      <c r="G862" t="n">
+        <v>1</v>
+      </c>
+      <c r="H862" t="n">
+        <v>0.5470931708555471</v>
+      </c>
+      <c r="I862" t="n">
+        <v>0.5319208482203956</v>
+      </c>
+      <c r="J862" t="n">
+        <v>1</v>
+      </c>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L862" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M862" t="n">
+        <v>34.78841689395949</v>
+      </c>
+      <c r="N862" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O862" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P862" t="inlineStr">
+        <is>
+          <t>BB%B=1.09 (extreme=1.31); RSI=66.9 (extreme=0.17); Wick ratio=0.87; ADX H1=26.4 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q862" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (4 นาทีหลัง) — block signal NZD</t>
+        </is>
+      </c>
+      <c r="R862" t="inlineStr">
+        <is>
+          <t>[0.5157, 0.0, -1.0, -1.0458, 1.0, -1.0, 2.0, 0.3375, 0.1985, 0.1403, 1.0, 0.1429, 0.7619, 1.0923, -0.1129, 2.2458, 0.0942, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.7142, 0.0, 0.0, 0.0, 0.0, 0.5688, 0.5134, 0.3724, 0.5565]</t>
+        </is>
+      </c>
+      <c r="S862" t="n">
+        <v>0</v>
+      </c>
+      <c r="T862" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:34:41.567774+00:00</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D863" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E863" t="n">
+        <v>75.74702983711272</v>
+      </c>
+      <c r="F863" t="n">
+        <v>0.0006050575199462577</v>
+      </c>
+      <c r="G863" t="n">
+        <v>1</v>
+      </c>
+      <c r="H863" t="n">
+        <v>0.5954485850852329</v>
+      </c>
+      <c r="I863" t="n">
+        <v>0.5472752675538595</v>
+      </c>
+      <c r="J863" t="n">
+        <v>1</v>
+      </c>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L863" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M863" t="n">
+        <v>34.78841689395949</v>
+      </c>
+      <c r="N863" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O863" t="n">
+        <v>0</v>
+      </c>
+      <c r="P863" t="inlineStr">
+        <is>
+          <t>BB%B=1.16 (extreme=1.53); RSI=70.1 (extreme=0.25); Wick ratio=0.54; ADX H1=19.3 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q863" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (5 นาทีหลัง) — block signal EUR</t>
+        </is>
+      </c>
+      <c r="R863" t="inlineStr">
+        <is>
+          <t>[0.5149, 0.0, -1.0, -0.8949, 1.0, -1.0, 1.6527, 0.4028, 0.281, 0.072, 1.0, 0.2421, 0.7524, 1.1601, 0.2685, 3.0, 0.1909, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5157, 0.0, 0.0, 0.0, 0.0, 0.5708, 0.7044, 0.4604, 0.3657]</t>
+        </is>
+      </c>
+      <c r="S863" t="n">
+        <v>0</v>
+      </c>
+      <c r="T863" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:35:42.554877+00:00</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D864" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E864" t="n">
+        <v>76.66554043534069</v>
+      </c>
+      <c r="F864" t="n">
+        <v>0.0006050575199462577</v>
+      </c>
+      <c r="G864" t="n">
+        <v>1</v>
+      </c>
+      <c r="H864" t="n">
+        <v>0.5897765097479788</v>
+      </c>
+      <c r="I864" t="n">
+        <v>0.5431821982283581</v>
+      </c>
+      <c r="J864" t="n">
+        <v>1</v>
+      </c>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L864" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M864" t="n">
+        <v>34.78841689395949</v>
+      </c>
+      <c r="N864" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O864" t="n">
+        <v>0</v>
+      </c>
+      <c r="P864" t="inlineStr">
+        <is>
+          <t>BB%B=1.14 (extreme=1.45); RSI=69.5 (extreme=0.24); Wick ratio=0.79; ADX H1=19.3 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q864" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (6 นาทีหลัง) — block signal EUR</t>
+        </is>
+      </c>
+      <c r="R864" t="inlineStr">
+        <is>
+          <t>[0.5333, 0.0, -1.0, -0.8949, 1.0, -1.0, 1.6527, 0.3892, 0.2705, 0.0727, 1.0, 0.2421, 0.6873, 1.1356, 0.2685, 3.0, 0.1909, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5157, 0.0, 0.0, 0.0, 0.0, 0.5729, 0.6643, 0.4504, 0.3657]</t>
+        </is>
+      </c>
+      <c r="S864" t="n">
+        <v>0</v>
+      </c>
+      <c r="T864" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:45:46.685083+00:00</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D865" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E865" t="n">
+        <v>78.48129349738426</v>
+      </c>
+      <c r="F865" t="n">
+        <v>0.0004742362682711113</v>
+      </c>
+      <c r="G865" t="n">
+        <v>1</v>
+      </c>
+      <c r="H865" t="n">
+        <v>0.5376988297946883</v>
+      </c>
+      <c r="I865" t="n">
+        <v>0.5315200213527096</v>
+      </c>
+      <c r="J865" t="n">
+        <v>1</v>
+      </c>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L865" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M865" t="n">
+        <v>34.06041322431041</v>
+      </c>
+      <c r="N865" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O865" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P865" t="inlineStr">
+        <is>
+          <t>BB%B=1.13 (extreme=1.42); RSI=73.0 (extreme=0.32); Wick ratio=0.80; ADX H1=26.9 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q865" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (16 นาทีหลัง) — block signal NZ</t>
+        </is>
+      </c>
+      <c r="R865" t="inlineStr">
+        <is>
+          <t>[0.5696, 0.0, -1.0, -1.0258, 1.0, -1.0, 2.0, 0.4593, 0.3544, 0.1659, 1.0, 0.173, 0.8615, 1.1256, -0.0753, 3.0, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.654, 0.0, 0.0, 0.0, 0.0, 0.5938, 0.7607, 0.5944, 0.5377]</t>
+        </is>
+      </c>
+      <c r="S865" t="n">
+        <v>0</v>
+      </c>
+      <c r="T865" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:45:47.383091+00:00</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D866" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E866" t="n">
+        <v>75.09932460645501</v>
+      </c>
+      <c r="F866" t="n">
+        <v>0.08097432956889893</v>
+      </c>
+      <c r="G866" t="n">
+        <v>1</v>
+      </c>
+      <c r="H866" t="n">
+        <v>0.5897765097479788</v>
+      </c>
+      <c r="I866" t="n">
+        <v>0.5433933653856204</v>
+      </c>
+      <c r="J866" t="n">
+        <v>1</v>
+      </c>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L866" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M866" t="n">
+        <v>34.06041322431041</v>
+      </c>
+      <c r="N866" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O866" t="n">
+        <v>1.200000000000045</v>
+      </c>
+      <c r="P866" t="inlineStr">
+        <is>
+          <t>BB%B=1.04 (extreme=1.15); RSI=67.5 (extreme=0.19); Wick ratio=0.67; ADX H1=22.7 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q866" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC filter: dist 0.59 &lt; 0.6 — price not overextended up</t>
+        </is>
+      </c>
+      <c r="R866" t="inlineStr">
+        <is>
+          <t>[0.502, 0.0, -1.0, -0.6903, 1.0, -1.0, 1.8524, 0.3506, 0.3841, 0.0624, 1.0, 0.2786, 0.9084, 1.0437, 0.2041, 2.9392, 0.1796, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.4429, 0.0, 0.0, 0.0, 0.0, 0.5938, 0.5858, 0.5484, 0.3979]</t>
+        </is>
+      </c>
+      <c r="S866" t="n">
+        <v>0</v>
+      </c>
+      <c r="T866" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:46:48.412795+00:00</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D867" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E867" t="n">
+        <v>81.94145852805019</v>
+      </c>
+      <c r="F867" t="n">
+        <v>0.000474950554246571</v>
+      </c>
+      <c r="G867" t="n">
+        <v>1</v>
+      </c>
+      <c r="H867" t="n">
+        <v>0.5376988297946883</v>
+      </c>
+      <c r="I867" t="n">
+        <v>0.5315200213527096</v>
+      </c>
+      <c r="J867" t="n">
+        <v>1</v>
+      </c>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L867" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M867" t="n">
+        <v>33.8514422334292</v>
+      </c>
+      <c r="N867" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O867" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P867" t="inlineStr">
+        <is>
+          <t>BB%B=1.12 (extreme=1.41); RSI=72.9 (extreme=0.32); Wick ratio=1.50; ADX H1=26.9 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q867" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (17 นาทีหลัง) — block signal NZ</t>
+        </is>
+      </c>
+      <c r="R867" t="inlineStr">
+        <is>
+          <t>[0.6388, 0.0, -1.0, -1.025, 1.0, -1.0, 2.0, 0.4577, 0.3525, 0.1657, 1.0, 0.173, 0.8528, 1.1229, -0.074, 3.0, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.654, 0.0, 0.0, 0.0, 0.0, 0.5958, 0.7544, 0.5922, 0.537]</t>
+        </is>
+      </c>
+      <c r="S867" t="n">
+        <v>0</v>
+      </c>
+      <c r="T867" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:46:49.148427+00:00</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D868" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E868" t="n">
+        <v>76.70817220520615</v>
+      </c>
+      <c r="F868" t="n">
+        <v>0.08097432956889893</v>
+      </c>
+      <c r="G868" t="n">
+        <v>1</v>
+      </c>
+      <c r="H868" t="n">
+        <v>0.5897765097479788</v>
+      </c>
+      <c r="I868" t="n">
+        <v>0.5433933653856204</v>
+      </c>
+      <c r="J868" t="n">
+        <v>1</v>
+      </c>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L868" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M868" t="n">
+        <v>33.8514422334292</v>
+      </c>
+      <c r="N868" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O868" t="n">
+        <v>1.099999999999568</v>
+      </c>
+      <c r="P868" t="inlineStr">
+        <is>
+          <t>BB%B=1.04 (extreme=1.13); RSI=67.4 (extreme=0.19); Wick ratio=1.00; ADX H1=22.7 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q868" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=185.36200 &lt; C=185.37700) — SELL needs beari</t>
+        </is>
+      </c>
+      <c r="R868" t="inlineStr">
+        <is>
+          <t>[0.5342, 0.0, -1.0, -0.6903, 1.0, -1.0, 1.8524, 0.3483, 0.3825, 0.0625, 1.0, 0.2786, 0.8976, 1.0399, 0.2041, 2.9145, 0.1796, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.4429, 0.0, 0.0, 0.0, 0.0, 0.5958, 0.5798, 0.5469, 0.3979]</t>
+        </is>
+      </c>
+      <c r="S868" t="n">
+        <v>0</v>
+      </c>
+      <c r="T868" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:47:50.045694+00:00</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D869" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E869" t="n">
+        <v>85.49378775961583</v>
+      </c>
+      <c r="F869" t="n">
+        <v>0.0005781656504934121</v>
+      </c>
+      <c r="G869" t="n">
+        <v>1</v>
+      </c>
+      <c r="H869" t="n">
+        <v>0.6239275040971753</v>
+      </c>
+      <c r="I869" t="n">
+        <v>0.5521718977804378</v>
+      </c>
+      <c r="J869" t="n">
+        <v>1</v>
+      </c>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L869" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M869" t="n">
+        <v>33.8514422334292</v>
+      </c>
+      <c r="N869" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O869" t="n">
+        <v>0</v>
+      </c>
+      <c r="P869" t="inlineStr">
+        <is>
+          <t>BB%B=1.06 (extreme=1.20); RSI=71.0 (extreme=0.27); Wick ratio=3.00; ADX H1=19.3 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q869" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (18 นาทีหลัง) — block signal EU</t>
+        </is>
+      </c>
+      <c r="R869" t="inlineStr">
+        <is>
+          <t>[0.7099, 0.0, -1.0, -0.9218, 1.0, -1.0, 1.7296, 0.4198, 0.3835, 0.0575, 1.0, 0.2619, 0.8576, 1.0595, 0.2038, 3.0, 0.0942, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4763, 0.0, 0.0, 0.0, 0.0, 0.5979, 0.7376, 0.6771, 0.3981]</t>
+        </is>
+      </c>
+      <c r="S869" t="n">
+        <v>0</v>
+      </c>
+      <c r="T869" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:47:50.615159+00:00</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D870" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E870" t="n">
+        <v>83.14289545899784</v>
+      </c>
+      <c r="F870" t="n">
+        <v>0.08154575834926801</v>
+      </c>
+      <c r="G870" t="n">
+        <v>1</v>
+      </c>
+      <c r="H870" t="n">
+        <v>0.5897765097479788</v>
+      </c>
+      <c r="I870" t="n">
+        <v>0.5433933653856204</v>
+      </c>
+      <c r="J870" t="n">
+        <v>1</v>
+      </c>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L870" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M870" t="n">
+        <v>33.8514422334292</v>
+      </c>
+      <c r="N870" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O870" t="n">
+        <v>0.9999999999990905</v>
+      </c>
+      <c r="P870" t="inlineStr">
+        <is>
+          <t>BB%B=1.01 (extreme=1.04); RSI=66.3 (extreme=0.16); Wick ratio=5.00; ADX H1=22.7 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q870" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC filter: dist 0.53 &lt; 0.6 — price not overextended up</t>
+        </is>
+      </c>
+      <c r="R870" t="inlineStr">
+        <is>
+          <t>[0.6629, 0.0, -1.0, -0.6845, 1.0, -1.0, 1.8395, 0.3257, 0.3689, 0.0631, 1.0, 0.2786, 0.8221, 1.012, 0.2124, 2.7224, 0.1796, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.4429, 0.0, 0.0, 0.0, 0.0, 0.5979, 0.5342, 0.5327, 0.3938]</t>
+        </is>
+      </c>
+      <c r="S870" t="n">
+        <v>0</v>
+      </c>
+      <c r="T870" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:47:51.263259+00:00</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D871" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E871" t="n">
+        <v>77.19310731796659</v>
+      </c>
+      <c r="F871" t="n">
+        <v>0.0004799505560748132</v>
+      </c>
+      <c r="G871" t="n">
+        <v>1</v>
+      </c>
+      <c r="H871" t="n">
+        <v>0.5627603642945385</v>
+      </c>
+      <c r="I871" t="n">
+        <v>0.5371341987598852</v>
+      </c>
+      <c r="J871" t="n">
+        <v>1</v>
+      </c>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L871" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M871" t="n">
+        <v>33.8514422334292</v>
+      </c>
+      <c r="N871" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O871" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P871" t="inlineStr">
+        <is>
+          <t>BB%B=1.08 (extreme=1.26); RSI=70.1 (extreme=0.25); Wick ratio=0.83; ADX H1=26.9 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q871" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (18 นาทีหลัง) — block signal NZ</t>
+        </is>
+      </c>
+      <c r="R871" t="inlineStr">
+        <is>
+          <t>[0.5439, 0.0, -1.0, -1.02, 1.0, -1.0, 2.0, 0.4011, 0.3276, 0.1636, 1.0, 0.173, 0.7143, 1.0775, -0.0644, 2.8753, 0.0942, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.654, 0.0, 0.0, 0.0, 0.0, 0.5979, 0.6657, 0.5658, 0.5322]</t>
+        </is>
+      </c>
+      <c r="S871" t="n">
+        <v>0</v>
+      </c>
+      <c r="T871" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:48:52.296864+00:00</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D872" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E872" t="n">
+        <v>86.06805477177237</v>
+      </c>
+      <c r="F872" t="n">
+        <v>0.0004799505560748132</v>
+      </c>
+      <c r="G872" t="n">
+        <v>1</v>
+      </c>
+      <c r="H872" t="n">
+        <v>0.5627603642945385</v>
+      </c>
+      <c r="I872" t="n">
+        <v>0.5374933856507491</v>
+      </c>
+      <c r="J872" t="n">
+        <v>1</v>
+      </c>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L872" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M872" t="n">
+        <v>33.59240443773189</v>
+      </c>
+      <c r="N872" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O872" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P872" t="inlineStr">
+        <is>
+          <t>BB%B=1.12 (extreme=1.40); RSI=72.8 (extreme=0.32); Wick ratio=2.33; ADX H1=26.9 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q872" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (19 นาทีหลัง) — block signal NZ</t>
+        </is>
+      </c>
+      <c r="R872" t="inlineStr">
+        <is>
+          <t>[0.7214, 0.0, -1.0, -1.02, 1.0, -1.0, 2.0, 0.4561, 0.3475, 0.1656, 1.0, 0.173, 0.8442, 1.1202, -0.0644, 3.0, 0.0798, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.654, 0.0, 0.0, 0.0, 0.0, 0.6, 0.7415, 0.5848, 0.5322]</t>
+        </is>
+      </c>
+      <c r="S872" t="n">
+        <v>0</v>
+      </c>
+      <c r="T872" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:48:53.214597+00:00</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D873" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E873" t="n">
+        <v>78.43192797562973</v>
+      </c>
+      <c r="F873" t="n">
+        <v>0.0005781656504934121</v>
+      </c>
+      <c r="G873" t="n">
+        <v>1</v>
+      </c>
+      <c r="H873" t="n">
+        <v>0.7072434607645876</v>
+      </c>
+      <c r="I873" t="n">
+        <v>0.5710592844012818</v>
+      </c>
+      <c r="J873" t="n">
+        <v>0.4010518491268158</v>
+      </c>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L873" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M873" t="n">
+        <v>33.59240443773189</v>
+      </c>
+      <c r="N873" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O873" t="n">
+        <v>0</v>
+      </c>
+      <c r="P873" t="inlineStr">
+        <is>
+          <t>BB%B=1.09 (extreme=1.29); RSI=72.1 (extreme=0.30); Wick ratio=0.87; ADX H1=19.3 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q873" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (19 นาทีหลัง) — block signal EU</t>
+        </is>
+      </c>
+      <c r="R873" t="inlineStr">
+        <is>
+          <t>[0.5686, 0.0, -1.0, -0.9218, 1.0, -1.0, 1.7296, 0.4423, 0.3979, 0.0566, 1.0, 0.2619, 0.9417, 1.0882, 0.2038, 3.0, 0.0566, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4763, 0.0, 0.0, 0.0, 0.0, 0.6, 0.7921, 0.6907, 0.3981]</t>
+        </is>
+      </c>
+      <c r="S873" t="n">
+        <v>0</v>
+      </c>
+      <c r="T873" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:48:53.828460+00:00</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D874" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E874" t="n">
+        <v>75.09932460645501</v>
+      </c>
+      <c r="F874" t="n">
+        <v>0.08154575834926801</v>
+      </c>
+      <c r="G874" t="n">
+        <v>1</v>
+      </c>
+      <c r="H874" t="n">
+        <v>0.5897765097479788</v>
+      </c>
+      <c r="I874" t="n">
+        <v>0.5437300682110793</v>
+      </c>
+      <c r="J874" t="n">
+        <v>1</v>
+      </c>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L874" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M874" t="n">
+        <v>33.59240443773189</v>
+      </c>
+      <c r="N874" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O874" t="n">
+        <v>0.9999999999990905</v>
+      </c>
+      <c r="P874" t="inlineStr">
+        <is>
+          <t>BB%B=1.04 (extreme=1.15); RSI=67.5 (extreme=0.19); Wick ratio=0.67; ADX H1=22.7 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q874" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC filter: dist 0.58 &lt; 0.6 — price not overextended up</t>
+        </is>
+      </c>
+      <c r="R874" t="inlineStr">
+        <is>
+          <t>[0.502, 0.0, -1.0, -0.6845, 1.0, -1.0, 1.8395, 0.3506, 0.3814, 0.0624, 1.0, 0.2786, 0.9084, 1.0437, 0.2124, 2.9186, 0.1796, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.4429, 0.0, 0.0, 0.0, 0.0, 0.6, 0.5817, 0.5445, 0.3938]</t>
+        </is>
+      </c>
+      <c r="S874" t="n">
+        <v>0</v>
+      </c>
+      <c r="T874" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:49:54.801294+00:00</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D875" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E875" t="n">
+        <v>86.08807314908367</v>
+      </c>
+      <c r="F875" t="n">
+        <v>0.000592451370002671</v>
+      </c>
+      <c r="G875" t="n">
+        <v>1</v>
+      </c>
+      <c r="H875" t="n">
+        <v>0.7072434607645876</v>
+      </c>
+      <c r="I875" t="n">
+        <v>0.5696532336726123</v>
+      </c>
+      <c r="J875" t="n">
+        <v>1</v>
+      </c>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L875" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M875" t="n">
+        <v>33.57201400331805</v>
+      </c>
+      <c r="N875" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O875" t="n">
+        <v>0</v>
+      </c>
+      <c r="P875" t="inlineStr">
+        <is>
+          <t>BB%B=1.09 (extreme=1.30); RSI=72.2 (extreme=0.30); Wick ratio=2.89; ADX H1=19.5 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q875" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (20 นาทีหลัง) — block signal EU</t>
+        </is>
+      </c>
+      <c r="R875" t="inlineStr">
+        <is>
+          <t>[0.7218, 0.0, -1.0, -0.9075, 1.0, -1.0, 1.6879, 0.4435, 0.3893, 0.0566, 1.0, 0.2633, 0.841, 1.0903, 0.2328, 3.0, 0.2364, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4733, 0.0, 0.0, 0.0, 0.0, 0.6021, 0.7771, 0.6751, 0.3836]</t>
+        </is>
+      </c>
+      <c r="S875" t="n">
+        <v>0</v>
+      </c>
+      <c r="T875" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:49:55.486021+00:00</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D876" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E876" t="n">
+        <v>83.70817220522036</v>
+      </c>
+      <c r="F876" t="n">
+        <v>0.08276004450755486</v>
+      </c>
+      <c r="G876" t="n">
+        <v>1</v>
+      </c>
+      <c r="H876" t="n">
+        <v>0.5897765097479788</v>
+      </c>
+      <c r="I876" t="n">
+        <v>0.5437300682110793</v>
+      </c>
+      <c r="J876" t="n">
+        <v>1</v>
+      </c>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L876" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M876" t="n">
+        <v>33.57201400331805</v>
+      </c>
+      <c r="N876" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O876" t="n">
+        <v>1.099999999999568</v>
+      </c>
+      <c r="P876" t="inlineStr">
+        <is>
+          <t>BB%B=1.04 (extreme=1.13); RSI=67.4 (extreme=0.19); Wick ratio=2.70; ADX H1=22.8 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q876" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=185.36000 &lt; C=185.36800) — SELL needs beari</t>
+        </is>
+      </c>
+      <c r="R876" t="inlineStr">
+        <is>
+          <t>[0.6742, 0.0, -1.0, -0.6724, 1.0, -1.0, 1.8125, 0.3483, 0.3743, 0.0625, 1.0, 0.2792, 0.8575, 1.0399, 0.23, 2.8516, 0.1796, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.4416, 0.0, 0.0, 0.0, 0.0, 0.6021, 0.5673, 0.5351, 0.385]</t>
+        </is>
+      </c>
+      <c r="S876" t="n">
+        <v>0</v>
+      </c>
+      <c r="T876" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:49:56.165049+00:00</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D877" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E877" t="n">
+        <v>79.59940625496186</v>
+      </c>
+      <c r="F877" t="n">
+        <v>0.0004842362719275957</v>
+      </c>
+      <c r="G877" t="n">
+        <v>1</v>
+      </c>
+      <c r="H877" t="n">
+        <v>0.5627603642945385</v>
+      </c>
+      <c r="I877" t="n">
+        <v>0.5374933856507491</v>
+      </c>
+      <c r="J877" t="n">
+        <v>1</v>
+      </c>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L877" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M877" t="n">
+        <v>33.57201400331805</v>
+      </c>
+      <c r="N877" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O877" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P877" t="inlineStr">
+        <is>
+          <t>BB%B=1.13 (extreme=1.45); RSI=73.2 (extreme=0.33); Wick ratio=1.00; ADX H1=26.9 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q877" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (20 นาทีหลัง) — block signal NZ</t>
+        </is>
+      </c>
+      <c r="R877" t="inlineStr">
+        <is>
+          <t>[0.592, 0.0, -1.0, -1.0158, 1.0, -1.0, 2.0, 0.464, 0.351, 0.1663, 1.0, 0.173, 0.8874, 1.1335, -0.0562, 3.0, 0.0798, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.654, 0.0, 0.0, 0.0, 0.0, 0.6021, 0.76, 0.5858, 0.5281]</t>
+        </is>
+      </c>
+      <c r="S877" t="n">
+        <v>0</v>
+      </c>
+      <c r="T877" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:50:57.380537+00:00</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D878" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E878" t="n">
+        <v>85.8990866511444</v>
+      </c>
+      <c r="F878" t="n">
+        <v>0.000592451370002671</v>
+      </c>
+      <c r="G878" t="n">
+        <v>1</v>
+      </c>
+      <c r="H878" t="n">
+        <v>0.7072434607645876</v>
+      </c>
+      <c r="I878" t="n">
+        <v>0.5696532336726123</v>
+      </c>
+      <c r="J878" t="n">
+        <v>1</v>
+      </c>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L878" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M878" t="n">
+        <v>33.46898142129872</v>
+      </c>
+      <c r="N878" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O878" t="n">
+        <v>0</v>
+      </c>
+      <c r="P878" t="inlineStr">
+        <is>
+          <t>BB%B=1.08 (extreme=1.26); RSI=71.8 (extreme=0.29); Wick ratio=10.67; ADX H1=19.5 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q878" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (21 นาทีหลัง) — block signal EU</t>
+        </is>
+      </c>
+      <c r="R878" t="inlineStr">
+        <is>
+          <t>[0.718, 0.0, -1.0, -0.9075, 1.0, -1.0, 1.6879, 0.436, 0.3829, 0.057, 1.0, 0.2633, 0.8043, 1.0774, 0.2328, 3.0, 0.2364, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4733, 0.0, 0.0, 0.0, 0.0, 0.6042, 0.7525, 0.6689, 0.3836]</t>
+        </is>
+      </c>
+      <c r="S878" t="n">
+        <v>0</v>
+      </c>
+      <c r="T878" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:50:58.058566+00:00</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D879" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E879" t="n">
+        <v>85.48129349738649</v>
+      </c>
+      <c r="F879" t="n">
+        <v>0.0004842362719275957</v>
+      </c>
+      <c r="G879" t="n">
+        <v>1</v>
+      </c>
+      <c r="H879" t="n">
+        <v>0.5627603642945385</v>
+      </c>
+      <c r="I879" t="n">
+        <v>0.5374933856507491</v>
+      </c>
+      <c r="J879" t="n">
+        <v>1</v>
+      </c>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L879" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M879" t="n">
+        <v>33.46898142129872</v>
+      </c>
+      <c r="N879" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O879" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P879" t="inlineStr">
+        <is>
+          <t>BB%B=1.13 (extreme=1.42); RSI=73.0 (extreme=0.32); Wick ratio=2.20; ADX H1=26.9 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q879" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (21 นาทีหลัง) — block signal NZ</t>
+        </is>
+      </c>
+      <c r="R879" t="inlineStr">
+        <is>
+          <t>[0.7096, 0.0, -1.0, -1.0158, 1.0, -1.0, 2.0, 0.4593, 0.3471, 0.1659, 1.0, 0.173, 0.8615, 1.1256, -0.0562, 3.0, 0.0798, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.654, 0.0, 0.0, 0.0, 0.0, 0.6042, 0.745, 0.5821, 0.5281]</t>
+        </is>
+      </c>
+      <c r="S879" t="n">
+        <v>0</v>
+      </c>
+      <c r="T879" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:50:58.699042+00:00</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D880" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E880" t="n">
+        <v>83.08355756097266</v>
+      </c>
+      <c r="F880" t="n">
+        <v>0.08276004450755486</v>
+      </c>
+      <c r="G880" t="n">
+        <v>1</v>
+      </c>
+      <c r="H880" t="n">
+        <v>0.5897765097479788</v>
+      </c>
+      <c r="I880" t="n">
+        <v>0.5437300682110793</v>
+      </c>
+      <c r="J880" t="n">
+        <v>1</v>
+      </c>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L880" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M880" t="n">
+        <v>33.46898142129872</v>
+      </c>
+      <c r="N880" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O880" t="n">
+        <v>1.099999999999568</v>
+      </c>
+      <c r="P880" t="inlineStr">
+        <is>
+          <t>BB%B=1.01 (extreme=1.03); RSI=66.2 (extreme=0.15); Wick ratio=7.40; ADX H1=22.8 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q880" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=185.36900 &lt; C=185.37200) — SELL needs beari</t>
+        </is>
+      </c>
+      <c r="R880" t="inlineStr">
+        <is>
+          <t>[0.6617, 0.0, -1.0, -0.6724, 1.0, -1.0, 1.8125, 0.3233, 0.3627, 0.0632, 1.0, 0.2792, 0.7784, 1.01, 0.23, 2.6704, 0.1796, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.4416, 0.0, 0.0, 0.0, 0.0, 0.6042, 0.5234, 0.5241, 0.385]</t>
+        </is>
+      </c>
+      <c r="S880" t="n">
+        <v>0</v>
+      </c>
+      <c r="T880" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:54:00.558288+00:00</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D881" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E881" t="n">
+        <v>78.43230276838526</v>
+      </c>
+      <c r="F881" t="n">
+        <v>0.0006081656614628496</v>
+      </c>
+      <c r="G881" t="n">
+        <v>1</v>
+      </c>
+      <c r="H881" t="n">
+        <v>0.6886341929321872</v>
+      </c>
+      <c r="I881" t="n">
+        <v>0.5649735204549993</v>
+      </c>
+      <c r="J881" t="n">
+        <v>1</v>
+      </c>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L881" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M881" t="n">
+        <v>32.9836934917158</v>
+      </c>
+      <c r="N881" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O881" t="n">
+        <v>0</v>
+      </c>
+      <c r="P881" t="inlineStr">
+        <is>
+          <t>BB%B=1.14 (extreme=1.46); RSI=73.6 (extreme=0.34); Wick ratio=0.73; ADX H1=19.6 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q881" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (24 นาทีหลัง) — block signal EU</t>
+        </is>
+      </c>
+      <c r="R881" t="inlineStr">
+        <is>
+          <t>[0.5686, 0.0, -1.0, -0.8918, 1.0, -1.0, 1.6443, 0.4718, 0.4045, 0.0549, 1.0, 0.2649, 0.8625, 1.1385, 0.2647, 3.0, 0.2364, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4701, 0.0, 0.0, 0.0, 0.0, 0.6125, 0.8527, 0.6816, 0.3676]</t>
+        </is>
+      </c>
+      <c r="S881" t="n">
+        <v>0</v>
+      </c>
+      <c r="T881" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:54:01.334578+00:00</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D882" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E882" t="n">
+        <v>77.63156618739013</v>
+      </c>
+      <c r="F882" t="n">
+        <v>0.0004992362774123144</v>
+      </c>
+      <c r="G882" t="n">
+        <v>1</v>
+      </c>
+      <c r="H882" t="n">
+        <v>0.5897765097479788</v>
+      </c>
+      <c r="I882" t="n">
+        <v>0.5446352538771899</v>
+      </c>
+      <c r="J882" t="n">
+        <v>1</v>
+      </c>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L882" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M882" t="n">
+        <v>32.9836934917158</v>
+      </c>
+      <c r="N882" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O882" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P882" t="inlineStr">
+        <is>
+          <t>BB%B=1.18 (extreme=1.58); RSI=74.5 (extreme=0.36); Wick ratio=0.48; ADX H1=27.0 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q882" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (24 นาทีหลัง) — block signal NZ</t>
+        </is>
+      </c>
+      <c r="R882" t="inlineStr">
+        <is>
+          <t>[0.5526, 0.0, -1.0, -1.0008, 1.0, -1.0, 2.0, 0.4893, 0.3622, 0.1685, 1.0, 0.1749, 0.9028, 1.1755, -0.0276, 3.0, 0.0754, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.6502, 0.0, 0.0, 0.0, 0.0, 0.6125, 0.8197, 0.5889, 0.5138]</t>
+        </is>
+      </c>
+      <c r="S882" t="n">
+        <v>0</v>
+      </c>
+      <c r="T882" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:55:02.485877+00:00</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D883" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E883" t="n">
+        <v>81.10367871220537</v>
+      </c>
+      <c r="F883" t="n">
+        <v>0.08376004487320382</v>
+      </c>
+      <c r="G883" t="n">
+        <v>1</v>
+      </c>
+      <c r="H883" t="n">
+        <v>0.5897765097479788</v>
+      </c>
+      <c r="I883" t="n">
+        <v>0.5437300682110793</v>
+      </c>
+      <c r="J883" t="n">
+        <v>1</v>
+      </c>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L883" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M883" t="n">
+        <v>32.9057501610075</v>
+      </c>
+      <c r="N883" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O883" t="n">
+        <v>1.900000000000546</v>
+      </c>
+      <c r="P883" t="inlineStr">
+        <is>
+          <t>BB%B=1.06 (extreme=1.18); RSI=67.9 (extreme=0.20); Wick ratio=1.83; ADX H1=22.9 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q883" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC filter: dist 0.58 &lt; 0.6 — price not overextended up</t>
+        </is>
+      </c>
+      <c r="R883" t="inlineStr">
+        <is>
+          <t>[0.6221, 0.0, -1.0, -0.6624, 1.0, -1.0, 1.7908, 0.3575, 0.3759, 0.0622, 1.0, 0.2803, 0.8321, 1.0551, 0.2445, 2.9131, 0.1909, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0002, 0.0, 0.4394, 0.0, 0.0, 0.0, 0.0, 0.6146, 0.5837, 0.5345, 0.3777]</t>
+        </is>
+      </c>
+      <c r="S883" t="n">
+        <v>0</v>
+      </c>
+      <c r="T883" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:55:03.206344+00:00</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D884" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E884" t="n">
+        <v>80.18136850440634</v>
+      </c>
+      <c r="F884" t="n">
+        <v>0.0006081656614628496</v>
+      </c>
+      <c r="G884" t="n">
+        <v>1</v>
+      </c>
+      <c r="H884" t="n">
+        <v>0.6886341929321872</v>
+      </c>
+      <c r="I884" t="n">
+        <v>0.5638815239648264</v>
+      </c>
+      <c r="J884" t="n">
+        <v>1</v>
+      </c>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L884" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M884" t="n">
+        <v>32.9057501610075</v>
+      </c>
+      <c r="N884" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O884" t="n">
+        <v>0.2000000000013102</v>
+      </c>
+      <c r="P884" t="inlineStr">
+        <is>
+          <t>BB%B=1.13 (extreme=1.42); RSI=73.3 (extreme=0.33); Wick ratio=1.11; ADX H1=19.6 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q884" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (25 นาทีหลัง) — block signal EU</t>
+        </is>
+      </c>
+      <c r="R884" t="inlineStr">
+        <is>
+          <t>[0.6036, 0.0, -1.0, -0.8918, 1.0, -1.0, 1.6443, 0.465, 0.3982, 0.0553, 1.0, 0.2649, 0.8281, 1.127, 0.2647, 3.0, 0.2364, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4701, 0.0, 0.0, 0.0, 0.0, 0.6146, 0.8288, 0.6756, 0.3676]</t>
+        </is>
+      </c>
+      <c r="S884" t="n">
+        <v>0</v>
+      </c>
+      <c r="T884" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:55:03.841169+00:00</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D885" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E885" t="n">
+        <v>77.90436925542036</v>
+      </c>
+      <c r="F885" t="n">
+        <v>0.0004992362774123144</v>
+      </c>
+      <c r="G885" t="n">
+        <v>1</v>
+      </c>
+      <c r="H885" t="n">
+        <v>0.7366044184059564</v>
+      </c>
+      <c r="I885" t="n">
+        <v>0.5901144136959454</v>
+      </c>
+      <c r="J885" t="n">
+        <v>1</v>
+      </c>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L885" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M885" t="n">
+        <v>32.9057501610075</v>
+      </c>
+      <c r="N885" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O885" t="n">
+        <v>0.700000000000145</v>
+      </c>
+      <c r="P885" t="inlineStr">
+        <is>
+          <t>BB%B=1.17 (extreme=1.58); RSI=74.4 (extreme=0.36); Wick ratio=0.54; ADX H1=27.0 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q885" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (25 นาทีหลัง) — block signal NZ</t>
+        </is>
+      </c>
+      <c r="R885" t="inlineStr">
+        <is>
+          <t>[0.5581, 0.0, -1.0, -1.0008, 1.0, -1.0, 2.0, 0.4878, 0.3609, 0.1684, 1.0, 0.1749, 0.8947, 1.1732, -0.0276, 3.0, 0.1909, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.6502, 0.0, 0.0, 0.0, 0.0, 0.6146, 0.8148, 0.5877, 0.5138]</t>
+        </is>
+      </c>
+      <c r="S885" t="n">
+        <v>0</v>
+      </c>
+      <c r="T885" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:56:04.931237+00:00</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D886" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E886" t="n">
+        <v>77.99454724674136</v>
+      </c>
+      <c r="F886" t="n">
+        <v>0.0006081656614628496</v>
+      </c>
+      <c r="G886" t="n">
+        <v>1</v>
+      </c>
+      <c r="H886" t="n">
+        <v>0.7366044184059564</v>
+      </c>
+      <c r="I886" t="n">
+        <v>0.5875169174643052</v>
+      </c>
+      <c r="J886" t="n">
+        <v>1</v>
+      </c>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L886" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M886" t="n">
+        <v>32.51795498424165</v>
+      </c>
+      <c r="N886" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O886" t="n">
+        <v>0</v>
+      </c>
+      <c r="P886" t="inlineStr">
+        <is>
+          <t>BB%B=1.14 (extreme=1.47); RSI=73.7 (extreme=0.34); Wick ratio=0.63; ADX H1=19.6 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q886" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (26 นาทีหลัง) — block signal EU</t>
+        </is>
+      </c>
+      <c r="R886" t="inlineStr">
+        <is>
+          <t>[0.5599, 0.0, -1.0, -0.8918, 1.0, -1.0, 1.6443, 0.4741, 0.4066, 0.0548, 1.0, 0.2649, 0.8739, 1.1423, 0.2647, 3.0, 0.2364, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4701, 0.0, 0.0, 0.0, 0.0, 0.6167, 0.8607, 0.6836, 0.3676]</t>
+        </is>
+      </c>
+      <c r="S886" t="n">
+        <v>0</v>
+      </c>
+      <c r="T886" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:56:05.621775+00:00</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D887" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E887" t="n">
+        <v>77.90436925542036</v>
+      </c>
+      <c r="F887" t="n">
+        <v>0.0004992362774123144</v>
+      </c>
+      <c r="G887" t="n">
+        <v>1</v>
+      </c>
+      <c r="H887" t="n">
+        <v>0.7775722543352601</v>
+      </c>
+      <c r="I887" t="n">
+        <v>0.6122491381020549</v>
+      </c>
+      <c r="J887" t="n">
+        <v>1</v>
+      </c>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L887" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M887" t="n">
+        <v>32.51795498424165</v>
+      </c>
+      <c r="N887" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O887" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P887" t="inlineStr">
+        <is>
+          <t>BB%B=1.17 (extreme=1.58); RSI=74.4 (extreme=0.36); Wick ratio=0.54; ADX H1=27.0 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q887" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (26 นาทีหลัง) — block signal NZ</t>
+        </is>
+      </c>
+      <c r="R887" t="inlineStr">
+        <is>
+          <t>[0.5581, 0.0, -1.0, -1.0008, 1.0, -1.0, 2.0, 0.4878, 0.3609, 0.1684, 1.0, 0.1749, 0.8947, 1.1732, -0.0276, 3.0, 0.1909, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.6502, 0.0, 0.0, 0.0, 0.0, 0.6167, 0.8148, 0.5877, 0.5138]</t>
+        </is>
+      </c>
+      <c r="S887" t="n">
+        <v>0</v>
+      </c>
+      <c r="T887" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:57:06.767719+00:00</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D888" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E888" t="n">
+        <v>77.11402934109752</v>
+      </c>
+      <c r="F888" t="n">
+        <v>0.0006081656614628496</v>
+      </c>
+      <c r="G888" t="n">
+        <v>1</v>
+      </c>
+      <c r="H888" t="n">
+        <v>0.7366044184059564</v>
+      </c>
+      <c r="I888" t="n">
+        <v>0.5875169174643052</v>
+      </c>
+      <c r="J888" t="n">
+        <v>1</v>
+      </c>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L888" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M888" t="n">
+        <v>32.49055107443976</v>
+      </c>
+      <c r="N888" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O888" t="n">
+        <v>0</v>
+      </c>
+      <c r="P888" t="inlineStr">
+        <is>
+          <t>BB%B=1.15 (extreme=1.51); RSI=74.0 (extreme=0.35); Wick ratio=0.43; ADX H1=19.6 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q888" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (27 นาทีหลัง) — block signal EU</t>
+        </is>
+      </c>
+      <c r="R888" t="inlineStr">
+        <is>
+          <t>[0.5423, 0.0, -1.0, -0.8918, 1.0, -1.0, 1.6443, 0.4796, 0.4118, 0.0544, 1.0, 0.2649, 0.9026, 1.1516, 0.2647, 3.0, 0.2364, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4701, 0.0, 0.0, 0.0, 0.0, 0.6187, 0.8806, 0.6885, 0.3676]</t>
+        </is>
+      </c>
+      <c r="S888" t="n">
+        <v>0</v>
+      </c>
+      <c r="T888" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:58:07.735899+00:00</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D889" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E889" t="n">
+        <v>80.25640911128404</v>
+      </c>
+      <c r="F889" t="n">
+        <v>0.0004992362774123144</v>
+      </c>
+      <c r="G889" t="n">
+        <v>1</v>
+      </c>
+      <c r="H889" t="n">
+        <v>0.639676113360324</v>
+      </c>
+      <c r="I889" t="n">
+        <v>0.5565684389811208</v>
+      </c>
+      <c r="J889" t="n">
+        <v>1</v>
+      </c>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L889" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M889" t="n">
+        <v>32.49055107443976</v>
+      </c>
+      <c r="N889" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O889" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P889" t="inlineStr">
+        <is>
+          <t>BB%B=1.16 (extreme=1.53); RSI=74.0 (extreme=0.35); Wick ratio=1.06; ADX H1=27.0 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q889" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (28 นาทีหลัง) — block signal NZ</t>
+        </is>
+      </c>
+      <c r="R889" t="inlineStr">
+        <is>
+          <t>[0.6051, 0.0, -1.0, -1.0008, 1.0, -1.0, 2.0, 0.4791, 0.3533, 0.1676, 1.0, 0.1749, 0.8462, 1.1588, -0.0276, 3.0, 0.0754, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.6502, 0.0, 0.0, 0.0, 0.0, 0.6208, 0.7857, 0.5804, 0.5138]</t>
+        </is>
+      </c>
+      <c r="S889" t="n">
+        <v>0</v>
+      </c>
+      <c r="T889" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:59:08.726115+00:00</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D890" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E890" t="n">
+        <v>85.17038305815261</v>
+      </c>
+      <c r="F890" t="n">
+        <v>0.0004992362774123144</v>
+      </c>
+      <c r="G890" t="n">
+        <v>1</v>
+      </c>
+      <c r="H890" t="n">
+        <v>0.639676113360324</v>
+      </c>
+      <c r="I890" t="n">
+        <v>0.5565684389811208</v>
+      </c>
+      <c r="J890" t="n">
+        <v>1</v>
+      </c>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L890" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M890" t="n">
+        <v>32.47816311894335</v>
+      </c>
+      <c r="N890" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O890" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P890" t="inlineStr">
+        <is>
+          <t>BB%B=1.14 (extreme=1.48); RSI=73.5 (extreme=0.34); Wick ratio=2.08; ADX H1=27.0 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q890" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (29 นาทีหลัง) — block signal NZ</t>
+        </is>
+      </c>
+      <c r="R890" t="inlineStr">
+        <is>
+          <t>[0.7034, 0.0, -1.0, -1.0008, 1.0, -1.0, 2.0, 0.4701, 0.3456, 0.1668, 1.0, 0.1749, 0.7976, 1.1438, -0.0276, 3.0, 0.0754, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.6502, 0.0, 0.0, 0.0, 0.0, 0.6229, 0.7566, 0.5731, 0.5138]</t>
+        </is>
+      </c>
+      <c r="S890" t="n">
+        <v>0</v>
+      </c>
+      <c r="T890" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>2026-05-28 12:59:09.422163+00:00</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D891" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E891" t="n">
+        <v>77.99454724674136</v>
+      </c>
+      <c r="F891" t="n">
+        <v>0.0006081656614628496</v>
+      </c>
+      <c r="G891" t="n">
+        <v>1</v>
+      </c>
+      <c r="H891" t="n">
+        <v>0.7366044184059564</v>
+      </c>
+      <c r="I891" t="n">
+        <v>0.5875169174643052</v>
+      </c>
+      <c r="J891" t="n">
+        <v>1</v>
+      </c>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L891" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M891" t="n">
+        <v>32.47816311894335</v>
+      </c>
+      <c r="N891" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O891" t="n">
+        <v>0</v>
+      </c>
+      <c r="P891" t="inlineStr">
+        <is>
+          <t>BB%B=1.14 (extreme=1.47); RSI=73.7 (extreme=0.34); Wick ratio=0.63; ADX H1=19.6 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q891" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (29 นาทีหลัง) — block signal EU</t>
+        </is>
+      </c>
+      <c r="R891" t="inlineStr">
+        <is>
+          <t>[0.5599, 0.0, -1.0, -0.8918, 1.0, -1.0, 1.6443, 0.4741, 0.4066, 0.0548, 1.0, 0.2649, 0.8739, 1.1423, 0.2647, 3.0, 0.2364, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4701, 0.0, 0.0, 0.0, 0.0, 0.6229, 0.8607, 0.6836, 0.3676]</t>
+        </is>
+      </c>
+      <c r="S891" t="n">
+        <v>0</v>
+      </c>
+      <c r="T891" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:00:10.496926+00:00</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D892" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E892" t="n">
+        <v>83.44781963211484</v>
+      </c>
+      <c r="F892" t="n">
+        <v>0.08130269411169919</v>
+      </c>
+      <c r="G892" t="n">
+        <v>1</v>
+      </c>
+      <c r="H892" t="n">
+        <v>0.575399320840146</v>
+      </c>
+      <c r="I892" t="n">
+        <v>0.5400516661860228</v>
+      </c>
+      <c r="J892" t="n">
+        <v>-0.4051564037799835</v>
+      </c>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L892" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M892" t="n">
+        <v>30.35539717798591</v>
+      </c>
+      <c r="N892" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O892" t="n">
+        <v>0.9999999999990905</v>
+      </c>
+      <c r="P892" t="inlineStr">
+        <is>
+          <t>BB%B=1.04 (extreme=1.13); RSI=70.9 (extreme=0.27); Wick ratio=2.00; ADX H1=22.6 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R892" t="inlineStr">
+        <is>
+          <t>[0.669, 0.0, -1.0, -0.687, 1.0, -1.0, 1.845, 0.4179, 0.483, 0.0483, 1.0, 0.2987, 0.9721, 1.0398, 0.1994, 2.423, 0.0125, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.4027, 0.0, 0.0, 0.0, 0.0, 0.0, 0.7194, 0.6928, 0.4003]</t>
+        </is>
+      </c>
+      <c r="S892" t="n">
+        <v>0</v>
+      </c>
+      <c r="T892" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:01:11.634781+00:00</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D893" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E893" t="n">
+        <v>85.65200846562009</v>
+      </c>
+      <c r="F893" t="n">
+        <v>0.08194555148961695</v>
+      </c>
+      <c r="G893" t="n">
+        <v>1</v>
+      </c>
+      <c r="H893" t="n">
+        <v>0.5627603642945385</v>
+      </c>
+      <c r="I893" t="n">
+        <v>0.5388824443233473</v>
+      </c>
+      <c r="J893" t="n">
+        <v>-0.4627560973167419</v>
+      </c>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L893" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M893" t="n">
+        <v>30.43599362383996</v>
+      </c>
+      <c r="N893" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O893" t="n">
+        <v>0.9999999999990905</v>
+      </c>
+      <c r="P893" t="inlineStr">
+        <is>
+          <t>BB%B=1.05 (extreme=1.15); RSI=71.3 (extreme=0.28); Wick ratio=5.50; ADX H1=22.7 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R893" t="inlineStr">
+        <is>
+          <t>[0.713, 0.0, -1.0, -0.6805, 1.0, -1.0, 1.8305, 0.4261, 0.4823, 0.0481, 1.0, 0.2993, 0.9499, 1.0458, 0.2086, 2.4528, 0.0125, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.4014, 0.0, 0.0, 0.0, 0.0, 0.0021, 0.7255, 0.6904, 0.3957]</t>
+        </is>
+      </c>
+      <c r="S893" t="n">
+        <v>0</v>
+      </c>
+      <c r="T893" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:04:13.439512+00:00</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D894" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E894" t="n">
+        <v>78.57819203796828</v>
+      </c>
+      <c r="F894" t="n">
+        <v>0.0006140109773654444</v>
+      </c>
+      <c r="G894" t="n">
+        <v>1</v>
+      </c>
+      <c r="H894" t="n">
+        <v>0.5897765097479788</v>
+      </c>
+      <c r="I894" t="n">
+        <v>0.5449920150697948</v>
+      </c>
+      <c r="J894" t="n">
+        <v>1</v>
+      </c>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L894" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M894" t="n">
+        <v>30.45169515405955</v>
+      </c>
+      <c r="N894" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O894" t="n">
+        <v>0</v>
+      </c>
+      <c r="P894" t="inlineStr">
+        <is>
+          <t>BB%B=1.11 (extreme=1.38); RSI=76.4 (extreme=0.41); Wick ratio=0.48; ADX H1=19.4 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q894" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (34 นาทีหลัง) — block signal EU</t>
+        </is>
+      </c>
+      <c r="R894" t="inlineStr">
+        <is>
+          <t>[0.5716, 0.0, -1.0, -0.886, 1.0, -1.0, 1.6286, 0.5275, 0.4978, 0.0368, 1.0, 0.2893, 0.8897, 1.1133, 0.2663, 3.0, 0.2364, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4213, 0.0, 0.0, 0.0, 0.0, 0.0083, 0.9709, 0.8579, 0.3668]</t>
+        </is>
+      </c>
+      <c r="S894" t="n">
+        <v>0</v>
+      </c>
+      <c r="T894" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:04:14.136418+00:00</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D895" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E895" t="n">
+        <v>76.58380719826734</v>
+      </c>
+      <c r="F895" t="n">
+        <v>0.08523126697674631</v>
+      </c>
+      <c r="G895" t="n">
+        <v>1</v>
+      </c>
+      <c r="H895" t="n">
+        <v>0.7366044184059564</v>
+      </c>
+      <c r="I895" t="n">
+        <v>0.583895748606448</v>
+      </c>
+      <c r="J895" t="n">
+        <v>1</v>
+      </c>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L895" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M895" t="n">
+        <v>30.45169515405955</v>
+      </c>
+      <c r="N895" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O895" t="n">
+        <v>1.000000000001933</v>
+      </c>
+      <c r="P895" t="inlineStr">
+        <is>
+          <t>BB%B=1.10 (extreme=1.34); RSI=73.1 (extreme=0.33); Wick ratio=0.40; ADX H1=22.9 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q895" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC slope: 0.69 &gt; 0.15 — EMA rising too fast for SELL</t>
+        </is>
+      </c>
+      <c r="R895" t="inlineStr">
+        <is>
+          <t>[0.5317, 0.0, -1.0, -0.6477, 1.0, -1.0, 1.7599, 0.4624, 0.4937, 0.0464, 1.0, 0.3021, 0.9299, 1.1021, 0.2559, 2.8276, 0.4732, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.3957, 0.0, 0.0, 0.0, 0.0, 0.0083, 0.8113, 0.6922, 0.3721]</t>
+        </is>
+      </c>
+      <c r="S895" t="n">
+        <v>0</v>
+      </c>
+      <c r="T895" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:05:15.221794+00:00</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D896" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E896" t="n">
+        <v>81.63681736551743</v>
+      </c>
+      <c r="F896" t="n">
+        <v>0.0005050051217917954</v>
+      </c>
+      <c r="G896" t="n">
+        <v>1</v>
+      </c>
+      <c r="H896" t="n">
+        <v>0.5627603642945385</v>
+      </c>
+      <c r="I896" t="n">
+        <v>0.5368537063225534</v>
+      </c>
+      <c r="J896" t="n">
+        <v>1</v>
+      </c>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L896" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M896" t="n">
+        <v>30.48870255915507</v>
+      </c>
+      <c r="N896" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O896" t="n">
+        <v>0.3999999999992898</v>
+      </c>
+      <c r="P896" t="inlineStr">
+        <is>
+          <t>BB%B=1.11 (extreme=1.36); RSI=76.1 (extreme=0.40); Wick ratio=1.12; ADX H1=27.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q896" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (35 นาทีหลัง) — block signal NZ</t>
+        </is>
+      </c>
+      <c r="R896" t="inlineStr">
+        <is>
+          <t>[0.6327, 0.0, -1.0, -0.995, 1.0, -1.0, 2.0, 0.5224, 0.4261, 0.1889, 1.0, 0.2006, 0.7979, 1.1069, -0.0178, 3.0, 0.1565, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5988, 0.0, 0.0, 0.0, 0.0, 0.0104, 0.8484, 0.7612, 0.5089]</t>
+        </is>
+      </c>
+      <c r="S896" t="n">
+        <v>0</v>
+      </c>
+      <c r="T896" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:05:16.094651+00:00</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D897" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E897" t="n">
+        <v>76.03856156091892</v>
+      </c>
+      <c r="F897" t="n">
+        <v>0.113832109468181</v>
+      </c>
+      <c r="G897" t="n">
+        <v>1</v>
+      </c>
+      <c r="H897" t="n">
+        <v>0.5627603642945385</v>
+      </c>
+      <c r="I897" t="n">
+        <v>0.5366812709509257</v>
+      </c>
+      <c r="J897" t="n">
+        <v>1</v>
+      </c>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L897" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M897" t="n">
+        <v>30.48870255915507</v>
+      </c>
+      <c r="N897" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O897" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P897" t="inlineStr">
+        <is>
+          <t>BB%B=0.95 (extreme=0.83); RSI=63.5 (extreme=0.09); Wick ratio=2.29; ADX H1=23.3 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q897" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC filter: dist 0.43 &lt; 0.6 — price not overextended up</t>
+        </is>
+      </c>
+      <c r="R897" t="inlineStr">
+        <is>
+          <t>[0.5208, 0.0, -1.0, -0.3617, 0.8278, -1.0, 1.757, 0.2699, 0.3521, 0.1216, 1.0, 0.206, 0.7982, 0.9483, 0.1802, 1.0454, 0.1565, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0002, 0.0, 0.588, 0.0, 0.0, 0.0, 0.0, 0.0104, 0.4323, 0.4242, 0.4099]</t>
+        </is>
+      </c>
+      <c r="S897" t="n">
+        <v>0</v>
+      </c>
+      <c r="T897" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:06:17.052902+00:00</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D898" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E898" t="n">
+        <v>79.62231540669818</v>
+      </c>
+      <c r="F898" t="n">
+        <v>0.0005050051217917954</v>
+      </c>
+      <c r="G898" t="n">
+        <v>1</v>
+      </c>
+      <c r="H898" t="n">
+        <v>0.6603960396039604</v>
+      </c>
+      <c r="I898" t="n">
+        <v>0.5581719385240633</v>
+      </c>
+      <c r="J898" t="n">
+        <v>1</v>
+      </c>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L898" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M898" t="n">
+        <v>30.61283094628035</v>
+      </c>
+      <c r="N898" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O898" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P898" t="inlineStr">
+        <is>
+          <t>BB%B=1.12 (extreme=1.41); RSI=76.6 (extreme=0.41); Wick ratio=0.67; ADX H1=27.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q898" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (36 นาทีหลัง) — block signal NZ</t>
+        </is>
+      </c>
+      <c r="R898" t="inlineStr">
+        <is>
+          <t>[0.5924, 0.0, -1.0, -0.995, 1.0, -1.0, 2.0, 0.5316, 0.4349, 0.1898, 1.0, 0.2006, 0.8467, 1.1221, -0.0178, 3.0, 0.1565, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5988, 0.0, 0.0, 0.0, 0.0, 0.0125, 0.882, 0.7696, 0.5089]</t>
+        </is>
+      </c>
+      <c r="S898" t="n">
+        <v>0</v>
+      </c>
+      <c r="T898" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:06:17.696051+00:00</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D899" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E899" t="n">
+        <v>78.44501111434988</v>
+      </c>
+      <c r="F899" t="n">
+        <v>0.0006140109773654444</v>
+      </c>
+      <c r="G899" t="n">
+        <v>1</v>
+      </c>
+      <c r="H899" t="n">
+        <v>0.6886341929321872</v>
+      </c>
+      <c r="I899" t="n">
+        <v>0.5677787140446606</v>
+      </c>
+      <c r="J899" t="n">
+        <v>1</v>
+      </c>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L899" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M899" t="n">
+        <v>30.61283094628035</v>
+      </c>
+      <c r="N899" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O899" t="n">
+        <v>0</v>
+      </c>
+      <c r="P899" t="inlineStr">
+        <is>
+          <t>BB%B=1.11 (extreme=1.38); RSI=76.4 (extreme=0.41); Wick ratio=0.45; ADX H1=19.4 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q899" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (36 นาทีหลัง) — block signal EU</t>
+        </is>
+      </c>
+      <c r="R899" t="inlineStr">
+        <is>
+          <t>[0.5689, 0.0, -1.0, -0.886, 1.0, -1.0, 1.6286, 0.5284, 0.4989, 0.0367, 1.0, 0.2893, 0.8947, 1.1149, 0.2663, 3.0, 0.2364, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4213, 0.0, 0.0, 0.0, 0.0, 0.0125, 0.9749, 0.8589, 0.3668]</t>
+        </is>
+      </c>
+      <c r="S899" t="n">
+        <v>0</v>
+      </c>
+      <c r="T899" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:06:18.332784+00:00</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D900" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E900" t="n">
+        <v>77.18821151655473</v>
+      </c>
+      <c r="F900" t="n">
+        <v>0.08530269557429296</v>
+      </c>
+      <c r="G900" t="n">
+        <v>1</v>
+      </c>
+      <c r="H900" t="n">
+        <v>0.6182242082766661</v>
+      </c>
+      <c r="I900" t="n">
+        <v>0.5515619672693549</v>
+      </c>
+      <c r="J900" t="n">
+        <v>1</v>
+      </c>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L900" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M900" t="n">
+        <v>30.61283094628035</v>
+      </c>
+      <c r="N900" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O900" t="n">
+        <v>1.099999999999568</v>
+      </c>
+      <c r="P900" t="inlineStr">
+        <is>
+          <t>BB%B=1.10 (extreme=1.33); RSI=73.0 (extreme=0.32); Wick ratio=0.54; ADX H1=22.9 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q900" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC slope: 0.69 &gt; 0.15 — EMA rising too fast for SELL</t>
+        </is>
+      </c>
+      <c r="R900" t="inlineStr">
+        <is>
+          <t>[0.5438, 0.0, -1.0, -0.647, 1.0, -1.0, 1.7584, 0.4598, 0.491, 0.0465, 1.0, 0.3022, 0.9136, 1.0981, 0.2569, 2.7901, 0.1796, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.3956, 0.0, 0.0, 0.0, 0.0, 0.0125, 0.8021, 0.6895, 0.3715]</t>
+        </is>
+      </c>
+      <c r="S900" t="n">
+        <v>0</v>
+      </c>
+      <c r="T900" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:06:19.082049+00:00</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D901" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E901" t="n">
+        <v>75.52570741166846</v>
+      </c>
+      <c r="F901" t="n">
+        <v>0.113832109468181</v>
+      </c>
+      <c r="G901" t="n">
+        <v>1</v>
+      </c>
+      <c r="H901" t="n">
+        <v>0.5954485850852329</v>
+      </c>
+      <c r="I901" t="n">
+        <v>0.5458960055777585</v>
+      </c>
+      <c r="J901" t="n">
+        <v>1</v>
+      </c>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L901" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M901" t="n">
+        <v>30.61283094628035</v>
+      </c>
+      <c r="N901" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O901" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P901" t="inlineStr">
+        <is>
+          <t>BB%B=0.94 (extreme=0.80); RSI=63.2 (extreme=0.08); Wick ratio=3.39; ADX H1=23.3 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q901" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC filter: dist 0.42 &lt; 0.6 — price not overextended up</t>
+        </is>
+      </c>
+      <c r="R901" t="inlineStr">
+        <is>
+          <t>[0.5105, 0.0, -1.0, -0.3617, 0.7975, -1.0, 1.757, 0.264, 0.3488, 0.1218, 1.0, 0.206, 0.7761, 0.9393, 0.1802, 0.9927, 0.1565, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0002, 0.0, 0.588, 0.0, 0.0, 0.0, 0.0, 0.0125, 0.4196, 0.421, 0.4099]</t>
+        </is>
+      </c>
+      <c r="S901" t="n">
+        <v>0</v>
+      </c>
+      <c r="T901" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:07:20.133300+00:00</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D902" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E902" t="n">
+        <v>84.60627809689949</v>
+      </c>
+      <c r="F902" t="n">
+        <v>0.0005050051217917954</v>
+      </c>
+      <c r="G902" t="n">
+        <v>1</v>
+      </c>
+      <c r="H902" t="n">
+        <v>0.6182242082766661</v>
+      </c>
+      <c r="I902" t="n">
+        <v>0.5500816447227067</v>
+      </c>
+      <c r="J902" t="n">
+        <v>1</v>
+      </c>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L902" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M902" t="n">
+        <v>30.61283094628035</v>
+      </c>
+      <c r="N902" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O902" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P902" t="inlineStr">
+        <is>
+          <t>BB%B=1.09 (extreme=1.31); RSI=75.7 (extreme=0.39); Wick ratio=1.75; ADX H1=27.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q902" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (37 นาทีหลัง) — block signal NZ</t>
+        </is>
+      </c>
+      <c r="R902" t="inlineStr">
+        <is>
+          <t>[0.6921, 0.0, -1.0, -0.995, 1.0, -1.0, 2.0, 0.5143, 0.4185, 0.1881, 1.0, 0.2006, 0.7561, 1.0935, -0.0178, 3.0, 0.0942, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5988, 0.0, 0.0, 0.0, 0.0, 0.0146, 0.8196, 0.754, 0.5089]</t>
+        </is>
+      </c>
+      <c r="S902" t="n">
+        <v>0</v>
+      </c>
+      <c r="T902" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:07:20.792148+00:00</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D903" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E903" t="n">
+        <v>79.73347578023791</v>
+      </c>
+      <c r="F903" t="n">
+        <v>0.0006140109773654444</v>
+      </c>
+      <c r="G903" t="n">
+        <v>1</v>
+      </c>
+      <c r="H903" t="n">
+        <v>0.6886341929321872</v>
+      </c>
+      <c r="I903" t="n">
+        <v>0.5677787140446606</v>
+      </c>
+      <c r="J903" t="n">
+        <v>1</v>
+      </c>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L903" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M903" t="n">
+        <v>30.61283094628035</v>
+      </c>
+      <c r="N903" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O903" t="n">
+        <v>0</v>
+      </c>
+      <c r="P903" t="inlineStr">
+        <is>
+          <t>BB%B=1.10 (extreme=1.34); RSI=76.0 (extreme=0.40); Wick ratio=0.74; ADX H1=19.4 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q903" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (37 นาทีหลัง) — block signal EU</t>
+        </is>
+      </c>
+      <c r="R903" t="inlineStr">
+        <is>
+          <t>[0.5947, 0.0, -1.0, -0.886, 1.0, -1.0, 1.6286, 0.5206, 0.4905, 0.0373, 1.0, 0.2893, 0.8546, 1.1019, 0.2663, 3.0, 0.2364, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4213, 0.0, 0.0, 0.0, 0.0, 0.0146, 0.9433, 0.851, 0.3668]</t>
+        </is>
+      </c>
+      <c r="S903" t="n">
+        <v>0</v>
+      </c>
+      <c r="T903" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:07:21.364493+00:00</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D904" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E904" t="n">
+        <v>78.21124079596474</v>
+      </c>
+      <c r="F904" t="n">
+        <v>0.08530269557429296</v>
+      </c>
+      <c r="G904" t="n">
+        <v>1</v>
+      </c>
+      <c r="H904" t="n">
+        <v>0.6182242082766661</v>
+      </c>
+      <c r="I904" t="n">
+        <v>0.550017417695147</v>
+      </c>
+      <c r="J904" t="n">
+        <v>1</v>
+      </c>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L904" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M904" t="n">
+        <v>30.61283094628035</v>
+      </c>
+      <c r="N904" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O904" t="n">
+        <v>1.099999999999568</v>
+      </c>
+      <c r="P904" t="inlineStr">
+        <is>
+          <t>BB%B=1.09 (extreme=1.30); RSI=72.8 (extreme=0.32); Wick ratio=0.76; ADX H1=22.9 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q904" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC slope: 0.69 &gt; 0.15 — EMA rising too fast for SELL</t>
+        </is>
+      </c>
+      <c r="R904" t="inlineStr">
+        <is>
+          <t>[0.5642, 0.0, -1.0, -0.647, 1.0, -1.0, 1.7584, 0.4555, 0.4873, 0.0467, 1.0, 0.3022, 0.893, 1.0914, 0.2569, 2.7314, 0.1655, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.3956, 0.0, 0.0, 0.0, 0.0, 0.0146, 0.7879, 0.6859, 0.3715]</t>
+        </is>
+      </c>
+      <c r="S904" t="n">
+        <v>0</v>
+      </c>
+      <c r="T904" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:07:22.029566+00:00</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D905" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E905" t="n">
+        <v>75.34857933351036</v>
+      </c>
+      <c r="F905" t="n">
+        <v>0.113832109468181</v>
+      </c>
+      <c r="G905" t="n">
+        <v>1</v>
+      </c>
+      <c r="H905" t="n">
+        <v>0.5954485850852329</v>
+      </c>
+      <c r="I905" t="n">
+        <v>0.5458960055777585</v>
+      </c>
+      <c r="J905" t="n">
+        <v>1</v>
+      </c>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L905" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M905" t="n">
+        <v>30.61283094628035</v>
+      </c>
+      <c r="N905" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O905" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P905" t="inlineStr">
+        <is>
+          <t>BB%B=0.94 (extreme=0.79); RSI=63.2 (extreme=0.08); Wick ratio=3.65; ADX H1=23.3 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q905" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=213.88000 &lt; C=213.88400) — SELL needs beari</t>
+        </is>
+      </c>
+      <c r="R905" t="inlineStr">
+        <is>
+          <t>[0.507, 0.0, -1.0, -0.3617, 0.7925, -1.0, 1.757, 0.263, 0.3482, 0.1219, 1.0, 0.206, 0.7725, 0.9377, 0.1802, 0.9839, 0.1565, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0002, 0.0, 0.588, 0.0, 0.0, 0.0, 0.0, 0.0146, 0.4174, 0.4205, 0.4099]</t>
+        </is>
+      </c>
+      <c r="S905" t="n">
+        <v>0</v>
+      </c>
+      <c r="T905" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:08:23.052129+00:00</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D906" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E906" t="n">
+        <v>87.57373580871067</v>
+      </c>
+      <c r="F906" t="n">
+        <v>0.0005050051217917954</v>
+      </c>
+      <c r="G906" t="n">
+        <v>1</v>
+      </c>
+      <c r="H906" t="n">
+        <v>0.5282837066108902</v>
+      </c>
+      <c r="I906" t="n">
+        <v>0.5236918335714773</v>
+      </c>
+      <c r="J906" t="n">
+        <v>0.5954324007034302</v>
+      </c>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L906" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M906" t="n">
+        <v>30.61283094628035</v>
+      </c>
+      <c r="N906" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O906" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P906" t="inlineStr">
+        <is>
+          <t>BB%B=1.07 (extreme=1.25); RSI=75.1 (extreme=0.38); Wick ratio=3.58; ADX H1=27.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q906" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (38 นาทีหลัง) — block signal NZ</t>
+        </is>
+      </c>
+      <c r="R906" t="inlineStr">
+        <is>
+          <t>[0.7515, 0.0, -1.0, -0.995, 1.0, -1.0, 2.0, 0.5029, 0.4084, 0.1871, 1.0, 0.2006, 0.7003, 1.0748, -0.0178, 3.0, -0.0059, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5988, 0.0, 0.0, 0.0, 0.0, 0.0167, 0.7812, 0.7444, 0.5089]</t>
+        </is>
+      </c>
+      <c r="S906" t="n">
+        <v>0</v>
+      </c>
+      <c r="T906" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:08:23.940553+00:00</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D907" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E907" t="n">
+        <v>85.98343776388157</v>
+      </c>
+      <c r="F907" t="n">
+        <v>0.08530269557429296</v>
+      </c>
+      <c r="G907" t="n">
+        <v>1</v>
+      </c>
+      <c r="H907" t="n">
+        <v>0.6182242082766661</v>
+      </c>
+      <c r="I907" t="n">
+        <v>0.550017417695147</v>
+      </c>
+      <c r="J907" t="n">
+        <v>1</v>
+      </c>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L907" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M907" t="n">
+        <v>30.61283094628035</v>
+      </c>
+      <c r="N907" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O907" t="n">
+        <v>1.099999999999568</v>
+      </c>
+      <c r="P907" t="inlineStr">
+        <is>
+          <t>BB%B=1.07 (extreme=1.22); RSI=72.0 (extreme=0.30); Wick ratio=2.75; ADX H1=22.9 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q907" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC slope: 0.67 &gt; 0.15 — EMA rising too fast for SELL</t>
+        </is>
+      </c>
+      <c r="R907" t="inlineStr">
+        <is>
+          <t>[0.7197, 0.0, -1.0, -0.647, 1.0, -1.0, 1.7584, 0.4393, 0.4738, 0.0475, 1.0, 0.3022, 0.8189, 1.0663, 0.2569, 2.5204, 0.1655, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.3956, 0.0, 0.0, 0.0, 0.0, 0.0167, 0.7368, 0.6731, 0.3715]</t>
+        </is>
+      </c>
+      <c r="S907" t="n">
+        <v>0</v>
+      </c>
+      <c r="T907" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:08:24.563363+00:00</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D908" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E908" t="n">
+        <v>85.38714561051094</v>
+      </c>
+      <c r="F908" t="n">
+        <v>0.0006140109773654444</v>
+      </c>
+      <c r="G908" t="n">
+        <v>1</v>
+      </c>
+      <c r="H908" t="n">
+        <v>0.7129521586931156</v>
+      </c>
+      <c r="I908" t="n">
+        <v>0.5769941851395349</v>
+      </c>
+      <c r="J908" t="n">
+        <v>1</v>
+      </c>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L908" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M908" t="n">
+        <v>30.61283094628035</v>
+      </c>
+      <c r="N908" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O908" t="n">
+        <v>0</v>
+      </c>
+      <c r="P908" t="inlineStr">
+        <is>
+          <t>BB%B=1.07 (extreme=1.25); RSI=75.2 (extreme=0.38); Wick ratio=1.96; ADX H1=19.4 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q908" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (38 นาทีหลัง) — block signal EU</t>
+        </is>
+      </c>
+      <c r="R908" t="inlineStr">
+        <is>
+          <t>[0.7077, 0.0, -1.0, -0.886, 1.0, -1.0, 1.6286, 0.5042, 0.4739, 0.0384, 1.0, 0.2893, 0.7744, 1.0746, 0.2663, 3.0, 0.3604, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4213, 0.0, 0.0, 0.0, 0.0, 0.0167, 0.8801, 0.8352, 0.3668]</t>
+        </is>
+      </c>
+      <c r="S908" t="n">
+        <v>0</v>
+      </c>
+      <c r="T908" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:08:25.203762+00:00</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D909" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E909" t="n">
+        <v>75.34857933351036</v>
+      </c>
+      <c r="F909" t="n">
+        <v>0.1141178238583655</v>
+      </c>
+      <c r="G909" t="n">
+        <v>1</v>
+      </c>
+      <c r="H909" t="n">
+        <v>0.5954485850852329</v>
+      </c>
+      <c r="I909" t="n">
+        <v>0.5458960055777585</v>
+      </c>
+      <c r="J909" t="n">
+        <v>1</v>
+      </c>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L909" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M909" t="n">
+        <v>30.61283094628035</v>
+      </c>
+      <c r="N909" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O909" t="n">
+        <v>2.400000000000091</v>
+      </c>
+      <c r="P909" t="inlineStr">
+        <is>
+          <t>BB%B=0.94 (extreme=0.79); RSI=63.2 (extreme=0.08); Wick ratio=3.65; ADX H1=23.3 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q909" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC filter: dist 0.42 &lt; 0.6 — price not overextended up</t>
+        </is>
+      </c>
+      <c r="R909" t="inlineStr">
+        <is>
+          <t>[0.507, 0.0, -1.0, -0.3588, 0.7925, -1.0, 1.7526, 0.263, 0.3473, 0.1219, 1.0, 0.206, 0.7725, 0.9377, 0.1831, 0.9814, 0.1565, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0002, 0.0, 0.588, 0.0, 0.0, 0.0, 0.0, 0.0167, 0.4164, 0.4194, 0.4084]</t>
+        </is>
+      </c>
+      <c r="S909" t="n">
+        <v>0</v>
+      </c>
+      <c r="T909" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:09:26.220620+00:00</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D910" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E910" t="n">
+        <v>87.33304000682716</v>
+      </c>
+      <c r="F910" t="n">
+        <v>0.0006140109773654444</v>
+      </c>
+      <c r="G910" t="n">
+        <v>1</v>
+      </c>
+      <c r="H910" t="n">
+        <v>0.6182242082766661</v>
+      </c>
+      <c r="I910" t="n">
+        <v>0.5505450323391774</v>
+      </c>
+      <c r="J910" t="n">
+        <v>1</v>
+      </c>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L910" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M910" t="n">
+        <v>30.61283094628035</v>
+      </c>
+      <c r="N910" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O910" t="n">
+        <v>0</v>
+      </c>
+      <c r="P910" t="inlineStr">
+        <is>
+          <t>BB%B=1.06 (extreme=1.19); RSI=74.7 (extreme=0.37); Wick ratio=4.23; ADX H1=19.4 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q910" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (39 นาทีหลัง) — block signal EU</t>
+        </is>
+      </c>
+      <c r="R910" t="inlineStr">
+        <is>
+          <t>[0.7467, 0.0, -1.0, -0.886, 1.0, -1.0, 1.6286, 0.4933, 0.4635, 0.0391, 1.0, 0.2893, 0.7243, 1.0567, 0.2663, 3.0, 0.1796, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4213, 0.0, 0.0, 0.0, 0.0, 0.0188, 0.8407, 0.8254, 0.3668]</t>
+        </is>
+      </c>
+      <c r="S910" t="n">
+        <v>0</v>
+      </c>
+      <c r="T910" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:09:26.921962+00:00</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D911" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E911" t="n">
+        <v>86.92831397301296</v>
+      </c>
+      <c r="F911" t="n">
+        <v>0.0005050051217917954</v>
+      </c>
+      <c r="G911" t="n">
+        <v>1</v>
+      </c>
+      <c r="H911" t="n">
+        <v>0.5782687572891021</v>
+      </c>
+      <c r="I911" t="n">
+        <v>0.5406860192764515</v>
+      </c>
+      <c r="J911" t="n">
+        <v>1</v>
+      </c>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L911" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M911" t="n">
+        <v>30.61283094628035</v>
+      </c>
+      <c r="N911" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O911" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P911" t="inlineStr">
+        <is>
+          <t>BB%B=1.09 (extreme=1.29); RSI=75.5 (extreme=0.39); Wick ratio=2.24; ADX H1=27.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q911" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (39 นาทีหลัง) — block signal NZ</t>
+        </is>
+      </c>
+      <c r="R911" t="inlineStr">
+        <is>
+          <t>[0.7386, 0.0, -1.0, -0.995, 1.0, -1.0, 2.0, 0.5101, 0.4147, 0.1877, 1.0, 0.2006, 0.7352, 1.0866, -0.0178, 3.0, 0.0942, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5988, 0.0, 0.0, 0.0, 0.0, 0.0188, 0.8052, 0.7504, 0.5089]</t>
+        </is>
+      </c>
+      <c r="S911" t="n">
+        <v>0</v>
+      </c>
+      <c r="T911" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:09:27.743589+00:00</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D912" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E912" t="n">
+        <v>85.70031188916042</v>
+      </c>
+      <c r="F912" t="n">
+        <v>0.08530269557429296</v>
+      </c>
+      <c r="G912" t="n">
+        <v>1</v>
+      </c>
+      <c r="H912" t="n">
+        <v>0.5954485850852329</v>
+      </c>
+      <c r="I912" t="n">
+        <v>0.5479778097423761</v>
+      </c>
+      <c r="J912" t="n">
+        <v>1</v>
+      </c>
+      <c r="K912" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L912" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M912" t="n">
+        <v>30.61283094628035</v>
+      </c>
+      <c r="N912" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O912" t="n">
+        <v>1.10000000000241</v>
+      </c>
+      <c r="P912" t="inlineStr">
+        <is>
+          <t>BB%B=1.05 (extreme=1.16); RSI=71.4 (extreme=0.29); Wick ratio=14.00; ADX H1=22.9 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q912" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=185.46200 &lt; C=185.46300) — SELL needs beari</t>
+        </is>
+      </c>
+      <c r="R912" t="inlineStr">
+        <is>
+          <t>[0.714, 0.0, -1.0, -0.647, 1.0, -1.0, 1.7584, 0.428, 0.4648, 0.048, 1.0, 0.3022, 0.7695, 1.0488, 0.2569, 2.3798, 0.1685, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.3956, 0.0, 0.0, 0.0, 0.0, 0.0188, 0.7027, 0.6646, 0.3715]</t>
+        </is>
+      </c>
+      <c r="S912" t="n">
+        <v>0</v>
+      </c>
+      <c r="T912" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:10:28.753116+00:00</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D913" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E913" t="n">
+        <v>87.50103391165754</v>
+      </c>
+      <c r="F913" t="n">
+        <v>0.0005050051217917954</v>
+      </c>
+      <c r="G913" t="n">
+        <v>1</v>
+      </c>
+      <c r="H913" t="n">
+        <v>0.6182242082766661</v>
+      </c>
+      <c r="I913" t="n">
+        <v>0.5500213381448467</v>
+      </c>
+      <c r="J913" t="n">
+        <v>1</v>
+      </c>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L913" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M913" t="n">
+        <v>30.61283094628035</v>
+      </c>
+      <c r="N913" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O913" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P913" t="inlineStr">
+        <is>
+          <t>BB%B=1.07 (extreme=1.23); RSI=75.0 (extreme=0.38); Wick ratio=4.50; ADX H1=27.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q913" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (40 นาทีหลัง) — block signal NZ</t>
+        </is>
+      </c>
+      <c r="R913" t="inlineStr">
+        <is>
+          <t>[0.75, 0.0, -1.0, -0.995, 1.0, -1.0, 2.0, 0.5, 0.4059, 0.1868, 1.0, 0.2006, 0.6864, 1.0701, -0.0178, 3.0, 0.1685, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5988, 0.0, 0.0, 0.0, 0.0, 0.0208, 0.7716, 0.742, 0.5089]</t>
+        </is>
+      </c>
+      <c r="S913" t="n">
+        <v>0</v>
+      </c>
+      <c r="T913" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:10:29.410361+00:00</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D914" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E914" t="n">
+        <v>87.1071266889948</v>
+      </c>
+      <c r="F914" t="n">
+        <v>0.0006147252633409121</v>
+      </c>
+      <c r="G914" t="n">
+        <v>1</v>
+      </c>
+      <c r="H914" t="n">
+        <v>0.6239275040971753</v>
+      </c>
+      <c r="I914" t="n">
+        <v>0.5530174401864634</v>
+      </c>
+      <c r="J914" t="n">
+        <v>1</v>
+      </c>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L914" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M914" t="n">
+        <v>30.61283094628035</v>
+      </c>
+      <c r="N914" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O914" t="n">
+        <v>0</v>
+      </c>
+      <c r="P914" t="inlineStr">
+        <is>
+          <t>BB%B=1.04 (extreme=1.14); RSI=74.2 (extreme=0.36); Wick ratio=12.60; ADX H1=19.4 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q914" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (40 นาทีหลัง) — block signal EU</t>
+        </is>
+      </c>
+      <c r="R914" t="inlineStr">
+        <is>
+          <t>[0.7421, 0.0, -1.0, -0.8853, 1.0, -1.0, 1.6267, 0.4843, 0.4547, 0.0396, 1.0, 0.2893, 0.6842, 1.0419, 0.2678, 3.0, 0.1796, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4213, 0.0, 0.0, 0.0, 0.0, 0.0208, 0.8081, 0.8165, 0.3661]</t>
+        </is>
+      </c>
+      <c r="S914" t="n">
+        <v>0</v>
+      </c>
+      <c r="T914" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:10:30.094185+00:00</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D915" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E915" t="n">
+        <v>84.97681299459958</v>
+      </c>
+      <c r="F915" t="n">
+        <v>0.08623126734239527</v>
+      </c>
+      <c r="G915" t="n">
+        <v>1</v>
+      </c>
+      <c r="H915" t="n">
+        <v>0.575399320840146</v>
+      </c>
+      <c r="I915" t="n">
+        <v>0.5399463742839169</v>
+      </c>
+      <c r="J915" t="n">
+        <v>1</v>
+      </c>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L915" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M915" t="n">
+        <v>30.61283094628035</v>
+      </c>
+      <c r="N915" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O915" t="n">
+        <v>0.9999999999990905</v>
+      </c>
+      <c r="P915" t="inlineStr">
+        <is>
+          <t>BB%B=1.03 (extreme=1.09); RSI=70.0 (extreme=0.25); Wick ratio=6.00; ADX H1=22.9 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q915" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC slope: 0.65 &gt; 0.15 — EMA rising too fast for SELL</t>
+        </is>
+      </c>
+      <c r="R915" t="inlineStr">
+        <is>
+          <t>[0.6995, 0.0, -1.0, -0.6377, 1.0, -1.0, 1.7395, 0.3991, 0.4495, 0.0486, 1.0, 0.3022, 0.7119, 1.0275, 0.2702, 2.1918, 0.0942, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.3956, 0.0, 0.0, 0.0, 0.0, 0.0208, 0.6557, 0.6476, 0.3649]</t>
+        </is>
+      </c>
+      <c r="S915" t="n">
+        <v>0</v>
+      </c>
+      <c r="T915" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:11:31.113265+00:00</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D916" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E916" t="n">
+        <v>86.54978766005135</v>
+      </c>
+      <c r="F916" t="n">
+        <v>0.0006168681212672994</v>
+      </c>
+      <c r="G916" t="n">
+        <v>1</v>
+      </c>
+      <c r="H916" t="n">
+        <v>0.5954485850852329</v>
+      </c>
+      <c r="I916" t="n">
+        <v>0.5472775074835279</v>
+      </c>
+      <c r="J916" t="n">
+        <v>1</v>
+      </c>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L916" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M916" t="n">
+        <v>30.61283094628034</v>
+      </c>
+      <c r="N916" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O916" t="n">
+        <v>0.09999999999843467</v>
+      </c>
+      <c r="P916" t="inlineStr">
+        <is>
+          <t>BB%B=1.02 (extreme=1.08); RSI=73.1 (extreme=0.33); Wick ratio=13.60; ADX H1=19.4 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q916" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (42 นาทีหลัง) — block signal EU</t>
+        </is>
+      </c>
+      <c r="R916" t="inlineStr">
+        <is>
+          <t>[0.731, 0.0, -1.0, -0.8831, 1.0, -1.0, 1.6211, 0.462, 0.4428, 0.0403, 1.0, 0.2893, 0.6341, 1.0228, 0.2721, 3.0, 0.1565, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4213, 0.0, 0.0, 0.0, 0.0, 0.0229, 0.766, 0.8039, 0.364]</t>
+        </is>
+      </c>
+      <c r="S916" t="n">
+        <v>0</v>
+      </c>
+      <c r="T916" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:11:31.922655+00:00</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D917" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E917" t="n">
+        <v>84.57483189814087</v>
+      </c>
+      <c r="F917" t="n">
+        <v>0.08623126734239527</v>
+      </c>
+      <c r="G917" t="n">
+        <v>1</v>
+      </c>
+      <c r="H917" t="n">
+        <v>0.575399320840146</v>
+      </c>
+      <c r="I917" t="n">
+        <v>0.5399463742839169</v>
+      </c>
+      <c r="J917" t="n">
+        <v>1</v>
+      </c>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L917" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M917" t="n">
+        <v>30.61283094628034</v>
+      </c>
+      <c r="N917" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O917" t="n">
+        <v>1.10000000000241</v>
+      </c>
+      <c r="P917" t="inlineStr">
+        <is>
+          <t>BB%B=1.02 (extreme=1.06); RSI=69.1 (extreme=0.23); Wick ratio=3.53; ADX H1=22.9 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q917" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=185.43800 &lt; C=185.44700) — SELL needs beari</t>
+        </is>
+      </c>
+      <c r="R917" t="inlineStr">
+        <is>
+          <t>[0.6915, 0.0, -1.0, -0.6377, 1.0, -1.0, 1.7395, 0.383, 0.4443, 0.0489, 1.0, 0.3022, 0.6831, 1.0166, 0.2702, 2.1106, 0.0942, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.3956, 0.0, 0.0, 0.0, 0.0, 0.0229, 0.6361, 0.6427, 0.3649]</t>
+        </is>
+      </c>
+      <c r="S917" t="n">
+        <v>0</v>
+      </c>
+      <c r="T917" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:12:32.862322+00:00</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D918" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E918" t="n">
+        <v>86.79176479507321</v>
+      </c>
+      <c r="F918" t="n">
+        <v>0.0005121479815464249</v>
+      </c>
+      <c r="G918" t="n">
+        <v>1</v>
+      </c>
+      <c r="H918" t="n">
+        <v>0.5470931708555471</v>
+      </c>
+      <c r="I918" t="n">
+        <v>0.5326087265649753</v>
+      </c>
+      <c r="J918" t="n">
+        <v>1</v>
+      </c>
+      <c r="K918" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L918" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M918" t="n">
+        <v>30.61283094628034</v>
+      </c>
+      <c r="N918" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O918" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P918" t="inlineStr">
+        <is>
+          <t>BB%B=1.04 (extreme=1.13); RSI=73.6 (extreme=0.34); Wick ratio=18.33; ADX H1=27.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q918" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (43 นาทีหลัง) — block signal NZ</t>
+        </is>
+      </c>
+      <c r="R918" t="inlineStr">
+        <is>
+          <t>[0.7358, 0.0, -1.0, -0.9879, 1.0, -1.0, 2.0, 0.4717, 0.384, 0.1851, 1.0, 0.2006, 0.5958, 1.0378, -0.0042, 3.0, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5988, 0.0, 0.0, 0.0, 0.0, 0.025, 0.6993, 0.7162, 0.5021]</t>
+        </is>
+      </c>
+      <c r="S918" t="n">
+        <v>0</v>
+      </c>
+      <c r="T918" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:12:33.526470+00:00</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D919" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E919" t="n">
+        <v>86.06734591093459</v>
+      </c>
+      <c r="F919" t="n">
+        <v>0.0006268681249237838</v>
+      </c>
+      <c r="G919" t="n">
+        <v>1</v>
+      </c>
+      <c r="H919" t="n">
+        <v>0.5376988297946883</v>
+      </c>
+      <c r="I919" t="n">
+        <v>0.5305005236759699</v>
+      </c>
+      <c r="J919" t="n">
+        <v>0.726165771484375</v>
+      </c>
+      <c r="K919" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L919" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M919" t="n">
+        <v>30.61283094628034</v>
+      </c>
+      <c r="N919" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O919" t="n">
+        <v>0</v>
+      </c>
+      <c r="P919" t="inlineStr">
+        <is>
+          <t>BB%B=1.01 (extreme=1.04); RSI=72.1 (extreme=0.30); Wick ratio=6.18; ADX H1=19.4 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q919" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (43 นาทีหลัง) — block signal EU</t>
+        </is>
+      </c>
+      <c r="R919" t="inlineStr">
+        <is>
+          <t>[0.7213, 0.0, -1.0, -0.8731, 1.0, -1.0, 1.5952, 0.4427, 0.4296, 0.0407, 1.0, 0.2893, 0.604, 1.011, 0.2922, 2.9512, 0.0566, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4213, 0.0, 0.0, 0.0, 0.0, 0.025, 0.7306, 0.7852, 0.3539]</t>
+        </is>
+      </c>
+      <c r="S919" t="n">
+        <v>0</v>
+      </c>
+      <c r="T919" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:12:34.323882+00:00</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D920" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E920" t="n">
+        <v>84.40536892204774</v>
+      </c>
+      <c r="F920" t="n">
+        <v>0.08708841051295094</v>
+      </c>
+      <c r="G920" t="n">
+        <v>1</v>
+      </c>
+      <c r="H920" t="n">
+        <v>0.575399320840146</v>
+      </c>
+      <c r="I920" t="n">
+        <v>0.5399463742839169</v>
+      </c>
+      <c r="J920" t="n">
+        <v>1</v>
+      </c>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L920" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M920" t="n">
+        <v>30.61283094628034</v>
+      </c>
+      <c r="N920" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O920" t="n">
+        <v>0.9999999999990905</v>
+      </c>
+      <c r="P920" t="inlineStr">
+        <is>
+          <t>BB%B=1.01 (extreme=1.04); RSI=68.8 (extreme=0.22); Wick ratio=3.00; ADX H1=22.9 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q920" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC slope: 0.63 &gt; 0.15 — EMA rising too fast for SELL</t>
+        </is>
+      </c>
+      <c r="R920" t="inlineStr">
+        <is>
+          <t>[0.6881, 0.0, -1.0, -0.6291, 1.0, -1.0, 1.7224, 0.3762, 0.4377, 0.049, 1.0, 0.3022, 0.6708, 1.0119, 0.2826, 2.0554, 0.0942, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.3956, 0.0, 0.0, 0.0, 0.0, 0.025, 0.6215, 0.6343, 0.3587]</t>
+        </is>
+      </c>
+      <c r="S920" t="n">
+        <v>0</v>
+      </c>
+      <c r="T920" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:13:35.392102+00:00</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D921" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E921" t="n">
+        <v>85.41673367141085</v>
+      </c>
+      <c r="F921" t="n">
+        <v>0.0005157194114237396</v>
+      </c>
+      <c r="G921" t="n">
+        <v>1</v>
+      </c>
+      <c r="H921" t="n">
+        <v>0.5376988297946883</v>
+      </c>
+      <c r="I921" t="n">
+        <v>0.5298392245199637</v>
+      </c>
+      <c r="J921" t="n">
+        <v>1</v>
+      </c>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L921" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M921" t="n">
+        <v>30.61283094628034</v>
+      </c>
+      <c r="N921" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O921" t="n">
+        <v>0.5000000000010552</v>
+      </c>
+      <c r="P921" t="inlineStr">
+        <is>
+          <t>BB%B=1.00 (extreme=1.01); RSI=70.8 (extreme=0.27); Wick ratio=3.44; ADX H1=27.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q921" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (44 นาทีหลัง) — block signal NZ</t>
+        </is>
+      </c>
+      <c r="R921" t="inlineStr">
+        <is>
+          <t>[0.7083, 0.0, -1.0, -0.9843, 1.0, -1.0, 2.0, 0.4167, 0.3653, 0.1834, 1.0, 0.2006, 0.5052, 1.0034, 0.0026, 2.9861, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5988, 0.0, 0.0, 0.0, 0.0, 0.0271, 0.6333, 0.696, 0.4987]</t>
+        </is>
+      </c>
+      <c r="S921" t="n">
+        <v>0</v>
+      </c>
+      <c r="T921" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:13:36.273739+00:00</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D922" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E922" t="n">
+        <v>79.85955325035519</v>
+      </c>
+      <c r="F922" t="n">
+        <v>0.0006375824145557202</v>
+      </c>
+      <c r="G922" t="n">
+        <v>1</v>
+      </c>
+      <c r="H922" t="n">
+        <v>0.5470931708555471</v>
+      </c>
+      <c r="I922" t="n">
+        <v>0.5335061230844375</v>
+      </c>
+      <c r="J922" t="n">
+        <v>1</v>
+      </c>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L922" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M922" t="n">
+        <v>30.61283094628034</v>
+      </c>
+      <c r="N922" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O922" t="n">
+        <v>0</v>
+      </c>
+      <c r="P922" t="inlineStr">
+        <is>
+          <t>BB%B=0.97 (extreme=0.89); RSI=68.9 (extreme=0.22); Wick ratio=2.12; ADX H1=19.4 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q922" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (44 นาทีหลัง) — block signal EU</t>
+        </is>
+      </c>
+      <c r="R922" t="inlineStr">
+        <is>
+          <t>[0.5972, 0.0, -1.0, -0.8624, 0.892, -1.0, 1.5684, 0.379, 0.4013, 0.0422, 1.0, 0.2893, 0.4987, 0.9676, 0.3137, 2.5722, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4213, 0.0, 0.0, 0.0, 0.0, 0.0271, 0.6385, 0.7521, 0.3432]</t>
+        </is>
+      </c>
+      <c r="S922" t="n">
+        <v>0</v>
+      </c>
+      <c r="T922" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:13:36.889572+00:00</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D923" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E923" t="n">
+        <v>75.93017386510033</v>
+      </c>
+      <c r="F923" t="n">
+        <v>0.0875884106957754</v>
+      </c>
+      <c r="G923" t="n">
+        <v>1</v>
+      </c>
+      <c r="H923" t="n">
+        <v>0.5329623982091302</v>
+      </c>
+      <c r="I923" t="n">
+        <v>0.5258324420657028</v>
+      </c>
+      <c r="J923" t="n">
+        <v>0.07546883076429367</v>
+      </c>
+      <c r="K923" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L923" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M923" t="n">
+        <v>30.61283094628034</v>
+      </c>
+      <c r="N923" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O923" t="n">
+        <v>0.9999999999990905</v>
+      </c>
+      <c r="P923" t="inlineStr">
+        <is>
+          <t>BB%B=0.98 (extreme=0.92); RSI=66.4 (extreme=0.16); Wick ratio=1.43; ADX H1=22.9 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q923" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=185.41500 &lt; C=185.41700) — SELL needs beari</t>
+        </is>
+      </c>
+      <c r="R923" t="inlineStr">
+        <is>
+          <t>[0.5186, 0.0, -1.0, -0.6241, 0.9192, -1.0, 1.7126, 0.3285, 0.4192, 0.05, 1.0, 0.3022, 0.5802, 0.9758, 0.2897, 1.7925, 0.0125, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.3956, 0.0, 0.0, 0.0, 0.0, 0.0271, 0.557, 0.6154, 0.3551]</t>
+        </is>
+      </c>
+      <c r="S923" t="n">
+        <v>0</v>
+      </c>
+      <c r="T923" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:14:37.862556+00:00</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D924" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E924" t="n">
+        <v>85.82874594620829</v>
+      </c>
+      <c r="F924" t="n">
+        <v>0.0005157194114237396</v>
+      </c>
+      <c r="G924" t="n">
+        <v>1</v>
+      </c>
+      <c r="H924" t="n">
+        <v>0.5376988297946883</v>
+      </c>
+      <c r="I924" t="n">
+        <v>0.5298392245199637</v>
+      </c>
+      <c r="J924" t="n">
+        <v>1</v>
+      </c>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L924" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M924" t="n">
+        <v>30.61283094628034</v>
+      </c>
+      <c r="N924" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O924" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P924" t="inlineStr">
+        <is>
+          <t>BB%B=1.01 (extreme=1.05); RSI=71.7 (extreme=0.29); Wick ratio=4.58; ADX H1=27.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q924" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (45 นาทีหลัง) — block signal NZ</t>
+        </is>
+      </c>
+      <c r="R924" t="inlineStr">
+        <is>
+          <t>[0.7166, 0.0, -1.0, -0.9843, 1.0, -1.0, 2.0, 0.4331, 0.3702, 0.1839, 1.0, 0.2006, 0.5331, 1.0143, 0.0026, 3.0, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5988, 0.0, 0.0, 0.0, 0.0, 0.0292, 0.6521, 0.7007, 0.4987]</t>
+        </is>
+      </c>
+      <c r="S924" t="n">
+        <v>0</v>
+      </c>
+      <c r="T924" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:14:38.574996+00:00</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D925" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E925" t="n">
+        <v>83.22937240396396</v>
+      </c>
+      <c r="F925" t="n">
+        <v>0.0006382967005311879</v>
+      </c>
+      <c r="G925" t="n">
+        <v>1</v>
+      </c>
+      <c r="H925" t="n">
+        <v>0.5470931708555471</v>
+      </c>
+      <c r="I925" t="n">
+        <v>0.5335061230844375</v>
+      </c>
+      <c r="J925" t="n">
+        <v>1</v>
+      </c>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L925" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M925" t="n">
+        <v>30.61283094628034</v>
+      </c>
+      <c r="N925" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O925" t="n">
+        <v>0</v>
+      </c>
+      <c r="P925" t="inlineStr">
+        <is>
+          <t>BB%B=0.98 (extreme=0.94); RSI=70.0 (extreme=0.25); Wick ratio=2.72; ADX H1=19.4 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q925" t="inlineStr">
+        <is>
+          <t>risk_manager:📰 ⚠️ Core PCE Price Index m/m [USD] (45 นาทีหลัง) — block signal EU</t>
+        </is>
+      </c>
+      <c r="R925" t="inlineStr">
+        <is>
+          <t>[0.6646, 0.0, -1.0, -0.8617, 0.9413, -1.0, 1.5667, 0.3996, 0.4079, 0.0417, 1.0, 0.2893, 0.5338, 0.9824, 0.3151, 2.679, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4213, 0.0, 0.0, 0.0, 0.0, 0.0292, 0.6643, 0.7579, 0.3424]</t>
+        </is>
+      </c>
+      <c r="S925" t="n">
+        <v>0</v>
+      </c>
+      <c r="T925" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:14:39.327194+00:00</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D926" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E926" t="n">
+        <v>82.5740182710304</v>
+      </c>
+      <c r="F926" t="n">
+        <v>0.08787412508595994</v>
+      </c>
+      <c r="G926" t="n">
+        <v>1</v>
+      </c>
+      <c r="H926" t="n">
+        <v>0.575399320840146</v>
+      </c>
+      <c r="I926" t="n">
+        <v>0.5399463742839169</v>
+      </c>
+      <c r="J926" t="n">
+        <v>1</v>
+      </c>
+      <c r="K926" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L926" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M926" t="n">
+        <v>30.61283094628034</v>
+      </c>
+      <c r="N926" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O926" t="n">
+        <v>1.099999999999568</v>
+      </c>
+      <c r="P926" t="inlineStr">
+        <is>
+          <t>BB%B=1.00 (extreme=1.00); RSI=67.9 (extreme=0.20); Wick ratio=2.14; ADX H1=22.9 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q926" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC filter: dist 0.59 &lt; 0.6 — price not overextended up</t>
+        </is>
+      </c>
+      <c r="R926" t="inlineStr">
+        <is>
+          <t>[0.6515, 0.0, -1.0, -0.6213, 0.9966, -1.0, 1.707, 0.3585, 0.428, 0.0494, 1.0, 0.3022, 0.6379, 0.999, 0.2938, 1.946, 0.0942, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.3956, 0.0, 0.0, 0.0, 0.0, 0.0292, 0.5938, 0.6231, 0.3531]</t>
+        </is>
+      </c>
+      <c r="S926" t="n">
+        <v>0</v>
+      </c>
+      <c r="T926" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:15:40.472592+00:00</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D927" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E927" t="n">
+        <v>77.73551374746276</v>
+      </c>
+      <c r="F927" t="n">
+        <v>0.0004914843495025632</v>
+      </c>
+      <c r="G927" t="n">
+        <v>1</v>
+      </c>
+      <c r="H927" t="n">
+        <v>0.5062639137456895</v>
+      </c>
+      <c r="I927" t="n">
+        <v>0.5180051254863425</v>
+      </c>
+      <c r="J927" t="n">
+        <v>1</v>
+      </c>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L927" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M927" t="n">
+        <v>30.61283094628034</v>
+      </c>
+      <c r="N927" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O927" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P927" t="inlineStr">
+        <is>
+          <t>BB%B=0.93 (extreme=0.76); RSI=69.8 (extreme=0.25); Wick ratio=10.00; ADX H1=27.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q927" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC filter: dist 0.58 &lt; 0.6 — price not overextended up</t>
+        </is>
+      </c>
+      <c r="R927" t="inlineStr">
+        <is>
+          <t>[0.5547, 0.0, -1.0, -1.0085, 0.7607, -1.0, 2.0, 0.3966, 0.3605, 0.1955, 1.0, 0.2244, 0.4704, 0.9282, -0.0455, 2.3399, 0.0566, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5511, 0.0, 0.0, 0.0, 0.0, 0.0312, 0.5817, 0.8001, 0.5227]</t>
+        </is>
+      </c>
+      <c r="S927" t="n">
+        <v>0</v>
+      </c>
+      <c r="T927" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:16:41.469711+00:00</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D928" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E928" t="n">
+        <v>77.34683194064799</v>
+      </c>
+      <c r="F928" t="n">
+        <v>0.0004914843495025632</v>
+      </c>
+      <c r="G928" t="n">
+        <v>1</v>
+      </c>
+      <c r="H928" t="n">
+        <v>0.5062639137456895</v>
+      </c>
+      <c r="I928" t="n">
+        <v>0.5180051254863425</v>
+      </c>
+      <c r="J928" t="n">
+        <v>1</v>
+      </c>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L928" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M928" t="n">
+        <v>30.61283094628034</v>
+      </c>
+      <c r="N928" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O928" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P928" t="inlineStr">
+        <is>
+          <t>BB%B=0.93 (extreme=0.75); RSI=69.6 (extreme=0.24); Wick ratio=5.00; ADX H1=27.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q928" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=0.59055 &lt; C=0.59059) — SELL needs bearish c</t>
+        </is>
+      </c>
+      <c r="R928" t="inlineStr">
+        <is>
+          <t>[0.5469, 0.0, -1.0, -1.0085, 0.7513, -1.0, 2.0, 0.3923, 0.3592, 0.1954, 1.0, 0.2244, 0.4634, 0.9254, -0.0455, 2.3195, 0.0566, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5511, 0.0, 0.0, 0.0, 0.0, 0.0333, 0.5768, 0.7989, 0.5227]</t>
+        </is>
+      </c>
+      <c r="S928" t="n">
+        <v>0</v>
+      </c>
+      <c r="T928" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:17:42.470946+00:00</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D929" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E929" t="n">
+        <v>78.38867775750279</v>
+      </c>
+      <c r="F929" t="n">
+        <v>0.0004921986354780309</v>
+      </c>
+      <c r="G929" t="n">
+        <v>1</v>
+      </c>
+      <c r="H929" t="n">
+        <v>0.5062639137456895</v>
+      </c>
+      <c r="I929" t="n">
+        <v>0.5180051254863425</v>
+      </c>
+      <c r="J929" t="n">
+        <v>1</v>
+      </c>
+      <c r="K929" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L929" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M929" t="n">
+        <v>30.61283094628034</v>
+      </c>
+      <c r="N929" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O929" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P929" t="inlineStr">
+        <is>
+          <t>BB%B=0.93 (extreme=0.78); RSI=70.0 (extreme=0.25); Wick ratio=9.00; ADX H1=27.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q929" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC filter: dist 0.59 &lt; 0.6 — price not overextended up</t>
+        </is>
+      </c>
+      <c r="R929" t="inlineStr">
+        <is>
+          <t>[0.5678, 0.0, -1.0, -1.0078, 0.7794, -1.0, 2.0, 0.4003, 0.3625, 0.1958, 1.0, 0.2241, 0.4843, 0.9338, -0.0441, 2.3771, 0.0566, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5518, 0.0, 0.0, 0.0, 0.0, 0.0354, 0.5907, 0.8014, 0.5221]</t>
+        </is>
+      </c>
+      <c r="S929" t="n">
+        <v>0</v>
+      </c>
+      <c r="T929" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:23:46.020724+00:00</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D930" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E930" t="n">
+        <v>75.02768108312178</v>
+      </c>
+      <c r="F930" t="n">
+        <v>0.0005014843531590476</v>
+      </c>
+      <c r="G930" t="n">
+        <v>1</v>
+      </c>
+      <c r="H930" t="n">
+        <v>0.5124386825508059</v>
+      </c>
+      <c r="I930" t="n">
+        <v>0.5183447420129407</v>
+      </c>
+      <c r="J930" t="n">
+        <v>1</v>
+      </c>
+      <c r="K930" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L930" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M930" t="n">
+        <v>30.61283094628034</v>
+      </c>
+      <c r="N930" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O930" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P930" t="inlineStr">
+        <is>
+          <t>BB%B=0.96 (extreme=0.87); RSI=70.9 (extreme=0.27); Wick ratio=1.09; ADX H1=27.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q930" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=0.59067 &lt; C=0.59072) — SELL needs bearish c</t>
+        </is>
+      </c>
+      <c r="R930" t="inlineStr">
+        <is>
+          <t>[0.5006, 0.0, -1.0, -0.9985, 0.8708, -1.0, 2.0, 0.4179, 0.3686, 0.1971, 1.0, 0.2241, 0.554, 0.9613, -0.0264, 2.5325, 0.0566, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5518, 0.0, 0.0, 0.0, 0.0, 0.0479, 0.6281, 0.7987, 0.5132]</t>
+        </is>
+      </c>
+      <c r="S930" t="n">
+        <v>0</v>
+      </c>
+      <c r="T930" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:27:48.373602+00:00</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D931" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E931" t="n">
+        <v>76.09086170328622</v>
+      </c>
+      <c r="F931" t="n">
+        <v>0.0006154081562013378</v>
+      </c>
+      <c r="G931" t="n">
+        <v>1</v>
+      </c>
+      <c r="H931" t="n">
+        <v>0.5329623982091302</v>
+      </c>
+      <c r="I931" t="n">
+        <v>0.5270151757539335</v>
+      </c>
+      <c r="J931" t="n">
+        <v>1</v>
+      </c>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L931" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M931" t="n">
+        <v>30.61283094628034</v>
+      </c>
+      <c r="N931" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O931" t="n">
+        <v>0</v>
+      </c>
+      <c r="P931" t="inlineStr">
+        <is>
+          <t>BB%B=0.92 (extreme=0.72); RSI=68.8 (extreme=0.22); Wick ratio=2.50; ADX H1=19.4 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q931" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC slope: 0.85 &gt; 0.15 — EMA rising too fast for SELL</t>
+        </is>
+      </c>
+      <c r="R931" t="inlineStr">
+        <is>
+          <t>[0.5218, 0.0, -1.0, -0.8846, 0.7232, -1.0, 1.6249, 0.3758, 0.3961, 0.0311, 1.0, 0.312, 0.5138, 0.917, 0.2576, 2.3399, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.376, 0.0, 0.0, 0.0, 0.0, 0.0562, 0.615, 0.8457, 0.3712]</t>
+        </is>
+      </c>
+      <c r="S931" t="n">
+        <v>0</v>
+      </c>
+      <c r="T931" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:28:49.405685+00:00</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D932" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E932" t="n">
+        <v>75.59829151728952</v>
+      </c>
+      <c r="F932" t="n">
+        <v>0.0006161224421768055</v>
+      </c>
+      <c r="G932" t="n">
+        <v>1</v>
+      </c>
+      <c r="H932" t="n">
+        <v>0.5329623982091302</v>
+      </c>
+      <c r="I932" t="n">
+        <v>0.5270151757539335</v>
+      </c>
+      <c r="J932" t="n">
+        <v>1</v>
+      </c>
+      <c r="K932" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L932" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M932" t="n">
+        <v>30.61283094628034</v>
+      </c>
+      <c r="N932" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O932" t="n">
+        <v>0</v>
+      </c>
+      <c r="P932" t="inlineStr">
+        <is>
+          <t>BB%B=0.91 (extreme=0.71); RSI=68.7 (extreme=0.22); Wick ratio=3.67; ADX H1=19.4 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q932" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC slope: 0.84 &gt; 0.15 — EMA rising too fast for SELL</t>
+        </is>
+      </c>
+      <c r="R932" t="inlineStr">
+        <is>
+          <t>[0.512, 0.0, -1.0, -0.8839, 0.7091, -1.0, 1.6231, 0.3731, 0.3936, 0.0313, 1.0, 0.3117, 0.5038, 0.9127, 0.2591, 2.3047, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.3765, 0.0, 0.0, 0.0, 0.0, 0.0583, 0.6064, 0.8427, 0.3705]</t>
+        </is>
+      </c>
+      <c r="S932" t="n">
+        <v>0</v>
+      </c>
+      <c r="T932" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:29:50.375619+00:00</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D933" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E933" t="n">
+        <v>76.67115143794197</v>
+      </c>
+      <c r="F933" t="n">
+        <v>0.08545454440926449</v>
+      </c>
+      <c r="G933" t="n">
+        <v>1</v>
+      </c>
+      <c r="H933" t="n">
+        <v>0.5782687572891021</v>
+      </c>
+      <c r="I933" t="n">
+        <v>0.5414550494537336</v>
+      </c>
+      <c r="J933" t="n">
+        <v>1</v>
+      </c>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L933" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M933" t="n">
+        <v>30.61283094628034</v>
+      </c>
+      <c r="N933" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O933" t="n">
+        <v>1.099999999999568</v>
+      </c>
+      <c r="P933" t="inlineStr">
+        <is>
+          <t>BB%B=0.93 (extreme=0.77); RSI=67.2 (extreme=0.18); Wick ratio=3.88; ADX H1=22.9 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q933" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=185.40600 &lt; C=185.40900) — SELL needs beari</t>
+        </is>
+      </c>
+      <c r="R933" t="inlineStr">
+        <is>
+          <t>[0.5334, 0.0, -1.0, -0.6455, 0.7684, -1.0, 1.7553, 0.3447, 0.4224, 0.041, 1.0, 0.3187, 0.6255, 0.9305, 0.2493, 2.1532, 0.1796, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.3627, 0.0, 0.0, 0.0, 0.0, 0.0604, 0.5492, 0.7065, 0.3754]</t>
+        </is>
+      </c>
+      <c r="S933" t="n">
+        <v>0</v>
+      </c>
+      <c r="T933" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:29:51.110105+00:00</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D934" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E934" t="n">
+        <v>75.80233288464348</v>
+      </c>
+      <c r="F934" t="n">
+        <v>0.0005071986409627575</v>
+      </c>
+      <c r="G934" t="n">
+        <v>1</v>
+      </c>
+      <c r="H934" t="n">
+        <v>0.5062639137456895</v>
+      </c>
+      <c r="I934" t="n">
+        <v>0.5178802384412138</v>
+      </c>
+      <c r="J934" t="n">
+        <v>1</v>
+      </c>
+      <c r="K934" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L934" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M934" t="n">
+        <v>30.61283094628034</v>
+      </c>
+      <c r="N934" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O934" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P934" t="inlineStr">
+        <is>
+          <t>BB%B=0.97 (extreme=0.92); RSI=71.3 (extreme=0.28); Wick ratio=0.94; ADX H1=27.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q934" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=0.59072 &lt; C=0.59080) — SELL needs bearish c</t>
+        </is>
+      </c>
+      <c r="R934" t="inlineStr">
+        <is>
+          <t>[0.516, 0.0, -1.0, -0.9928, 0.9152, -1.0, 2.0, 0.4264, 0.3707, 0.1978, 1.0, 0.2241, 0.5889, 0.9746, -0.0155, 2.6025, 0.0566, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5518, 0.0, 0.0, 0.0, 0.0, 0.0604, 0.645, 0.7957, 0.5078]</t>
+        </is>
+      </c>
+      <c r="S934" t="n">
+        <v>0</v>
+      </c>
+      <c r="T934" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:31:52.471909+00:00</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D935" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E935" t="n">
+        <v>77.41208137579898</v>
+      </c>
+      <c r="F935" t="n">
+        <v>0.0004866844413531132</v>
+      </c>
+      <c r="G935" t="n">
+        <v>1</v>
+      </c>
+      <c r="H935" t="n">
+        <v>0.5062639137456895</v>
+      </c>
+      <c r="I935" t="n">
+        <v>0.5168506224670302</v>
+      </c>
+      <c r="J935" t="n">
+        <v>1</v>
+      </c>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L935" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M935" t="n">
+        <v>30.61283094628034</v>
+      </c>
+      <c r="N935" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O935" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P935" t="inlineStr">
+        <is>
+          <t>BB%B=0.92 (extreme=0.73); RSI=71.3 (extreme=0.28); Wick ratio=5.00; ADX H1=27.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q935" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=0.59068 &lt; C=0.59073) — SELL needs bearish c</t>
+        </is>
+      </c>
+      <c r="R935" t="inlineStr">
+        <is>
+          <t>[0.5482, 0.0, -1.0, -1.0133, 0.726, -1.0, 2.0, 0.4253, 0.3585, 0.21, 1.0, 0.246, 0.5819, 0.9178, -0.0544, 2.1575, 0.0566, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5081, 0.0, 0.0, 0.0, 0.0, 0.0646, 0.6088, 0.8778, 0.5272]</t>
+        </is>
+      </c>
+      <c r="S935" t="n">
+        <v>0</v>
+      </c>
+      <c r="T935" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:36:55.140413+00:00</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D936" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E936" t="n">
+        <v>77.09906864254492</v>
+      </c>
+      <c r="F936" t="n">
+        <v>0.0004952558730586702</v>
+      </c>
+      <c r="G936" t="n">
+        <v>1</v>
+      </c>
+      <c r="H936" t="n">
+        <v>0.5062639137456895</v>
+      </c>
+      <c r="I936" t="n">
+        <v>0.5168506224670302</v>
+      </c>
+      <c r="J936" t="n">
+        <v>1</v>
+      </c>
+      <c r="K936" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L936" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M936" t="n">
+        <v>30.61283094628033</v>
+      </c>
+      <c r="N936" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O936" t="n">
+        <v>0.3999999999992898</v>
+      </c>
+      <c r="P936" t="inlineStr">
+        <is>
+          <t>BB%B=0.92 (extreme=0.72); RSI=71.2 (extreme=0.28); Wick ratio=11.00; ADX H1=27.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q936" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=0.59053 &lt; C=0.59059) — SELL needs bearish c</t>
+        </is>
+      </c>
+      <c r="R936" t="inlineStr">
+        <is>
+          <t>[0.542, 0.0, -1.0, -1.0047, 0.717, -1.0, 2.0, 0.4235, 0.351, 0.2099, 1.0, 0.2442, 0.5749, 0.9151, -0.0381, 2.0999, 0.0566, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5117, 0.0, 0.0, 0.0, 0.0, 0.075, 0.5933, 0.8614, 0.5191]</t>
+        </is>
+      </c>
+      <c r="S936" t="n">
+        <v>0</v>
+      </c>
+      <c r="T936" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:42:57.980254+00:00</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D937" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E937" t="n">
+        <v>76.15269110242994</v>
+      </c>
+      <c r="F937" t="n">
+        <v>0.0004952558730586702</v>
+      </c>
+      <c r="G937" t="n">
+        <v>1</v>
+      </c>
+      <c r="H937" t="n">
+        <v>0.5062639137456895</v>
+      </c>
+      <c r="I937" t="n">
+        <v>0.515054277139767</v>
+      </c>
+      <c r="J937" t="n">
+        <v>1</v>
+      </c>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L937" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M937" t="n">
+        <v>30.61283094628033</v>
+      </c>
+      <c r="N937" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O937" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P937" t="inlineStr">
+        <is>
+          <t>BB%B=0.91 (extreme=0.69); RSI=70.9 (extreme=0.27); Wick ratio=6.00; ADX H1=27.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q937" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC filter: dist 0.58 &lt; 0.6 — price not overextended up</t>
+        </is>
+      </c>
+      <c r="R937" t="inlineStr">
+        <is>
+          <t>[0.5231, 0.0, -1.0, -1.0047, 0.6901, -1.0, 2.0, 0.418, 0.3471, 0.2095, 1.0, 0.2442, 0.554, 0.907, -0.0381, 2.0393, 0.0566, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5117, 0.0, 0.0, 0.0, 0.0, 0.0875, 0.5787, 0.8577, 0.5191]</t>
+        </is>
+      </c>
+      <c r="S937" t="n">
+        <v>0</v>
+      </c>
+      <c r="T937" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:44:59.503245+00:00</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D938" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E938" t="n">
+        <v>75.83478242463809</v>
+      </c>
+      <c r="F938" t="n">
+        <v>0.0004952558730586702</v>
+      </c>
+      <c r="G938" t="n">
+        <v>1</v>
+      </c>
+      <c r="H938" t="n">
+        <v>0.5062639137456895</v>
+      </c>
+      <c r="I938" t="n">
+        <v>0.515054277139767</v>
+      </c>
+      <c r="J938" t="n">
+        <v>1</v>
+      </c>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L938" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M938" t="n">
+        <v>30.61283094628033</v>
+      </c>
+      <c r="N938" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O938" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P938" t="inlineStr">
+        <is>
+          <t>BB%B=0.90 (extreme=0.68); RSI=70.8 (extreme=0.27); Wick ratio=4.00; ADX H1=27.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q938" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=0.59067 &lt; C=0.59077) — SELL needs bearish c</t>
+        </is>
+      </c>
+      <c r="R938" t="inlineStr">
+        <is>
+          <t>[0.5167, 0.0, -1.0, -1.0047, 0.681, -1.0, 2.0, 0.4162, 0.3458, 0.2094, 1.0, 0.2442, 0.547, 0.9043, -0.0381, 2.0192, 0.0566, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.5117, 0.0, 0.0, 0.0, 0.0, 0.0917, 0.5738, 0.8565, 0.5191]</t>
+        </is>
+      </c>
+      <c r="S938" t="n">
+        <v>0</v>
+      </c>
+      <c r="T938" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:46:00.705996+00:00</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D939" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E939" t="n">
+        <v>75.80233649203399</v>
+      </c>
+      <c r="F939" t="n">
+        <v>0.08333070476652657</v>
+      </c>
+      <c r="G939" t="n">
+        <v>1</v>
+      </c>
+      <c r="H939" t="n">
+        <v>0.575399320840146</v>
+      </c>
+      <c r="I939" t="n">
+        <v>0.5395535649182325</v>
+      </c>
+      <c r="J939" t="n">
+        <v>0.9316186904907227</v>
+      </c>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L939" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M939" t="n">
+        <v>30.61283094628033</v>
+      </c>
+      <c r="N939" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O939" t="n">
+        <v>1.099999999999568</v>
+      </c>
+      <c r="P939" t="inlineStr">
+        <is>
+          <t>BB%B=0.94 (extreme=0.81); RSI=71.8 (extreme=0.30); Wick ratio=1.50; ADX H1=23.1 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q939" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC slope: 0.87 &gt; 0.15 — EMA rising too fast for SELL</t>
+        </is>
+      </c>
+      <c r="R939" t="inlineStr">
+        <is>
+          <t>[0.516, 0.0, -1.0, -0.6667, 0.8133, -1.0, 1.8001, 0.4361, 0.4738, 0.018, 1.0, 0.3575, 0.9293, 0.944, 0.1998, 1.7761, 0.0942, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.2851, 0.0, 0.0, 0.0, 0.0, 0.0958, 0.7185, 0.8652, 0.4001]</t>
+        </is>
+      </c>
+      <c r="S939" t="n">
+        <v>0</v>
+      </c>
+      <c r="T939" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:47:01.934975+00:00</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D940" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E940" t="n">
+        <v>78.48791123529405</v>
+      </c>
+      <c r="F940" t="n">
+        <v>0.08340213336407322</v>
+      </c>
+      <c r="G940" t="n">
+        <v>1</v>
+      </c>
+      <c r="H940" t="n">
+        <v>0.575399320840146</v>
+      </c>
+      <c r="I940" t="n">
+        <v>0.5395535649182325</v>
+      </c>
+      <c r="J940" t="n">
+        <v>0.3746824860572815</v>
+      </c>
+      <c r="K940" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L940" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M940" t="n">
+        <v>30.61283094628033</v>
+      </c>
+      <c r="N940" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O940" t="n">
+        <v>1.099999999999568</v>
+      </c>
+      <c r="P940" t="inlineStr">
+        <is>
+          <t>BB%B=0.95 (extreme=0.82); RSI=71.9 (extreme=0.30); Wick ratio=2.00; ADX H1=23.1 (block=30.0); SL=0.15000 TP=0.15000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q940" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC slope: 0.87 &gt; 0.15 — EMA rising too fast for SELL</t>
+        </is>
+      </c>
+      <c r="R940" t="inlineStr">
+        <is>
+          <t>[0.5698, 0.0, -1.0, -0.666, 0.8175, -1.0, 1.7985, 0.4385, 0.4741, 0.018, 1.0, 0.3575, 0.9332, 0.9453, 0.2008, 1.7865, 0.0566, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0001, 0.0, 0.2851, 0.0, 0.0, 0.0, 0.0, 0.0979, 0.7208, 0.8652, 0.3996]</t>
+        </is>
+      </c>
+      <c r="S940" t="n">
+        <v>0</v>
+      </c>
+      <c r="T940" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>2026-05-28 13:47:03.025616+00:00</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D941" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E941" t="n">
+        <v>75.73120697714289</v>
+      </c>
+      <c r="F941" t="n">
+        <v>0.1163302804257741</v>
+      </c>
+      <c r="G941" t="n">
+        <v>1</v>
+      </c>
+      <c r="H941" t="n">
+        <v>0.5124386825508059</v>
+      </c>
+      <c r="I941" t="n">
+        <v>0.5186374371165382</v>
+      </c>
+      <c r="J941" t="n">
+        <v>1</v>
+      </c>
+      <c r="K941" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L941" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M941" t="n">
+        <v>30.61283094628033</v>
+      </c>
+      <c r="N941" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O941" t="n">
+        <v>2.199999999999136</v>
+      </c>
+      <c r="P941" t="inlineStr">
+        <is>
+          <t>BB%B=0.93 (extreme=0.77); RSI=65.5 (extreme=0.14); Wick ratio=34.00; ADX H1=23.2 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q941" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC filter: dist 0.48 &lt; 0.6 — price not overextended up</t>
+        </is>
+      </c>
+      <c r="R941" t="inlineStr">
+        <is>
+          <t>[0.5146, 0.0, -1.0, -0.3367, 0.7654, -1.0, 1.7192, 0.3108, 0.3376, 0.0962, 1.0, 0.2039, 0.8742, 0.9296, 0.1768, 1.2293, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0002, 0.0, 0.5921, 0.0, 0.0, 0.0, 0.0, 0.0979, 0.4834, 0.4925, 0.4116]</t>
+        </is>
+      </c>
+      <c r="S941" t="n">
+        <v>0</v>
+      </c>
+      <c r="T941" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>2026-05-28 14:15:13.890809+00:00</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D942" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E942" t="n">
+        <v>78.01924468157704</v>
+      </c>
+      <c r="F942" t="n">
+        <v>0.06504458328851224</v>
+      </c>
+      <c r="G942" t="n">
+        <v>1</v>
+      </c>
+      <c r="H942" t="n">
+        <v>0.4716195685202066</v>
+      </c>
+      <c r="I942" t="n">
+        <v>0.4766177171831362</v>
+      </c>
+      <c r="J942" t="n">
+        <v>0.3345665335655212</v>
+      </c>
+      <c r="K942" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L942" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M942" t="n">
+        <v>29.989580969771</v>
+      </c>
+      <c r="N942" t="inlineStr">
+        <is>
+          <t>NY_AFTERNOON</t>
+        </is>
+      </c>
+      <c r="O942" t="n">
+        <v>0.200000000000955</v>
+      </c>
+      <c r="P942" t="inlineStr">
+        <is>
+          <t>BB%B=-0.07 (extreme=1.24); RSI=33.3 (extreme=0.17); Wick ratio=1.33; ADX H1=25.8 (block=30.0); SL=0.10000 TP=0.10000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q942" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC filter: dist -0.50 &gt; -0.6 — price not overextended down</t>
+        </is>
+      </c>
+      <c r="R942" t="inlineStr">
+        <is>
+          <t>[0.5604, 0.0, 1.0, -0.8496, 1.0, -1.0, 1.5374, -0.3341, -0.1194, 0.0235, 1.0, 0.3198, -0.3654, -0.0732, 0.5195, -1.6297, -0.0568, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.3605, 0.0, 0.0, 0.0, 0.0, 0.1562, -0.5012, -0.2734, 0.2402]</t>
+        </is>
+      </c>
+      <c r="S942" t="n">
+        <v>0</v>
+      </c>
+      <c r="T942" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>2026-05-28 14:17:15.268233+00:00</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D943" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E943" t="n">
+        <v>87.59182544721457</v>
+      </c>
+      <c r="F943" t="n">
+        <v>14.41322586502053</v>
+      </c>
+      <c r="G943" t="n">
+        <v>1</v>
+      </c>
+      <c r="H943" t="n">
+        <v>0.6603960396039604</v>
+      </c>
+      <c r="I943" t="n">
+        <v>0.5580775910430631</v>
+      </c>
+      <c r="J943" t="n">
+        <v>1</v>
+      </c>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L943" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M943" t="n">
+        <v>29.989580969771</v>
+      </c>
+      <c r="N943" t="inlineStr">
+        <is>
+          <t>NY_AFTERNOON</t>
+        </is>
+      </c>
+      <c r="O943" t="n">
+        <v>56.9999999999709</v>
+      </c>
+      <c r="P943" t="inlineStr">
+        <is>
+          <t>BB%B=1.05 (extreme=1.16); RSI=75.2 (extreme=0.38); Wick ratio=6.00; ADX H1=30.0 (block=30.0); SL=14.41323 TP=14.41323 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q943" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=4455.53000 &lt; C=4459.20000) — SELL needs bea</t>
+        </is>
+      </c>
+      <c r="R943" t="inlineStr">
+        <is>
+          <t>[0.7518, 0.0, -1.0, 2.0, 1.0, -1.0, 1.0, 0.5037, 0.5161, 0.4792, 1.0, 0.2686, 0.9245, 1.0479, 0.3831, 2.583, 0.4732, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0004, 0.0, 0.4629, 0.0, 0.0, 0.0, 0.0, 0.1604, 0.9057, 0.8172, 0.3084]</t>
+        </is>
+      </c>
+      <c r="S943" t="n">
+        <v>0</v>
+      </c>
+      <c r="T943" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>2026-05-28 14:17:16.122742+00:00</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D944" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E944" t="n">
+        <v>75.12345467057814</v>
+      </c>
+      <c r="F944" t="n">
+        <v>0.0007989058249307279</v>
+      </c>
+      <c r="G944" t="n">
+        <v>1</v>
+      </c>
+      <c r="H944" t="n">
+        <v>0.5782687572891021</v>
+      </c>
+      <c r="I944" t="n">
+        <v>0.54081376211407</v>
+      </c>
+      <c r="J944" t="n">
+        <v>1</v>
+      </c>
+      <c r="K944" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L944" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M944" t="n">
+        <v>29.989580969771</v>
+      </c>
+      <c r="N944" t="inlineStr">
+        <is>
+          <t>NY_AFTERNOON</t>
+        </is>
+      </c>
+      <c r="O944" t="n">
+        <v>0.1000000000006551</v>
+      </c>
+      <c r="P944" t="inlineStr">
+        <is>
+          <t>BB%B=0.99 (extreme=0.95); RSI=72.6 (extreme=0.32); Wick ratio=0.45; ADX H1=19.9 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q944" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=1.16441 &lt; C=1.16497) — SELL needs bearish c</t>
+        </is>
+      </c>
+      <c r="R944" t="inlineStr">
+        <is>
+          <t>[0.5025, 0.0, -1.0, -0.7011, 0.9515, -1.0, 1.2517, 0.4528, 0.3376, 0.0223, 1.0, 0.3895, 0.7922, 0.9855, 0.5546, 2.0403, 0.1255, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.221, 0.0, 0.0, 0.0, 0.0, 0.1604, 0.759, 0.6986, 0.2227]</t>
+        </is>
+      </c>
+      <c r="S944" t="n">
+        <v>0</v>
+      </c>
+      <c r="T944" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>2026-05-28 14:18:17.227054+00:00</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D945" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E945" t="n">
+        <v>87.50863308925626</v>
+      </c>
+      <c r="F945" t="n">
+        <v>14.4767973168367</v>
+      </c>
+      <c r="G945" t="n">
+        <v>1</v>
+      </c>
+      <c r="H945" t="n">
+        <v>0.6603960396039604</v>
+      </c>
+      <c r="I945" t="n">
+        <v>0.5582020850130858</v>
+      </c>
+      <c r="J945" t="n">
+        <v>1</v>
+      </c>
+      <c r="K945" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L945" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M945" t="n">
+        <v>29.989580969771</v>
+      </c>
+      <c r="N945" t="inlineStr">
+        <is>
+          <t>NY_AFTERNOON</t>
+        </is>
+      </c>
+      <c r="O945" t="n">
+        <v>73.00000000004729</v>
+      </c>
+      <c r="P945" t="inlineStr">
+        <is>
+          <t>BB%B=1.05 (extreme=1.15); RSI=75.0 (extreme=0.38); Wick ratio=4.91; ADX H1=30.0 (block=30.0); SL=14.47680 TP=14.47680 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q945" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=4459.22000 &lt; C=4465.90000) — SELL needs bea</t>
+        </is>
+      </c>
+      <c r="R945" t="inlineStr">
+        <is>
+          <t>[0.7502, 0.0, -1.0, 2.0, 1.0, -1.0, 1.0, 0.5003, 0.5128, 0.4796, 1.0, 0.2686, 0.9189, 1.0462, 0.3891, 2.5544, 0.5364, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0005, 0.0, 0.4629, 0.0, 0.0, 0.0, 0.0, 0.1625, 0.8976, 0.8125, 0.3055]</t>
+        </is>
+      </c>
+      <c r="S945" t="n">
+        <v>0</v>
+      </c>
+      <c r="T945" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>2026-05-28 14:18:18.323824+00:00</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D946" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E946" t="n">
+        <v>77.9816361317546</v>
+      </c>
+      <c r="F946" t="n">
+        <v>0.0006357060230489112</v>
+      </c>
+      <c r="G946" t="n">
+        <v>1</v>
+      </c>
+      <c r="H946" t="n">
+        <v>0.5398987933047878</v>
+      </c>
+      <c r="I946" t="n">
+        <v>0.5317961935076927</v>
+      </c>
+      <c r="J946" t="n">
+        <v>0.9070109128952026</v>
+      </c>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L946" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M946" t="n">
+        <v>29.989580969771</v>
+      </c>
+      <c r="N946" t="inlineStr">
+        <is>
+          <t>NY_AFTERNOON</t>
+        </is>
+      </c>
+      <c r="O946" t="n">
+        <v>0.3999999999992898</v>
+      </c>
+      <c r="P946" t="inlineStr">
+        <is>
+          <t>BB%B=1.02 (extreme=1.08); RSI=75.6 (extreme=0.39); Wick ratio=0.43; ADX H1=28.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q946" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=0.59176 &lt; C=0.59182) — SELL needs bearish c</t>
+        </is>
+      </c>
+      <c r="R946" t="inlineStr">
+        <is>
+          <t>[0.5596, 0.0, -1.0, -0.8643, 1.0, -1.0, 1.8877, 0.5123, 0.328, 0.2611, 1.0, 0.2942, 0.8441, 1.0234, 0.2254, 2.0764, 0.1086, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4116, 0.0, 0.0, 0.0, 0.0, 0.1625, 0.7752, 0.683, 0.3873]</t>
+        </is>
+      </c>
+      <c r="S946" t="n">
+        <v>0</v>
+      </c>
+      <c r="T946" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>2026-05-28 14:20:19.669062+00:00</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D947" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E947" t="n">
+        <v>82.5303114205547</v>
+      </c>
+      <c r="F947" t="n">
+        <v>0.07354458639652224</v>
+      </c>
+      <c r="G947" t="n">
+        <v>1</v>
+      </c>
+      <c r="H947" t="n">
+        <v>0.4046882436934794</v>
+      </c>
+      <c r="I947" t="n">
+        <v>0.4530479213180393</v>
+      </c>
+      <c r="J947" t="n">
+        <v>-0.311690628528595</v>
+      </c>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L947" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M947" t="n">
+        <v>30.19601843908199</v>
+      </c>
+      <c r="N947" t="inlineStr">
+        <is>
+          <t>NY_AFTERNOON</t>
+        </is>
+      </c>
+      <c r="O947" t="n">
+        <v>0</v>
+      </c>
+      <c r="P947" t="inlineStr">
+        <is>
+          <t>BB%B=-0.12 (extreme=1.39); RSI=32.2 (extreme=0.20); Wick ratio=2.12; ADX H1=25.8 (block=30.0); SL=0.10000 TP=0.10000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R947" t="inlineStr">
+        <is>
+          <t>[0.6506, 0.0, 1.0, -0.7646, 1.0, -1.0, 1.3597, -0.3562, -0.1186, 0.0243, 0.9997, 0.3198, -0.4615, -0.1182, 0.7113, -1.6453, -0.1493, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.3605, 0.0, 0.0, 0.0, 0.0, 0.1667, -0.4927, -0.2542, 0.1443]</t>
+        </is>
+      </c>
+      <c r="S947" t="n">
+        <v>0</v>
+      </c>
+      <c r="T947" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>2026-05-28 14:20:20.367099+00:00</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D948" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E948" t="n">
+        <v>78.61048981546027</v>
+      </c>
+      <c r="F948" t="n">
+        <v>0.0006485631706072426</v>
+      </c>
+      <c r="G948" t="n">
+        <v>1</v>
+      </c>
+      <c r="H948" t="n">
+        <v>0.5470931708555471</v>
+      </c>
+      <c r="I948" t="n">
+        <v>0.5322871564440759</v>
+      </c>
+      <c r="J948" t="n">
+        <v>0.7127395868301392</v>
+      </c>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L948" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M948" t="n">
+        <v>30.19601843908199</v>
+      </c>
+      <c r="N948" t="inlineStr">
+        <is>
+          <t>NY_AFTERNOON</t>
+        </is>
+      </c>
+      <c r="O948" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P948" t="inlineStr">
+        <is>
+          <t>BB%B=1.04 (extreme=1.14); RSI=76.2 (extreme=0.41); Wick ratio=0.50; ADX H1=28.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q948" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC slope: 0.68 &gt; 0.15 — EMA rising too fast for SELL</t>
+        </is>
+      </c>
+      <c r="R948" t="inlineStr">
+        <is>
+          <t>[0.5722, 0.0, -1.0, -0.8514, 1.0, -1.0, 1.8502, 0.5244, 0.3323, 0.2625, 1.0, 0.2942, 0.9032, 1.0431, 0.2495, 2.2049, 0.1086, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4116, 0.0, 0.0, 0.0, 0.0, 0.1667, 0.801, 0.6797, 0.3752]</t>
+        </is>
+      </c>
+      <c r="S948" t="n">
+        <v>0</v>
+      </c>
+      <c r="T948" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>2026-05-28 14:20:21.049691+00:00</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>GBPJPY</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D949" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E949" t="n">
+        <v>75.24044537081053</v>
+      </c>
+      <c r="F949" t="n">
+        <v>0.1366244406949155</v>
+      </c>
+      <c r="G949" t="n">
+        <v>1</v>
+      </c>
+      <c r="H949" t="n">
+        <v>0.5124386825508059</v>
+      </c>
+      <c r="I949" t="n">
+        <v>0.5183261306414362</v>
+      </c>
+      <c r="J949" t="n">
+        <v>1</v>
+      </c>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L949" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M949" t="n">
+        <v>30.19601843908199</v>
+      </c>
+      <c r="N949" t="inlineStr">
+        <is>
+          <t>NY_AFTERNOON</t>
+        </is>
+      </c>
+      <c r="O949" t="n">
+        <v>2.299999999999613</v>
+      </c>
+      <c r="P949" t="inlineStr">
+        <is>
+          <t>BB%B=0.93 (extreme=0.77); RSI=64.8 (extreme=0.12); Wick ratio=2.36; ADX H1=22.2 (block=30.0); SL=0.20000 TP=0.20000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q949" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=213.99400 &lt; C=214.00100) — SELL needs beari</t>
+        </is>
+      </c>
+      <c r="R949" t="inlineStr">
+        <is>
+          <t>[0.5048, 0.0, -1.0, -0.1338, 0.7678, -1.0, 1.4639, 0.2955, 0.2855, 0.0774, 1.0, 0.2284, 0.7406, 0.9303, 0.3482, 1.7054, 0.0659, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0002, 0.0, 0.5433, 0.0, 0.0, 0.0, 0.0, 0.1667, 0.4764, 0.4694, 0.3259]</t>
+        </is>
+      </c>
+      <c r="S949" t="n">
+        <v>0</v>
+      </c>
+      <c r="T949" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>2026-05-28 14:21:23.489475+00:00</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D950" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E950" t="n">
+        <v>86.686893877735</v>
+      </c>
+      <c r="F950" t="n">
+        <v>0.0006485631706072426</v>
+      </c>
+      <c r="G950" t="n">
+        <v>1</v>
+      </c>
+      <c r="H950" t="n">
+        <v>0.5376988297946883</v>
+      </c>
+      <c r="I950" t="n">
+        <v>0.5312744243402954</v>
+      </c>
+      <c r="J950" t="n">
+        <v>0.8944621086120605</v>
+      </c>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L950" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M950" t="n">
+        <v>30.19601843908199</v>
+      </c>
+      <c r="N950" t="inlineStr">
+        <is>
+          <t>NY_AFTERNOON</t>
+        </is>
+      </c>
+      <c r="O950" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P950" t="inlineStr">
+        <is>
+          <t>BB%B=0.99 (extreme=0.98); RSI=74.7 (extreme=0.37); Wick ratio=6.29; ADX H1=28.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q950" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=0.59183 &lt; C=0.59187) — SELL needs bearish c</t>
+        </is>
+      </c>
+      <c r="R950" t="inlineStr">
+        <is>
+          <t>[0.7337, 0.0, -1.0, -0.8514, 0.9783, -1.0, 1.8502, 0.4936, 0.3057, 0.259, 1.0, 0.2942, 0.7581, 0.9935, 0.2495, 1.7886, 0.1086, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4116, 0.0, 0.0, 0.0, 0.0, 0.1688, 0.7001, 0.6545, 0.3752]</t>
+        </is>
+      </c>
+      <c r="S950" t="n">
+        <v>0</v>
+      </c>
+      <c r="T950" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>2026-05-28 14:21:24.176153+00:00</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D951" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E951" t="n">
+        <v>83.35809530039138</v>
+      </c>
+      <c r="F951" t="n">
+        <v>0.0008531915590659247</v>
+      </c>
+      <c r="G951" t="n">
+        <v>1</v>
+      </c>
+      <c r="H951" t="n">
+        <v>0.5627603642945385</v>
+      </c>
+      <c r="I951" t="n">
+        <v>0.5383007397263316</v>
+      </c>
+      <c r="J951" t="n">
+        <v>1</v>
+      </c>
+      <c r="K951" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L951" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M951" t="n">
+        <v>30.19601843908199</v>
+      </c>
+      <c r="N951" t="inlineStr">
+        <is>
+          <t>NY_AFTERNOON</t>
+        </is>
+      </c>
+      <c r="O951" t="n">
+        <v>0</v>
+      </c>
+      <c r="P951" t="inlineStr">
+        <is>
+          <t>BB%B=1.00 (extreme=1.01); RSI=73.2 (extreme=0.33); Wick ratio=1.75; ADX H1=20.1 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q951" t="inlineStr">
+        <is>
+          <t>entry_confirm:M1 last bar bullish (O=1.16531 &lt; C=1.16548) — SELL needs bearish c</t>
+        </is>
+      </c>
+      <c r="R951" t="inlineStr">
+        <is>
+          <t>[0.6672, 0.0, -1.0, -0.6468, 1.0, -1.0, 1.1721, 0.4643, 0.3259, 0.0232, 1.0, 0.3912, 0.7185, 1.0032, 0.6567, 2.0628, 0.1255, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.2177, 0.0, 0.0, 0.0, 0.0, 0.1688, 0.7476, 0.6634, 0.1716]</t>
+        </is>
+      </c>
+      <c r="S951" t="n">
+        <v>0</v>
+      </c>
+      <c r="T951" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>2026-05-28 14:21:24.889180+00:00</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D952" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E952" t="n">
+        <v>80.50833932434762</v>
+      </c>
+      <c r="F952" t="n">
+        <v>0.07354458639652224</v>
+      </c>
+      <c r="G952" t="n">
+        <v>1</v>
+      </c>
+      <c r="H952" t="n">
+        <v>0.441096541380181</v>
+      </c>
+      <c r="I952" t="n">
+        <v>0.4678716176685311</v>
+      </c>
+      <c r="J952" t="n">
+        <v>1</v>
+      </c>
+      <c r="K952" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L952" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M952" t="n">
+        <v>30.19601843908199</v>
+      </c>
+      <c r="N952" t="inlineStr">
+        <is>
+          <t>NY_AFTERNOON</t>
+        </is>
+      </c>
+      <c r="O952" t="n">
+        <v>0.1000000000004775</v>
+      </c>
+      <c r="P952" t="inlineStr">
+        <is>
+          <t>BB%B=0.01 (extreme=0.96); RSI=36.4 (extreme=0.09); Wick ratio=4.69; ADX H1=25.8 (block=30.0); SL=0.10000 TP=0.10000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q952" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC filter: dist -0.36 &gt; -0.6 — price not overextended down</t>
+        </is>
+      </c>
+      <c r="R952" t="inlineStr">
+        <is>
+          <t>[0.6102, 0.0, 1.0, -0.7646, 0.9575, -1.0, 1.3597, -0.2713, -0.0839, 0.0223, 0.9148, 0.3198, -0.2051, 0.0127, 0.7113, -1.1014, -0.0667, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.3605, 0.0, 0.0, 0.0, 0.0, 0.1688, -0.3609, -0.2212, 0.1443]</t>
+        </is>
+      </c>
+      <c r="S952" t="n">
+        <v>0</v>
+      </c>
+      <c r="T952" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>2026-05-28 14:22:26.133006+00:00</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D953" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E953" t="n">
+        <v>84.42495017155754</v>
+      </c>
+      <c r="F953" t="n">
+        <v>0.0008531915590659247</v>
+      </c>
+      <c r="G953" t="n">
+        <v>1</v>
+      </c>
+      <c r="H953" t="n">
+        <v>0.5627603642945385</v>
+      </c>
+      <c r="I953" t="n">
+        <v>0.5383007397263316</v>
+      </c>
+      <c r="J953" t="n">
+        <v>1</v>
+      </c>
+      <c r="K953" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L953" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M953" t="n">
+        <v>30.19601843908199</v>
+      </c>
+      <c r="N953" t="inlineStr">
+        <is>
+          <t>NY_AFTERNOON</t>
+        </is>
+      </c>
+      <c r="O953" t="n">
+        <v>0.1000000000006551</v>
+      </c>
+      <c r="P953" t="inlineStr">
+        <is>
+          <t>BB%B=1.00 (extreme=0.99); RSI=73.0 (extreme=0.33); Wick ratio=2.03; ADX H1=20.1 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q953" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC slope: 0.66 &gt; 0.15 — EMA rising too fast for SELL</t>
+        </is>
+      </c>
+      <c r="R953" t="inlineStr">
+        <is>
+          <t>[0.6885, 0.0, -1.0, -0.6468, 0.9926, -1.0, 1.1721, 0.4608, 0.3229, 0.0229, 1.0, 0.3912, 0.7038, 0.9978, 0.6567, 2.016, 0.1255, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.2177, 0.0, 0.0, 0.0, 0.0, 0.1708, 0.7363, 0.6606, 0.1716]</t>
+        </is>
+      </c>
+      <c r="S953" t="n">
+        <v>0</v>
+      </c>
+      <c r="T953" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>2026-05-28 14:22:27.860813+00:00</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D954" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E954" t="n">
+        <v>81.06391323501822</v>
+      </c>
+      <c r="F954" t="n">
+        <v>0.0006485631706072426</v>
+      </c>
+      <c r="G954" t="n">
+        <v>1</v>
+      </c>
+      <c r="H954" t="n">
+        <v>0.5376988297946883</v>
+      </c>
+      <c r="I954" t="n">
+        <v>0.5312744243402954</v>
+      </c>
+      <c r="J954" t="n">
+        <v>0.6802976727485657</v>
+      </c>
+      <c r="K954" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L954" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M954" t="n">
+        <v>30.19601843908199</v>
+      </c>
+      <c r="N954" t="inlineStr">
+        <is>
+          <t>NY_AFTERNOON</t>
+        </is>
+      </c>
+      <c r="O954" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P954" t="inlineStr">
+        <is>
+          <t>BB%B=1.03 (extreme=1.09); RSI=75.7 (extreme=0.39); Wick ratio=1.04; ADX H1=28.5 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q954" t="inlineStr">
+        <is>
+          <t>entry_confirm:KC slope: 0.67 &gt; 0.15 — EMA rising too fast for SELL</t>
+        </is>
+      </c>
+      <c r="R954" t="inlineStr">
+        <is>
+          <t>[0.6213, 0.0, -1.0, -0.8514, 1.0, -1.0, 1.8502, 0.5146, 0.3234, 0.2614, 1.0, 0.2942, 0.8548, 1.0271, 0.2495, 2.0661, 0.1086, -0.3533, -0.0, -0.3533, 0.5333, 0.0, -0.2, 0.0, 0.0, 0.0, 0.4116, 0.0, 0.0, 0.0, 0.0, 0.1708, 0.7673, 0.6713, 0.3752]</t>
+        </is>
+      </c>
+      <c r="S954" t="n">
+        <v>0</v>
+      </c>
+      <c r="T954" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ftmo_trading_bot/logs/ftmo_trades.xlsx
+++ b/ftmo_trading_bot/logs/ftmo_trades.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH2"/>
+  <dimension ref="A1:BH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1073,6 +1073,214 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>558961569</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.1632</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.16219</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.16419</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.006941077725120507</v>
+      </c>
+      <c r="I3" t="n">
+        <v>65</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>81.73906240288541</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.000563166242660489</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:19:57.064230</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1.16218</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:36:43.158804</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n">
+        <v>-68.89999999999999</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-106</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>🔴 SL Hit</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>BB%B=-0.11 (extreme=1.36); RSI=27.5 (extreme=0.31); Wick ratio=1.50; ADX H1=14.3 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00; KC dist=-0.68 slope=-0.39 consec=2</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>16</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>quiet</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1006</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>🔴 SL Hit</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.4135348168793276</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.4643204727552281</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AK3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.16219</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.16319</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.16319</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.16219</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.16219</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>14.3370699212636</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9364.540000000001</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>9295.639999999999</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>9295.639999999999</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>[0.6348, 0.0, 1.0, -0.9368, 1.0, -1.0, 1.7757, -0.4496, -0.2833, 0.0378, 1.0, 0.2895, -0.6552, -0.1068, 0.3057, -2.5037, -0.1729, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.421, 0.0, 0.0, 0.0, 0.0, 0.0396, -0.6829, -0.3928, 0.3472]</t>
+        </is>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1355,7 +1563,7 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1375,7 +1583,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1398,7 +1606,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$-57.28</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1630,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$57.28</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1642,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$-57.28</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1654,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$-57.28</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1688,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$-57.28</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1797,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1612,7 +1820,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$-57.28</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1832,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$-57.28</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1853,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1680,7 +1888,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-5.7%</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1900,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>$1,000.00</t>
+          <t>$1,057.28</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1912,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>3.21% / 10%</t>
+          <t>3.77% / 10%</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1924,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>0.00% / 4%</t>
+          <t>0.57% / 4%</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V437"/>
+  <dimension ref="A1:V479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -39014,7 +39222,6 @@
           <t>TF BUY ADX=33.0 trend_age=60 pullback=1.80×ATR H4=1 D1=1</t>
         </is>
       </c>
-      <c r="Q437" t="inlineStr"/>
       <c r="R437" t="inlineStr">
         <is>
           <t>[0.4763, 0.375, 1.0, -0.6048, 1.0, 1.0, 2.0, -0.2545, -0.4813, 1.0, 1.0, 0.3303, -0.9023, -0.0976, -0.0903, -1.8432, -0.9843, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6605, 0.0, 0.0, 0.0, 0.0, 0.2292, 0.0, 0.0, 0.5]</t>
@@ -39034,6 +39241,3611 @@
       <c r="V437" t="inlineStr">
         <is>
           <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:02:07.657248+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D438" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>76.69203673711351</v>
+      </c>
+      <c r="F438" t="n">
+        <v>0.000833777456004398</v>
+      </c>
+      <c r="G438" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0.1394640682095007</v>
+      </c>
+      <c r="I438" t="n">
+        <v>0.3207155936232235</v>
+      </c>
+      <c r="J438" t="n">
+        <v>0</v>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L438" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M438" t="n">
+        <v>34.20336984856146</v>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O438" t="n">
+        <v>0.3999999999992898</v>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.2 trend_age=60 pullback=1.38×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>[0.5338, 0.375, 1.0, -0.6662, 1.0, 1.0, 2.0, -0.1897, -0.5152, 1.0, 1.0, 0.342, -0.7, 0.0878, -0.1441, -2.0269, -0.7211, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6841, 0.0, 0.0, 0.0, 0.0, 0.3792, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S438" t="n">
+        <v>0</v>
+      </c>
+      <c r="T438" t="n">
+        <v>0</v>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V438" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:03:08.312087+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D439" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>76.52245102179667</v>
+      </c>
+      <c r="F439" t="n">
+        <v>0.0008344917417188464</v>
+      </c>
+      <c r="G439" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H439" t="n">
+        <v>0.1394640682095007</v>
+      </c>
+      <c r="I439" t="n">
+        <v>0.3207155936232235</v>
+      </c>
+      <c r="J439" t="n">
+        <v>0</v>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L439" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M439" t="n">
+        <v>34.20336984856145</v>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O439" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.2 trend_age=60 pullback=1.42×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>[0.5304, 0.375, 1.0, -0.6655, 1.0, 1.0, 2.0, -0.1954, -0.5178, 1.0, 1.0, 0.342, -0.7222, 0.0805, -0.1434, -2.0731, -0.7211, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6841, 0.0, 0.0, 0.0, 0.0, 0.3812, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S439" t="n">
+        <v>0</v>
+      </c>
+      <c r="T439" t="n">
+        <v>0</v>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V439" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:04:08.937439+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D440" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>76.65792503004968</v>
+      </c>
+      <c r="F440" t="n">
+        <v>0.0008352060274332868</v>
+      </c>
+      <c r="G440" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H440" t="n">
+        <v>0.1394640682095007</v>
+      </c>
+      <c r="I440" t="n">
+        <v>0.3207155936232235</v>
+      </c>
+      <c r="J440" t="n">
+        <v>0</v>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L440" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M440" t="n">
+        <v>34.20336984856144</v>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O440" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.2 trend_age=60 pullback=1.39×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>[0.5332, 0.375, 1.0, -0.6648, 1.0, 1.0, 2.0, -0.1911, -0.515, 1.0, 1.0, 0.342, -0.7056, 0.0859, -0.1427, -2.0354, -0.7211, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6841, 0.0, 0.0, 0.0, 0.0, 0.3833, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S440" t="n">
+        <v>0</v>
+      </c>
+      <c r="T440" t="n">
+        <v>0</v>
+      </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V440" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:05:09.625236+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D441" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>76.61438650761451</v>
+      </c>
+      <c r="F441" t="n">
+        <v>0.0008352060274332868</v>
+      </c>
+      <c r="G441" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H441" t="n">
+        <v>0.1394640682095007</v>
+      </c>
+      <c r="I441" t="n">
+        <v>0.3207155936232235</v>
+      </c>
+      <c r="J441" t="n">
+        <v>0</v>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L441" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M441" t="n">
+        <v>34.20336984856144</v>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O441" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.2 trend_age=60 pullback=1.40×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>[0.5323, 0.375, 1.0, -0.6648, 1.0, 1.0, 2.0, -0.1926, -0.5158, 1.0, 1.0, 0.342, -0.7111, 0.0841, -0.1427, -2.0474, -0.7211, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6841, 0.0, 0.0, 0.0, 0.0, 0.3854, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S441" t="n">
+        <v>0</v>
+      </c>
+      <c r="T441" t="n">
+        <v>0</v>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:06:10.300326+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D442" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>76.13345319874979</v>
+      </c>
+      <c r="F442" t="n">
+        <v>0.0008409203131488338</v>
+      </c>
+      <c r="G442" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H442" t="n">
+        <v>0.1394640682095007</v>
+      </c>
+      <c r="I442" t="n">
+        <v>0.3207155936232235</v>
+      </c>
+      <c r="J442" t="n">
+        <v>0</v>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L442" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M442" t="n">
+        <v>34.20336984856139</v>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O442" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.2 trend_age=60 pullback=1.52×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>[0.5227, 0.375, 1.0, -0.6591, 1.0, 1.0, 2.0, -0.2092, -0.5214, 1.0, 1.0, 0.342, -0.7778, 0.0626, -0.1369, -2.1762, -0.7211, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6841, 0.0, 0.0, 0.0, 0.0, 0.3875, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S442" t="n">
+        <v>0</v>
+      </c>
+      <c r="T442" t="n">
+        <v>0</v>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V442" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:07:10.909176+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D443" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>76.13860466799392</v>
+      </c>
+      <c r="F443" t="n">
+        <v>0.0008416345988632821</v>
+      </c>
+      <c r="G443" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H443" t="n">
+        <v>0.1394640682095007</v>
+      </c>
+      <c r="I443" t="n">
+        <v>0.3207155936232235</v>
+      </c>
+      <c r="J443" t="n">
+        <v>0</v>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L443" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M443" t="n">
+        <v>34.20336984856139</v>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O443" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.2 trend_age=60 pullback=1.52×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>[0.5228, 0.375, 1.0, -0.6584, 1.0, 1.0, 2.0, -0.2092, -0.521, 1.0, 1.0, 0.342, -0.7778, 0.0626, -0.1362, -2.1743, -0.7211, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6841, 0.0, 0.0, 0.0, 0.0, 0.3896, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S443" t="n">
+        <v>0</v>
+      </c>
+      <c r="T443" t="n">
+        <v>0</v>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:08:11.689593+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D444" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>76.20218319011671</v>
+      </c>
+      <c r="F444" t="n">
+        <v>0.0008444917417210516</v>
+      </c>
+      <c r="G444" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H444" t="n">
+        <v>0.1394640682095007</v>
+      </c>
+      <c r="I444" t="n">
+        <v>0.3216968672893233</v>
+      </c>
+      <c r="J444" t="n">
+        <v>0</v>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L444" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M444" t="n">
+        <v>34.20336984856137</v>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O444" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.2 trend_age=60 pullback=1.50×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>[0.524, 0.375, 1.0, -0.6555, 1.0, 1.0, 2.0, -0.2079, -0.5185, 1.0, 1.0, 0.342, -0.7722, 0.0644, -0.1333, -2.1551, -0.7211, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6841, 0.0, 0.0, 0.0, 0.0, 0.3917, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S444" t="n">
+        <v>0</v>
+      </c>
+      <c r="T444" t="n">
+        <v>0</v>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V444" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:09:12.395341+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D445" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>76.28830276847874</v>
+      </c>
+      <c r="F445" t="n">
+        <v>0.0008444917417210516</v>
+      </c>
+      <c r="G445" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H445" t="n">
+        <v>0.1394640682095007</v>
+      </c>
+      <c r="I445" t="n">
+        <v>0.3216968672893233</v>
+      </c>
+      <c r="J445" t="n">
+        <v>0</v>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L445" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M445" t="n">
+        <v>34.20336984856137</v>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O445" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.2 trend_age=60 pullback=1.48×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>[0.5258, 0.375, 1.0, -0.6555, 1.0, 1.0, 2.0, -0.2051, -0.5169, 1.0, 1.0, 0.342, -0.7611, 0.0679, -0.1333, -2.1315, -0.7211, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6841, 0.0, 0.0, 0.0, 0.0, 0.3938, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S445" t="n">
+        <v>0</v>
+      </c>
+      <c r="T445" t="n">
+        <v>0</v>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V445" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:10:13.112900+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D446" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>76.50360171438352</v>
+      </c>
+      <c r="F446" t="n">
+        <v>0.0008444917417210516</v>
+      </c>
+      <c r="G446" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H446" t="n">
+        <v>0.1394640682095007</v>
+      </c>
+      <c r="I446" t="n">
+        <v>0.3216968672893233</v>
+      </c>
+      <c r="J446" t="n">
+        <v>0</v>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L446" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M446" t="n">
+        <v>34.20336984856137</v>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O446" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.2 trend_age=60 pullback=1.42×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>[0.5301, 0.375, 1.0, -0.6555, 1.0, 1.0, 2.0, -0.1982, -0.5132, 1.0, 1.0, 0.342, -0.7333, 0.0769, -0.1333, -2.0723, -0.7211, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6841, 0.0, 0.0, 0.0, 0.0, 0.3958, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S446" t="n">
+        <v>0</v>
+      </c>
+      <c r="T446" t="n">
+        <v>0</v>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V446" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:11:13.976184+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D447" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>76.33136255766001</v>
+      </c>
+      <c r="F447" t="n">
+        <v>0.0008444917417210516</v>
+      </c>
+      <c r="G447" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H447" t="n">
+        <v>0.1394640682095007</v>
+      </c>
+      <c r="I447" t="n">
+        <v>0.3216968672893233</v>
+      </c>
+      <c r="J447" t="n">
+        <v>0</v>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L447" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M447" t="n">
+        <v>34.20336984856137</v>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O447" t="n">
+        <v>0.3999999999992898</v>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.2 trend_age=60 pullback=1.47×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>[0.5266, 0.375, 1.0, -0.6555, 1.0, 1.0, 2.0, -0.2037, -0.5162, 1.0, 1.0, 0.342, -0.7556, 0.0697, -0.1333, -2.1196, -0.7211, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6841, 0.0, 0.0, 0.0, 0.0, 0.3979, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S447" t="n">
+        <v>0</v>
+      </c>
+      <c r="T447" t="n">
+        <v>0</v>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V447" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:12:14.634755+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D448" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>76.38426614386513</v>
+      </c>
+      <c r="F448" t="n">
+        <v>0.0008459203131499403</v>
+      </c>
+      <c r="G448" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H448" t="n">
+        <v>0.1998880179171333</v>
+      </c>
+      <c r="I448" t="n">
+        <v>0.3308976919305722</v>
+      </c>
+      <c r="J448" t="n">
+        <v>0</v>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L448" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M448" t="n">
+        <v>34.20336984856134</v>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O448" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.2 trend_age=60 pullback=1.45×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>[0.5277, 0.375, 1.0, -0.6541, 1.0, 1.0, 2.0, -0.2024, -0.5146, 1.0, 1.0, 0.342, -0.75, 0.0715, -0.1319, -2.1042, -0.6002, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6841, 0.0, 0.0, 0.0, 0.0, 0.4, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S448" t="n">
+        <v>0</v>
+      </c>
+      <c r="T448" t="n">
+        <v>0</v>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V448" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:13:15.270910+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D449" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>76.16933079003581</v>
+      </c>
+      <c r="F449" t="n">
+        <v>0.0008459203131499403</v>
+      </c>
+      <c r="G449" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H449" t="n">
+        <v>0.1998880179171333</v>
+      </c>
+      <c r="I449" t="n">
+        <v>0.3308976919305722</v>
+      </c>
+      <c r="J449" t="n">
+        <v>0</v>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L449" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M449" t="n">
+        <v>34.20336984856134</v>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O449" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.2 trend_age=60 pullback=1.51×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>[0.5234, 0.375, 1.0, -0.6541, 1.0, 1.0, 2.0, -0.2092, -0.5183, 1.0, 1.0, 0.342, -0.7778, 0.0626, -0.1319, -2.1633, -0.6002, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6841, 0.0, 0.0, 0.0, 0.0, 0.4021, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S449" t="n">
+        <v>0</v>
+      </c>
+      <c r="T449" t="n">
+        <v>0</v>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V449" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:14:15.927248+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D450" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>76.51322735616229</v>
+      </c>
+      <c r="F450" t="n">
+        <v>0.0008459203131499403</v>
+      </c>
+      <c r="G450" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H450" t="n">
+        <v>0.1998880179171333</v>
+      </c>
+      <c r="I450" t="n">
+        <v>0.3308976919305722</v>
+      </c>
+      <c r="J450" t="n">
+        <v>0</v>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L450" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M450" t="n">
+        <v>34.20336984856134</v>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O450" t="n">
+        <v>0.5000000000010552</v>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.2 trend_age=60 pullback=1.42×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>[0.5303, 0.375, 1.0, -0.6541, 1.0, 1.0, 2.0, -0.1982, -0.5123, 1.0, 1.0, 0.342, -0.7333, 0.0769, -0.1319, -2.0688, -0.6002, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6841, 0.0, 0.0, 0.0, 0.0, 0.4042, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S450" t="n">
+        <v>0</v>
+      </c>
+      <c r="T450" t="n">
+        <v>0</v>
+      </c>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V450" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:15:16.575312+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D451" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>76.55621442692836</v>
+      </c>
+      <c r="F451" t="n">
+        <v>0.0008459203131499403</v>
+      </c>
+      <c r="G451" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H451" t="n">
+        <v>0.1998880179171333</v>
+      </c>
+      <c r="I451" t="n">
+        <v>0.3308976919305722</v>
+      </c>
+      <c r="J451" t="n">
+        <v>0</v>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L451" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M451" t="n">
+        <v>34.20336984856134</v>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O451" t="n">
+        <v>0.3999999999992898</v>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.2 trend_age=60 pullback=1.41×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>[0.5311, 0.375, 1.0, -0.6541, 1.0, 1.0, 2.0, -0.1968, -0.5115, 1.0, 1.0, 0.342, -0.7278, 0.0787, -0.1319, -2.0569, -0.6002, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6841, 0.0, 0.0, 0.0, 0.0, 0.4062, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S451" t="n">
+        <v>0</v>
+      </c>
+      <c r="T451" t="n">
+        <v>0</v>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V451" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:16:17.232650+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D452" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E452" t="n">
+        <v>77.02907220535253</v>
+      </c>
+      <c r="F452" t="n">
+        <v>0.0008459203131499403</v>
+      </c>
+      <c r="G452" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H452" t="n">
+        <v>0.1556291390728477</v>
+      </c>
+      <c r="I452" t="n">
+        <v>0.3228863230633262</v>
+      </c>
+      <c r="J452" t="n">
+        <v>0</v>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L452" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M452" t="n">
+        <v>34.20336984856134</v>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O452" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.2 trend_age=60 pullback=1.29×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>[0.5406, 0.375, 1.0, -0.6541, 1.0, 1.0, 2.0, -0.181, -0.5032, 1.0, 1.0, 0.342, -0.6667, 0.0988, -0.1319, -1.9269, -0.6887, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6841, 0.0, 0.0, 0.0, 0.0, 0.4083, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S452" t="n">
+        <v>0</v>
+      </c>
+      <c r="T452" t="n">
+        <v>0</v>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V452" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:17:17.958399+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D453" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>76.94309806382091</v>
+      </c>
+      <c r="F453" t="n">
+        <v>0.0008459203131499403</v>
+      </c>
+      <c r="G453" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H453" t="n">
+        <v>0.1556291390728477</v>
+      </c>
+      <c r="I453" t="n">
+        <v>0.3228863230633262</v>
+      </c>
+      <c r="J453" t="n">
+        <v>0</v>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L453" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M453" t="n">
+        <v>34.20336984856134</v>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O453" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.2 trend_age=60 pullback=1.32×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>[0.5389, 0.375, 1.0, -0.6541, 1.0, 1.0, 2.0, -0.1839, -0.5048, 1.0, 1.0, 0.342, -0.6778, 0.0951, -0.1319, -1.9505, -0.6887, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6841, 0.0, 0.0, 0.0, 0.0, 0.4104, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S453" t="n">
+        <v>0</v>
+      </c>
+      <c r="T453" t="n">
+        <v>0</v>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V453" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:18:18.680646+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D454" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>77.15803341765022</v>
+      </c>
+      <c r="F454" t="n">
+        <v>0.0008459203131499403</v>
+      </c>
+      <c r="G454" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H454" t="n">
+        <v>0.1556291390728477</v>
+      </c>
+      <c r="I454" t="n">
+        <v>0.3228863230633262</v>
+      </c>
+      <c r="J454" t="n">
+        <v>0</v>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L454" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M454" t="n">
+        <v>34.20336984856134</v>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O454" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.2 trend_age=60 pullback=1.26×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>[0.5432, 0.375, 1.0, -0.6541, 1.0, 1.0, 2.0, -0.1766, -0.501, 1.0, 1.0, 0.342, -0.65, 0.1043, -0.1319, -1.8914, -0.6887, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6841, 0.0, 0.0, 0.0, 0.0, 0.4125, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S454" t="n">
+        <v>0</v>
+      </c>
+      <c r="T454" t="n">
+        <v>0</v>
+      </c>
+      <c r="U454" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V454" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:19:19.589339+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D455" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>85.42805251695148</v>
+      </c>
+      <c r="F455" t="n">
+        <v>0.0008480631702932773</v>
+      </c>
+      <c r="G455" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H455" t="n">
+        <v>0.1998880179171333</v>
+      </c>
+      <c r="I455" t="n">
+        <v>0.3365432769085063</v>
+      </c>
+      <c r="J455" t="n">
+        <v>0</v>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L455" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M455" t="n">
+        <v>34.20336984856133</v>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O455" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.2 trend_age=60 pullback=1.19×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>[0.7086, 0.375, 1.0, -0.6519, 1.0, 1.0, 2.0, -0.1641, -0.4952, 1.0, 1.0, 0.342, -0.6167, 0.1156, -0.1297, -1.8159, -0.6002, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6841, 0.0, 0.0, 0.0, 0.0, 0.4146, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S455" t="n">
+        <v>0</v>
+      </c>
+      <c r="T455" t="n">
+        <v>0</v>
+      </c>
+      <c r="U455" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V455" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:20:20.274919+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D456" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>85.51244937411902</v>
+      </c>
+      <c r="F456" t="n">
+        <v>0.0008516345988654952</v>
+      </c>
+      <c r="G456" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H456" t="n">
+        <v>0.4853202846975089</v>
+      </c>
+      <c r="I456" t="n">
+        <v>0.4095125375109766</v>
+      </c>
+      <c r="J456" t="n">
+        <v>-0.9263066053390503</v>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L456" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M456" t="n">
+        <v>34.09694631112428</v>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O456" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.1 trend_age=60 pullback=1.15×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>[0.7102, 0.375, 1.0, -0.6484, 1.0, 1.0, 2.0, -0.1559, -0.4901, 1.0, 1.0, 0.341, -0.5944, 0.1232, -0.1261, -1.7613, -0.0294, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6819, 0.0, 0.0, 0.0, 0.0, 0.4167, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S456" t="n">
+        <v>0</v>
+      </c>
+      <c r="T456" t="n">
+        <v>0</v>
+      </c>
+      <c r="U456" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V456" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:21:20.896948+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D457" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>85.46975073738881</v>
+      </c>
+      <c r="F457" t="n">
+        <v>0.0008516345988654952</v>
+      </c>
+      <c r="G457" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H457" t="n">
+        <v>0.5202907328891581</v>
+      </c>
+      <c r="I457" t="n">
+        <v>0.4285810230730019</v>
+      </c>
+      <c r="J457" t="n">
+        <v>-0.8851801156997681</v>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L457" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M457" t="n">
+        <v>34.09694631112428</v>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O457" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.1 trend_age=60 pullback=1.16×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>[0.7094, 0.375, 1.0, -0.6484, 1.0, 1.0, 2.0, -0.158, -0.4909, 1.0, 1.0, 0.341, -0.6, 0.1213, -0.1261, -1.7731, 0.0406, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6819, 0.0, 0.0, 0.0, 0.0, 0.4187, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S457" t="n">
+        <v>0</v>
+      </c>
+      <c r="T457" t="n">
+        <v>0</v>
+      </c>
+      <c r="U457" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V457" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:22:21.517066+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D458" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>85.12816164354922</v>
+      </c>
+      <c r="F458" t="n">
+        <v>0.0008516345988654952</v>
+      </c>
+      <c r="G458" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H458" t="n">
+        <v>0.1810089020771513</v>
+      </c>
+      <c r="I458" t="n">
+        <v>0.3276380325408354</v>
+      </c>
+      <c r="J458" t="n">
+        <v>0</v>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L458" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M458" t="n">
+        <v>34.09694631112428</v>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O458" t="n">
+        <v>0.3999999999992898</v>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.1 trend_age=60 pullback=1.24×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>[0.7026, 0.375, 1.0, -0.6484, 1.0, 1.0, 2.0, -0.1745, -0.4969, 1.0, 1.0, 0.341, -0.6444, 0.1062, -0.1261, -1.867, -0.638, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6819, 0.0, 0.0, 0.0, 0.0, 0.4208, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S458" t="n">
+        <v>0</v>
+      </c>
+      <c r="T458" t="n">
+        <v>0</v>
+      </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V458" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:23:22.208614+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D459" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E459" t="n">
+        <v>77.00006573335912</v>
+      </c>
+      <c r="F459" t="n">
+        <v>0.0008516345988654952</v>
+      </c>
+      <c r="G459" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H459" t="n">
+        <v>0.1556291390728477</v>
+      </c>
+      <c r="I459" t="n">
+        <v>0.3228863230633262</v>
+      </c>
+      <c r="J459" t="n">
+        <v>0</v>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L459" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M459" t="n">
+        <v>34.09694631112428</v>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O459" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.1 trend_age=60 pullback=1.27×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>[0.54, 0.375, 1.0, -0.6484, 1.0, 1.0, 2.0, -0.1796, -0.4991, 1.0, 1.0, 0.341, -0.6611, 0.1006, -0.1261, -1.9022, -0.6887, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6819, 0.0, 0.0, 0.0, 0.0, 0.4229, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S459" t="n">
+        <v>0</v>
+      </c>
+      <c r="T459" t="n">
+        <v>0</v>
+      </c>
+      <c r="U459" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V459" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:24:22.892576+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D460" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E460" t="n">
+        <v>77.08546300681901</v>
+      </c>
+      <c r="F460" t="n">
+        <v>0.0008516345988654952</v>
+      </c>
+      <c r="G460" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H460" t="n">
+        <v>0.1556291390728477</v>
+      </c>
+      <c r="I460" t="n">
+        <v>0.3228863230633262</v>
+      </c>
+      <c r="J460" t="n">
+        <v>0</v>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L460" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M460" t="n">
+        <v>34.09694631112428</v>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O460" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.1 trend_age=60 pullback=1.25×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>[0.5417, 0.375, 1.0, -0.6484, 1.0, 1.0, 2.0, -0.1766, -0.4976, 1.0, 1.0, 0.341, -0.65, 0.1043, -0.1261, -1.8787, -0.6887, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6819, 0.0, 0.0, 0.0, 0.0, 0.425, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S460" t="n">
+        <v>0</v>
+      </c>
+      <c r="T460" t="n">
+        <v>0</v>
+      </c>
+      <c r="U460" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V460" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:25:23.679179+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D461" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>85.12816164354922</v>
+      </c>
+      <c r="F461" t="n">
+        <v>0.0008516345988654952</v>
+      </c>
+      <c r="G461" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H461" t="n">
+        <v>0.1810089020771513</v>
+      </c>
+      <c r="I461" t="n">
+        <v>0.3276380325408354</v>
+      </c>
+      <c r="J461" t="n">
+        <v>0</v>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L461" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M461" t="n">
+        <v>34.09694631112428</v>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O461" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.1 trend_age=60 pullback=1.24×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>[0.7026, 0.375, 1.0, -0.6484, 1.0, 1.0, 2.0, -0.1745, -0.4969, 1.0, 1.0, 0.341, -0.6444, 0.1062, -0.1261, -1.867, -0.638, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6819, 0.0, 0.0, 0.0, 0.0, 0.4271, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S461" t="n">
+        <v>0</v>
+      </c>
+      <c r="T461" t="n">
+        <v>0</v>
+      </c>
+      <c r="U461" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V461" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:26:24.381663+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D462" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>77.0427643700888</v>
+      </c>
+      <c r="F462" t="n">
+        <v>0.0008516345988654952</v>
+      </c>
+      <c r="G462" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H462" t="n">
+        <v>0.1556291390728477</v>
+      </c>
+      <c r="I462" t="n">
+        <v>0.3228863230633262</v>
+      </c>
+      <c r="J462" t="n">
+        <v>0</v>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L462" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M462" t="n">
+        <v>34.09694631112428</v>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O462" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.1 trend_age=60 pullback=1.26×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>[0.5409, 0.375, 1.0, -0.6484, 1.0, 1.0, 2.0, -0.1781, -0.4984, 1.0, 1.0, 0.341, -0.6556, 0.1025, -0.1261, -1.8905, -0.6887, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6819, 0.0, 0.0, 0.0, 0.0, 0.4292, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S462" t="n">
+        <v>0</v>
+      </c>
+      <c r="T462" t="n">
+        <v>0</v>
+      </c>
+      <c r="U462" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V462" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:27:25.115545+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D463" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>85.46975073738881</v>
+      </c>
+      <c r="F463" t="n">
+        <v>0.0008516345988654952</v>
+      </c>
+      <c r="G463" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H463" t="n">
+        <v>0.5202907328891581</v>
+      </c>
+      <c r="I463" t="n">
+        <v>0.4285810230730019</v>
+      </c>
+      <c r="J463" t="n">
+        <v>-0.9668371677398682</v>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L463" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M463" t="n">
+        <v>34.09694631112428</v>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O463" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.1 trend_age=60 pullback=1.16×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>[0.7094, 0.375, 1.0, -0.6484, 1.0, 1.0, 2.0, -0.158, -0.4909, 1.0, 1.0, 0.341, -0.6, 0.1213, -0.1261, -1.7731, 0.0406, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6819, 0.0, 0.0, 0.0, 0.0, 0.4313, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S463" t="n">
+        <v>0</v>
+      </c>
+      <c r="T463" t="n">
+        <v>0</v>
+      </c>
+      <c r="U463" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V463" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:28:26.058043+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D464" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>85.3843534639289</v>
+      </c>
+      <c r="F464" t="n">
+        <v>0.0008516345988654952</v>
+      </c>
+      <c r="G464" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H464" t="n">
+        <v>0.5202907328891581</v>
+      </c>
+      <c r="I464" t="n">
+        <v>0.4285810230730019</v>
+      </c>
+      <c r="J464" t="n">
+        <v>-0.914963960647583</v>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L464" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M464" t="n">
+        <v>34.09694631112428</v>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O464" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.1 trend_age=60 pullback=1.18×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>[0.7077, 0.375, 1.0, -0.6484, 1.0, 1.0, 2.0, -0.1621, -0.4924, 1.0, 1.0, 0.341, -0.6111, 0.1175, -0.1261, -1.7965, 0.0406, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6819, 0.0, 0.0, 0.0, 0.0, 0.4333, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S464" t="n">
+        <v>0</v>
+      </c>
+      <c r="T464" t="n">
+        <v>0</v>
+      </c>
+      <c r="U464" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V464" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:29:27.076238+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D465" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>85.29895619046849</v>
+      </c>
+      <c r="F465" t="n">
+        <v>0.0008516345988654952</v>
+      </c>
+      <c r="G465" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H465" t="n">
+        <v>0.1998880179171333</v>
+      </c>
+      <c r="I465" t="n">
+        <v>0.3365432769085063</v>
+      </c>
+      <c r="J465" t="n">
+        <v>0</v>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L465" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M465" t="n">
+        <v>34.09694631112428</v>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O465" t="n">
+        <v>0.5999999999994898</v>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.1 trend_age=60 pullback=1.20×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>[0.706, 0.375, 1.0, -0.6484, 1.0, 1.0, 2.0, -0.1662, -0.4939, 1.0, 1.0, 0.341, -0.6222, 0.1137, -0.1261, -1.82, -0.6002, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6819, 0.0, 0.0, 0.0, 0.0, 0.4354, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S465" t="n">
+        <v>0</v>
+      </c>
+      <c r="T465" t="n">
+        <v>0</v>
+      </c>
+      <c r="U465" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V465" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:30:27.772265+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D466" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>85.3416548271987</v>
+      </c>
+      <c r="F466" t="n">
+        <v>0.0008516345988654952</v>
+      </c>
+      <c r="G466" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H466" t="n">
+        <v>0.1998880179171333</v>
+      </c>
+      <c r="I466" t="n">
+        <v>0.3365432769085063</v>
+      </c>
+      <c r="J466" t="n">
+        <v>0</v>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L466" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M466" t="n">
+        <v>34.09694631112428</v>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O466" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.1 trend_age=60 pullback=1.19×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>[0.7068, 0.375, 1.0, -0.6484, 1.0, 1.0, 2.0, -0.1641, -0.4931, 1.0, 1.0, 0.341, -0.6167, 0.1156, -0.1261, -1.8083, -0.6002, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6819, 0.0, 0.0, 0.0, 0.0, 0.4375, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S466" t="n">
+        <v>0</v>
+      </c>
+      <c r="T466" t="n">
+        <v>0</v>
+      </c>
+      <c r="U466" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V466" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:31:28.483514+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D467" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>77.08546300681901</v>
+      </c>
+      <c r="F467" t="n">
+        <v>0.0008516345988654952</v>
+      </c>
+      <c r="G467" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H467" t="n">
+        <v>0.1556291390728477</v>
+      </c>
+      <c r="I467" t="n">
+        <v>0.3228863230633262</v>
+      </c>
+      <c r="J467" t="n">
+        <v>0</v>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L467" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M467" t="n">
+        <v>34.09694631112428</v>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O467" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=34.1 trend_age=60 pullback=1.25×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>[0.5417, 0.375, 1.0, -0.6484, 1.0, 1.0, 2.0, -0.1766, -0.4976, 1.0, 1.0, 0.341, -0.65, 0.1043, -0.1261, -1.8787, -0.6887, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.6819, 0.0, 0.0, 0.0, 0.0, 0.4396, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S467" t="n">
+        <v>0</v>
+      </c>
+      <c r="T467" t="n">
+        <v>0</v>
+      </c>
+      <c r="U467" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V467" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:15:53.694542+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D468" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>74.83223480398466</v>
+      </c>
+      <c r="F468" t="n">
+        <v>0.0009280930980243068</v>
+      </c>
+      <c r="G468" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H468" t="n">
+        <v>0.1998880179171333</v>
+      </c>
+      <c r="I468" t="n">
+        <v>0.3344262468309432</v>
+      </c>
+      <c r="J468" t="n">
+        <v>0</v>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L468" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M468" t="n">
+        <v>36.4535621204986</v>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O468" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=36.5 trend_age=60 pullback=2.41×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>[0.4966, 0.375, 1.0, -0.5719, 0.9677, 1.0, 2.0, -0.3714, -0.4969, 0.9677, 1.0, 0.3645, -0.6853, -0.0585, -0.0399, -2.726, -0.6002, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.7291, 0.0, 0.0, 0.0, 0.0, 0.0312, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S468" t="n">
+        <v>0</v>
+      </c>
+      <c r="T468" t="n">
+        <v>0</v>
+      </c>
+      <c r="U468" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V468" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:16:54.485092+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D469" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>74.63632969251925</v>
+      </c>
+      <c r="F469" t="n">
+        <v>0.0009280930980243068</v>
+      </c>
+      <c r="G469" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H469" t="n">
+        <v>0.1998880179171333</v>
+      </c>
+      <c r="I469" t="n">
+        <v>0.3344262468309432</v>
+      </c>
+      <c r="J469" t="n">
+        <v>0</v>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L469" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M469" t="n">
+        <v>36.4535621204986</v>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O469" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=36.5 trend_age=60 pullback=2.45×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>[0.4927, 0.375, 1.0, -0.5719, 0.9671, 1.0, 2.0, -0.3764, -0.5004, 0.9671, 1.0, 0.3645, -0.706, -0.0651, -0.0399, -2.7799, -0.6002, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.7291, 0.0, 0.0, 0.0, 0.0, 0.0333, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S469" t="n">
+        <v>0</v>
+      </c>
+      <c r="T469" t="n">
+        <v>0</v>
+      </c>
+      <c r="U469" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V469" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:17:55.465247+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D470" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>75.73339831672247</v>
+      </c>
+      <c r="F470" t="n">
+        <v>0.0009280930980243068</v>
+      </c>
+      <c r="G470" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H470" t="n">
+        <v>0.1810089020771513</v>
+      </c>
+      <c r="I470" t="n">
+        <v>0.329303252514095</v>
+      </c>
+      <c r="J470" t="n">
+        <v>0</v>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L470" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M470" t="n">
+        <v>36.4535621204986</v>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O470" t="n">
+        <v>0.4999999999999449</v>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=36.5 trend_age=60 pullback=2.18×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>[0.5147, 0.375, 1.0, -0.5719, 0.9705, 1.0, 2.0, -0.3476, -0.4811, 0.9705, 1.0, 0.3645, -0.5901, -0.0266, -0.0399, -2.4782, -0.638, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.7291, 0.0, 0.0, 0.0, 0.0, 0.0354, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S470" t="n">
+        <v>0</v>
+      </c>
+      <c r="T470" t="n">
+        <v>0</v>
+      </c>
+      <c r="U470" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V470" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:18:56.146623+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D471" s="9" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>76.00766547277328</v>
+      </c>
+      <c r="F471" t="n">
+        <v>0.0009280930980243068</v>
+      </c>
+      <c r="G471" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H471" t="n">
+        <v>0.2021791767554479</v>
+      </c>
+      <c r="I471" t="n">
+        <v>0.3401248391858078</v>
+      </c>
+      <c r="J471" t="n">
+        <v>0</v>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L471" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M471" t="n">
+        <v>36.4535621204986</v>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O471" t="n">
+        <v>0.3999999999992898</v>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=36.5 trend_age=60 pullback=2.11×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>[0.5202, 0.375, 1.0, -0.5719, 0.9713, 1.0, 2.0, -0.34, -0.4763, 0.9713, 1.0, 0.3645, -0.5611, -0.0166, -0.0399, -2.4028, -0.5956, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.7291, 0.0, 0.0, 0.0, 0.0, 0.0375, 0.0, 0.0, 0.5]</t>
+        </is>
+      </c>
+      <c r="S471" t="n">
+        <v>0</v>
+      </c>
+      <c r="T471" t="n">
+        <v>0</v>
+      </c>
+      <c r="U471" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V471" t="inlineStr">
+        <is>
+          <t>tf_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:19:58.334024+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D472" s="6" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>81.73906240288541</v>
+      </c>
+      <c r="F472" t="n">
+        <v>0.000563166242660489</v>
+      </c>
+      <c r="G472" t="n">
+        <v>1</v>
+      </c>
+      <c r="H472" t="n">
+        <v>0.4135348168793276</v>
+      </c>
+      <c r="I472" t="n">
+        <v>0.4643204727552281</v>
+      </c>
+      <c r="J472" t="n">
+        <v>1</v>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L472" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M472" t="n">
+        <v>14.3370699212636</v>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O472" t="n">
+        <v>0</v>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>BB%B=-0.11 (extreme=1.36); RSI=27.5 (extreme=0.31); Wick ratio=1.50; ADX H1=14.3 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>[0.6348, 0.0, 1.0, -0.9368, 1.0, -1.0, 1.7757, -0.4496, -0.2833, 0.0378, 1.0, 0.2895, -0.6552, -0.1068, 0.3057, -2.5037, -0.1729, -0.6355, -0.1216, -0.6355, 0.5778, 0.0, -1.0, 0.2, 0.0, 0.0, 0.421, 0.0, 0.0, 0.0, 0.0, 0.0396, -0.6829, -0.3928, 0.3472]</t>
+        </is>
+      </c>
+      <c r="S472" t="n">
+        <v>0</v>
+      </c>
+      <c r="T472" t="n">
+        <v>0</v>
+      </c>
+      <c r="U472" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V472" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:26:00.410494+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D473" s="10" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>86.74057237862237</v>
+      </c>
+      <c r="F473" t="n">
+        <v>0.0006060234011882658</v>
+      </c>
+      <c r="G473" t="n">
+        <v>1</v>
+      </c>
+      <c r="H473" t="n">
+        <v>0.3958767408707096</v>
+      </c>
+      <c r="I473" t="n">
+        <v>0.4582172083646714</v>
+      </c>
+      <c r="J473" t="n">
+        <v>1</v>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L473" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M473" t="n">
+        <v>14.52539750407125</v>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O473" t="n">
+        <v>0</v>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>BB%B=-0.14 (extreme=1.47); RSI=26.5 (extreme=0.34); Wick ratio=3.06; ADX H1=14.5 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด EURUSD (BUY) เปิดอยู่แล้ว (Ticket 558961569)</t>
+        </is>
+      </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>[0.7348, 0.0, 1.0, -0.894, 1.0, -1.0, 1.6501, -0.4696, -0.278, 0.0387, 1.0, 0.2914, -0.6157, -0.14, 0.4023, -2.5577, -0.2082, -0.6478, -0.1478, -0.6381, 0.5778, 0.3333, -1.0, 0.2, 0.0, 0.0, 0.4173, 0.0, 0.0, 0.0, 0.0, 0.0542, -0.6906, -0.379, 0.2989]</t>
+        </is>
+      </c>
+      <c r="S473" t="n">
+        <v>0</v>
+      </c>
+      <c r="T473" t="n">
+        <v>0</v>
+      </c>
+      <c r="U473" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V473" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:27:00.571961+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D474" s="10" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>81.04014653002346</v>
+      </c>
+      <c r="F474" t="n">
+        <v>0.0006060234011882658</v>
+      </c>
+      <c r="G474" t="n">
+        <v>1</v>
+      </c>
+      <c r="H474" t="n">
+        <v>0.3958767408707096</v>
+      </c>
+      <c r="I474" t="n">
+        <v>0.4578742285943203</v>
+      </c>
+      <c r="J474" t="n">
+        <v>1</v>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L474" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M474" t="n">
+        <v>14.52539750407125</v>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O474" t="n">
+        <v>0.1000000000006551</v>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>BB%B=-0.17 (extreme=1.57); RSI=25.6 (extreme=0.36); Wick ratio=1.17; ADX H1=14.5 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด EURUSD (BUY) เปิดอยู่แล้ว (Ticket 558961569)</t>
+        </is>
+      </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>[0.6208, 0.0, 1.0, -0.894, 1.0, -1.0, 1.6501, -0.4883, -0.2928, 0.0397, 1.0, 0.2914, -0.7255, -0.1704, 0.4023, -2.7887, -0.2082, -0.6576, -0.1685, -0.6381, 0.5778, 0.3333, -1.0, 0.2, 0.0, 0.0, 0.4173, 0.0, 0.0, 0.0, 0.0, 0.0562, -0.7466, -0.393, 0.2989]</t>
+        </is>
+      </c>
+      <c r="S474" t="n">
+        <v>0</v>
+      </c>
+      <c r="T474" t="n">
+        <v>0</v>
+      </c>
+      <c r="U474" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V474" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:28:00.570875+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D475" s="10" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>86.843319836814</v>
+      </c>
+      <c r="F475" t="n">
+        <v>0.0006060234011882658</v>
+      </c>
+      <c r="G475" t="n">
+        <v>1</v>
+      </c>
+      <c r="H475" t="n">
+        <v>0.3958767408707096</v>
+      </c>
+      <c r="I475" t="n">
+        <v>0.4582172083646714</v>
+      </c>
+      <c r="J475" t="n">
+        <v>1</v>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L475" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M475" t="n">
+        <v>14.52539750407125</v>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O475" t="n">
+        <v>0</v>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>BB%B=-0.15 (extreme=1.49); RSI=26.3 (extreme=0.34); Wick ratio=2.42; ADX H1=14.5 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด EURUSD (BUY) เปิดอยู่แล้ว (Ticket 558961569)</t>
+        </is>
+      </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>[0.7369, 0.0, 1.0, -0.894, 1.0, -1.0, 1.6501, -0.4737, -0.2812, 0.0389, 1.0, 0.2914, -0.6392, -0.1467, 0.4023, -2.6072, -0.2082, -0.6517, -0.1561, -0.6381, 0.5778, 0.3333, -1.0, 0.2, 0.0, 0.0, 0.4173, 0.0, 0.0, 0.0, 0.0, 0.0583, -0.7026, -0.382, 0.2989]</t>
+        </is>
+      </c>
+      <c r="S475" t="n">
+        <v>0</v>
+      </c>
+      <c r="T475" t="n">
+        <v>0</v>
+      </c>
+      <c r="U475" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V475" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:29:00.604984+00:00</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D476" s="10" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>78.0277426181121</v>
+      </c>
+      <c r="F476" t="n">
+        <v>0.0006060234011882658</v>
+      </c>
+      <c r="G476" t="n">
+        <v>1</v>
+      </c>
+      <c r="H476" t="n">
+        <v>0.3958767408707096</v>
+      </c>
+      <c r="I476" t="n">
+        <v>0.4587318541252971</v>
+      </c>
+      <c r="J476" t="n">
+        <v>1</v>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L476" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M476" t="n">
+        <v>14.52539750407125</v>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O476" t="n">
+        <v>0</v>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>BB%B=-0.20 (extreme=1.66); RSI=24.7 (extreme=0.38); Wick ratio=0.48; ADX H1=14.5 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด EURUSD (BUY) เปิดอยู่แล้ว (Ticket 558961569)</t>
+        </is>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>[0.5606, 0.0, 1.0, -0.894, 1.0, -1.0, 1.6501, -0.5057, -0.3075, 0.0407, 1.0, 0.2914, -0.8353, -0.1984, 0.4023, -3.0, -0.2082, -0.6647, -0.1837, -0.6381, 0.5778, 0.3333, -1.0, 0.2, 0.0, 0.0, 0.4173, 0.0, 0.0, 0.0, 0.0, 0.0604, -0.8026, -0.407, 0.2989]</t>
+        </is>
+      </c>
+      <c r="S476" t="n">
+        <v>0</v>
+      </c>
+      <c r="T476" t="n">
+        <v>0</v>
+      </c>
+      <c r="U476" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V476" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:32:02.469982+00:00</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D477" s="10" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>80.35207420391511</v>
+      </c>
+      <c r="F477" t="n">
+        <v>0.0006034503052822237</v>
+      </c>
+      <c r="G477" t="n">
+        <v>1</v>
+      </c>
+      <c r="H477" t="n">
+        <v>0.4523219814241486</v>
+      </c>
+      <c r="I477" t="n">
+        <v>0.4684861105277761</v>
+      </c>
+      <c r="J477" t="n">
+        <v>1</v>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L477" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M477" t="n">
+        <v>14.73775803064691</v>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O477" t="n">
+        <v>0</v>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>BB%B=-0.14 (extreme=1.46); RSI=23.0 (extreme=0.43); Wick ratio=0.77; ADX H1=14.7 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด EURUSD (BUY) เปิดอยู่แล้ว (Ticket 558961569)</t>
+        </is>
+      </c>
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>[0.607, 0.0, 1.0, -0.8965, 1.0, -1.0, 1.6571, -0.5402, -0.4029, 0.0554, 1.0, 0.3182, -0.8561, -0.1388, 0.3862, -3.0, -0.0954, -0.6849, -0.2265, -0.6381, 0.5778, 0.3333, -1.0, 0.2, 0.0, 0.0, 0.3636, 0.0, 0.0, 0.0, 0.0, 0.0667, -0.8481, -0.6254, 0.3069]</t>
+        </is>
+      </c>
+      <c r="S477" t="n">
+        <v>0</v>
+      </c>
+      <c r="T477" t="n">
+        <v>0</v>
+      </c>
+      <c r="U477" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V477" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:33:03.488699+00:00</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D478" s="10" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>81.42150703077665</v>
+      </c>
+      <c r="F478" t="n">
+        <v>0.0006034503052822237</v>
+      </c>
+      <c r="G478" t="n">
+        <v>1</v>
+      </c>
+      <c r="H478" t="n">
+        <v>0.3958767408707096</v>
+      </c>
+      <c r="I478" t="n">
+        <v>0.4552427947415073</v>
+      </c>
+      <c r="J478" t="n">
+        <v>1</v>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L478" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M478" t="n">
+        <v>14.73775803064691</v>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O478" t="n">
+        <v>0</v>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>BB%B=-0.13 (extreme=1.44); RSI=23.2 (extreme=0.42); Wick ratio=1.00; ADX H1=14.7 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด EURUSD (BUY) เปิดอยู่แล้ว (Ticket 558961569)</t>
+        </is>
+      </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>[0.6284, 0.0, 1.0, -0.8965, 1.0, -1.0, 1.6571, -0.5369, -0.3997, 0.0552, 1.0, 0.3182, -0.8345, -0.1332, 0.3862, -3.0, -0.2082, -0.6842, -0.2251, -0.6381, 0.5778, 0.3333, -1.0, 0.2, 0.0, 0.0, 0.3636, 0.0, 0.0, 0.0, 0.0, 0.0688, -0.8361, -0.6224, 0.3069]</t>
+        </is>
+      </c>
+      <c r="S478" t="n">
+        <v>0</v>
+      </c>
+      <c r="T478" t="n">
+        <v>0</v>
+      </c>
+      <c r="U478" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V478" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:36:04.597557+00:00</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D479" s="10" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>81.03311556721665</v>
+      </c>
+      <c r="F479" t="n">
+        <v>0.0006034503052822237</v>
+      </c>
+      <c r="G479" t="n">
+        <v>1</v>
+      </c>
+      <c r="H479" t="n">
+        <v>0.4523219814241486</v>
+      </c>
+      <c r="I479" t="n">
+        <v>0.4684861105277761</v>
+      </c>
+      <c r="J479" t="n">
+        <v>1</v>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L479" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M479" t="n">
+        <v>14.73775803064691</v>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O479" t="n">
+        <v>0</v>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>BB%B=-0.14 (extreme=1.45); RSI=23.1 (extreme=0.42); Wick ratio=0.92; ADX H1=14.7 (block=30.0); SL=0.00100 TP=0.00100 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>correlation:มีเทรด EURUSD (BUY) เปิดอยู่แล้ว (Ticket 558961569)</t>
+        </is>
+      </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>[0.6207, 0.0, 1.0, -0.8965, 1.0, -1.0, 1.6571, -0.538, -0.4008, 0.0552, 1.0, 0.3182, -0.8417, -0.1351, 0.3862, -3.0, -0.0954, -0.681, -0.2182, -0.6381, 0.5778, 0.3333, -1.0, 0.2, 0.0, 0.0, 0.3636, 0.0, 0.0, 0.0, 0.0, 0.075, -0.8401, -0.6234, 0.3069]</t>
+        </is>
+      </c>
+      <c r="S479" t="n">
+        <v>0</v>
+      </c>
+      <c r="T479" t="n">
+        <v>0</v>
+      </c>
+      <c r="U479" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V479" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
         </is>
       </c>
     </row>

--- a/ftmo_trading_bot/logs/ftmo_trades.xlsx
+++ b/ftmo_trading_bot/logs/ftmo_trades.xlsx
@@ -1015,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1101,6 +1101,80 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9998.950000000001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1514,7 +1588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V30"/>
+  <dimension ref="A1:V81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4097,7 +4171,6 @@
           <t>TF BUY ADX=30.8 trend_age=60 pullback=0.33×ATR H4=1 D1=1</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>[0.4392, 0.375, 1.0, -0.3711, 0.2227, 1.0, 2.0, -0.0554, -0.1355, 0.2227, 1.0, 0.3081, 0.2444, 0.2263, 0.252, -0.124, 0.2321, -0.0042, -0.0084, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6163, -0.4789, 0.4782, 0.0, 0.0, 0.0, 0.0, -0.0699, 0.374, 0.1833]</t>
@@ -4115,6 +4188,4341 @@
         </is>
       </c>
       <c r="V30" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:31:44.688383+00:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>71.60396125933265</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.1136059764368443</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.6103092783505155</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.4414904635841283</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-0.2816441357135773</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M31" t="n">
+        <v>30.81321610973426</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>0.8000000000009777</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.8 trend_age=60 pullback=0.41×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>[0.4321, 0.375, 1.0, -0.3639, 0.2222, 1.0, 2.0, -0.0727, -0.1408, 0.2222, 1.0, 0.3081, 0.203, 0.1894, 0.2597, -0.2201, 0.2206, -0.0071, -0.0142, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0001, 0.0, 0.6163, -0.4759, 0.4782, 0.0, 0.0, 0.0, 0.0, -0.0753, 0.3701, 0.1702]</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:32:45.308478+00:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>71.76889640444715</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.1136059764368443</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.6103092783505155</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.4414904635841283</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-0.2881410717964172</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M32" t="n">
+        <v>30.81321610973426</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>0.4999999999995453</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.8 trend_age=60 pullback=0.37×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>[0.4354, 0.375, 1.0, -0.3639, 0.2224, 1.0, 2.0, -0.0649, -0.138, 0.2224, 1.0, 0.3081, 0.2218, 0.2061, 0.2597, -0.176, 0.2206, -0.0058, -0.0116, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6163, -0.4759, 0.4782, 0.0, 0.0, 0.0, 0.0, -0.0726, 0.3701, 0.1761]</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:33:45.985937+00:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>72.06577889454627</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.1136059764368443</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.6160377358490565</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.4498463275359473</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-0.27217698097229</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M33" t="n">
+        <v>30.81321610973426</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>0.2999999999985903</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.8 trend_age=60 pullback=0.30×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>[0.4413, 0.375, 1.0, -0.3639, 0.2228, 1.0, 2.0, -0.0505, -0.1329, 0.2228, 1.0, 0.3081, 0.2556, 0.2366, 0.2597, -0.0968, 0.2321, -0.0034, -0.0068, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6163, -0.4759, 0.4782, 0.0, 0.0, 0.0, 0.0, -0.0678, 0.3701, 0.1869]</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:34:46.734633+00:00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>71.99980509353004</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.1136059764368443</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.6160377358490565</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.4498463275359473</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-0.2733005583286285</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M34" t="n">
+        <v>30.81321610973426</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>0.2999999999985903</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.8 trend_age=60 pullback=0.32×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>[0.44, 0.375, 1.0, -0.3639, 0.2227, 1.0, 2.0, -0.0538, -0.1341, 0.2227, 1.0, 0.3081, 0.2481, 0.2297, 0.2597, -0.1144, 0.2321, -0.0039, -0.0079, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6163, -0.4759, 0.4782, 0.0, 0.0, 0.0, 0.0, -0.0689, 0.3701, 0.1845]</t>
+        </is>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:35:47.357394+00:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>72.03279200015731</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.1136059764368443</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.6103092783505155</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.4434446457058364</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-0.2882546782493591</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M35" t="n">
+        <v>30.81321610973426</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>0.2999999999985903</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.8 trend_age=60 pullback=0.31×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>[0.4407, 0.375, 1.0, -0.3639, 0.2228, 1.0, 2.0, -0.0522, -0.1335, 0.2228, 1.0, 0.3081, 0.2519, 0.2332, 0.2597, -0.1056, 0.2206, -0.0037, -0.0074, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6163, -0.4759, 0.4782, 0.0, 0.0, 0.0, 0.0, -0.0684, 0.3701, 0.1857]</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:36:47.982734+00:00</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>72.4286339251631</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.1136059764368443</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.6103092783505155</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.4434446457058364</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-0.2714778184890747</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M36" t="n">
+        <v>30.81321610973426</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>0.7000000000005002</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.8 trend_age=60 pullback=0.21×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>[0.4486, 0.375, 1.0, -0.3639, 0.2234, 1.0, 2.0, -0.0323, -0.1268, 0.2234, 1.0, 0.3081, 0.297, 0.2749, 0.2597, 0.0, 0.2206, -0.0005, -0.001, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0001, 0.0, 0.6163, -0.4759, 0.4782, 0.0, 0.0, 0.0, 0.0, -0.062, 0.3701, 0.2004]</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:37:48.686754+00:00</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>80.89070117122482</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.1136774050082889</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.6103092783505155</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.4434446457058364</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-0.1975826323032379</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M37" t="n">
+        <v>30.81321610973426</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>0.5000000000023874</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.8 trend_age=60 pullback=0.10×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>[0.6178, 0.375, 1.0, -0.3632, 0.2241, 1.0, 2.0, -0.0079, -0.1188, 0.2241, 1.0, 0.3081, 0.3496, 0.3249, 0.2605, 0.1232, 0.2206, 0.0, 0.0, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6163, -0.4756, 0.4782, 0.0, 0.0, 0.0, 0.0, -0.0545, 0.3698, 0.2144]</t>
+        </is>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:38:49.334531+00:00</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>72.39620274513753</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.1136774050082889</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.6103092783505155</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.4434446457058364</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-0.2689872682094574</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M38" t="n">
+        <v>30.81321610973426</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>0.2999999999985903</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.8 trend_age=60 pullback=0.22×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>[0.4479, 0.375, 1.0, -0.3632, 0.2233, 1.0, 2.0, -0.034, -0.1272, 0.2233, 1.0, 0.3081, 0.2932, 0.2713, 0.2605, -0.0088, 0.2206, -0.0008, -0.0016, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6163, -0.4756, 0.4782, 0.0, 0.0, 0.0, 0.0, -0.0624, 0.3698, 0.1992]</t>
+        </is>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:39:50.172264+00:00</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>80.89070117122482</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.1136774050082889</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.6103092783505155</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.4434446457058364</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-0.1975549757480621</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M39" t="n">
+        <v>30.81321610973426</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>0.3000000000014325</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.8 trend_age=60 pullback=0.10×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>[0.6178, 0.375, 1.0, -0.3632, 0.2241, 1.0, 2.0, -0.0079, -0.1188, 0.2241, 1.0, 0.3081, 0.3496, 0.3249, 0.2605, 0.1232, 0.2206, 0.0, 0.0, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6163, -0.4756, 0.4782, 0.0, 0.0, 0.0, 0.0, -0.0545, 0.3698, 0.2144]</t>
+        </is>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:40:50.819907+00:00</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>81.12247776334398</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.1143202621512893</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.4225698675156143</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-0.4274655282497406</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M40" t="n">
+        <v>30.81321610973421</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>0.3000000000014325</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.8 trend_age=60 pullback=0.04×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>[0.6224, 0.375, 1.0, -0.3568, 0.2244, 1.0, 2.0, 0.0042, -0.1142, 0.2244, 1.0, 0.3081, 0.3759, 0.3504, 0.2674, 0.1837, 0.0954, 0.0, 0.0, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6163, -0.4729, 0.4782, 0.0, 0.0, 0.0, 0.0, -0.0504, 0.3663, 0.2201]</t>
+        </is>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:41:51.430891+00:00</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>81.14824811309181</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.1148202621514002</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.4225698675156143</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-0.4317415356636047</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M41" t="n">
+        <v>30.7275365404732</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>0.4999999999995453</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.7 trend_age=60 pullback=0.02×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>[0.623, 0.375, 1.0, -0.3518, 0.2248, 1.0, 2.0, 0.0177, -0.1093, 0.2248, 1.0, 0.3073, 0.406, 0.3799, 0.2728, 0.2526, 0.0954, 0.0, 0.0, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6146, -0.4634, 0.4696, 0.0, 0.0, 0.0, 0.0, -0.046, 0.3636, 0.2264]</t>
+        </is>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:42:52.055666+00:00</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>81.20963251278188</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.1148202621514002</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.4225698675156143</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-0.4289396703243256</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M42" t="n">
+        <v>30.7275365404732</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>0.3000000000014325</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.7 trend_age=60 pullback=0.00×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>[0.6242, 0.375, 1.0, -0.3518, 0.2247, 1.0, 2.0, 0.0143, -0.1104, 0.2247, 1.0, 0.3073, 0.3985, 0.3725, 0.2728, 0.2352, 0.0954, 0.0, 0.0, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6146, -0.4634, 0.4696, 0.0, 0.0, 0.0, 0.0, -0.047, 0.3636, 0.2248]</t>
+        </is>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:43:52.706766+00:00</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>80.90698510980826</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.1148202621514002</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-0.4363410174846649</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M43" t="n">
+        <v>30.7275365404732</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>0.2999999999985903</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.7 trend_age=60 pullback=0.08×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>[0.6181, 0.375, 1.0, -0.3518, 0.2242, 1.0, 2.0, -0.0027, -0.116, 0.2242, 1.0, 0.3073, 0.3609, 0.3358, 0.2728, 0.1481, 0.0954, 0.0, 0.0, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6146, -0.4634, 0.4696, 0.0, 0.0, 0.0, 0.0, -0.0523, 0.3636, 0.2169]</t>
+        </is>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:44:53.305947+00:00</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>72.18872531222462</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.1148202621514002</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J44" t="n">
+        <v>-0.3869649171829224</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M44" t="n">
+        <v>30.7275365404732</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>0.899999999998613</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.7 trend_age=60 pullback=0.25×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>[0.4438, 0.375, 1.0, -0.3518, 0.2231, 1.0, 2.0, -0.0407, -0.1282, 0.2231, 1.0, 0.3073, 0.2782, 0.2573, 0.2728, -0.0435, 0.0954, -0.0018, -0.0037, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0001, 0.0, 0.6146, -0.4634, 0.4696, 0.0, 0.0, 0.0, 0.0, -0.0639, 0.3636, 0.1942]</t>
+        </is>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:45:53.969061+00:00</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>72.18872531222462</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.1148202621514002</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-0.3869453072547913</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M45" t="n">
+        <v>30.7275365404732</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>0.7999999999981355</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.7 trend_age=60 pullback=0.25×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>[0.4438, 0.375, 1.0, -0.3518, 0.2231, 1.0, 2.0, -0.0407, -0.1282, 0.2231, 1.0, 0.3073, 0.2782, 0.2573, 0.2728, -0.0435, 0.0954, -0.0018, -0.0037, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0001, 0.0, 0.6146, -0.4634, 0.4696, 0.0, 0.0, 0.0, 0.0, -0.0639, 0.3636, 0.1942]</t>
+        </is>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:46:54.622650+00:00</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>72.25402190215554</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.1148202621514002</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J46" t="n">
+        <v>-0.379583865404129</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M46" t="n">
+        <v>30.7275365404732</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>0.3000000000014325</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.7 trend_age=60 pullback=0.23×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>[0.4451, 0.375, 1.0, -0.3518, 0.2232, 1.0, 2.0, -0.0374, -0.1271, 0.2232, 1.0, 0.3073, 0.2857, 0.2643, 0.2728, -0.0261, 0.0954, -0.0013, -0.0026, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6146, -0.4634, 0.4696, 0.0, 0.0, 0.0, 0.0, -0.0629, 0.3636, 0.1967]</t>
+        </is>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:47:55.267803+00:00</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>72.25402190215554</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.1148202621514002</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J47" t="n">
+        <v>-0.379583865404129</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M47" t="n">
+        <v>30.7275365404732</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>0.3000000000014325</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.7 trend_age=60 pullback=0.23×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>[0.4451, 0.375, 1.0, -0.3518, 0.2232, 1.0, 2.0, -0.0374, -0.1271, 0.2232, 1.0, 0.3073, 0.2857, 0.2643, 0.2728, -0.0261, 0.0954, -0.0013, -0.0026, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6146, -0.4634, 0.4696, 0.0, 0.0, 0.0, 0.0, -0.0629, 0.3636, 0.1967]</t>
+        </is>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:48:55.915288+00:00</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>72.12342867334499</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.1148202621514002</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-0.3941910266876221</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M48" t="n">
+        <v>30.7275365404732</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>0.2999999999985903</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.7 trend_age=60 pullback=0.27×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>[0.4425, 0.375, 1.0, -0.3518, 0.223, 1.0, 2.0, -0.044, -0.1293, 0.223, 1.0, 0.3073, 0.2707, 0.2504, 0.2728, -0.061, 0.0954, -0.0024, -0.0047, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6146, -0.4634, 0.4696, 0.0, 0.0, 0.0, 0.0, -0.065, 0.3636, 0.1918]</t>
+        </is>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:49:56.573636+00:00</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>71.92753846301065</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.1148202621514002</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J49" t="n">
+        <v>-0.4186246991157532</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M49" t="n">
+        <v>30.7275365404732</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>0.3000000000014325</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.7 trend_age=60 pullback=0.31×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>[0.4386, 0.375, 1.0, -0.3518, 0.2227, 1.0, 2.0, -0.0538, -0.1326, 0.2227, 1.0, 0.3073, 0.2481, 0.2297, 0.2728, -0.1132, 0.0954, -0.0042, -0.0084, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6146, -0.4634, 0.4696, 0.0, 0.0, 0.0, 0.0, -0.0682, 0.3636, 0.1845]</t>
+        </is>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:50:57.215424+00:00</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>71.73164781208925</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.1148202621514002</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.4219210325523936</v>
+      </c>
+      <c r="J50" t="n">
+        <v>-0.4391078352928162</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M50" t="n">
+        <v>30.7275365404732</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>0.899999999998613</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.7 trend_age=60 pullback=0.36×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>[0.4346, 0.375, 1.0, -0.3518, 0.2225, 1.0, 2.0, -0.0634, -0.136, 0.2225, 1.0, 0.3073, 0.2256, 0.2094, 0.2728, -0.1655, 0.0954, -0.0055, -0.011, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0001, 0.0, 0.6146, -0.4634, 0.4696, 0.0, 0.0, 0.0, 0.0, -0.0713, 0.3636, 0.1773]</t>
+        </is>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:51:57.839732+00:00</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>71.96018686199474</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.1148202621514002</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-0.4131303727626801</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M51" t="n">
+        <v>30.7275365404732</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>0.7999999999981355</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.7 trend_age=60 pullback=0.31×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>[0.4392, 0.375, 1.0, -0.3518, 0.2228, 1.0, 2.0, -0.0522, -0.1321, 0.2228, 1.0, 0.3073, 0.2519, 0.2332, 0.2728, -0.1045, 0.0954, -0.0037, -0.0074, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0001, 0.0, 0.6146, -0.4634, 0.4696, 0.0, 0.0, 0.0, 0.0, -0.0676, 0.3636, 0.1857]</t>
+        </is>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:52:58.413568+00:00</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>72.05813198551778</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.1148202621514002</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J52" t="n">
+        <v>-0.4017432034015656</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M52" t="n">
+        <v>30.7275365404732</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>0.4999999999995453</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.7 trend_age=60 pullback=0.28×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>[0.4412, 0.375, 1.0, -0.3518, 0.2229, 1.0, 2.0, -0.0473, -0.1304, 0.2229, 1.0, 0.3073, 0.2632, 0.2435, 0.2728, -0.0784, 0.0954, -0.0029, -0.0058, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6146, -0.4634, 0.4696, 0.0, 0.0, 0.0, 0.0, -0.0661, 0.3636, 0.1894]</t>
+        </is>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:53:59.031028+00:00</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>72.31931844314255</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.1148202621514002</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J53" t="n">
+        <v>-0.372572660446167</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M53" t="n">
+        <v>30.7275365404732</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>0.2999999999985903</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.7 trend_age=60 pullback=0.22×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>[0.4464, 0.375, 1.0, -0.3518, 0.2233, 1.0, 2.0, -0.034, -0.126, 0.2233, 1.0, 0.3073, 0.2932, 0.2713, 0.2728, -0.0087, 0.0954, -0.0008, -0.0016, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6146, -0.4634, 0.4696, 0.0, 0.0, 0.0, 0.0, -0.0618, 0.3636, 0.1992]</t>
+        </is>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:54:59.601584+00:00</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>72.41726316285505</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.1148202621514002</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-0.3624171018600464</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M54" t="n">
+        <v>30.7275365404732</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>0.3000000000014325</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.7 trend_age=60 pullback=0.19×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>[0.4483, 0.375, 1.0, -0.3518, 0.2235, 1.0, 2.0, -0.029, -0.1243, 0.2235, 1.0, 0.3073, 0.3045, 0.2819, 0.2728, 0.0174, 0.0954, -0.0, -0.0, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6146, -0.4634, 0.4696, 0.0, 0.0, 0.0, 0.0, -0.0602, 0.3636, 0.2029]</t>
+        </is>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:56:00.227845+00:00</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>72.31931844314255</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.1148202621514002</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J55" t="n">
+        <v>-0.372572660446167</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M55" t="n">
+        <v>30.7275365404732</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>0.2999999999985903</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.7 trend_age=60 pullback=0.22×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>[0.4464, 0.375, 1.0, -0.3518, 0.2233, 1.0, 2.0, -0.034, -0.126, 0.2233, 1.0, 0.3073, 0.2932, 0.2713, 0.2728, -0.0087, 0.0954, -0.0008, -0.0016, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6146, -0.4634, 0.4696, 0.0, 0.0, 0.0, 0.0, -0.0618, 0.3636, 0.1992]</t>
+        </is>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:57:00.825050+00:00</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>72.3519666952823</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.1148202621514002</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J56" t="n">
+        <v>-0.370951235294342</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M56" t="n">
+        <v>30.7275365404732</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>0.2999999999985903</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.7 trend_age=60 pullback=0.21×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>[0.447, 0.375, 1.0, -0.3518, 0.2234, 1.0, 2.0, -0.0323, -0.1254, 0.2234, 1.0, 0.3073, 0.297, 0.2749, 0.2728, 0.0, 0.0954, -0.0008, -0.0016, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6146, -0.4634, 0.4696, 0.0, 0.0, 0.0, 0.0, -0.0613, 0.3636, 0.2004]</t>
+        </is>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:58:01.467078+00:00</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>80.77639285974908</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.1148202621514002</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J57" t="n">
+        <v>-0.4394687116146088</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M57" t="n">
+        <v>30.7275365404732</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>0.7999999999981355</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.7 trend_age=60 pullback=0.11×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>[0.6155, 0.375, 1.0, -0.3518, 0.224, 1.0, 2.0, -0.0097, -0.1182, 0.224, 1.0, 0.3073, 0.3459, 0.3213, 0.2728, 0.1132, 0.0954, 0.0, 0.0, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0001, 0.0, 0.6146, -0.4634, 0.4696, 0.0, 0.0, 0.0, 0.0, -0.0544, 0.3636, 0.2136]</t>
+        </is>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-06-04 07:59:02.113693+00:00</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>72.54785595118219</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.1148202621514002</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J58" t="n">
+        <v>-0.3578170239925385</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M58" t="n">
+        <v>30.7275365404732</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>0.899999999998613</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=30.7 trend_age=60 pullback=0.16×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>[0.451, 0.375, 1.0, -0.3518, 0.2237, 1.0, 2.0, -0.0221, -0.1221, 0.2237, 1.0, 0.3073, 0.3195, 0.2962, 0.2728, 0.0523, 0.0954, 0.0, 0.0, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0001, 0.0, 0.6146, -0.4634, 0.4696, 0.0, 0.0, 0.0, 0.0, -0.0581, 0.3636, 0.2079]</t>
+        </is>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:00:02.734056+00:00</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>73.61574185556589</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.1073331005662459</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M59" t="n">
+        <v>32.06356173628639</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>0.899999999998613</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.21×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>[0.4723, 0.375, 1.0, -0.4267, 0.22, 1.0, 2.0, -0.0332, -0.1196, 0.22, 1.0, 0.3206, 0.297, 0.2786, 0.1808, -0.7081, 0.0954, -0.0005, -0.001, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0001, 0.0, 0.6413, -0.4603, 0.4417, 0.0, 0.0, 0.0, 0.0, -0.0979, 0.4096, 0.1522]</t>
+        </is>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:01:03.416141+00:00</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>82.31446692972261</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.1083331005664677</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J60" t="n">
+        <v>-0.5708571672439575</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M60" t="n">
+        <v>32.06356173628632</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>0.9000000000014552</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.04×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>[0.6463, 0.375, 1.0, -0.4167, 0.221, 1.0, 2.0, 0.0039, -0.1067, 0.221, 1.0, 0.3206, 0.3722, 0.3502, 0.1916, -0.5169, 0.0954, 0.0, 0.0, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0001, 0.0, 0.6413, -0.4561, 0.4417, 0.0, 0.0, 0.0021, 0.0, -0.0858, 0.4042, 0.1735]</t>
+        </is>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:02:04.044284+00:00</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>82.07265247870198</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.1083331005664677</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J61" t="n">
+        <v>-0.5381783843040466</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M61" t="n">
+        <v>32.06356173628632</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>0.2999999999985903</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.10×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>[0.6415, 0.375, 1.0, -0.4167, 0.2206, 1.0, 2.0, -0.0091, -0.1108, 0.2206, 1.0, 0.3206, 0.3459, 0.3248, 0.1916, -0.5815, 0.0954, 0.0, 0.0, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6413, -0.4561, 0.4417, 0.0, 0.0, 0.0042, 0.0, -0.0897, 0.4042, 0.1672]</t>
+        </is>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:03:04.701739+00:00</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>73.58902177761527</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.1083331005664677</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J62" t="n">
+        <v>-0.9816379547119141</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M62" t="n">
+        <v>32.06356173628632</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>0.6000000000000227</v>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.22×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>[0.4718, 0.375, 1.0, -0.4167, 0.2199, 1.0, 2.0, -0.035, -0.1191, 0.2199, 1.0, 0.3206, 0.2932, 0.2751, 0.1916, -0.7108, 0.0954, -0.0008, -0.0016, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0001, 0.0, 0.6413, -0.4561, 0.4417, 0.0, 0.0, 0.0063, 0.0, -0.0976, 0.4042, 0.1509]</t>
+        </is>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:04:05.558425+00:00</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>73.39227706913907</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.1094045291381322</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J63" t="n">
+        <v>-0.9035657644271851</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M63" t="n">
+        <v>32.06356173628624</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
+        <v>0.899999999998613</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.27×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>[0.4678, 0.375, 1.0, -0.406, 0.2197, 1.0, 2.0, -0.0456, -0.1214, 0.2197, 1.0, 0.3206, 0.2707, 0.2543, 0.2031, -0.7587, 0.0954, -0.0024, -0.0047, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0001, 0.0, 0.6413, -0.4516, 0.4417, 0.0, 0.0, 0.0083, 0.0, -0.0999, 0.3985, 0.1435]</t>
+        </is>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:05:06.146679+00:00</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>73.32384407823712</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.1094045291381322</v>
+      </c>
+      <c r="G64" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J64" t="n">
+        <v>-0.901315450668335</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M64" t="n">
+        <v>32.06356173628624</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
+        <v>0.6000000000000227</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.28×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>[0.4665, 0.375, 1.0, -0.406, 0.2196, 1.0, 2.0, -0.049, -0.1226, 0.2196, 1.0, 0.3206, 0.2632, 0.2474, 0.2031, -0.7769, 0.0954, -0.0029, -0.0058, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0001, 0.0, 0.6413, -0.4516, 0.4417, 0.0, 0.0, 0.0104, 0.0, -0.101, 0.3985, 0.141]</t>
+        </is>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:06:06.767510+00:00</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>73.8370903164415</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.1094045291381322</v>
+      </c>
+      <c r="G65" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J65" t="n">
+        <v>-0.9161676168441772</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M65" t="n">
+        <v>32.06356173628624</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O65" t="n">
+        <v>0.3999999999990678</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.16×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>[0.4767, 0.375, 1.0, -0.406, 0.2203, 1.0, 2.0, -0.0223, -0.1138, 0.2203, 1.0, 0.3206, 0.3195, 0.2998, 0.2031, -0.6398, 0.0954, 0.0, 0.0, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6413, -0.4516, 0.4417, 0.0, 0.0, 0.0125, 0.0, -0.0927, 0.3985, 0.1597]</t>
+        </is>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:07:07.434184+00:00</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>73.56335933215355</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.1094045291381322</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J66" t="n">
+        <v>-0.8954083919525146</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M66" t="n">
+        <v>32.06356173628624</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>0.3000000000014325</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.22×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>[0.4713, 0.375, 1.0, -0.406, 0.2199, 1.0, 2.0, -0.0367, -0.1185, 0.2199, 1.0, 0.3206, 0.2895, 0.2716, 0.2031, -0.713, 0.0954, -0.001, -0.0021, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6413, -0.4516, 0.4417, 0.0, 0.0, 0.0146, 0.0, -0.0972, 0.3985, 0.1497]</t>
+        </is>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:08:08.051696+00:00</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>82.00817178383137</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.1094045291381322</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J67" t="n">
+        <v>-0.480199933052063</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M67" t="n">
+        <v>32.06356173628624</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>0.2999999999985903</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.12×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>[0.6402, 0.375, 1.0, -0.406, 0.2205, 1.0, 2.0, -0.0129, -0.1109, 0.2205, 1.0, 0.3206, 0.3383, 0.3177, 0.2031, -0.5941, 0.0954, 0.0, 0.0, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6413, -0.4516, 0.4417, 0.0, 0.0, 0.0167, 0.0, -0.09, 0.3985, 0.1654]</t>
+        </is>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:09:08.688194+00:00</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>81.97395551483086</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.1094045291381322</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J68" t="n">
+        <v>-0.4763023853302002</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M68" t="n">
+        <v>32.06356173628624</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>0.3000000000014325</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.12×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>[0.6395, 0.375, 1.0, -0.406, 0.2205, 1.0, 2.0, -0.0148, -0.1115, 0.2205, 1.0, 0.3206, 0.3346, 0.3141, 0.2031, -0.6033, 0.0954, 0.0, 0.0, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6413, -0.4516, 0.4417, 0.0, 0.0, 0.0188, 0.0, -0.0905, 0.3985, 0.1645]</t>
+        </is>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:10:09.340370+00:00</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>73.59757574803166</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.1094045291381322</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J69" t="n">
+        <v>-0.8855031728744507</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M69" t="n">
+        <v>32.06356173628624</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>0.2999999999985903</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.22×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>[0.472, 0.375, 1.0, -0.406, 0.2199, 1.0, 2.0, -0.035, -0.1179, 0.2199, 1.0, 0.3206, 0.2932, 0.2751, 0.2031, -0.7038, 0.0954, -0.0008, -0.0016, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6413, -0.4516, 0.4417, 0.0, 0.0, 0.0208, 0.0, -0.0966, 0.3985, 0.1509]</t>
+        </is>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:11:09.991603+00:00</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>73.63179215166871</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.1094045291381322</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-0.8813532590866089</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M70" t="n">
+        <v>32.06356173628624</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>0.2999999999985903</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.21×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>[0.4726, 0.375, 1.0, -0.406, 0.22, 1.0, 2.0, -0.0332, -0.1173, 0.22, 1.0, 0.3206, 0.297, 0.2786, 0.2031, -0.6947, 0.0954, -0.0005, -0.001, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6413, -0.4516, 0.4417, 0.0, 0.0, 0.0229, 0.0, -0.0961, 0.3985, 0.1522]</t>
+        </is>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:12:10.677729+00:00</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>73.93973923359182</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.1094045291381322</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J71" t="n">
+        <v>-0.8996361494064331</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M71" t="n">
+        <v>32.06356173628624</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>0.3000000000014325</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.13×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>[0.4788, 0.375, 1.0, -0.406, 0.2204, 1.0, 2.0, -0.0167, -0.1121, 0.2204, 1.0, 0.3206, 0.3308, 0.3105, 0.2031, -0.6124, 0.0954, 0.0, 0.0, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6413, -0.4516, 0.4417, 0.0, 0.0, 0.025, 0.0, -0.0911, 0.3985, 0.1636]</t>
+        </is>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:13:11.325131+00:00</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>73.59757574803166</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.1094045291381322</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J72" t="n">
+        <v>-0.8760213851928711</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M72" t="n">
+        <v>32.06356173628624</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
+        <v>0.2999999999985903</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.22×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>[0.472, 0.375, 1.0, -0.406, 0.2199, 1.0, 2.0, -0.035, -0.1179, 0.2199, 1.0, 0.3206, 0.2932, 0.2751, 0.2031, -0.7038, 0.0954, -0.0008, -0.0016, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6413, -0.4516, 0.4417, 0.0, 0.0, 0.0271, 0.0, -0.0966, 0.3985, 0.1509]</t>
+        </is>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:14:12.333779+00:00</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>73.63179215166871</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.1094045291381322</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J73" t="n">
+        <v>-0.8713645935058594</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M73" t="n">
+        <v>32.06356173628624</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>0.2999999999985903</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.21×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>[0.4726, 0.375, 1.0, -0.406, 0.22, 1.0, 2.0, -0.0332, -0.1173, 0.22, 1.0, 0.3206, 0.297, 0.2786, 0.2031, -0.6947, 0.0954, -0.0005, -0.001, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6413, -0.4516, 0.4417, 0.0, 0.0, 0.0292, 0.0, -0.0961, 0.3985, 0.1522]</t>
+        </is>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:15:12.976005+00:00</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>73.28962756442225</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.1094045291381322</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J74" t="n">
+        <v>-0.8867217302322388</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M74" t="n">
+        <v>32.06356173628624</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O74" t="n">
+        <v>0.8000000000009777</v>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.29×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>[0.4658, 0.375, 1.0, -0.406, 0.2195, 1.0, 2.0, -0.0508, -0.1232, 0.2195, 1.0, 0.3206, 0.2594, 0.244, 0.2031, -0.7861, 0.0954, -0.0032, -0.0063, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0001, 0.0, 0.6413, -0.4516, 0.4417, 0.0, 0.0, 0.0312, 0.0, -0.1016, 0.3985, 0.1398]</t>
+        </is>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:16:13.636342+00:00</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>73.56335933215355</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.1094045291381322</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-0.8688775300979614</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M75" t="n">
+        <v>32.06356173628624</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O75" t="n">
+        <v>0.3000000000014325</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.22×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>[0.4713, 0.375, 1.0, -0.406, 0.2199, 1.0, 2.0, -0.0367, -0.1185, 0.2199, 1.0, 0.3206, 0.2895, 0.2716, 0.2031, -0.713, 0.0954, -0.001, -0.0021, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6413, -0.4516, 0.4417, 0.0, 0.0, 0.0333, 0.0, -0.0972, 0.3985, 0.1497]</t>
+        </is>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:17:14.273450+00:00</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>73.66600854306492</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.1094045291381322</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J76" t="n">
+        <v>-0.8597112894058228</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M76" t="n">
+        <v>32.06356173628624</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O76" t="n">
+        <v>0.2999999999985903</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.20×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>[0.4733, 0.375, 1.0, -0.406, 0.22, 1.0, 2.0, -0.0314, -0.1167, 0.22, 1.0, 0.3206, 0.3008, 0.2821, 0.2031, -0.6855, 0.0954, -0.0003, -0.0005, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6413, -0.4516, 0.4417, 0.0, 0.0, 0.0354, 0.0, -0.0955, 0.3985, 0.1534]</t>
+        </is>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:18:14.892647+00:00</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>73.22119450006393</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.1094045291381322</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J77" t="n">
+        <v>-0.8883569240570068</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M77" t="n">
+        <v>32.06356173628624</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O77" t="n">
+        <v>0.899999999998613</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.31×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>[0.4644, 0.375, 1.0, -0.406, 0.2194, 1.0, 2.0, -0.0542, -0.1243, 0.2194, 1.0, 0.3206, 0.2519, 0.2371, 0.2031, -0.8044, 0.0954, -0.0037, -0.0074, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0001, 0.0, 0.6413, -0.4516, 0.4417, 0.0, 0.0, 0.0375, 0.0, -0.1027, 0.3985, 0.1373]</t>
+        </is>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:19:15.532526+00:00</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>73.42649354622593</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.1094045291381322</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J78" t="n">
+        <v>-0.871842622756958</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M78" t="n">
+        <v>32.06356173628624</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O78" t="n">
+        <v>0.899999999998613</v>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.26×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>[0.4685, 0.375, 1.0, -0.406, 0.2197, 1.0, 2.0, -0.0438, -0.1208, 0.2197, 1.0, 0.3206, 0.2744, 0.2577, 0.2031, -0.7495, 0.0954, -0.0021, -0.0042, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0001, 0.0, 0.6413, -0.4516, 0.4417, 0.0, 0.0, 0.0396, 0.0, -0.0994, 0.3985, 0.1447]</t>
+        </is>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:20:16.188294+00:00</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>73.59757574803166</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.1094045291381322</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J79" t="n">
+        <v>-0.8555499315261841</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M79" t="n">
+        <v>32.06356173628624</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O79" t="n">
+        <v>0.7000000000005002</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.22×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>[0.472, 0.375, 1.0, -0.406, 0.2199, 1.0, 2.0, -0.035, -0.1179, 0.2199, 1.0, 0.3206, 0.2932, 0.2751, 0.2031, -0.7038, 0.0954, -0.0008, -0.0016, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0001, 0.0, 0.6413, -0.4516, 0.4417, 0.0, 0.0, 0.0417, 0.0, -0.0966, 0.3985, 0.1509]</t>
+        </is>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:21:16.828602+00:00</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>73.66600854306492</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.1094045291381322</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J80" t="n">
+        <v>-0.8466349840164185</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M80" t="n">
+        <v>32.06356173628624</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O80" t="n">
+        <v>0.2999999999985903</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.20×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>[0.4733, 0.375, 1.0, -0.406, 0.22, 1.0, 2.0, -0.0314, -0.1167, 0.22, 1.0, 0.3206, 0.3008, 0.2821, 0.2031, -0.6855, 0.0954, -0.0003, -0.0005, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0, 0.0, 0.6413, -0.4516, 0.4417, 0.0, 0.0, 0.0437, 0.0, -0.0955, 0.3985, 0.1534]</t>
+        </is>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-06-04 08:22:17.507659+00:00</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>73.46071001107093</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.1094045291381322</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.5476830087306916</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.430191801449035</v>
+      </c>
+      <c r="J81" t="n">
+        <v>-0.8668428659439087</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M81" t="n">
+        <v>32.06356173628624</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O81" t="n">
+        <v>0.7999999999981355</v>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>TF BUY ADX=32.1 trend_age=60 pullback=0.25×ATR H4=1 D1=1</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>[0.4692, 0.375, 1.0, -0.406, 0.2197, 1.0, 2.0, -0.042, -0.1202, 0.2197, 1.0, 0.3206, 0.2782, 0.2612, 0.2031, -0.7404, 0.0954, -0.0021, -0.0042, -0.001, 0.6444, 0.3333, 0.0, 0.0, 0.0001, 0.0, 0.6413, -0.4516, 0.4417, 0.0, 0.0, 0.0458, 0.0, -0.0988, 0.3985, 0.1459]</t>
+        </is>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
         <is>
           <t>tf_v2</t>
         </is>

--- a/ftmo_trading_bot/logs/ftmo_trades.xlsx
+++ b/ftmo_trading_bot/logs/ftmo_trades.xlsx
@@ -41,7 +41,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -78,6 +78,11 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -97,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -117,6 +122,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -899,6 +905,25 @@
           <t>2026-06-04 10:03:28.847094</t>
         </is>
       </c>
+      <c r="N2" t="n">
+        <v>159.883</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026-06-04 11:38:22.570517</t>
+        </is>
+      </c>
+      <c r="P2" s="9" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Manual Close (Mobile)</t>
+        </is>
+      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>TF BUY ADX=30.8 trend_age=60 pullback=0.28×ATR H4=1 D1=1</t>
@@ -932,6 +957,20 @@
       <c r="AA2" t="n">
         <v>0.03</v>
       </c>
+      <c r="AB2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-19505</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Manual Close (Mobile)</t>
+        </is>
+      </c>
       <c r="AF2" t="n">
         <v>0.6160377358490565</v>
       </c>
@@ -949,6 +988,18 @@
       <c r="AJ2" t="n">
         <v>0.3</v>
       </c>
+      <c r="AK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>159.668</v>
+      </c>
       <c r="AO2" t="n">
         <v>159.886</v>
       </c>
@@ -958,6 +1009,12 @@
       <c r="AQ2" t="n">
         <v>0.6000000000000227</v>
       </c>
+      <c r="AR2" t="n">
+        <v>159.883</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>159.886</v>
+      </c>
       <c r="AT2" t="n">
         <v>30.81321610973439</v>
       </c>
@@ -966,6 +1023,12 @@
       </c>
       <c r="AV2" t="n">
         <v>10000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>9995.540000000001</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>9995.540000000001</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -1212,7 +1275,7 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1232,7 +1295,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1255,7 +1318,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$-4.46</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1342,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$4.46</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1354,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$-4.46</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1366,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$-4.46</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1400,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$-4.46</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1509,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1469,7 +1532,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$-4.46</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1544,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$-4.46</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1565,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1537,7 +1600,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.4%</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1612,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>$1,000.00</t>
+          <t>$1,004.46</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1624,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.00% / 10%</t>
+          <t>0.04% / 10%</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1636,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>0.00% / 4%</t>
+          <t>0.04% / 4%</t>
         </is>
       </c>
     </row>

--- a/ftmo_trading_bot/logs/ftmo_trades.xlsx
+++ b/ftmo_trading_bot/logs/ftmo_trades.xlsx
@@ -41,7 +41,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +83,11 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -102,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -123,6 +128,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1078,7 +1084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1238,6 +1244,43 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9995.540000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1651,7 +1694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V81"/>
+  <dimension ref="A1:V125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8591,6 +8634,3886 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-06-04 23:06:15.481405+00:00</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>81.06947624438814</v>
+      </c>
+      <c r="F82" t="n">
+        <v>5.746861489048227</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.2242146033567637</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.2501947677717079</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M82" t="n">
+        <v>17.29991565183553</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O82" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>BB%B=-0.17 (extreme=1.56); RSI=37.9 (extreme=0.05); Wick ratio=2.72; ADX H1=17.3 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>[0.6214, 0.0, 1.0, 2.0, 1.0, -1.0, 1.7401, -0.2428, -0.1362, 0.1471, 0.7276, 0.1151, -0.5828, -0.1669, -0.3219, -1.1502, -0.5516, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0009, 0.0, 0.7698, 0.0, 0.0, 0.0, 0.0, 0.0, -0.3789, -0.2379, 0.6609, 0.086]</t>
+        </is>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-06-04 23:07:15.950015+00:00</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>80.46225258829277</v>
+      </c>
+      <c r="F83" t="n">
+        <v>5.746861489048227</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.588888888888889</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.4002502449921833</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M83" t="n">
+        <v>17.29991565183553</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O83" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>BB%B=-0.11 (extreme=1.36); RSI=39.1 (extreme=0.02); Wick ratio=19.37; ADX H1=17.3 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>[0.6092, 0.0, 1.0, 2.0, 1.0, -1.0, 1.7401, -0.2185, -0.1227, 0.1493, 0.6899, 0.1151, -0.4572, -0.1067, -0.3219, -0.9396, 0.1778, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0009, 0.0, 0.7698, 0.0, 0.0, 0.0, 0.0, 0.0, -0.3279, -0.2251, 0.6609, 0.0919]</t>
+        </is>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-06-04 23:46:23.646354+00:00</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>76.44989707500574</v>
+      </c>
+      <c r="F84" t="n">
+        <v>5.861201252861291</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.2559880999891159</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.2748717136055608</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M84" t="n">
+        <v>17.54799034796378</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O84" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>BB%B=-0.11 (extreme=1.37); RSI=32.6 (extreme=0.18); Wick ratio=0.95; ADX H1=17.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>[0.529, 0.0, 1.0, 2.0, 1.0, -1.0, 1.7061, -0.348, -0.2461, 0.0907, 1.0, 0.1531, -0.8775, -0.1124, -0.3014, -2.2794, -0.488, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6939, 0.0, 0.0, 0.0, 0.0, 0.0, -0.5339, -0.4903, 0.6507, 0.0563]</t>
+        </is>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-06-04 23:47:24.065023+00:00</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>81.49550146339509</v>
+      </c>
+      <c r="F85" t="n">
+        <v>5.861201252861291</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.2697389622945537</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.2938242993601961</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M85" t="n">
+        <v>17.54799034796378</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O85" t="n">
+        <v>49.00000000006912</v>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>BB%B=-0.10 (extreme=1.32); RSI=33.0 (extreme=0.17); Wick ratio=2.00; ADX H1=17.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>[0.6299, 0.0, 1.0, 2.0, 1.0, -1.0, 1.7061, -0.3398, -0.2408, 0.0916, 1.0, 0.1531, -0.8324, -0.0974, -0.3014, -2.1958, -0.4605, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6939, 0.0, 0.0, 0.0, 0.0, 0.0, -0.5137, -0.4853, 0.6507, 0.0586]</t>
+        </is>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-06-04 23:48:24.400402+00:00</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>83.27724702152356</v>
+      </c>
+      <c r="F86" t="n">
+        <v>5.861201252861291</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.2913733319323316</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.3025294029895725</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M86" t="n">
+        <v>17.54799034796378</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O86" t="n">
+        <v>44.00000000005093</v>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>BB%B=-0.08 (extreme=1.27); RSI=33.4 (extreme=0.16); Wick ratio=5.82; ADX H1=17.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>[0.6655, 0.0, 1.0, 2.0, 1.0, -1.0, 1.7061, -0.3311, -0.2352, 0.0925, 1.0, 0.1531, -0.7855, -0.0813, -0.3014, -2.1088, -0.4173, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6939, 0.0, 0.0, 0.0, 0.0, 0.0, -0.4926, -0.48, 0.6507, 0.0609]</t>
+        </is>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-06-04 23:49:24.765072+00:00</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>83.28591470794856</v>
+      </c>
+      <c r="F87" t="n">
+        <v>5.861201252861291</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.2913733319323316</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.3025294029895725</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M87" t="n">
+        <v>17.54799034796378</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O87" t="n">
+        <v>43.99999999995998</v>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>BB%B=-0.08 (extreme=1.27); RSI=33.4 (extreme=0.16); Wick ratio=5.50; ADX H1=17.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>[0.6657, 0.0, 1.0, 2.0, 1.0, -1.0, 1.7061, -0.3314, -0.2355, 0.0924, 1.0, 0.1531, -0.7873, -0.0819, -0.3014, -2.1122, -0.4173, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6939, 0.0, 0.0, 0.0, 0.0, 0.0, -0.4934, -0.4802, 0.6507, 0.0608]</t>
+        </is>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-06-04 23:50:25.117387+00:00</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>77.03658370842359</v>
+      </c>
+      <c r="F88" t="n">
+        <v>6.004772733929375</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.3431110305118555</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.3264608084334348</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.8394176959991455</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M88" t="n">
+        <v>17.54799034796378</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O88" t="n">
+        <v>46.99999999993452</v>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>BB%B=-0.00 (extreme=1.01); RSI=36.8 (extreme=0.08); Wick ratio=1.49; ADX H1=17.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>[0.5407, 0.0, 1.0, 2.0, 1.0, -1.0, 1.6653, -0.2631, -0.2059, 0.0964, 1.0, 0.1531, -0.5801, -0.0035, -0.2845, -1.687, -0.3138, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6939, 0.0, 0.0, 0.0, 0.0, 0.0, -0.3908, -0.446, 0.6423, 0.0713]</t>
+        </is>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-06-04 23:52:25.625918+00:00</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>83.14173898607649</v>
+      </c>
+      <c r="F89" t="n">
+        <v>6.044772748555333</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.334814193908913</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.3192484680103851</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M89" t="n">
+        <v>17.54799034796378</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O89" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>BB%B=-0.07 (extreme=1.24); RSI=33.7 (extreme=0.16); Wick ratio=29.33; ADX H1=17.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>[0.6628, 0.0, 1.0, 2.0, 1.0, -1.0, 1.6543, -0.3257, -0.2248, 0.093, 1.0, 0.1531, -0.7569, -0.0711, -0.2798, -1.9935, -0.3304, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6939, 0.0, 0.0, 0.0, 0.0, 0.0, -0.4652, -0.4623, 0.6399, 0.0624]</t>
+        </is>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-06-04 23:53:25.918585+00:00</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>82.95134810007053</v>
+      </c>
+      <c r="F90" t="n">
+        <v>6.044772748555333</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.3473775251745227</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.3304414316634389</v>
+      </c>
+      <c r="J90" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M90" t="n">
+        <v>17.54799034796378</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O90" t="n">
+        <v>47.00000000002547</v>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>BB%B=-0.06 (extreme=1.21); RSI=34.1 (extreme=0.15); Wick ratio=17.06; ADX H1=17.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>[0.659, 0.0, 1.0, 2.0, 1.0, -1.0, 1.6543, -0.3181, -0.2222, 0.0934, 1.0, 0.1531, -0.7339, -0.0628, -0.2798, -1.9521, -0.3052, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6939, 0.0, 0.0, 0.0, 0.0, 0.0, -0.4551, -0.4598, 0.6399, 0.0635]</t>
+        </is>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-06-04 23:54:26.286769+00:00</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>82.53602803768943</v>
+      </c>
+      <c r="F91" t="n">
+        <v>6.044772748555333</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.3473775251745227</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.3304414316634389</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M91" t="n">
+        <v>17.54799034796378</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O91" t="n">
+        <v>39.00000000003274</v>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>BB%B=-0.05 (extreme=1.15); RSI=34.9 (extreme=0.13); Wick ratio=4.20; ADX H1=17.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>[0.6507, 0.0, 1.0, 2.0, 1.0, -1.0, 1.6543, -0.3014, -0.217, 0.0943, 1.0, 0.1531, -0.6888, -0.0461, -0.2798, -1.871, -0.3052, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0006, 0.0, 0.6939, 0.0, 0.0, 0.0, 0.0, 0.0, -0.4355, -0.4549, 0.6399, 0.0658]</t>
+        </is>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-06-04 23:55:26.621193+00:00</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>82.20467379229626</v>
+      </c>
+      <c r="F92" t="n">
+        <v>6.044772748555333</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.3473775251745227</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.3304414316634389</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M92" t="n">
+        <v>17.54799034796378</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O92" t="n">
+        <v>39.00000000003274</v>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>BB%B=-0.03 (extreme=1.11); RSI=35.6 (extreme=0.11); Wick ratio=2.60; ADX H1=17.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>[0.6441, 0.0, 1.0, 2.0, 1.0, -1.0, 1.6543, -0.2882, -0.2128, 0.095, 1.0, 0.1531, -0.6519, -0.032, -0.2798, -1.8049, -0.3052, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0006, 0.0, 0.6939, 0.0, 0.0, 0.0, 0.0, 0.0, -0.4195, -0.4509, 0.6399, 0.0677]</t>
+        </is>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-06-04 23:56:26.927646+00:00</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>82.8742717842391</v>
+      </c>
+      <c r="F93" t="n">
+        <v>6.044772748555333</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.3473775251745227</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.3304414316634389</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M93" t="n">
+        <v>17.54799034796378</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O93" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>BB%B=-0.06 (extreme=1.20); RSI=34.3 (extreme=0.14); Wick ratio=10.92; ADX H1=17.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>[0.6575, 0.0, 1.0, 2.0, 1.0, -1.0, 1.6543, -0.315, -0.2212, 0.0936, 1.0, 0.1531, -0.7256, -0.0598, -0.2798, -1.9372, -0.3052, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6939, 0.0, 0.0, 0.0, 0.0, 0.0, -0.4515, -0.4589, 0.6399, 0.0639]</t>
+        </is>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-06-04 23:57:27.284205+00:00</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>83.35493406724552</v>
+      </c>
+      <c r="F94" t="n">
+        <v>6.044772748555333</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.3473775251745227</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.3304414316634389</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M94" t="n">
+        <v>17.54799034796378</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O94" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>BB%B=-0.09 (extreme=1.29); RSI=33.3 (extreme=0.17); Wick ratio=3.71; ADX H1=17.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>[0.6671, 0.0, 1.0, 2.0, 1.0, -1.0, 1.6543, -0.3342, -0.23, 0.0921, 1.0, 0.1531, -0.802, -0.087, -0.2798, -2.0745, -0.3052, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6939, 0.0, 0.0, 0.0, 0.0, 0.0, -0.4848, -0.4672, 0.6399, 0.0601]</t>
+        </is>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-06-04 23:58:27.618673+00:00</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>83.35063706137231</v>
+      </c>
+      <c r="F95" t="n">
+        <v>6.044772748555333</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.3473775251745227</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.3304414316634389</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M95" t="n">
+        <v>17.54799034796378</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O95" t="n">
+        <v>49.00000000006912</v>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>BB%B=-0.09 (extreme=1.29); RSI=33.3 (extreme=0.17); Wick ratio=3.79; ADX H1=17.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>[0.667, 0.0, 1.0, 2.0, 1.0, -1.0, 1.6543, -0.334, -0.2299, 0.0922, 1.0, 0.1531, -0.8011, -0.0867, -0.2798, -2.0729, -0.3052, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6939, 0.0, 0.0, 0.0, 0.0, 0.0, -0.4844, -0.4671, 0.6399, 0.0601]</t>
+        </is>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-06-04 23:59:27.965998+00:00</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>76.44989707500574</v>
+      </c>
+      <c r="F96" t="n">
+        <v>6.044772748555333</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.2913733319323316</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.3032316100372871</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M96" t="n">
+        <v>17.54799034796378</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O96" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>BB%B=-0.11 (extreme=1.37); RSI=32.6 (extreme=0.18); Wick ratio=0.95; ADX H1=17.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>[0.529, 0.0, 1.0, 2.0, 1.0, -1.0, 1.6543, -0.348, -0.2387, 0.0907, 1.0, 0.1531, -0.8775, -0.1124, -0.2798, -2.2102, -0.4173, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6939, 0.0, 0.0, 0.0, 0.0, 0.0, -0.5177, -0.4755, 0.6399, 0.0563]</t>
+        </is>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:00:28.310449+00:00</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>83.89063076738944</v>
+      </c>
+      <c r="F97" t="n">
+        <v>5.718717539954587</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.2559880999891159</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.2789432750088114</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M97" t="n">
+        <v>17.49785287389077</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O97" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>BB%B=-0.02 (extreme=1.08); RSI=32.2 (extreme=0.19); Wick ratio=3.46; ADX H1=17.5 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>[0.6778, 0.0, 1.0, 2.0, 1.0, -1.0, 1.7486, -0.3556, -0.271, 0.0685, 1.0, 0.1675, -0.918, -0.0227, -0.3161, -1.4321, -0.488, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0009, 0.0, 0.665, 0.0, 0.0, 0.0, 0.0, 0.0, -0.5159, -0.5443, 0.6581, 0.0185]</t>
+        </is>
+      </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:02:28.826724+00:00</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>83.92090726517394</v>
+      </c>
+      <c r="F98" t="n">
+        <v>5.915146183206984</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.2963480947382897</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M98" t="n">
+        <v>17.55329532126696</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O98" t="n">
+        <v>49.00000000006912</v>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>BB%B=-0.02 (extreme=1.08); RSI=32.2 (extreme=0.20); Wick ratio=5.19; ADX H1=17.6 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>[0.6784, 0.0, 1.0, 2.0, 1.0, -1.0, 1.6906, -0.3568, -0.2627, 0.0684, 1.0, 0.1686, -0.857, -0.0248, -0.293, -1.3964, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6628, 0.0, 0.0, 0.0, 0.0, 0.0, -0.5016, -0.527, 0.6465, 0.0182]</t>
+        </is>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:04:29.378652+00:00</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>76.33203596673724</v>
+      </c>
+      <c r="F99" t="n">
+        <v>5.915146183206984</v>
+      </c>
+      <c r="G99" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.2697389622945537</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.2941623539436035</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M99" t="n">
+        <v>17.55329532126696</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O99" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>BB%B=0.02 (extreme=0.92); RSI=34.5 (extreme=0.14); Wick ratio=1.57; ADX H1=17.6 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>[0.5266, 0.0, 1.0, 2.0, 0.9235, -1.0, 1.6906, -0.3103, -0.2462, 0.0711, 1.0, 0.1686, -0.721, 0.023, -0.293, -1.1378, -0.4605, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6628, 0.0, 0.0, 0.0, 0.0, 0.0, -0.4389, -0.5113, 0.6465, 0.025]</t>
+        </is>
+      </c>
+      <c r="S99" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:06:29.918014+00:00</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>82.54704623542281</v>
+      </c>
+      <c r="F100" t="n">
+        <v>5.98443192282685</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.2946940940019578</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M100" t="n">
+        <v>17.55329532126694</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O100" t="n">
+        <v>47.99999999995634</v>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>BB%B=0.01 (extreme=0.98); RSI=33.6 (extreme=0.16); Wick ratio=2.70; ADX H1=17.6 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>[0.6509, 0.0, 1.0, 2.0, 0.9781, -1.0, 1.671, -0.3282, -0.2488, 0.0702, 1.0, 0.1686, -0.7663, 0.0066, -0.2848, -1.2098, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6628, 0.0, 0.0, 0.0, 0.0, 0.0, -0.4545, -0.5106, 0.6424, 0.0228]</t>
+        </is>
+      </c>
+      <c r="S100" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:07:30.261929+00:00</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>83.78156334371567</v>
+      </c>
+      <c r="F101" t="n">
+        <v>5.98443192282685</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.2964523585487214</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M101" t="n">
+        <v>17.55329532126694</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O101" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>BB%B=-0.02 (extreme=1.05); RSI=32.4 (extreme=0.19); Wick ratio=192.00; ADX H1=17.6 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>[0.6756, 0.0, 1.0, 2.0, 1.0, -1.0, 1.671, -0.3513, -0.2563, 0.0689, 1.0, 0.1686, -0.8285, -0.0152, -0.2848, -1.3268, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6628, 0.0, 0.0, 0.0, 0.0, 0.0, -0.4828, -0.5176, 0.6424, 0.0197]</t>
+        </is>
+      </c>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:08:30.791258+00:00</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>83.8297344198055</v>
+      </c>
+      <c r="F102" t="n">
+        <v>5.98443192282685</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.3275691931770123</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.316888388704329</v>
+      </c>
+      <c r="J102" t="n">
+        <v>1</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M102" t="n">
+        <v>17.55329532126694</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O102" t="n">
+        <v>44.00000000005093</v>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>BB%B=-0.02 (extreme=1.06); RSI=32.3 (extreme=0.19); Wick ratio=18.20; ADX H1=17.6 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>[0.6766, 0.0, 1.0, 2.0, 1.0, -1.0, 1.671, -0.3532, -0.2575, 0.0687, 1.0, 0.1686, -0.8383, -0.0185, -0.2848, -1.3452, -0.3449, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0007, 0.0, 0.6628, 0.0, 0.0, 0.0, 0.0, 0.0, -0.4873, -0.5188, 0.6424, 0.0192]</t>
+        </is>
+      </c>
+      <c r="S102" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:09:31.149791+00:00</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>76.54623093287867</v>
+      </c>
+      <c r="F103" t="n">
+        <v>5.98443192282685</v>
+      </c>
+      <c r="G103" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.334814193908913</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.318055251448119</v>
+      </c>
+      <c r="J103" t="n">
+        <v>1</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M103" t="n">
+        <v>17.55329532126694</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O103" t="n">
+        <v>50</v>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>BB%B=-0.05 (extreme=1.15); RSI=31.5 (extreme=0.21); Wick ratio=0.86; ADX H1=17.6 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>[0.5309, 0.0, 1.0, 2.0, 1.0, -1.0, 1.671, -0.369, -0.2674, 0.0671, 1.0, 0.1686, -0.9209, -0.046, -0.2848, -1.5006, -0.3304, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6628, 0.0, 0.0, 0.0, 0.0, 0.0, -0.525, -0.5282, 0.6424, 0.0149]</t>
+        </is>
+      </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:10:31.490571+00:00</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>83.64640901960675</v>
+      </c>
+      <c r="F104" t="n">
+        <v>5.98443192282685</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.3275691931770123</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.316888388704329</v>
+      </c>
+      <c r="J104" t="n">
+        <v>1</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M104" t="n">
+        <v>17.55329532126694</v>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O104" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>BB%B=-0.01 (extreme=1.03); RSI=32.7 (extreme=0.18); Wick ratio=8.73; ADX H1=17.6 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>[0.6729, 0.0, 1.0, 2.0, 1.0, -1.0, 1.671, -0.3459, -0.2541, 0.0693, 1.0, 0.1686, -0.8099, -0.0087, -0.2848, -1.2917, -0.3449, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6628, 0.0, 0.0, 0.0, 0.0, 0.0, -0.4743, -0.5155, 0.6424, 0.0206]</t>
+        </is>
+      </c>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:11:31.838386+00:00</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>76.87099376366295</v>
+      </c>
+      <c r="F105" t="n">
+        <v>5.986574780753221</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.334814193908913</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.318055251448119</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M105" t="n">
+        <v>17.55538033880779</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O105" t="n">
+        <v>49.00000000006912</v>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>BB%B=-0.05 (extreme=1.15); RSI=31.6 (extreme=0.21); Wick ratio=0.93; ADX H1=17.6 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>[0.5374, 0.0, 1.0, 2.0, 1.0, -1.0, 1.6704, -0.3687, -0.2671, 0.0671, 1.0, 0.1687, -0.9166, -0.0454, -0.2845, -1.4967, -0.3304, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6627, 0.0, 0.0, 0.0, 0.0, 0.0, -0.524, -0.5278, 0.6423, 0.015]</t>
+        </is>
+      </c>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:13:32.383713+00:00</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>76.14042663766517</v>
+      </c>
+      <c r="F106" t="n">
+        <v>6.442289233098641</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.5904993065187241</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.4026691365622299</v>
+      </c>
+      <c r="J106" t="n">
+        <v>1</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M106" t="n">
+        <v>17.9675749567938</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O106" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>BB%B=-0.17 (extreme=1.55); RSI=28.0 (extreme=0.30); Wick ratio=0.43; ADX H1=18.0 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>[0.5228, 0.0, 1.0, 2.0, 1.0, -1.0, 1.5522, -0.4399, -0.2959, 0.0586, 1.0, 0.176, -0.8271, -0.1662, -0.2309, -2.139, 0.181, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6479, 0.0, 0.0, 0.0, 0.0, 0.0, -0.6683, -0.5358, 0.6155, -0.0064]</t>
+        </is>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:18:33.456595+00:00</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>79.95664775874738</v>
+      </c>
+      <c r="F107" t="n">
+        <v>6.355697180801493</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.5551487414187642</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.3912214052777804</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M107" t="n">
+        <v>18.02582617131825</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O107" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>BB%B=-0.08 (extreme=1.27); RSI=26.7 (extreme=0.33); Wick ratio=1.06; ADX H1=18.0 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>[0.5991, 0.0, 1.0, 2.0, 1.0, -1.0, 1.5734, -0.4657, -0.3487, 0.0255, 1.0, 0.1984, -0.8957, -0.0806, -0.2398, -2.6921, 0.1103, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6033, 0.0, 0.0, 0.0, 0.0, 0.0, -0.6886, -0.6618, 0.6199, -0.0149]</t>
+        </is>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:22:34.450922+00:00</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>85.7958085979041</v>
+      </c>
+      <c r="F108" t="n">
+        <v>6.474982938703759</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.5290763968072978</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.3790539513465784</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M108" t="n">
+        <v>18.12228340368912</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O108" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>BB%B=-0.08 (extreme=1.27); RSI=26.7 (extreme=0.33); Wick ratio=2.23; ADX H1=18.1 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>[0.7159, 0.0, 1.0, 2.0, 1.0, -1.0, 1.5444, -0.4657, -0.3423, 0.0255, 1.0, 0.1999, -0.793, -0.0806, -0.2258, -2.6425, 0.0582, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6001, 0.0, 0.0, 0.0, 0.0, 0.0, -0.6759, -0.6496, 0.6129, -0.0149]</t>
+        </is>
+      </c>
+      <c r="S108" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:23:35.080737+00:00</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>86.45652396181933</v>
+      </c>
+      <c r="F109" t="n">
+        <v>6.474982938703759</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.5290763968072978</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.3790539513465784</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M109" t="n">
+        <v>18.12228340368912</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O109" t="n">
+        <v>47.00000000002547</v>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>BB%B=-0.07 (extreme=1.23); RSI=27.1 (extreme=0.32); Wick ratio=4.37; ADX H1=18.1 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>[0.7291, 0.0, 1.0, 2.0, 1.0, -1.0, 1.5444, -0.4583, -0.3367, 0.0265, 1.0, 0.1999, -0.756, -0.0686, -0.2258, -2.5544, 0.0582, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0007, 0.0, 0.6001, 0.0, 0.0, 0.0, 0.0, 0.0, -0.6546, -0.6443, 0.6129, -0.0124]</t>
+        </is>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:24:35.610961+00:00</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>84.04729759085086</v>
+      </c>
+      <c r="F110" t="n">
+        <v>6.474982938703759</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.5290763968072978</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.3790539513465784</v>
+      </c>
+      <c r="J110" t="n">
+        <v>1</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M110" t="n">
+        <v>18.12228340368912</v>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O110" t="n">
+        <v>45.00000000007276</v>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>BB%B=-0.08 (extreme=1.28); RSI=26.6 (extreme=0.33); Wick ratio=1.87; ADX H1=18.1 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>[0.6809, 0.0, 1.0, 2.0, 1.0, -1.0, 1.5444, -0.468, -0.3441, 0.0252, 1.0, 0.1999, -0.8047, -0.0843, -0.2258, -2.6703, 0.0582, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0007, 0.0, 0.6001, 0.0, 0.0, 0.0, 0.0, 0.0, -0.6826, -0.6513, 0.6129, -0.0156]</t>
+        </is>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:25:35.942615+00:00</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>81.9489853492025</v>
+      </c>
+      <c r="F111" t="n">
+        <v>6.474982938703759</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.5290763968072978</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.3784516704883393</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M111" t="n">
+        <v>18.12228340368912</v>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O111" t="n">
+        <v>47.00000000002547</v>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>BB%B=-0.09 (extreme=1.30); RSI=26.4 (extreme=0.34); Wick ratio=1.43; ADX H1=18.1 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>[0.639, 0.0, 1.0, 2.0, 1.0, -1.0, 1.5444, -0.4716, -0.3469, 0.0247, 1.0, 0.1999, -0.8235, -0.0903, -0.2258, -2.7151, 0.0582, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0007, 0.0, 0.6001, 0.0, 0.0, 0.0, 0.0, 0.0, -0.6935, -0.654, 0.6129, -0.0169]</t>
+        </is>
+      </c>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:26:36.303830+00:00</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>86.3968900826988</v>
+      </c>
+      <c r="F112" t="n">
+        <v>6.474982938703759</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.5290763968072978</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.3790539513465784</v>
+      </c>
+      <c r="J112" t="n">
+        <v>1</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M112" t="n">
+        <v>18.12228340368912</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O112" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>BB%B=-0.06 (extreme=1.22); RSI=27.2 (extreme=0.32); Wick ratio=5.79; ADX H1=18.1 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>[0.7279, 0.0, 1.0, 2.0, 1.0, -1.0, 1.5444, -0.4559, -0.3349, 0.0268, 1.0, 0.1999, -0.7443, -0.0647, -0.2258, -2.5266, 0.0582, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6001, 0.0, 0.0, 0.0, 0.0, 0.0, -0.6478, -0.6426, 0.6129, -0.0116]</t>
+        </is>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:27:36.651948+00:00</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>86.25907708747266</v>
+      </c>
+      <c r="F113" t="n">
+        <v>6.474982938703759</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.4829787234042554</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.3643060519984556</v>
+      </c>
+      <c r="J113" t="n">
+        <v>1</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M113" t="n">
+        <v>18.12228340368912</v>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O113" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>BB%B=-0.06 (extreme=1.19); RSI=27.5 (extreme=0.31); Wick ratio=16.11; ADX H1=18.1 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>[0.7252, 0.0, 1.0, 2.0, 1.0, -1.0, 1.5444, -0.4504, -0.3309, 0.0276, 1.0, 0.1999, -0.7177, -0.0558, -0.2258, -2.4633, -0.034, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0008, 0.0, 0.6001, 0.0, 0.0, 0.0, 0.0, 0.0, -0.6325, -0.6388, 0.6129, -0.0099]</t>
+        </is>
+      </c>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:28:36.989758+00:00</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>86.3266500612815</v>
+      </c>
+      <c r="F114" t="n">
+        <v>6.474982938703759</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.5290763968072978</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.3790539513465784</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M114" t="n">
+        <v>18.12228340368912</v>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O114" t="n">
+        <v>47.00000000002547</v>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>BB%B=-0.06 (extreme=1.20); RSI=27.3 (extreme=0.32); Wick ratio=8.83; ADX H1=18.1 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>[0.7265, 0.0, 1.0, 2.0, 1.0, -1.0, 1.5444, -0.4531, -0.3328, 0.0272, 1.0, 0.1999, -0.7307, -0.0601, -0.2258, -2.4942, 0.0582, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0007, 0.0, 0.6001, 0.0, 0.0, 0.0, 0.0, 0.0, -0.64, -0.6406, 0.6129, -0.0107]</t>
+        </is>
+      </c>
+      <c r="S114" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:29:37.345499+00:00</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>85.34607278696025</v>
+      </c>
+      <c r="F115" t="n">
+        <v>6.474982938703759</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.4464285714285715</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.3577833634306956</v>
+      </c>
+      <c r="J115" t="n">
+        <v>1</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M115" t="n">
+        <v>18.12228340368912</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O115" t="n">
+        <v>46.00000000000364</v>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>BB%B=-0.03 (extreme=1.10); RSI=29.3 (extreme=0.27); Wick ratio=5.08; ADX H1=18.1 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>[0.7069, 0.0, 1.0, 2.0, 1.0, -1.0, 1.5444, -0.4138, -0.3192, 0.0296, 1.0, 0.1999, -0.6411, -0.0291, -0.2258, -2.2811, -0.1071, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0007, 0.0, 0.6001, 0.0, 0.0, 0.0, 0.0, 0.0, -0.5883, -0.6277, 0.6129, -0.0047]</t>
+        </is>
+      </c>
+      <c r="S115" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-06-05 01:45:52.011270+00:00</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D116" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>83.85535155738332</v>
+      </c>
+      <c r="F116" t="n">
+        <v>8.166409916800323</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.2913733319323316</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.303294603751007</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M116" t="n">
+        <v>19.02665157292311</v>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O116" t="n">
+        <v>46.00000000000364</v>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>BB%B=0.02 (extreme=0.93); RSI=27.9 (extreme=0.30); Wick ratio=4.95; ADX H1=19.0 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>[0.6771, 0.0, 1.0, 2.0, 0.9267, -1.0, 1.2245, -0.4422, -0.2193, 0.0998, 1.0, 0.2467, -0.8787, 0.022, -0.0063, -2.0584, -0.4173, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0006, 0.0, 0.5066, 0.0, 0.0, 0.0, 0.0, 0.0, -0.563, -0.5134, 0.5032, -0.0089]</t>
+        </is>
+      </c>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-06-05 01:48:52.825700+00:00</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>83.9865699694838</v>
+      </c>
+      <c r="F117" t="n">
+        <v>8.367124275905397</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.2913733319323316</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.303294603751007</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M117" t="n">
+        <v>19.02665157292311</v>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O117" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>BB%B=0.02 (extreme=0.93); RSI=27.8 (extreme=0.30); Wick ratio=5.70; ADX H1=19.0 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>[0.6797, 0.0, 1.0, 2.0, 0.9298, -1.0, 1.1952, -0.4437, -0.2144, 0.0999, 1.0, 0.2467, -0.8813, 0.0211, 0.0176, -2.015, -0.4173, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0006, 0.0, 0.5066, 0.0, 0.0, 0.0, 0.0, 0.0, -0.5509, -0.5014, 0.4912, -0.0091]</t>
+        </is>
+      </c>
+      <c r="S117" t="n">
+        <v>0</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-06-05 01:50:53.388805+00:00</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>85.83087122444238</v>
+      </c>
+      <c r="F118" t="n">
+        <v>8.367124275905397</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.3915677546983185</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.3463008520604209</v>
+      </c>
+      <c r="J118" t="n">
+        <v>1</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M118" t="n">
+        <v>19.02665157292311</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O118" t="n">
+        <v>43.99999999995998</v>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>BB%B=0.01 (extreme=0.98); RSI=27.0 (extreme=0.32); Wick ratio=3.09; ADX H1=19.0 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>[0.7166, 0.0, 1.0, 2.0, 0.9783, -1.0, 1.1952, -0.4593, -0.2204, 0.1013, 1.0, 0.2467, -0.9238, 0.0065, 0.0176, -2.1094, -0.2169, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0005, 0.0, 0.5066, 0.0, 0.0, 0.0, 0.0, 0.0, -0.5738, -0.5071, 0.4912, -0.0125]</t>
+        </is>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-06-05 01:51:53.746284+00:00</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>76.41837569113356</v>
+      </c>
+      <c r="F119" t="n">
+        <v>8.367124275905397</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.3249679000817089</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3146978149636397</v>
+      </c>
+      <c r="J119" t="n">
+        <v>1</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M119" t="n">
+        <v>19.02665157292311</v>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O119" t="n">
+        <v>39.00000000003274</v>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>BB%B=0.04 (extreme=0.87); RSI=29.3 (extreme=0.27); Wick ratio=1.41; ADX H1=19.0 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>[0.5284, 0.0, 1.0, 2.0, 0.8667, -1.0, 1.1952, -0.414, -0.2068, 0.0981, 1.0, 0.2467, -0.8277, 0.04, 0.0176, -1.8955, -0.3501, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0005, 0.0, 0.5066, 0.0, 0.0, 0.0, 0.0, 0.0, -0.522, -0.4942, 0.4912, -0.0048]</t>
+        </is>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-06-05 01:52:54.086824+00:00</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>78.36051830847893</v>
+      </c>
+      <c r="F120" t="n">
+        <v>8.367124275905397</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.2559880999891159</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.2662260729814817</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M120" t="n">
+        <v>19.02665157292311</v>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O120" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>BB%B=-0.00 (extreme=1.02); RSI=26.7 (extreme=0.33); Wick ratio=0.74; ADX H1=19.0 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>[0.5672, 0.0, 1.0, 2.0, 1.0, -1.0, 1.1952, -0.4663, -0.2252, 0.1025, 1.0, 0.2467, -0.957, -0.0047, 0.0176, -2.1835, -0.488, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0006, 0.0, 0.5066, 0.0, 0.0, 0.0, 0.0, 0.0, -0.5918, -0.5116, 0.4912, -0.0152]</t>
+        </is>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-06-05 01:53:54.462994+00:00</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>76.10606966154988</v>
+      </c>
+      <c r="F121" t="n">
+        <v>8.367124275905397</v>
+      </c>
+      <c r="G121" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3249679000817089</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3146978149636397</v>
+      </c>
+      <c r="J121" t="n">
+        <v>1</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M121" t="n">
+        <v>19.02665157292311</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O121" t="n">
+        <v>48.00000000004729</v>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>BB%B=0.04 (extreme=0.86); RSI=29.4 (extreme=0.27); Wick ratio=1.37; ADX H1=19.0 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>[0.5221, 0.0, 1.0, 2.0, 0.8642, -1.0, 1.1952, -0.4128, -0.2065, 0.098, 1.0, 0.2467, -0.8255, 0.0408, 0.0176, -1.8907, -0.3501, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0006, 0.0, 0.5066, 0.0, 0.0, 0.0, 0.0, 0.0, -0.5208, -0.4939, 0.4912, -0.0046]</t>
+        </is>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-06-05 01:57:55.476043+00:00</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>85.17544028146426</v>
+      </c>
+      <c r="F122" t="n">
+        <v>8.464981454543825</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.3843233386146901</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.335116017092195</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M122" t="n">
+        <v>19.02665157292311</v>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O122" t="n">
+        <v>42.99999999993815</v>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>BB%B=0.01 (extreme=0.96); RSI=27.2 (extreme=0.32); Wick ratio=11.53; ADX H1=19.0 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>[0.7035, 0.0, 1.0, 2.0, 0.9594, -1.0, 1.1813, -0.4558, -0.2155, 0.1008, 1.0, 0.2467, -0.9071, 0.0122, 0.0292, -2.0484, -0.2314, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0005, 0.0, 0.5066, 0.0, 0.0, 0.0, 0.0, 0.0, -0.5583, -0.4991, 0.4854, -0.0112]</t>
+        </is>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-06-05 01:58:55.840463+00:00</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE_FAIL</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>85.36639519300616</v>
+      </c>
+      <c r="F123" t="n">
+        <v>8.464981454543825</v>
+      </c>
+      <c r="G123" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3843233386146901</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.335116017092195</v>
+      </c>
+      <c r="J123" t="n">
+        <v>1</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M123" t="n">
+        <v>19.02665157292311</v>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O123" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>BB%B=0.01 (extreme=0.96); RSI=27.2 (extreme=0.32); Wick ratio=6.83; ADX H1=19.0 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>risk_manager:🥇 XAU weekday delay: รอ 05:00 EET (09:00 ICT) Mon-Fri ก่อนเทรด XAU</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>[0.7073, 0.0, 1.0, 2.0, 0.9649, -1.0, 1.1813, -0.4568, -0.2162, 0.1009, 1.0, 0.2467, -0.9119, 0.0105, 0.0292, -2.0591, -0.2314, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0006, 0.0, 0.5066, 0.0, 0.0, 0.0, 0.0, 0.0, -0.5609, -0.4997, 0.4854, -0.0116]</t>
+        </is>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-06-05 01:59:56.182420+00:00</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>84.37987359281203</v>
+      </c>
+      <c r="F124" t="n">
+        <v>8.464981454543825</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.2913733319323316</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.303294603751007</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M124" t="n">
+        <v>19.02665157292311</v>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O124" t="n">
+        <v>47.00000000002547</v>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>BB%B=0.02 (extreme=0.94); RSI=27.6 (extreme=0.31); Wick ratio=10.44; ADX H1=19.0 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>[0.6876, 0.0, 1.0, 2.0, 0.9391, -1.0, 1.1813, -0.4483, -0.213, 0.1002, 1.0, 0.2467, -0.8894, 0.0183, 0.0292, -2.0095, -0.4173, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0006, 0.0, 0.5066, 0.0, 0.0, 0.0, 0.0, 0.0, -0.5489, -0.4967, 0.4854, -0.0098]</t>
+        </is>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-06-05 02:02:56.927778+00:00</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>75.8944964169858</v>
+      </c>
+      <c r="F125" t="n">
+        <v>8.303911382511471</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.2586450700604193</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.2859928651474124</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M125" t="n">
+        <v>19.95694390176356</v>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>ASIAN</t>
+        </is>
+      </c>
+      <c r="O125" t="n">
+        <v>48.99999999997817</v>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>BB%B=0.05 (extreme=0.82); RSI=27.4 (extreme=0.31); Wick ratio=1.37; ADX H1=20.0 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>[0.5179, 0.0, 1.0, 2.0, 0.8247, -1.0, 1.2043, -0.4518, -0.2252, 0.1305, 1.0, 0.2614, -0.851, 0.0526, 0.0133, -1.7462, -0.4827, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0006, 0.0, 0.4772, 0.0, 0.0, 0.0, 0.0, 0.0, -0.5444, -0.5621, 0.4933, -0.0979]</t>
+        </is>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ftmo_trading_bot/logs/ftmo_trades.xlsx
+++ b/ftmo_trading_bot/logs/ftmo_trades.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH2"/>
+  <dimension ref="A1:BH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1073,6 +1073,214 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>465474194</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4470.65</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4480.41</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4460.41</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.006002677194028536</v>
+      </c>
+      <c r="I3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>75.28355342333997</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6.76445205606566</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-06-05 15:11:04.398177</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>4470.74</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-06-05 15:18:24.869006</t>
+        </is>
+      </c>
+      <c r="P3" s="9" t="n">
+        <v>-0.9199999999999999</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>🔴 SL Hit</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>BB%B=1.00 (extreme=1.01); RSI=61.1 (extreme=0.03); Wick ratio=1.35; ADX H1=19.7 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00; KC dist=0.29 slope=0.24 consec=0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>LONDON_NY_OVERLAP</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
+      </c>
+      <c r="V3" t="n">
+        <v>15</v>
+      </c>
+      <c r="W3" t="n">
+        <v>44</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>340</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>440</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>🔴 SL Hit</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.3275691931770123</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.3154891730254545</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AK3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>4470.65</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>4470.41</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>4470.85</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>44.00000000005093</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4470.42</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4470.83</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>19.72499039483182</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9995.540000000001</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>9994.620000000001</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>9994.620000000001</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>[0.5057, 0.0, -1.0, 2.0, 1.0, -1.0, 1.4783, 0.2218, 0.0411, 0.0049, 0.5484, 0.212, 0.4267, 1.0017, -0.1229, 0.5218, -0.3449, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0007, 0.0, 0.576, 0.0, 0.0, 0.0, 0.0, 0.5229, 0.2911, 0.2361, 0.5614, -0.274]</t>
+        </is>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1084,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1281,6 +1489,80 @@
         <v>9995.540000000001</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K6" t="n">
+        <v>9994.620000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>100</v>
+      </c>
+      <c r="J7" t="n">
+        <v>100</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1318,7 +1600,7 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1338,7 +1620,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1361,7 +1643,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>$-4.46</t>
+          <t>$-5.38</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1667,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>$4.46</t>
+          <t>$2.69</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1679,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$-4.46</t>
+          <t>$-0.92</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1725,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>$-4.46</t>
+          <t>$-2.69</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1736,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1768,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>0</v>
+        <v>-24.13</v>
       </c>
     </row>
     <row r="18">
@@ -1496,7 +1778,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>0</v>
+        <v>-13.26</v>
       </c>
     </row>
     <row r="19">
@@ -1507,7 +1789,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$5.38</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1801,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1812,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1552,7 +1834,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1575,7 +1857,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>$-4.46</t>
+          <t>$-0.92</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1890,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1643,7 +1925,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.5%</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1937,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>$1,004.46</t>
+          <t>$1,005.38</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1949,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.04% / 10%</t>
+          <t>0.05% / 10%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V125"/>
+  <dimension ref="A1:V200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12514,6 +12796,6381 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-06-05 04:53:27.976561+00:00</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>72.25931213859701</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.0007292483409302858</v>
+      </c>
+      <c r="G126" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.9852941176470589</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.6279994875323155</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-0.718287467956543</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M126" t="n">
+        <v>28.38583846941343</v>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O126" t="n">
+        <v>0.900000000000345</v>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.4 trend_age=34 pullback=0.28×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>[0.4452, 0.375, -1.0, -0.7708, 0.502, 1.0, 2.0, -0.0831, -0.0301, 0.502, 1.0, 0.2839, 0.0649, 0.3583, -0.127, -0.2331, 0.9706, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5677, -0.2934, 0.3, 0.0, 0.0, 0.0, 0.0, -0.341, 0.5635, -0.0657]</t>
+        </is>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-06-05 04:54:28.321149+00:00</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>72.60000361793631</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.0007328197695025115</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.9985744832501782</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.7102231035144896</v>
+      </c>
+      <c r="J127" t="n">
+        <v>-0.4770302772521973</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M127" t="n">
+        <v>28.27444602664063</v>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O127" t="n">
+        <v>0.900000000000345</v>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.3 trend_age=34 pullback=0.17×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>[0.452, 0.375, -1.0, -0.7672, 0.5007, 1.0, 2.0, -0.0646, -0.0221, 0.5007, 1.0, 0.2827, 0.1234, 0.3861, -0.1228, -0.1092, 0.9971, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5655, -0.2822, 0.2889, 0.0, 0.0, 0.0, 0.0, -0.3319, 0.5614, -0.0546]</t>
+        </is>
+      </c>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-06-05 04:55:28.690863+00:00</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>72.5786899841368</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.000733534055216952</v>
+      </c>
+      <c r="G128" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.9985744832501782</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.7102231035144896</v>
+      </c>
+      <c r="J128" t="n">
+        <v>-0.4769386351108551</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M128" t="n">
+        <v>28.25247564817559</v>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O128" t="n">
+        <v>0.8999999999992347</v>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.3 trend_age=34 pullback=0.17×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>[0.4516, 0.375, -1.0, -0.7665, 0.5007, 1.0, 2.0, -0.0646, -0.0221, 0.5007, 1.0, 0.2825, 0.1234, 0.3861, -0.1219, -0.1091, 0.9971, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.565, -0.28, 0.2867, 0.0, 0.0, 0.0, 0.0, -0.3315, 0.561, -0.0546]</t>
+        </is>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-06-05 04:56:29.047091+00:00</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>72.6368702732365</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.0007399626266469473</v>
+      </c>
+      <c r="G129" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.9985744832501782</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.6907841992445339</v>
+      </c>
+      <c r="J129" t="n">
+        <v>-0.3564703464508057</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M129" t="n">
+        <v>28.05920734798288</v>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O129" t="n">
+        <v>0.8999999999992347</v>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.1 trend_age=34 pullback=0.11×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>[0.4527, 0.375, -1.0, -0.76, 0.5, 1.0, 2.0, -0.0546, -0.0176, 0.5, 1.0, 0.2806, 0.1558, 0.4016, -0.1144, -0.0405, 0.9971, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5612, -0.2602, 0.2673, 0.0, 0.0, 0.0, 0.0, -0.3246, 0.5572, -0.0485]</t>
+        </is>
+      </c>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:27:34.068731+00:00</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>65.29869405449918</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.000701393867596945</v>
+      </c>
+      <c r="G130" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.859504132231405</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.5170915375607466</v>
+      </c>
+      <c r="J130" t="n">
+        <v>-0.9938942193984985</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M130" t="n">
+        <v>28.22854352520355</v>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O130" t="n">
+        <v>0.6000000000006001</v>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.2 trend_age=36 pullback=0.23×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>[0.306, 0.375, -1.0, -0.7986, 0.4994, 1.0, 2.0, -0.0767, 0.0195, 0.4994, 1.0, 0.2823, 0.1361, 0.3779, -0.1579, 0.2566, 0.719, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5646, -0.2549, 0.149, 0.0, 0.0, 0.0, 0.0, -0.3052, 0.579, -0.0384]</t>
+        </is>
+      </c>
+      <c r="S130" t="n">
+        <v>0</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:28:34.454292+00:00</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>73.05064201557414</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.000701393867596945</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.9158415841584159</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.5452129541124771</v>
+      </c>
+      <c r="J131" t="n">
+        <v>-0.7755587100982666</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M131" t="n">
+        <v>28.22854352520355</v>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O131" t="n">
+        <v>0.900000000000345</v>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.2 trend_age=36 pullback=0.29×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>[0.461, 0.375, -1.0, -0.7986, 0.5002, 1.0, 2.0, -0.0865, 0.0149, 0.5002, 1.0, 0.2823, 0.102, 0.3626, -0.1579, 0.1853, 0.8317, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5646, -0.2549, 0.149, 0.0, 0.0, 0.0, 0.0, -0.3095, 0.579, -0.0442]</t>
+        </is>
+      </c>
+      <c r="S131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:29:34.784659+00:00</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>72.89510756605746</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.000701393867596945</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.9158415841584159</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.5452129541124771</v>
+      </c>
+      <c r="J132" t="n">
+        <v>-0.8013300895690918</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M132" t="n">
+        <v>28.22854352520355</v>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O132" t="n">
+        <v>0.8999999999992347</v>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.2 trend_age=36 pullback=0.33×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>[0.4579, 0.375, -1.0, -0.7986, 0.5006, 1.0, 2.0, -0.0921, 0.0122, 0.5006, 1.0, 0.2823, 0.0816, 0.3535, -0.1579, 0.1426, 0.8317, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5646, -0.2549, 0.149, 0.0, 0.0, 0.0, 0.0, -0.3121, 0.579, -0.0476]</t>
+        </is>
+      </c>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:30:35.116453+00:00</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>73.20082869634277</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.000701393867596945</v>
+      </c>
+      <c r="G133" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.9158415841584159</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.5452129541124771</v>
+      </c>
+      <c r="J133" t="n">
+        <v>-0.7440509796142578</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M133" t="n">
+        <v>28.22854352520355</v>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O133" t="n">
+        <v>0.900000000000345</v>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.2 trend_age=36 pullback=0.26×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>[0.464, 0.375, -1.0, -0.7986, 0.4997, 1.0, 2.0, -0.0808, 0.0177, 0.4997, 1.0, 0.2823, 0.1224, 0.3718, -0.1579, 0.2281, 0.8317, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5646, -0.2549, 0.149, 0.0, 0.0, 0.0, 0.0, -0.3069, 0.579, -0.0408]</t>
+        </is>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:31:35.473479+00:00</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>65.83731504728055</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.0007021081533113934</v>
+      </c>
+      <c r="G134" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.859504132231405</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.5106162786892869</v>
+      </c>
+      <c r="J134" t="n">
+        <v>-0.7615368366241455</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M134" t="n">
+        <v>28.22854352520354</v>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O134" t="n">
+        <v>0.8999999999992347</v>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.2 trend_age=36 pullback=0.09×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>[0.3167, 0.375, -1.0, -0.7979, 0.4978, 1.0, 2.0, -0.0527, 0.0295, 0.4978, 1.0, 0.2823, 0.2109, 0.4118, -0.1571, 0.413, 0.719, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5646, -0.2546, 0.149, 0.0, 0.0, 0.0, 0.0, -0.2953, 0.5785, -0.0249]</t>
+        </is>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:32:35.856147+00:00</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>65.30056137724223</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.0007028224390258338</v>
+      </c>
+      <c r="G135" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.859504132231405</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.5170915375607466</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.9984625577926636</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M135" t="n">
+        <v>28.22854352520354</v>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O135" t="n">
+        <v>0.900000000000345</v>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.2 trend_age=36 pullback=0.23×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>[0.306, 0.375, -1.0, -0.7972, 0.4994, 1.0, 2.0, -0.0767, 0.0195, 0.4994, 1.0, 0.2823, 0.1361, 0.3779, -0.1562, 0.2561, 0.719, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5646, -0.2543, 0.149, 0.0, 0.0, 0.0, 0.0, -0.3045, 0.5781, -0.0384]</t>
+        </is>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:33:36.228362+00:00</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>65.59352754870872</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.0007028224390258338</v>
+      </c>
+      <c r="G136" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.859504132231405</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.5170915375607466</v>
+      </c>
+      <c r="J136" t="n">
+        <v>-0.8995026350021362</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M136" t="n">
+        <v>28.22854352520354</v>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O136" t="n">
+        <v>0.8999999999992347</v>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.2 trend_age=36 pullback=0.15×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>[0.3119, 0.375, -1.0, -0.7972, 0.4986, 1.0, 2.0, -0.0635, 0.0249, 0.4986, 1.0, 0.2823, 0.1769, 0.3964, -0.1562, 0.3415, 0.719, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5646, -0.2543, 0.149, 0.0, 0.0, 0.0, 0.0, -0.2994, 0.5781, -0.031]</t>
+        </is>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:34:36.557761+00:00</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>65.59352754870872</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.0007028224390258338</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.859504132231405</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.5170915375607466</v>
+      </c>
+      <c r="J137" t="n">
+        <v>-0.8995026350021362</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M137" t="n">
+        <v>28.22854352520354</v>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O137" t="n">
+        <v>0.6999999999990347</v>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.2 trend_age=36 pullback=0.15×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>[0.3119, 0.375, -1.0, -0.7972, 0.4986, 1.0, 2.0, -0.0635, 0.0249, 0.4986, 1.0, 0.2823, 0.1769, 0.3964, -0.1562, 0.3415, 0.719, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5646, -0.2543, 0.149, 0.0, 0.0, 0.0, 0.0, -0.2994, 0.5781, -0.031]</t>
+        </is>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:35:36.892387+00:00</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>65.88649729243608</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.0007028224390258338</v>
+      </c>
+      <c r="G138" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.859504132231405</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.5193270036667341</v>
+      </c>
+      <c r="J138" t="n">
+        <v>-0.7275365591049194</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M138" t="n">
+        <v>28.22854352520354</v>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O138" t="n">
+        <v>0.5999999999994898</v>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.2 trend_age=36 pullback=0.07×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>[0.3177, 0.375, -1.0, -0.7972, 0.4977, 1.0, 2.0, -0.0506, 0.0304, 0.4977, 1.0, 0.2823, 0.2177, 0.4149, -0.1562, 0.4269, 0.719, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5646, -0.2543, 0.149, 0.0, 0.0, 0.0, 0.0, -0.2942, 0.5781, -0.0236]</t>
+        </is>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:36:37.352798+00:00</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>65.88709759965633</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.0007042510104547225</v>
+      </c>
+      <c r="G139" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.9852941176470589</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.6105392316312934</v>
+      </c>
+      <c r="J139" t="n">
+        <v>-0.3332669734954834</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M139" t="n">
+        <v>28.22854352520353</v>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O139" t="n">
+        <v>0.5999999999994898</v>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.2 trend_age=36 pullback=0.07×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>[0.3177, 0.375, -1.0, -0.7957, 0.4977, 1.0, 2.0, -0.0506, 0.0303, 0.4977, 1.0, 0.2823, 0.2177, 0.4149, -0.1546, 0.426, 0.9706, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5646, -0.2538, 0.149, 0.0, 0.0, 0.0, 0.0, -0.2936, 0.5773, -0.0236]</t>
+        </is>
+      </c>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:37:37.715126+00:00</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>65.84754391923789</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.0007085367247413807</v>
+      </c>
+      <c r="G140" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.9985744832501782</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.6668630844986539</v>
+      </c>
+      <c r="J140" t="n">
+        <v>-0.2176234275102615</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M140" t="n">
+        <v>28.13879208350026</v>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O140" t="n">
+        <v>0.700000000000145</v>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.1 trend_age=36 pullback=0.06×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>[0.317, 0.375, -1.0, -0.7915, 0.4975, 1.0, 2.0, -0.0485, 0.031, 0.4975, 1.0, 0.2814, 0.2245, 0.418, -0.1495, 0.4375, 0.9971, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5628, -0.2442, 0.14, 0.0, 0.0, 0.0, 0.0, -0.291, 0.5748, -0.0224]</t>
+        </is>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:38:38.051195+00:00</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>65.70231012514806</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.0007085367247413807</v>
+      </c>
+      <c r="G141" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.9852941176470589</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.6239788118855585</v>
+      </c>
+      <c r="J141" t="n">
+        <v>-0.3495007157325745</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M141" t="n">
+        <v>28.13879208350026</v>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O141" t="n">
+        <v>0.7999999999996898</v>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.1 trend_age=36 pullback=0.10×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>[0.314, 0.375, -1.0, -0.7915, 0.498, 1.0, 2.0, -0.0549, 0.0283, 0.498, 1.0, 0.2814, 0.2041, 0.4087, -0.1495, 0.3952, 0.9706, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5628, -0.2442, 0.14, 0.0, 0.0, 0.0, 0.0, -0.2935, 0.5748, -0.0261]</t>
+        </is>
+      </c>
+      <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:39:38.432118+00:00</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>65.46025578591802</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.0007085367247413807</v>
+      </c>
+      <c r="G142" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.9903536977491961</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.6300408859337449</v>
+      </c>
+      <c r="J142" t="n">
+        <v>-0.415225625038147</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M142" t="n">
+        <v>28.13879208350026</v>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O142" t="n">
+        <v>0.900000000000345</v>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.1 trend_age=36 pullback=0.16×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>[0.3092, 0.375, -1.0, -0.7915, 0.4987, 1.0, 2.0, -0.0657, 0.0238, 0.4987, 1.0, 0.2814, 0.1701, 0.3933, -0.1495, 0.3246, 0.9807, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5628, -0.2442, 0.14, 0.0, 0.0, 0.0, 0.0, -0.2978, 0.5748, -0.0322]</t>
+        </is>
+      </c>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:40:38.779836+00:00</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>73.02408732431846</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.0007085367247413807</v>
+      </c>
+      <c r="G143" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.9903536977491961</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.6559610654405023</v>
+      </c>
+      <c r="J143" t="n">
+        <v>-0.4109259247779846</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M143" t="n">
+        <v>28.13879208350026</v>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O143" t="n">
+        <v>0.900000000000345</v>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.1 trend_age=36 pullback=0.28×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>[0.4605, 0.375, -1.0, -0.7915, 0.5, 1.0, 2.0, -0.0846, 0.0157, 0.5, 1.0, 0.2814, 0.1088, 0.3657, -0.1495, 0.1976, 0.9807, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5628, -0.2442, 0.14, 0.0, 0.0, 0.0, 0.0, -0.3055, 0.5748, -0.0431]</t>
+        </is>
+      </c>
+      <c r="S143" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:41:39.169665+00:00</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>72.7674765157761</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.0007085367247413807</v>
+      </c>
+      <c r="G144" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.9903536977491961</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0.6494572168948856</v>
+      </c>
+      <c r="J144" t="n">
+        <v>-0.4084146320819855</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M144" t="n">
+        <v>28.13879208350026</v>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O144" t="n">
+        <v>0.900000000000345</v>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.1 trend_age=36 pullback=0.34×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>[0.4553, 0.375, -1.0, -0.7915, 0.5008, 1.0, 2.0, -0.0939, 0.0112, 0.5008, 1.0, 0.2814, 0.0748, 0.3505, -0.1495, 0.127, 0.9807, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5628, -0.2442, 0.14, 0.0, 0.0, 0.0, 0.0, -0.3098, 0.5748, -0.0488]</t>
+        </is>
+      </c>
+      <c r="S144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0</v>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:42:39.799863+00:00</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>72.7674765157761</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.0007085367247413807</v>
+      </c>
+      <c r="G145" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.9903536977491961</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0.6494572168948856</v>
+      </c>
+      <c r="J145" t="n">
+        <v>-0.4084138870239258</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M145" t="n">
+        <v>28.13879208350026</v>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O145" t="n">
+        <v>0.8000000000008001</v>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.1 trend_age=36 pullback=0.34×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>[0.4553, 0.375, -1.0, -0.7915, 0.5008, 1.0, 2.0, -0.0939, 0.0112, 0.5008, 1.0, 0.2814, 0.0748, 0.3505, -0.1495, 0.127, 0.9807, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5628, -0.2442, 0.14, 0.0, 0.0, 0.0, 0.0, -0.3098, 0.5748, -0.0488]</t>
+        </is>
+      </c>
+      <c r="S145" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:44:40.359939+00:00</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>72.82541882660615</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.0007121081533135986</v>
+      </c>
+      <c r="G146" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.9903536977491961</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0.6494572168948856</v>
+      </c>
+      <c r="J146" t="n">
+        <v>-0.4099821448326111</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M146" t="n">
+        <v>28.13879208350023</v>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O146" t="n">
+        <v>0.5999999999994898</v>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.1 trend_age=36 pullback=0.33×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>[0.4565, 0.375, -1.0, -0.7879, 0.5006, 1.0, 2.0, -0.0921, 0.012, 0.5006, 1.0, 0.2814, 0.0816, 0.3535, -0.1453, 0.1404, 0.9807, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5628, -0.243, 0.14, 0.0, 0.0, 0.0, 0.0, -0.3074, 0.5726, -0.0476]</t>
+        </is>
+      </c>
+      <c r="S146" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" t="n">
+        <v>0</v>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:45:40.723525+00:00</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>72.77435406039805</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.0007121081533135986</v>
+      </c>
+      <c r="G147" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.9903536977491961</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0.6494572168948856</v>
+      </c>
+      <c r="J147" t="n">
+        <v>-0.4077266454696655</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M147" t="n">
+        <v>28.13879208350023</v>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O147" t="n">
+        <v>0.700000000000145</v>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.1 trend_age=36 pullback=0.34×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>[0.4555, 0.375, -1.0, -0.7879, 0.5008, 1.0, 2.0, -0.0939, 0.0111, 0.5008, 1.0, 0.2814, 0.0748, 0.3505, -0.1453, 0.1264, 0.9807, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5628, -0.243, 0.14, 0.0, 0.0, 0.0, 0.0, -0.3082, 0.5726, -0.0488]</t>
+        </is>
+      </c>
+      <c r="S147" t="n">
+        <v>0</v>
+      </c>
+      <c r="T147" t="n">
+        <v>0</v>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:48:41.456089+00:00</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>72.72612327143688</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.0007135367247424872</v>
+      </c>
+      <c r="G148" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.9903536977491961</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0.6494572168948856</v>
+      </c>
+      <c r="J148" t="n">
+        <v>-0.403795599937439</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M148" t="n">
+        <v>28.13879208350022</v>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O148" t="n">
+        <v>0.900000000000345</v>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.1 trend_age=36 pullback=0.35×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>[0.4545, 0.375, -1.0, -0.7865, 0.5009, 1.0, 2.0, -0.0958, 0.0102, 0.5009, 1.0, 0.2814, 0.068, 0.3474, -0.1436, 0.1121, 0.9807, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5628, -0.2425, 0.14, 0.0, 0.0, 0.0, 0.0, -0.3085, 0.5718, -0.0499]</t>
+        </is>
+      </c>
+      <c r="S148" t="n">
+        <v>0</v>
+      </c>
+      <c r="T148" t="n">
+        <v>0</v>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:49:41.794273+00:00</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>72.72612327143688</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.0007135367247424872</v>
+      </c>
+      <c r="G149" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0.9903536977491961</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0.6494572168948856</v>
+      </c>
+      <c r="J149" t="n">
+        <v>-0.4037947952747345</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M149" t="n">
+        <v>28.13879208350022</v>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O149" t="n">
+        <v>0.5999999999994898</v>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.1 trend_age=36 pullback=0.35×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>[0.4545, 0.375, -1.0, -0.7865, 0.5009, 1.0, 2.0, -0.0958, 0.0102, 0.5009, 1.0, 0.2814, 0.068, 0.3474, -0.1436, 0.1121, 0.9807, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5628, -0.2425, 0.14, 0.0, 0.0, 0.0, 0.0, -0.3085, 0.5718, -0.0499]</t>
+        </is>
+      </c>
+      <c r="S149" t="n">
+        <v>0</v>
+      </c>
+      <c r="T149" t="n">
+        <v>0</v>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:50:42.184252+00:00</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>72.82804833037967</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.0007135367247424872</v>
+      </c>
+      <c r="G150" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0.9903536977491961</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0.6494572168948856</v>
+      </c>
+      <c r="J150" t="n">
+        <v>-0.4091934859752655</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M150" t="n">
+        <v>28.13879208350022</v>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O150" t="n">
+        <v>0.5999999999994898</v>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.1 trend_age=36 pullback=0.33×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>[0.4566, 0.375, -1.0, -0.7865, 0.5006, 1.0, 2.0, -0.0921, 0.012, 0.5006, 1.0, 0.2814, 0.0816, 0.3535, -0.1436, 0.1401, 0.9807, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5628, -0.2425, 0.14, 0.0, 0.0, 0.0, 0.0, -0.3068, 0.5718, -0.0476]</t>
+        </is>
+      </c>
+      <c r="S150" t="n">
+        <v>0</v>
+      </c>
+      <c r="T150" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:51:42.529551+00:00</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>72.82804833037967</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.0007135367247424872</v>
+      </c>
+      <c r="G151" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0.9903536977491961</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0.6494572168948856</v>
+      </c>
+      <c r="J151" t="n">
+        <v>-0.4091934859752655</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M151" t="n">
+        <v>28.13879208350022</v>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O151" t="n">
+        <v>0.5999999999994898</v>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.1 trend_age=36 pullback=0.33×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>[0.4566, 0.375, -1.0, -0.7865, 0.5006, 1.0, 2.0, -0.0921, 0.012, 0.5006, 1.0, 0.2814, 0.0816, 0.3535, -0.1436, 0.1401, 0.9807, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5628, -0.2425, 0.14, 0.0, 0.0, 0.0, 0.0, -0.3068, 0.5718, -0.0476]</t>
+        </is>
+      </c>
+      <c r="S151" t="n">
+        <v>0</v>
+      </c>
+      <c r="T151" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:52:42.892431+00:00</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>72.72612327143688</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.0007135367247424872</v>
+      </c>
+      <c r="G152" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0.9903536977491961</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0.6494572168948856</v>
+      </c>
+      <c r="J152" t="n">
+        <v>-0.403795599937439</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M152" t="n">
+        <v>28.13879208350022</v>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O152" t="n">
+        <v>0.900000000000345</v>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.1 trend_age=36 pullback=0.35×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>[0.4545, 0.375, -1.0, -0.7865, 0.5009, 1.0, 2.0, -0.0958, 0.0102, 0.5009, 1.0, 0.2814, 0.068, 0.3474, -0.1436, 0.1121, 0.9807, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5628, -0.2425, 0.14, 0.0, 0.0, 0.0, 0.0, -0.3085, 0.5718, -0.0499]</t>
+        </is>
+      </c>
+      <c r="S152" t="n">
+        <v>0</v>
+      </c>
+      <c r="T152" t="n">
+        <v>0</v>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-06-05 05:53:43.254120+00:00</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>AGENT_SKIP</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>72.62419821249347</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.0007135367247424872</v>
+      </c>
+      <c r="G153" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0.7102473498233216</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0.4512358420984572</v>
+      </c>
+      <c r="J153" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M153" t="n">
+        <v>28.13879208350022</v>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O153" t="n">
+        <v>0.6000000000006001</v>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>TF SELL ADX=28.1 trend_age=36 pullback=0.38×ATR H4=0 D1=1</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>[0.4525, 0.375, -1.0, -0.7865, 0.5012, 1.0, 2.0, -0.0994, 0.0084, 0.5012, 1.0, 0.2814, 0.0544, 0.3414, -0.1436, 0.0841, 0.4205, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5628, -0.2425, 0.14, 0.0, 0.0, 0.0, 0.0, -0.3102, 0.5718, -0.0521]</t>
+        </is>
+      </c>
+      <c r="S153" t="n">
+        <v>0</v>
+      </c>
+      <c r="T153" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>tf_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:13:58.690245+00:00</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D154" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>76.13908668207087</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.0004036472890842924</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0.2974269903462227</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M154" t="n">
+        <v>18.30624503808509</v>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O154" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>BB%B=1.15 (extreme=1.51); RSI=70.1 (extreme=0.25); Wick ratio=0.62; ADX H1=18.3 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>[0.5228, 0.0, -1.0, -1.0964, 1.0, -1.0, 2.0, 0.4025, 0.279, 0.0058, 1.0, 0.2456, 0.7241, 1.1534, 0.0172, 3.0, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5088, 0.0, 0.0, 0.0, 0.0, 0.0, 0.6441, 0.4483, 0.4914, 0.1575]</t>
+        </is>
+      </c>
+      <c r="S154" t="n">
+        <v>0</v>
+      </c>
+      <c r="T154" t="n">
+        <v>0</v>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:14:59.061249+00:00</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D155" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>76.46765313383496</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.0004036472890842924</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0.2980630363553134</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M155" t="n">
+        <v>18.30624503808509</v>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O155" t="n">
+        <v>0.2999999999997449</v>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>BB%B=1.15 (extreme=1.49); RSI=69.9 (extreme=0.25); Wick ratio=0.70; ADX H1=18.3 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>[0.5294, 0.0, -1.0, -1.0964, 1.0, -1.0, 2.0, 0.3982, 0.2759, 0.0059, 1.0, 0.2456, 0.7011, 1.1459, 0.0172, 3.0, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.5088, 0.0, 0.0, 0.0, 0.0, 0.0, 0.6321, 0.4453, 0.4914, 0.1559]</t>
+        </is>
+      </c>
+      <c r="S155" t="n">
+        <v>0</v>
+      </c>
+      <c r="T155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:24:00.949820+00:00</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D156" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>78.20429236536336</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.0004069581870821094</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0.2967366367815861</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M156" t="n">
+        <v>18.42219590628001</v>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O156" t="n">
+        <v>0.5000000000010552</v>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>BB%B=1.10 (extreme=1.34); RSI=72.1 (extreme=0.30); Wick ratio=0.83; ADX H1=18.4 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>[0.5641, 0.0, -1.0, -1.093, 1.0, -1.0, 2.0, 0.4415, 0.3345, 0.0013, 1.0, 0.2636, 0.8361, 1.1011, 0.0316, 3.0, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.4727, 0.0, 0.0, 0.0, 0.0, 0.0, 0.6886, 0.6143, 0.4842, 0.1714]</t>
+        </is>
+      </c>
+      <c r="S156" t="n">
+        <v>0</v>
+      </c>
+      <c r="T156" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:25:01.633323+00:00</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D157" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>78.20429236536336</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.0004069581870821094</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0.2967366367815861</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M157" t="n">
+        <v>18.42219590628001</v>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O157" t="n">
+        <v>0.6000000000017103</v>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>BB%B=1.10 (extreme=1.34); RSI=72.1 (extreme=0.30); Wick ratio=0.83; ADX H1=18.4 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>[0.5641, 0.0, -1.0, -1.093, 1.0, -1.0, 2.0, 0.4415, 0.3345, 0.0013, 1.0, 0.2636, 0.8361, 1.1011, 0.0316, 3.0, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.4727, 0.0, 0.0, 0.0, 0.0, 0.0, 0.6886, 0.6143, 0.4842, 0.1714]</t>
+        </is>
+      </c>
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:27:02.206554+00:00</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D158" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>80.61856736217317</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.0004069581870821094</v>
+      </c>
+      <c r="G158" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0.297224290940991</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M158" t="n">
+        <v>18.42219590628001</v>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O158" t="n">
+        <v>0.8000000000008001</v>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>BB%B=1.09 (extreme=1.29); RSI=71.7 (extreme=0.29); Wick ratio=1.36; ADX H1=18.4 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>[0.6124, 0.0, -1.0, -1.093, 1.0, -1.0, 2.0, 0.4333, 0.3283, 0.0011, 1.0, 0.2636, 0.7923, 1.0875, 0.0316, 3.0, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.4727, 0.0, 0.0, 0.0, 0.0, 0.0, 0.6647, 0.6084, 0.4842, 0.1684]</t>
+        </is>
+      </c>
+      <c r="S158" t="n">
+        <v>0</v>
+      </c>
+      <c r="T158" t="n">
+        <v>0</v>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:28:02.600858+00:00</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D159" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>77.3878080925934</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.0004069581870821094</v>
+      </c>
+      <c r="G159" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0.2953685722315645</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M159" t="n">
+        <v>18.42219590628001</v>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O159" t="n">
+        <v>0.3000000000019654</v>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>BB%B=1.11 (extreme=1.36); RSI=72.3 (extreme=0.31); Wick ratio=0.65; ADX H1=18.4 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>[0.5478, 0.0, -1.0, -1.093, 1.0, -1.0, 2.0, 0.4455, 0.3377, 0.0014, 1.0, 0.2636, 0.8579, 1.1078, 0.0316, 3.0, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.4727, 0.0, 0.0, 0.0, 0.0, 0.0, 0.7005, 0.6173, 0.4842, 0.1729]</t>
+        </is>
+      </c>
+      <c r="S159" t="n">
+        <v>0</v>
+      </c>
+      <c r="T159" t="n">
+        <v>0</v>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:34:03.961696+00:00</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D160" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>78.27714483373471</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.000406869338178347</v>
+      </c>
+      <c r="G160" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0.2697389622945537</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0.2939545798985642</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M160" t="n">
+        <v>18.80301739488767</v>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O160" t="n">
+        <v>0.4999999999988347</v>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>BB%B=1.10 (extreme=1.32); RSI=75.6 (extreme=0.39); Wick ratio=0.50; ADX H1=18.8 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>[0.5655, 0.0, -1.0, -1.0931, 1.0, -1.0, 2.0, 0.5111, 0.4279, 0.0111, 1.0, 0.2853, 0.9163, 1.0968, 0.037, 3.0, -0.4605, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.4293, 0.0, 0.0, 0.0, 0.0, 0.0, 0.8417, 0.8225, 0.4815, 0.1993]</t>
+        </is>
+      </c>
+      <c r="S160" t="n">
+        <v>0</v>
+      </c>
+      <c r="T160" t="n">
+        <v>0</v>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:35:04.420277+00:00</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D161" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>80.65093799965267</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.0004090121961047342</v>
+      </c>
+      <c r="G161" t="n">
+        <v>1</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0.2947813340404503</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M161" t="n">
+        <v>18.83640747858227</v>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O161" t="n">
+        <v>0.700000000000145</v>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>BB%B=1.09 (extreme=1.30); RSI=75.3 (extreme=0.38); Wick ratio=1.00; ADX H1=18.8 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>[0.613, 0.0, -1.0, -1.091, 1.0, -1.0, 2.0, 0.506, 0.421, 0.0109, 1.0, 0.2857, 0.8624, 1.0886, 0.0424, 3.0, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.4287, 0.0, 0.0, 0.0, 0.0, 0.0, 0.8195, 0.8138, 0.4788, 0.1972]</t>
+        </is>
+      </c>
+      <c r="S161" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" t="n">
+        <v>0</v>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:37:05.326366+00:00</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D162" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>79.56364121630511</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.0004168693418348314</v>
+      </c>
+      <c r="G162" t="n">
+        <v>1</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0.2679050822353194</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0.2913820052312896</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M162" t="n">
+        <v>18.95572978527937</v>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O162" t="n">
+        <v>0.700000000000145</v>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>BB%B=1.11 (extreme=1.38); RSI=76.0 (extreme=0.40); Wick ratio=0.71; ADX H1=19.0 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>[0.5913, 0.0, -1.0, -1.0831, 1.0, -1.0, 2.0, 0.5209, 0.4269, 0.0114, 1.0, 0.2869, 0.8515, 1.1128, 0.062, 3.0, -0.4642, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.4262, 0.0, 0.0, 0.0, 0.0, 0.0, 0.8564, 0.8115, 0.469, 0.2035]</t>
+        </is>
+      </c>
+      <c r="S162" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:41:06.299611+00:00</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D163" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>87.50006937960403</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.0004282979174422354</v>
+      </c>
+      <c r="G163" t="n">
+        <v>1</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0.2974525619451053</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0.3067316353688869</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M163" t="n">
+        <v>19.12103186031952</v>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O163" t="n">
+        <v>0.700000000000145</v>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>BB%B=1.09 (extreme=1.31); RSI=75.5 (extreme=0.39); Wick ratio=2.35; ADX H1=19.1 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>[0.75, 0.0, -1.0, -1.0717, 1.0, -1.0, 2.0, 0.5094, 0.405, 0.011, 1.0, 0.2885, 0.6735, 1.0941, 0.0904, 3.0, -0.4051, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.423, 0.0, 0.0, 0.0, 0.0, 0.0, 0.7939, 0.78, 0.4548, 0.1986]</t>
+        </is>
+      </c>
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:42:06.687081+00:00</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D164" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>85.10985927934102</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0.0004282979174422354</v>
+      </c>
+      <c r="G164" t="n">
+        <v>1</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0.2974525619451053</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0.3067316353688869</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M164" t="n">
+        <v>19.12103186031952</v>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O164" t="n">
+        <v>0.2000000000013102</v>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>BB%B=1.10 (extreme=1.34); RSI=75.7 (extreme=0.39); Wick ratio=1.85; ADX H1=19.1 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>[0.7022, 0.0, -1.0, -1.0717, 1.0, -1.0, 2.0, 0.5144, 0.4095, 0.0112, 1.0, 0.2885, 0.698, 1.1022, 0.0904, 3.0, -0.4051, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.423, 0.0, 0.0, 0.0, 0.0, 0.0, 0.8109, 0.7842, 0.4548, 0.2007]</t>
+        </is>
+      </c>
+      <c r="S164" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" t="n">
+        <v>0</v>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:43:07.088924+00:00</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D165" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>83.89600721478209</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.0004282979174422354</v>
+      </c>
+      <c r="G165" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0.2913733319323316</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0.3019547222786972</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M165" t="n">
+        <v>19.12103186031952</v>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O165" t="n">
+        <v>0.2999999999997449</v>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>BB%B=1.11 (extreme=1.36); RSI=75.9 (extreme=0.40); Wick ratio=1.59; ADX H1=19.1 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>[0.6779, 0.0, -1.0, -1.0717, 1.0, -1.0, 2.0, 0.5177, 0.4125, 0.0113, 1.0, 0.2885, 0.7143, 1.1076, 0.0904, 3.0, -0.4173, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.423, 0.0, 0.0, 0.0, 0.0, 0.0, 0.8222, 0.787, 0.4548, 0.2021]</t>
+        </is>
+      </c>
+      <c r="S165" t="n">
+        <v>0</v>
+      </c>
+      <c r="T165" t="n">
+        <v>0</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:44:07.458668+00:00</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D166" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>84.47222668064701</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.0004282979174422354</v>
+      </c>
+      <c r="G166" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0.2913733319323316</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0.3037474968191438</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M166" t="n">
+        <v>19.12103186031952</v>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O166" t="n">
+        <v>0.2999999999997449</v>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>BB%B=1.10 (extreme=1.35); RSI=75.8 (extreme=0.40); Wick ratio=1.71; ADX H1=19.1 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>[0.6894, 0.0, -1.0, -1.0717, 1.0, -1.0, 2.0, 0.516, 0.411, 0.0113, 1.0, 0.2885, 0.7061, 1.1049, 0.0904, 3.0, -0.4173, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.423, 0.0, 0.0, 0.0, 0.0, 0.0, 0.8165, 0.7856, 0.4548, 0.2014]</t>
+        </is>
+      </c>
+      <c r="S166" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" t="n">
+        <v>0</v>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:52:09.166594+00:00</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D167" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>79.35208772200254</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0.0004319909212497868</v>
+      </c>
+      <c r="G167" t="n">
+        <v>1</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0.2971444843243858</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M167" t="n">
+        <v>19.12103186031952</v>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O167" t="n">
+        <v>0.5999999999994898</v>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>BB%B=1.07 (extreme=1.22); RSI=77.3 (extreme=0.43); Wick ratio=0.54; ADX H1=19.1 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>[0.587, 0.0, -1.0, -1.068, 1.0, -1.0, 2.0, 0.5469, 0.4381, 0.0196, 1.0, 0.3108, 0.8531, 1.0673, 0.1034, 2.5463, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.3784, 0.0, 0.0, 0.0, 0.0, 0.0, 0.8426, 0.8484, 0.4483, 0.2139]</t>
+        </is>
+      </c>
+      <c r="S167" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:54:09.751496+00:00</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D168" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>85.48312339756139</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.0004319909212497868</v>
+      </c>
+      <c r="G168" t="n">
+        <v>1</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0.2893888919228879</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0.3010206429953035</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M168" t="n">
+        <v>19.12103186031952</v>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O168" t="n">
+        <v>0.7999999999985796</v>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>BB%B=1.03 (extreme=1.11); RSI=76.3 (extreme=0.41); Wick ratio=1.87; ADX H1=19.1 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>[0.7097, 0.0, -1.0, -1.068, 1.0, -1.0, 2.0, 0.526, 0.4189, 0.0188, 1.0, 0.3108, 0.7469, 1.0334, 0.1034, 2.2454, -0.4212, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.3784, 0.0, 0.0, 0.0, 0.0, 0.0, 0.7696, 0.8301, 0.4483, 0.2049]</t>
+        </is>
+      </c>
+      <c r="S168" t="n">
+        <v>0</v>
+      </c>
+      <c r="T168" t="n">
+        <v>0</v>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:55:10.156824+00:00</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D169" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>84.62929012622685</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.0004319909212497868</v>
+      </c>
+      <c r="G169" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0.2893888919228879</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0.3010206429953035</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M169" t="n">
+        <v>19.12103186031952</v>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O169" t="n">
+        <v>0.6000000000017103</v>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>BB%B=1.04 (extreme=1.12); RSI=76.4 (extreme=0.41); Wick ratio=1.69; ADX H1=19.1 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>[0.6926, 0.0, -1.0, -1.068, 1.0, -1.0, 2.0, 0.5277, 0.4204, 0.0189, 1.0, 0.3108, 0.7551, 1.0361, 0.1034, 2.2686, -0.4212, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.3784, 0.0, 0.0, 0.0, 0.0, 0.0, 0.7753, 0.8316, 0.4483, 0.2056]</t>
+        </is>
+      </c>
+      <c r="S169" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" t="n">
+        <v>0</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:56:10.511322+00:00</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D170" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>79.35208772200254</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.0004319909212497868</v>
+      </c>
+      <c r="G170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0.2987399217410107</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M170" t="n">
+        <v>19.12103186031952</v>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O170" t="n">
+        <v>0.1999999999990898</v>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>BB%B=1.07 (extreme=1.22); RSI=77.3 (extreme=0.43); Wick ratio=0.54; ADX H1=19.1 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>[0.587, 0.0, -1.0, -1.068, 1.0, -1.0, 2.0, 0.5469, 0.4381, 0.0196, 1.0, 0.3108, 0.8531, 1.0673, 0.1034, 2.5463, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.3784, 0.0, 0.0, 0.0, 0.0, 0.0, 0.8426, 0.8484, 0.4483, 0.2139]</t>
+        </is>
+      </c>
+      <c r="S170" t="n">
+        <v>0</v>
+      </c>
+      <c r="T170" t="n">
+        <v>0</v>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:57:10.876857+00:00</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D171" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>79.59784175801906</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.0004319909212497868</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0.2990845551242492</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M171" t="n">
+        <v>19.12103186031952</v>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O171" t="n">
+        <v>0.2999999999997449</v>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>BB%B=1.06 (extreme=1.22); RSI=77.3 (extreme=0.43); Wick ratio=0.59; ADX H1=19.1 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>[0.592, 0.0, -1.0, -1.068, 1.0, -1.0, 2.0, 0.5454, 0.4366, 0.0195, 1.0, 0.3108, 0.8449, 1.0648, 0.1034, 2.5232, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.3784, 0.0, 0.0, 0.0, 0.0, 0.0, 0.837, 0.847, 0.4483, 0.2132]</t>
+        </is>
+      </c>
+      <c r="S171" t="n">
+        <v>0</v>
+      </c>
+      <c r="T171" t="n">
+        <v>0</v>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:58:11.255065+00:00</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D172" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>80.15680755227834</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.0004319909212497868</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0.2990845551242492</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M172" t="n">
+        <v>19.12103186031952</v>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O172" t="n">
+        <v>0.2999999999997449</v>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>BB%B=1.06 (extreme=1.20); RSI=77.1 (extreme=0.43); Wick ratio=0.72; ADX H1=19.1 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>[0.6031, 0.0, -1.0, -1.068, 1.0, -1.0, 2.0, 0.5423, 0.4337, 0.0194, 1.0, 0.3108, 0.8286, 1.0597, 0.1034, 2.4769, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.3784, 0.0, 0.0, 0.0, 0.0, 0.0, 0.8258, 0.8442, 0.4483, 0.2119]</t>
+        </is>
+      </c>
+      <c r="S172" t="n">
+        <v>0</v>
+      </c>
+      <c r="T172" t="n">
+        <v>0</v>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:59:11.637943+00:00</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D173" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>84.62929012622685</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.0004319909212497868</v>
+      </c>
+      <c r="G173" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0.2893888919228879</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0.3010206429953035</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L173" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M173" t="n">
+        <v>19.12103186031952</v>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O173" t="n">
+        <v>0.8000000000008001</v>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>BB%B=1.04 (extreme=1.12); RSI=76.4 (extreme=0.41); Wick ratio=1.69; ADX H1=19.1 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>[0.6926, 0.0, -1.0, -1.068, 1.0, -1.0, 2.0, 0.5277, 0.4204, 0.0189, 1.0, 0.3108, 0.7551, 1.0361, 0.1034, 2.2686, -0.4212, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.3784, 0.0, 0.0, 0.0, 0.0, 0.0, 0.7753, 0.8316, 0.4483, 0.2056]</t>
+        </is>
+      </c>
+      <c r="S173" t="n">
+        <v>0</v>
+      </c>
+      <c r="T173" t="n">
+        <v>0</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:01:12.335037+00:00</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D174" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>83.87235475784793</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.0004132772573775736</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0.2943811159314421</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L174" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M174" t="n">
+        <v>19.20046647189884</v>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O174" t="n">
+        <v>0.4999999999988347</v>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>BB%B=0.96 (extreme=0.86); RSI=76.2 (extreme=0.41); Wick ratio=6.00; ADX H1=19.2 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>[0.6774, 0.0, -1.0, -1.0867, 0.8588, -1.0, 2.0, 0.5243, 0.4248, 0.026, 1.0, 0.3315, 0.7388, 0.9576, 0.0591, 2.3713, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.337, 0.0, 0.0, 0.0, 0.0, 0.0021, 0.726, 0.9312, 0.4704, 0.1423]</t>
+        </is>
+      </c>
+      <c r="S174" t="n">
+        <v>0</v>
+      </c>
+      <c r="T174" t="n">
+        <v>0</v>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:04:13.110839+00:00</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D175" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>79.11900755978107</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.0004311344067641394</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0.2913733319323316</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0.3016176072526543</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L175" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M175" t="n">
+        <v>19.20046647189877</v>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O175" t="n">
+        <v>0.1999999999990898</v>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>BB%B=1.02 (extreme=1.06); RSI=78.1 (extreme=0.45); Wick ratio=0.41; ADX H1=19.2 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>[0.5824, 0.0, -1.0, -1.0689, 1.0, -1.0, 2.0, 0.5629, 0.4413, 0.0274, 1.0, 0.3318, 0.9265, 1.0178, 0.1039, 2.8065, -0.4173, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.3363, 0.0, 0.0, 0.0, 0.0, 0.0083, 0.8253, 0.925, 0.4481, 0.1606]</t>
+        </is>
+      </c>
+      <c r="S175" t="n">
+        <v>0</v>
+      </c>
+      <c r="T175" t="n">
+        <v>0</v>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:05:13.499104+00:00</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D176" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>85.14043149336665</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0.0004311344067641394</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I176" t="n">
+        <v>0.2965654720860558</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L176" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M176" t="n">
+        <v>19.20046647189877</v>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O176" t="n">
+        <v>0.5999999999994898</v>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>BB%B=0.97 (extreme=0.90); RSI=76.6 (extreme=0.41); Wick ratio=9.33; ADX H1=19.2 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>[0.7028, 0.0, -1.0, -1.0689, 0.8951, -1.0, 2.0, 0.5315, 0.4131, 0.0262, 1.0, 0.3318, 0.7714, 0.9685, 0.1039, 2.3659, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.3363, 0.0, 0.0, 0.0, 0.0, 0.0104, 0.7184, 0.8983, 0.4481, 0.1456]</t>
+        </is>
+      </c>
+      <c r="S176" t="n">
+        <v>0</v>
+      </c>
+      <c r="T176" t="n">
+        <v>0</v>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:06:13.923801+00:00</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D177" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>80.11443588658533</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0.0004311344067641394</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I177" t="n">
+        <v>0.2965124248055995</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M177" t="n">
+        <v>19.20046647189877</v>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O177" t="n">
+        <v>0.700000000000145</v>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>BB%B=1.01 (extreme=1.03); RSI=77.9 (extreme=0.45); Wick ratio=0.63; ADX H1=19.2 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>[0.6023, 0.0, -1.0, -1.0689, 1.0, -1.0, 2.0, 0.5583, 0.4368, 0.0272, 1.0, 0.3318, 0.902, 1.0102, 0.1039, 2.737, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.3363, 0.0, 0.0, 0.0, 0.0, 0.0125, 0.8084, 0.9208, 0.4481, 0.1583]</t>
+        </is>
+      </c>
+      <c r="S177" t="n">
+        <v>0</v>
+      </c>
+      <c r="T177" t="n">
+        <v>0</v>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:07:14.355248+00:00</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D178" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>86.69267509430153</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0.0004311344067641394</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0.2965654720860558</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M178" t="n">
+        <v>19.20046647189877</v>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O178" t="n">
+        <v>0.8000000000008001</v>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>BB%B=0.98 (extreme=0.94); RSI=77.0 (extreme=0.43); Wick ratio=2.88; ADX H1=19.2 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>[0.7339, 0.0, -1.0, -1.0689, 0.9396, -1.0, 2.0, 0.5402, 0.4205, 0.0265, 1.0, 0.3318, 0.8122, 0.9819, 0.1039, 2.4818, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.3363, 0.0, 0.0, 0.0, 0.0, 0.0146, 0.7466, 0.9053, 0.4481, 0.1496]</t>
+        </is>
+      </c>
+      <c r="S178" t="n">
+        <v>0</v>
+      </c>
+      <c r="T178" t="n">
+        <v>0</v>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:08:14.989021+00:00</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D179" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>84.69758534767192</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0.0004311344067641394</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0.2965654720860558</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M179" t="n">
+        <v>19.20046647189877</v>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O179" t="n">
+        <v>0.5999999999994898</v>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>BB%B=0.99 (extreme=0.97); RSI=77.3 (extreme=0.43); Wick ratio=1.82; ADX H1=19.2 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>[0.694, 0.0, -1.0, -1.0689, 0.9658, -1.0, 2.0, 0.5453, 0.425, 0.0267, 1.0, 0.3318, 0.8367, 0.9897, 0.1039, 2.5514, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.3363, 0.0, 0.0, 0.0, 0.0, 0.0167, 0.7634, 0.9095, 0.4481, 0.152]</t>
+        </is>
+      </c>
+      <c r="S179" t="n">
+        <v>0</v>
+      </c>
+      <c r="T179" t="n">
+        <v>0</v>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:10:15.563551+00:00</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D180" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>80.99477796946204</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0.0004311344067641394</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I180" t="n">
+        <v>0.2959779780401997</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M180" t="n">
+        <v>19.20046647189877</v>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O180" t="n">
+        <v>0.3000000000019654</v>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>BB%B=1.01 (extreme=1.02); RSI=77.8 (extreme=0.44); Wick ratio=0.82; ADX H1=19.2 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>[0.6199, 0.0, -1.0, -1.0689, 1.0, -1.0, 2.0, 0.5551, 0.4339, 0.0271, 1.0, 0.3318, 0.8857, 1.0052, 0.1039, 2.6906, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.3363, 0.0, 0.0, 0.0, 0.0, 0.0208, 0.7972, 0.918, 0.4481, 0.1567]</t>
+        </is>
+      </c>
+      <c r="S180" t="n">
+        <v>0</v>
+      </c>
+      <c r="T180" t="n">
+        <v>0</v>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:13:16.320554+00:00</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D181" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>79.79004513590289</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0.0004425629823715592</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0.2913733319323316</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0.3037474810451171</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M181" t="n">
+        <v>19.36836697751369</v>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O181" t="n">
+        <v>0.2999999999997449</v>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>BB%B=1.04 (extreme=1.14); RSI=78.9 (extreme=0.47); Wick ratio=0.47; ADX H1=19.4 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>[0.5958, 0.0, -1.0, -1.0574, 1.0, -1.0, 2.0, 0.5779, 0.4443, 0.0279, 1.0, 0.3334, 0.8851, 1.042, 0.1325, 2.96, -0.4173, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.3331, 0.0, 0.0, 0.0, 0.0, 0.0271, 0.8587, 0.9148, 0.4338, 0.1684]</t>
+        </is>
+      </c>
+      <c r="S181" t="n">
+        <v>0</v>
+      </c>
+      <c r="T181" t="n">
+        <v>0</v>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:15:16.922791+00:00</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D182" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>80.76714354640552</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0.0004378390819399534</v>
+      </c>
+      <c r="G182" t="n">
+        <v>1</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0.2559880999891159</v>
+      </c>
+      <c r="I182" t="n">
+        <v>0.2635735896441633</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M182" t="n">
+        <v>19.68520025915126</v>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O182" t="n">
+        <v>0.8000000000008001</v>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>BB%B=1.02 (extreme=1.06); RSI=80.5 (extreme=0.51); Wick ratio=0.50; ADX H1=19.7 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>[0.6153, 0.0, -1.0, -1.0622, 1.0, -1.0, 2.0, 0.6107, 0.5428, 0.0411, 1.0, 0.3599, 0.9592, 1.0195, 0.1207, 3.0, -0.488, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.2802, 0.0, 0.0, 0.0, 0.0, 0.0312, 0.998, 1.0, 0.4396, 0.1993]</t>
+        </is>
+      </c>
+      <c r="S182" t="n">
+        <v>0</v>
+      </c>
+      <c r="T182" t="n">
+        <v>0</v>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:16:17.310921+00:00</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D183" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>81.29625689553517</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0.0004464105136455025</v>
+      </c>
+      <c r="G183" t="n">
+        <v>1</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0.2679050822353194</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0.2906821390503902</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L183" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M183" t="n">
+        <v>19.71221227757985</v>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O183" t="n">
+        <v>0.700000000000145</v>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>BB%B=1.01 (extreme=1.02); RSI=78.8 (extreme=0.47); Wick ratio=0.78; ADX H1=19.7 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>[0.6259, 0.0, -1.0, -1.0536, 1.0, -1.0, 2.0, 0.5763, 0.5223, 0.0407, 1.0, 0.3602, 0.8923, 1.0053, 0.1421, 2.9569, -0.4642, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.2797, 0.0, 0.0, 0.0, 0.0, 0.0333, 0.9408, 1.0, 0.4289, 0.1943]</t>
+        </is>
+      </c>
+      <c r="S183" t="n">
+        <v>0</v>
+      </c>
+      <c r="T183" t="n">
+        <v>0</v>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:19:18.105403+00:00</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D184" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>90.96183416937248</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0.0004599819471793096</v>
+      </c>
+      <c r="G184" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0.2688319311289377</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0.2918920452706336</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L184" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M184" t="n">
+        <v>19.86014346307914</v>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O184" t="n">
+        <v>0.4999999999988347</v>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>BB%B=1.03 (extreme=1.11); RSI=81.9 (extreme=0.55); Wick ratio=3.80; ADX H1=19.9 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>[0.8192, 0.0, -1.0, -1.04, 1.0, -1.0, 2.0, 0.6385, 0.5264, 0.0415, 1.0, 0.3614, 0.879, 1.0334, 0.176, 3.0, -0.4623, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.2771, 0.0, 0.0, 0.0, 0.0, 0.0396, 0.9868, 1.0, 0.412, 0.2042]</t>
+        </is>
+      </c>
+      <c r="S184" t="n">
+        <v>0</v>
+      </c>
+      <c r="T184" t="n">
+        <v>0</v>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:20:18.520734+00:00</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D185" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>91.04634476760732</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.0004664105209584872</v>
+      </c>
+      <c r="G185" t="n">
+        <v>1</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0.2679050822353194</v>
+      </c>
+      <c r="I185" t="n">
+        <v>0.2909834561551336</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L185" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M185" t="n">
+        <v>19.9350940431956</v>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O185" t="n">
+        <v>0.7999999999985796</v>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>BB%B=1.04 (extreme=1.13); RSI=82.1 (extreme=0.55); Wick ratio=3.12; ADX H1=19.9 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>[0.8209, 0.0, -1.0, -1.0336, 1.0, -1.0, 2.0, 0.6419, 0.5232, 0.0417, 1.0, 0.3621, 0.8452, 1.0392, 0.1921, 3.0, -0.4642, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.2758, 0.0, 0.0, 0.0, 0.0, 0.0417, 0.9888, 1.0, 0.404, 0.2063]</t>
+        </is>
+      </c>
+      <c r="S185" t="n">
+        <v>0</v>
+      </c>
+      <c r="T185" t="n">
+        <v>0</v>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:21:18.921798+00:00</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D186" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>91.01835071925424</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0.0004664105209584872</v>
+      </c>
+      <c r="G186" t="n">
+        <v>1</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0.2679050822353194</v>
+      </c>
+      <c r="I186" t="n">
+        <v>0.2909834561551336</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L186" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M186" t="n">
+        <v>19.9350940431956</v>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O186" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>BB%B=1.04 (extreme=1.12); RSI=82.0 (extreme=0.55); Wick ratio=3.71; ADX H1=19.9 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>[0.8204, 0.0, -1.0, -1.0336, 1.0, -1.0, 2.0, 0.6407, 0.5218, 0.0416, 1.0, 0.3621, 0.839, 1.0373, 0.1921, 3.0, -0.4642, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.2758, 0.0, 0.0, 0.0, 0.0, 0.0437, 0.9836, 1.0, 0.404, 0.2056]</t>
+        </is>
+      </c>
+      <c r="S186" t="n">
+        <v>0</v>
+      </c>
+      <c r="T186" t="n">
+        <v>0</v>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:22:19.449504+00:00</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D187" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>82.61915276932724</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0.0004664105209584872</v>
+      </c>
+      <c r="G187" t="n">
+        <v>1</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0.2679050822353194</v>
+      </c>
+      <c r="I187" t="n">
+        <v>0.2908773143590113</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L187" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M187" t="n">
+        <v>19.9350940431956</v>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O187" t="n">
+        <v>0.2999999999997449</v>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>BB%B=1.06 (extreme=1.21); RSI=82.7 (extreme=0.57); Wick ratio=0.65; ADX H1=19.9 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>[0.6524, 0.0, -1.0, -1.0336, 1.0, -1.0, 2.0, 0.6548, 0.5396, 0.0424, 1.0, 0.3621, 0.9195, 1.0619, 0.1921, 3.0, -0.4642, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.2758, 0.0, 0.0, 0.0, 0.0, 0.0458, 1.0, 1.0, 0.404, 0.2146]</t>
+        </is>
+      </c>
+      <c r="S187" t="n">
+        <v>0</v>
+      </c>
+      <c r="T187" t="n">
+        <v>0</v>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:23:19.886000+00:00</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D188" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>87.90659740917806</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0.0004664105209584872</v>
+      </c>
+      <c r="G188" t="n">
+        <v>1</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0.2774774133883474</v>
+      </c>
+      <c r="I188" t="n">
+        <v>0.2966319740944788</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M188" t="n">
+        <v>19.9350940431956</v>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O188" t="n">
+        <v>0.2999999999997449</v>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>BB%B=1.05 (extreme=1.16); RSI=82.3 (extreme=0.56); Wick ratio=1.75; ADX H1=19.9 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>[0.7581, 0.0, -1.0, -1.0336, 1.0, -1.0, 2.0, 0.6463, 0.5287, 0.0419, 1.0, 0.3621, 0.87, 1.0469, 0.1921, 3.0, -0.445, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.2758, 0.0, 0.0, 0.0, 0.0, 0.0479, 1.0, 1.0, 0.404, 0.2091]</t>
+        </is>
+      </c>
+      <c r="S188" t="n">
+        <v>0</v>
+      </c>
+      <c r="T188" t="n">
+        <v>0</v>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:24:20.338317+00:00</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D189" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>81.92070462393004</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0.0004664105209584872</v>
+      </c>
+      <c r="G189" t="n">
+        <v>1</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0.2679050822353194</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0.2905382180220533</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L189" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M189" t="n">
+        <v>19.9350940431956</v>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O189" t="n">
+        <v>0.1999999999990898</v>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>BB%B=1.07 (extreme=1.22); RSI=82.8 (extreme=0.57); Wick ratio=0.50; ADX H1=19.9 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>[0.6384, 0.0, -1.0, -1.0336, 1.0, -1.0, 2.0, 0.6568, 0.5424, 0.0425, 1.0, 0.3621, 0.9319, 1.0656, 0.1921, 3.0, -0.4642, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.2758, 0.0, 0.0, 0.0, 0.0, 0.05, 1.0, 1.0, 0.404, 0.216]</t>
+        </is>
+      </c>
+      <c r="S189" t="n">
+        <v>0</v>
+      </c>
+      <c r="T189" t="n">
+        <v>0</v>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:29:22.139953+00:00</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D190" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>82.61915276932724</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0.0004664105209584872</v>
+      </c>
+      <c r="G190" t="n">
+        <v>1</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.2679050822353194</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0.2908773143590113</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L190" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M190" t="n">
+        <v>19.9350940431956</v>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O190" t="n">
+        <v>0.4000000000004</v>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>BB%B=1.06 (extreme=1.21); RSI=82.7 (extreme=0.57); Wick ratio=0.65; ADX H1=19.9 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>[0.6524, 0.0, -1.0, -1.0336, 1.0, -1.0, 2.0, 0.6548, 0.5396, 0.0424, 1.0, 0.3621, 0.9195, 1.0619, 0.1921, 3.0, -0.4642, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.2758, 0.0, 0.0, 0.0, 0.0, 0.0604, 1.0, 1.0, 0.404, 0.2146]</t>
+        </is>
+      </c>
+      <c r="S190" t="n">
+        <v>0</v>
+      </c>
+      <c r="T190" t="n">
+        <v>0</v>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:31:22.826717+00:00</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D191" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>82.07991445686635</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0.0004480954675541606</v>
+      </c>
+      <c r="G191" t="n">
+        <v>1</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0.2586450700604193</v>
+      </c>
+      <c r="I191" t="n">
+        <v>0.2862675789285311</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L191" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M191" t="n">
+        <v>19.95958443583349</v>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O191" t="n">
+        <v>0.8000000000008001</v>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>BB%B=0.97 (extreme=0.89); RSI=80.7 (extreme=0.52); Wick ratio=1.37; ADX H1=20.0 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>[0.6416, 0.0, -1.0, -1.0519, 0.8946, -1.0, 2.0, 0.6147, 0.5601, 0.0531, 1.0, 0.3863, 0.8834, 0.9684, 0.1453, 2.6557, -0.4827, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.2275, 0.0, 0.0, 0.0, 0.0, 0.0646, 0.9755, 1.0, 0.4274, 0.2125]</t>
+        </is>
+      </c>
+      <c r="S191" t="n">
+        <v>0</v>
+      </c>
+      <c r="T191" t="n">
+        <v>0</v>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:32:23.325742+00:00</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D192" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>81.00285689848184</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0.0004480954675541606</v>
+      </c>
+      <c r="G192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0.2586450700604193</v>
+      </c>
+      <c r="I192" t="n">
+        <v>0.2862675789285311</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L192" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M192" t="n">
+        <v>19.95958443583349</v>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O192" t="n">
+        <v>0.6000000000017103</v>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>BB%B=0.97 (extreme=0.89); RSI=80.5 (extreme=0.51); Wick ratio=1.22; ADX H1=20.0 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>[0.6201, 0.0, -1.0, -1.0519, 0.8883, -1.0, 2.0, 0.6097, 0.5587, 0.053, 1.0, 0.3863, 0.8773, 0.9665, 0.1453, 2.6334, -0.4827, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.2275, 0.0, 0.0, 0.0, 0.0, 0.0667, 0.9701, 1.0, 0.4274, 0.2119]</t>
+        </is>
+      </c>
+      <c r="S192" t="n">
+        <v>0</v>
+      </c>
+      <c r="T192" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:33:23.811644+00:00</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D193" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>82.07991445686635</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0.0004480954675541606</v>
+      </c>
+      <c r="G193" t="n">
+        <v>1</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0.2586450700604193</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0.2862675789285311</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L193" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M193" t="n">
+        <v>19.95958443583349</v>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O193" t="n">
+        <v>0.2999999999997449</v>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>BB%B=0.97 (extreme=0.89); RSI=80.7 (extreme=0.52); Wick ratio=1.37; ADX H1=20.0 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>[0.6416, 0.0, -1.0, -1.0519, 0.8946, -1.0, 2.0, 0.6147, 0.5601, 0.0531, 1.0, 0.3863, 0.8834, 0.9684, 0.1453, 2.6557, -0.4827, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.2275, 0.0, 0.0, 0.0, 0.0, 0.0688, 0.9755, 1.0, 0.4274, 0.2125]</t>
+        </is>
+      </c>
+      <c r="S193" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" t="n">
+        <v>0</v>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:34:24.480523+00:00</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D194" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>81.00285689848184</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0.0004480954675541606</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0.2586450700604193</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0.2862675789285311</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L194" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M194" t="n">
+        <v>19.95958443583349</v>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O194" t="n">
+        <v>0.3000000000019654</v>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>BB%B=0.97 (extreme=0.89); RSI=80.5 (extreme=0.51); Wick ratio=1.22; ADX H1=20.0 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>[0.6201, 0.0, -1.0, -1.0519, 0.8883, -1.0, 2.0, 0.6097, 0.5587, 0.053, 1.0, 0.3863, 0.8773, 0.9665, 0.1453, 2.6334, -0.4827, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.2275, 0.0, 0.0, 0.0, 0.0, 0.0708, 0.9701, 1.0, 0.4274, 0.2119]</t>
+        </is>
+      </c>
+      <c r="S194" t="n">
+        <v>0</v>
+      </c>
+      <c r="T194" t="n">
+        <v>0</v>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:35:24.911999+00:00</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D195" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>88.45987209053047</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0.0004480954675541606</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0.267092069279854</v>
+      </c>
+      <c r="I195" t="n">
+        <v>0.2873822720977369</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L195" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M195" t="n">
+        <v>19.95958443583349</v>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O195" t="n">
+        <v>0.1999999999990898</v>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>BB%B=0.98 (extreme=0.92); RSI=81.7 (extreme=0.54); Wick ratio=2.75; ADX H1=20.0 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>[0.7692, 0.0, -1.0, -1.0519, 0.9196, -1.0, 2.0, 0.6349, 0.5658, 0.0533, 1.0, 0.3863, 0.908, 0.9759, 0.1453, 2.745, -0.4658, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.2275, 0.0, 0.0, 0.0, 0.0, 0.0729, 0.9972, 1.0, 0.4274, 0.2153]</t>
+        </is>
+      </c>
+      <c r="S195" t="n">
+        <v>0</v>
+      </c>
+      <c r="T195" t="n">
+        <v>0</v>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:36:25.362330+00:00</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D196" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>90.24444718031833</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0.0004480954675541606</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0.2679050822353194</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0.2888518480374836</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L196" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M196" t="n">
+        <v>19.95958443583349</v>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O196" t="n">
+        <v>0.2999999999997449</v>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>BB%B=0.99 (extreme=0.96); RSI=83.1 (extreme=0.58); Wick ratio=4.50; ADX H1=20.0 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>[0.8049, 0.0, -1.0, -1.0519, 0.9565, -1.0, 2.0, 0.662, 0.5744, 0.0537, 1.0, 0.3863, 0.9448, 0.987, 0.1453, 2.8789, -0.4642, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.2275, 0.0, 0.0, 0.0, 0.0, 0.075, 1.0, 1.0, 0.4274, 0.2193]</t>
+        </is>
+      </c>
+      <c r="S196" t="n">
+        <v>0</v>
+      </c>
+      <c r="T196" t="n">
+        <v>0</v>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:37:25.805838+00:00</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D197" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>84.87069756209864</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0.0004480954675541606</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0.2893888919228879</v>
+      </c>
+      <c r="I197" t="n">
+        <v>0.3012752094483801</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L197" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M197" t="n">
+        <v>19.95958443583349</v>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O197" t="n">
+        <v>0.3000000000019654</v>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>BB%B=0.99 (extreme=0.97); RSI=83.3 (extreme=0.58); Wick ratio=1.20; ADX H1=20.0 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>[0.6974, 0.0, -1.0, -1.0519, 0.9747, -1.0, 2.0, 0.6651, 0.5786, 0.0539, 1.0, 0.3863, 0.9632, 0.9924, 0.1453, 2.9458, -0.4212, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.2275, 0.0, 0.0, 0.0, 0.0, 0.0771, 1.0, 1.0, 0.4274, 0.2214]</t>
+        </is>
+      </c>
+      <c r="S197" t="n">
+        <v>0</v>
+      </c>
+      <c r="T197" t="n">
+        <v>0</v>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:38:26.258103+00:00</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D198" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>82.14176872865589</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0.0004480954675541606</v>
+      </c>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0.2893888919228879</v>
+      </c>
+      <c r="I198" t="n">
+        <v>0.3008325224330667</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L198" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M198" t="n">
+        <v>19.95958443583349</v>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O198" t="n">
+        <v>0.700000000000145</v>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>BB%B=1.00 (extreme=0.99); RSI=83.4 (extreme=0.58); Wick ratio=0.57; ADX H1=20.0 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>[0.6428, 0.0, -1.0, -1.0519, 0.9868, -1.0, 2.0, 0.6672, 0.5815, 0.054, 1.0, 0.3863, 0.9755, 0.996, 0.1453, 2.9904, -0.4212, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.2275, 0.0, 0.0, 0.0, 0.0, 0.0792, 1.0, 1.0, 0.4274, 0.2227]</t>
+        </is>
+      </c>
+      <c r="S198" t="n">
+        <v>0</v>
+      </c>
+      <c r="T198" t="n">
+        <v>0</v>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-06-05 08:40:26.926723+00:00</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D199" s="10" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>84.50122923420717</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0.0004595240431615804</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0.2679050822353194</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0.2911639627490864</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>ML_FILTERED</t>
+        </is>
+      </c>
+      <c r="L199" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M199" t="n">
+        <v>20.08622249115401</v>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>LONDON</t>
+        </is>
+      </c>
+      <c r="O199" t="n">
+        <v>0.3999999999981796</v>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>BB%B=1.01 (extreme=1.03); RSI=83.7 (extreme=0.59); Wick ratio=0.93; ADX H1=20.1 (block=30.0); SL=0.00120 TP=0.00120 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>[0.69, 0.0, -1.0, -1.0405, 1.0, -1.0, 2.0, 0.6743, 0.5767, 0.0544, 1.0, 0.3874, 0.924, 1.0085, 0.1738, 3.0, -0.4642, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0, 0.0, 0.2253, 0.0, 0.0, 0.0, 0.0, 0.0833, 1.0, 1.0, 0.4131, 0.2274]</t>
+        </is>
+      </c>
+      <c r="S199" t="n">
+        <v>0</v>
+      </c>
+      <c r="T199" t="n">
+        <v>0</v>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-06-05 12:11:05.408320+00:00</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D200" s="8" t="inlineStr">
+        <is>
+          <t>AGENT_TAKE</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>75.28355342333997</v>
+      </c>
+      <c r="F200" t="n">
+        <v>6.76445205606566</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0.3275691931770123</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0.3154891730254545</v>
+      </c>
+      <c r="J200" t="n">
+        <v>1</v>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>TAKE</t>
+        </is>
+      </c>
+      <c r="L200" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M200" t="n">
+        <v>19.72499039483182</v>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>NEW_YORK</t>
+        </is>
+      </c>
+      <c r="O200" t="n">
+        <v>44.00000000005093</v>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>BB%B=1.00 (extreme=1.01); RSI=61.1 (extreme=0.03); Wick ratio=1.35; ADX H1=19.7 (block=30.0); SL=10.00000 TP=10.00000 RR=1.00</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>[0.5057, 0.0, -1.0, 2.0, 1.0, -1.0, 1.4783, 0.2218, 0.0411, 0.0049, 0.5484, 0.212, 0.4267, 1.0017, -0.1229, 0.5218, -0.3449, -0.0045, -0.0, -0.0045, 0.6667, 0.0, -1.0, 0.2, 0.0007, 0.0, 0.576, 0.0, 0.0, 0.0, 0.0, 0.5229, 0.2911, 0.2361, 0.5614, -0.274]</t>
+        </is>
+      </c>
+      <c r="S200" t="n">
+        <v>0</v>
+      </c>
+      <c r="T200" t="n">
+        <v>0</v>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>mr_v8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
